--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -20,19 +20,25 @@
     <sheet name="appointment_cancellation_lov" sheetId="15" r:id="rId15"/>
     <sheet name="eqc_inspection_checklist" sheetId="16" r:id="rId16"/>
     <sheet name="torque_verification_standards" sheetId="17" r:id="rId17"/>
-    <sheet name="bodyshop_process_stages" sheetId="18" r:id="rId18"/>
-    <sheet name="paint_booth_schedule" sheetId="19" r:id="rId19"/>
-    <sheet name="amc_pricing" sheetId="20" r:id="rId20"/>
-    <sheet name="warranty_defect_codes" sheetId="21" r:id="rId21"/>
-    <sheet name="goodwill_approval_limits" sheetId="22" r:id="rId22"/>
-    <sheet name="spd_issuance_priority" sheetId="23" r:id="rId23"/>
-    <sheet name="parts_delay_reasons" sheetId="24" r:id="rId24"/>
-    <sheet name="thd_escalation_categories" sheetId="25" r:id="rId25"/>
-    <sheet name="tib_bulletin_codes" sheetId="26" r:id="rId26"/>
-    <sheet name="driver_transit_roster" sheetId="27" r:id="rId27"/>
-    <sheet name="lounge_reception_checklist" sheetId="28" r:id="rId28"/>
-    <sheet name="gate_security_checklist" sheetId="29" r:id="rId29"/>
-    <sheet name="gate_denial_reasons" sheetId="30" r:id="rId30"/>
+    <sheet name="eqc_gc_mandate" sheetId="18" r:id="rId18"/>
+    <sheet name="eqc_gc_steps" sheetId="19" r:id="rId19"/>
+    <sheet name="eqc_ptd_risk" sheetId="20" r:id="rId20"/>
+    <sheet name="eqc_did_thresholds" sheetId="21" r:id="rId21"/>
+    <sheet name="eqc_general_checklist" sheetId="22" r:id="rId22"/>
+    <sheet name="eqc_schedule_checklist" sheetId="23" r:id="rId23"/>
+    <sheet name="bodyshop_process_stages" sheetId="24" r:id="rId24"/>
+    <sheet name="paint_booth_schedule" sheetId="25" r:id="rId25"/>
+    <sheet name="amc_pricing" sheetId="26" r:id="rId26"/>
+    <sheet name="warranty_defect_codes" sheetId="27" r:id="rId27"/>
+    <sheet name="goodwill_approval_limits" sheetId="28" r:id="rId28"/>
+    <sheet name="spd_issuance_priority" sheetId="29" r:id="rId29"/>
+    <sheet name="parts_delay_reasons" sheetId="30" r:id="rId30"/>
+    <sheet name="thd_escalation_categories" sheetId="31" r:id="rId31"/>
+    <sheet name="tib_bulletin_codes" sheetId="32" r:id="rId32"/>
+    <sheet name="driver_transit_roster" sheetId="33" r:id="rId33"/>
+    <sheet name="lounge_reception_checklist" sheetId="34" r:id="rId34"/>
+    <sheet name="gate_security_checklist" sheetId="35" r:id="rId35"/>
+    <sheet name="gate_denial_reasons" sheetId="36" r:id="rId36"/>
   </sheets>
 </workbook>
 </file>
@@ -475,7 +481,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support</v>
+        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support | Electronic Quality Check</v>
       </c>
     </row>
     <row r="11">
@@ -1616,6 +1622,2106 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ppl</v>
+      </c>
+      <c r="C1" t="str">
+        <v>complaintCode</v>
+      </c>
+      <c r="D1" t="str">
+        <v>gcApplicable</v>
+      </c>
+      <c r="E1" t="str">
+        <v>gcMandatory</v>
+      </c>
+      <c r="F1" t="str">
+        <v>gcMandatoryTill</v>
+      </c>
+      <c r="G1" t="str">
+        <v>roadTestMandatory</v>
+      </c>
+      <c r="H1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>GCM-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>BRK-VIB-02</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>GCM-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="C3" t="str">
+        <v>BAT-SOC-03</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2027-03-31</v>
+      </c>
+      <c r="G3" t="str">
+        <v>N</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>GCM-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>BAT-SOC-03</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E4" t="str">
+        <v>N</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>N</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>GCM-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ENG-NOIS-01</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-12-31</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>GCM-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v>AC-COOL-04</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E6" t="str">
+        <v>N</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v>N</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>GCM-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>INFO-SCR-05</v>
+      </c>
+      <c r="D7" t="str">
+        <v>N</v>
+      </c>
+      <c r="E7" t="str">
+        <v>N</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>N</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ppl</v>
+      </c>
+      <c r="C1" t="str">
+        <v>complaintCode</v>
+      </c>
+      <c r="D1" t="str">
+        <v>stepNo</v>
+      </c>
+      <c r="E1" t="str">
+        <v>gcStep</v>
+      </c>
+      <c r="F1" t="str">
+        <v>gcImage1</v>
+      </c>
+      <c r="G1" t="str">
+        <v>gcImage2</v>
+      </c>
+      <c r="H1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>GCS-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>BRK-VIB-02</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Measure front disc run-out with dial gauge (limit 0.05 mm)</v>
+      </c>
+      <c r="F2" t="str">
+        <v>gc/brk-disc-runout.jpg</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>GCS-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>BRK-VIB-02</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Check caliper guide pins for free movement and grease</v>
+      </c>
+      <c r="F3" t="str">
+        <v>gc/brk-guide-pins.jpg</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>GCS-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>BRK-VIB-02</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Inspect wheel balancing and tyre wear pattern</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>GCS-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="C5" t="str">
+        <v>BAT-SOC-03</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Read HV battery SOC and cell voltage spread via VCI</v>
+      </c>
+      <c r="F5" t="str">
+        <v>gc/ev-vci-soc.jpg</v>
+      </c>
+      <c r="G5" t="str">
+        <v>gc/ev-cell-spread.jpg</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>GCS-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="C6" t="str">
+        <v>BAT-SOC-03</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Check BMS DTC history and last OTA version</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>GCS-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>BAT-SOC-03</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Check 12V auxiliary battery voltage and terminals</v>
+      </c>
+      <c r="F7" t="str">
+        <v>gc/12v-terminals.jpg</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GCS-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ENG-NOIS-01</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Cold start: listen at timing belt tensioner with stethoscope</v>
+      </c>
+      <c r="F8" t="str">
+        <v>gc/eng-tensioner.jpg</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>GCS-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ENG-NOIS-01</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Check engine mount bushes for cracks</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>GCS-09</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>AC-COOL-04</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Measure vent outlet temperature at idle (target ≤ 8 °C)</v>
+      </c>
+      <c r="F10" t="str">
+        <v>gc/ac-vent-temp.jpg</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G34"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Master ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Master Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Module Code</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Logical Group</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Owner</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ppl_master</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PPL &amp; PL (Product Line) Master</v>
+      </c>
+      <c r="C2" t="str">
+        <v>jc_creation</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Vehicle Data</v>
+      </c>
+      <c r="E2" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Vehicle Hierarchy</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Parent Product Line (PPL) and Product Line (PL) variants defining OEM parts and service eligibility.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>model_checklists</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Tech Model Specific Checklist</v>
+      </c>
+      <c r="C3" t="str">
+        <v>jc_tracking</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Vehicle Data</v>
+      </c>
+      <c r="E3" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Vehicle Inspection</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Mandatory technical quality inspection checklist items per vehicle Parent Product Line and Product Line.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>complaint_codes</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Complaint Code Category Master</v>
+      </c>
+      <c r="C4" t="str">
+        <v>jc_creation</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Vehicle Data</v>
+      </c>
+      <c r="E4" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Complaints &amp; Diagnostics</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Hierarchical customer voice codes (Symptom, System, Sub-System) for standardization.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>job_codes</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Job Code &amp; FRT Master</v>
+      </c>
+      <c r="C5" t="str">
+        <v>jc_creation</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Vehicle Data</v>
+      </c>
+      <c r="E5" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Labor &amp; Billed Hours</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tata Motors Flat Rate Time (FRT) standard labor operations and standard billed hours.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>complaint_job_linkage</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Complaint Job Code PPL Linkage</v>
+      </c>
+      <c r="C6" t="str">
+        <v>jc_creation</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Vehicle Data</v>
+      </c>
+      <c r="E6" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Labor Mapping</v>
+      </c>
+      <c r="G6" t="str">
+        <v>AI-assisted routing mapping customer symptoms to standard labor job codes filtered by vehicle model.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ev_safety_protocols</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EV High-Voltage Safety &amp; Protocols</v>
+      </c>
+      <c r="C7" t="str">
+        <v>ira</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Vehicle Data</v>
+      </c>
+      <c r="E7" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F7" t="str">
+        <v>EV Protocols</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Mandatory OEM safety gates before touching high-voltage (350V - 400V DC) EV components.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>dtc_telematics_alerts</v>
+      </c>
+      <c r="B8" t="str">
+        <v>DTC Fault Code Alert &amp; Telematics</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ira</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Vehicle Data</v>
+      </c>
+      <c r="E8" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Telematics Codes</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Connected vehicle telemetry triggers from iRA modem triggering preemptive telecaller CRM outreach.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>bay_division_summary</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Dealership Division Bay Allocation</v>
+      </c>
+      <c r="C9" t="str">
+        <v>jc_tracking</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Dealer Network</v>
+      </c>
+      <c r="E9" t="str">
+        <v>DEALER_ADMIN</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Capacity Allocations</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Dealership division bay capacities across Mechanical, Bodyshop, Wheel Alignment, Electrical, AC, Speedo, Fleet.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>bay_technician</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Bay - Technician &amp; Supervisor Roster</v>
+      </c>
+      <c r="C10" t="str">
+        <v>jc_tracking</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Service Operations</v>
+      </c>
+      <c r="E10" t="str">
+        <v>DEALER_ADMIN</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Manpower Allocation</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Assigns certified technicians and technical supervisors to designated workshop bays.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>pause_reasons</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Clocking Pause Reason Master</v>
+      </c>
+      <c r="C11" t="str">
+        <v>jc_tracking</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Service Operations</v>
+      </c>
+      <c r="E11" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Bay Clocking Rules</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Governs bay clocking pauses. Configures mandatory dependent fields (SAP Part No, THD No, Ticket ID).</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>revisit_reasons</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Repeat Complaint &amp; Revisit LOV Master</v>
+      </c>
+      <c r="C12" t="str">
+        <v>jc_creation</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Service Operations</v>
+      </c>
+      <c r="E12" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Quality Root Causes</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Standardized root cause classifications for customer workshop revisits within 30 days.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>appointment_cancellation_lov</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Appointment Cancellation &amp; Reschedule LOV</v>
+      </c>
+      <c r="C13" t="str">
+        <v>appointment</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Service Operations</v>
+      </c>
+      <c r="E13" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Appointment Flow</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Standardized classifications for telecaller CRM reschedule and cancellation tracking.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>eqc_inspection_checklist</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Final Quality Inspection &amp; Road Test Checklist</v>
+      </c>
+      <c r="C14" t="str">
+        <v>eqc</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Electronic Quality Check</v>
+      </c>
+      <c r="E14" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Quality Sign-off</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Pre-delivery quality assurance checklists, OBD-II DTC error sweeps, and road test verifications.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>torque_verification_standards</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Critical Fastener Torque Verification Master</v>
+      </c>
+      <c r="C15" t="str">
+        <v>eqc</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Electronic Quality Check</v>
+      </c>
+      <c r="E15" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Torque Engineering</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Factory-specified torque values (Nm) for wheel hubs, calipers, subframes, and steering links.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>eqc_gc_mandate</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Guided Check &amp; Road Test Mandate Master</v>
+      </c>
+      <c r="C16" t="str">
+        <v>eqc</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Electronic Quality Check</v>
+      </c>
+      <c r="E16" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F16" t="str">
+        <v>EQC Rules</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Decides per PPL + Complaint Code whether a Guided Check (GC) applies / is mandatory and whether a road test is mandatory. Blank PPL = all PPLs; a PPL-specific row overrides it.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>eqc_gc_steps</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Guided Check Steps Master</v>
+      </c>
+      <c r="C17" t="str">
+        <v>eqc</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Electronic Quality Check</v>
+      </c>
+      <c r="E17" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F17" t="str">
+        <v>EQC Rules</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Step-by-step Guided Check shown to the technician in the dealer app, per PPL + Complaint Code. PPL-specific steps replace the all-PPL steps for that PPL.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>eqc_ptd_risk</v>
+      </c>
+      <c r="B18" t="str">
+        <v>PTD Risk Configuration Master</v>
+      </c>
+      <c r="C18" t="str">
+        <v>eqc</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Electronic Quality Check</v>
+      </c>
+      <c r="E18" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F18" t="str">
+        <v>EQC Rules</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Highlights a job at risk of missing its Promised Time of Delivery (PTD). Time left ≤ Red threshold → Red; ≤ Orange threshold → Orange. Red must be lower than Orange.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>eqc_did_thresholds</v>
+      </c>
+      <c r="B19" t="str">
+        <v>DID Parameter Threshold Mapping Master</v>
+      </c>
+      <c r="C19" t="str">
+        <v>eqc</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Electronic Quality Check</v>
+      </c>
+      <c r="E19" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F19" t="str">
+        <v>EQC Rules</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Expected values for VCI / OBD DID auto-scan parameters. Formats: "11.8-14.5", "&gt;=20", "&lt;=4.2", "&gt;0", or an exact value. Blank PPL = all PPLs; a PPL-specific row overrides it.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>eqc_general_checklist</v>
+      </c>
+      <c r="B20" t="str">
+        <v>General Checklist Master</v>
+      </c>
+      <c r="C20" t="str">
+        <v>eqc</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Electronic Quality Check</v>
+      </c>
+      <c r="E20" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F20" t="str">
+        <v>EQC Checklists</v>
+      </c>
+      <c r="G20" t="str">
+        <v>EQC checklist items by BU and type. Blank PPL or blank Km range = every vehicle. The Not-OK flags decide what the technician must capture when an item is marked Not OK.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>eqc_schedule_checklist</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Schedule Checklist Master (Section &amp; Sub-Section)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>eqc</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Electronic Quality Check</v>
+      </c>
+      <c r="E21" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F21" t="str">
+        <v>EQC Checklists</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Service-schedule checklist grouped by Section and Sub-Section, filtered by BU, PPL and odometer Km. Blank PPL or Km range = every vehicle.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>bodyshop_process_stages</v>
+      </c>
+      <c r="B22" t="str">
+        <v>BodyShop Denting &amp; Paint Stage Master</v>
+      </c>
+      <c r="C22" t="str">
+        <v>bodyshop</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Service Operations</v>
+      </c>
+      <c r="E22" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F22" t="str">
+        <v>BodyShop Workflow</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Sequenced bodyshop workflow stages from accident survey to bake oven finish.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>paint_booth_schedule</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Heated Spray Booth &amp; Oven Slot Master</v>
+      </c>
+      <c r="C23" t="str">
+        <v>bodyshop</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Service Operations</v>
+      </c>
+      <c r="E23" t="str">
+        <v>DEALER_ADMIN</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Paint Facilities</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Spray booth slotting, color batching, and energy consumption metrics.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>amc_pricing</v>
+      </c>
+      <c r="B24" t="str">
+        <v>AMC Products &amp; Pricing Master</v>
+      </c>
+      <c r="C24" t="str">
+        <v>claim</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E24" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Commercial Contracts</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Tata Motors Value Care AMC packages, tenure, coverage limits, and national price schedules.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>warranty_defect_codes</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Warranty Defect &amp; Causal Part Tagging Master</v>
+      </c>
+      <c r="C25" t="str">
+        <v>claim</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E25" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Warranty Tagging</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Defect classifications for processing OEM claims to Tata Motors and vendor chargebacks.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>goodwill_approval_limits</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Goodwill &amp; Special Concession Matrix</v>
+      </c>
+      <c r="C26" t="str">
+        <v>claim</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E26" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Approval Authorities</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Financial approval thresholds for out-of-warranty customer goodwill concessions.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>spd_issuance_priority</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Spare Parts Requisition &amp; Issuance Priority</v>
+      </c>
+      <c r="C27" t="str">
+        <v>spd</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E27" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Inventory Picking</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Prioritizes store counter picking slips by vehicle state: VOR (Vehicle Off Road), Warranty, Running Repair.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>parts_delay_reasons</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Spare Parts Stockout &amp; Backorder LOV</v>
+      </c>
+      <c r="C28" t="str">
+        <v>spd</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E28" t="str">
+        <v>DEALER_ADMIN</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Stockout Categories</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Stockroom delay categorization for auto-generating SAP parts backorders and customer notifications.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>thd_escalation_categories</v>
+      </c>
+      <c r="B29" t="str">
+        <v>THD Technical Escalation Category &amp; Severity</v>
+      </c>
+      <c r="C29" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E29" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Engineering Escalations</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Field technical issue tickets to Tata Motors plant engineering, crash diagnostics, and high-voltage defects.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Technical Information Bulletin (TIB) Advisory Codes</v>
+      </c>
+      <c r="C30" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E30" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Plant Bulletins</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Tata Motors factory service technical bulletins, software flash versions, and campaign advisories.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Chauffeur &amp; Pick-and-Drop Transit Roster</v>
+      </c>
+      <c r="C31" t="str">
+        <v>reception</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E31" t="str">
+        <v>DEALER_ADMIN</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Transit Chauffeurs</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Driver certifications, assigned zone geofences, and vehicle transit speed monitoring.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Customer Reception &amp; Greeting Checklist</v>
+      </c>
+      <c r="C32" t="str">
+        <v>reception</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E32" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Customer Welcome</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Standard OEM lounge customer greeting and advisor electronic tablet handover checklist.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Vehicle Gate Inward / Outward Barrier Checklist</v>
+      </c>
+      <c r="C33" t="str">
+        <v>security</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E33" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Perimeter Security</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Mandatory perimeter verification rules for automatic ANPR barrier opening and vehicle passes.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Gate Entry Denial &amp; Security Hold LOV</v>
+      </c>
+      <c r="C34" t="str">
+        <v>security</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E34" t="str">
+        <v>DEALER_ADMIN</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Perimeter Security</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Security gate vehicle hold classifications and escalation protocol for police or insurance hold.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G34"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>colorCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>thresholdHrs</v>
+      </c>
+      <c r="D1" t="str">
+        <v>thresholdMins</v>
+      </c>
+      <c r="E1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>PTD-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PTD-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Red</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>45</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F7"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>parameterName</v>
+      </c>
+      <c r="C1" t="str">
+        <v>expectedValue</v>
+      </c>
+      <c r="D1" t="str">
+        <v>unit</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ppl</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DID-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Battery SOC</v>
+      </c>
+      <c r="C2" t="str">
+        <v>&gt;=60</v>
+      </c>
+      <c r="D2" t="str">
+        <v>%</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DID-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>12V Battery Voltage</v>
+      </c>
+      <c r="C3" t="str">
+        <v>12.2-14.8</v>
+      </c>
+      <c r="D3" t="str">
+        <v>V</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DID-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>HV Battery SOC</v>
+      </c>
+      <c r="C4" t="str">
+        <v>&gt;=20</v>
+      </c>
+      <c r="D4" t="str">
+        <v>%</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DID-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>HV Battery SOC</v>
+      </c>
+      <c r="C5" t="str">
+        <v>&gt;=25</v>
+      </c>
+      <c r="D5" t="str">
+        <v>%</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Tiago EV</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DID-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>BMS Cell Voltage</v>
+      </c>
+      <c r="C6" t="str">
+        <v>3.2-4.2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>V</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>DID-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Coolant Temperature</v>
+      </c>
+      <c r="C7" t="str">
+        <v>80-105</v>
+      </c>
+      <c r="D7" t="str">
+        <v>°C</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>bu</v>
+      </c>
+      <c r="C1" t="str">
+        <v>checklistType</v>
+      </c>
+      <c r="D1" t="str">
+        <v>checklistItem</v>
+      </c>
+      <c r="E1" t="str">
+        <v>rangeStartKm</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rangeEndKm</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ppl</v>
+      </c>
+      <c r="H1" t="str">
+        <v>active</v>
+      </c>
+      <c r="I1" t="str">
+        <v>notOkPhoto</v>
+      </c>
+      <c r="J1" t="str">
+        <v>notOkAudio</v>
+      </c>
+      <c r="K1" t="str">
+        <v>notOkVideo</v>
+      </c>
+      <c r="L1" t="str">
+        <v>notOkText</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>GCL-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Pre-Delivery Inspection</v>
+      </c>
+      <c r="D2" t="str">
+        <v>All warning lamps OFF after engine start</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J2" t="str">
+        <v>N</v>
+      </c>
+      <c r="K2" t="str">
+        <v>N</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>GCL-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Road Test</v>
+      </c>
+      <c r="D3" t="str">
+        <v>No pull to either side under braking</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I3" t="str">
+        <v>N</v>
+      </c>
+      <c r="J3" t="str">
+        <v>N</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>GCL-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Underbody</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Clutch plate wear within limit</v>
+      </c>
+      <c r="E4">
+        <v>40000</v>
+      </c>
+      <c r="F4">
+        <v>80000</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J4" t="str">
+        <v>N</v>
+      </c>
+      <c r="K4" t="str">
+        <v>N</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>GCL-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Road Test</v>
+      </c>
+      <c r="D5" t="str">
+        <v>DCA gear shift smooth, no judder at 1st–2nd</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I5" t="str">
+        <v>N</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>GCL-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C6" t="str">
+        <v>EV Safety</v>
+      </c>
+      <c r="D6" t="str">
+        <v>HV connector seals and orange cable insulation intact</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J6" t="str">
+        <v>N</v>
+      </c>
+      <c r="K6" t="str">
+        <v>N</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>GCL-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Pre-Delivery Inspection</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Regen braking levels switch correctly</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="I7" t="str">
+        <v>N</v>
+      </c>
+      <c r="J7" t="str">
+        <v>N</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GCL-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Interior &amp; Cleanliness</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Paper floor mats and seat covers removed</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>N</v>
+      </c>
+      <c r="I8" t="str">
+        <v>N</v>
+      </c>
+      <c r="J8" t="str">
+        <v>N</v>
+      </c>
+      <c r="K8" t="str">
+        <v>N</v>
+      </c>
+      <c r="L8" t="str">
+        <v>N</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>bu</v>
+      </c>
+      <c r="C1" t="str">
+        <v>section</v>
+      </c>
+      <c r="D1" t="str">
+        <v>subSection</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ppl</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+      <c r="G1" t="str">
+        <v>notOkPhoto</v>
+      </c>
+      <c r="H1" t="str">
+        <v>notOkAudio</v>
+      </c>
+      <c r="I1" t="str">
+        <v>notOkVideo</v>
+      </c>
+      <c r="J1" t="str">
+        <v>notOkText</v>
+      </c>
+      <c r="K1" t="str">
+        <v>rangeStartKm</v>
+      </c>
+      <c r="L1" t="str">
+        <v>rangeEndKm</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SCL-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Engine Compartment</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Engine oil level and leakage</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H2" t="str">
+        <v>N</v>
+      </c>
+      <c r="I2" t="str">
+        <v>N</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SCL-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Engine Compartment</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Drive belt condition</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H3" t="str">
+        <v>N</v>
+      </c>
+      <c r="I3" t="str">
+        <v>N</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K3">
+        <v>20000</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SCL-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Brakes</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Front pad thickness ≥ 3 mm</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H4" t="str">
+        <v>N</v>
+      </c>
+      <c r="I4" t="str">
+        <v>N</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K4">
+        <v>10000</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SCL-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Underbody</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Turbo intercooler hoses</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Harrier</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H5" t="str">
+        <v>N</v>
+      </c>
+      <c r="I5" t="str">
+        <v>N</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SCL-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C6" t="str">
+        <v>HV System</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Battery pack mounting bolts torque</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H6" t="str">
+        <v>N</v>
+      </c>
+      <c r="I6" t="str">
+        <v>N</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K6">
+        <v>15000</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SCL-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C7" t="str">
+        <v>HV System</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Coolant level in battery thermal loop</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H7" t="str">
+        <v>N</v>
+      </c>
+      <c r="I7" t="str">
+        <v>N</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SCL-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Electricals</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Headlamp aim and fog lamps</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G8" t="str">
+        <v>N</v>
+      </c>
+      <c r="H8" t="str">
+        <v>N</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8">
+        <v>30000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
     <row r="1">
@@ -1725,7 +3831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetData>
@@ -1796,662 +3902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Master ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Master Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Module Code</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Logical Group</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Description</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>ppl_master</v>
-      </c>
-      <c r="B2" t="str">
-        <v>PPL &amp; PL (Product Line) Master</v>
-      </c>
-      <c r="C2" t="str">
-        <v>jc_creation</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Vehicle Data</v>
-      </c>
-      <c r="E2" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Vehicle Hierarchy</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Parent Product Line (PPL) and Product Line (PL) variants defining OEM parts and service eligibility.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>model_checklists</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Tech Model Specific Checklist</v>
-      </c>
-      <c r="C3" t="str">
-        <v>jc_tracking</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Vehicle Data</v>
-      </c>
-      <c r="E3" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Vehicle Inspection</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Mandatory technical quality inspection checklist items per vehicle Parent Product Line and Product Line.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>complaint_codes</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Complaint Code Category Master</v>
-      </c>
-      <c r="C4" t="str">
-        <v>jc_creation</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Vehicle Data</v>
-      </c>
-      <c r="E4" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Complaints &amp; Diagnostics</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Hierarchical customer voice codes (Symptom, System, Sub-System) for standardization.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>job_codes</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Job Code &amp; FRT Master</v>
-      </c>
-      <c r="C5" t="str">
-        <v>jc_creation</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Vehicle Data</v>
-      </c>
-      <c r="E5" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Labor &amp; Billed Hours</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Tata Motors Flat Rate Time (FRT) standard labor operations and standard billed hours.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>complaint_job_linkage</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Complaint Job Code PPL Linkage</v>
-      </c>
-      <c r="C6" t="str">
-        <v>jc_creation</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Vehicle Data</v>
-      </c>
-      <c r="E6" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Labor Mapping</v>
-      </c>
-      <c r="G6" t="str">
-        <v>AI-assisted routing mapping customer symptoms to standard labor job codes filtered by vehicle model.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ev_safety_protocols</v>
-      </c>
-      <c r="B7" t="str">
-        <v>EV High-Voltage Safety &amp; Protocols</v>
-      </c>
-      <c r="C7" t="str">
-        <v>ira</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Vehicle Data</v>
-      </c>
-      <c r="E7" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F7" t="str">
-        <v>EV Protocols</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Mandatory OEM safety gates before touching high-voltage (350V - 400V DC) EV components.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>dtc_telematics_alerts</v>
-      </c>
-      <c r="B8" t="str">
-        <v>DTC Fault Code Alert &amp; Telematics</v>
-      </c>
-      <c r="C8" t="str">
-        <v>ira</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Vehicle Data</v>
-      </c>
-      <c r="E8" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Telematics Codes</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Connected vehicle telemetry triggers from iRA modem triggering preemptive telecaller CRM outreach.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>bay_division_summary</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Dealership Division Bay Allocation</v>
-      </c>
-      <c r="C9" t="str">
-        <v>jc_tracking</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Dealer Network</v>
-      </c>
-      <c r="E9" t="str">
-        <v>DEALER_ADMIN</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Capacity Allocations</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Dealership division bay capacities across Mechanical, Bodyshop, Wheel Alignment, Electrical, AC, Speedo, Fleet.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>bay_technician</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Bay - Technician &amp; Supervisor Roster</v>
-      </c>
-      <c r="C10" t="str">
-        <v>jc_tracking</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Service Operations</v>
-      </c>
-      <c r="E10" t="str">
-        <v>DEALER_ADMIN</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Manpower Allocation</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Assigns certified technicians and technical supervisors to designated workshop bays.</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>pause_reasons</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Clocking Pause Reason Master</v>
-      </c>
-      <c r="C11" t="str">
-        <v>jc_tracking</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Service Operations</v>
-      </c>
-      <c r="E11" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Bay Clocking Rules</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Governs bay clocking pauses. Configures mandatory dependent fields (SAP Part No, THD No, Ticket ID).</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>revisit_reasons</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Repeat Complaint &amp; Revisit LOV Master</v>
-      </c>
-      <c r="C12" t="str">
-        <v>jc_creation</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Service Operations</v>
-      </c>
-      <c r="E12" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Quality Root Causes</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Standardized root cause classifications for customer workshop revisits within 30 days.</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>appointment_cancellation_lov</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Appointment Cancellation &amp; Reschedule LOV</v>
-      </c>
-      <c r="C13" t="str">
-        <v>appointment</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Service Operations</v>
-      </c>
-      <c r="E13" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Appointment Flow</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Standardized classifications for telecaller CRM reschedule and cancellation tracking.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>eqc_inspection_checklist</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Final Quality Inspection &amp; Road Test Checklist</v>
-      </c>
-      <c r="C14" t="str">
-        <v>eqc</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Service Operations</v>
-      </c>
-      <c r="E14" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Quality Sign-off</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Pre-delivery quality assurance checklists, OBD-II DTC error sweeps, and road test verifications.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>torque_verification_standards</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Critical Fastener Torque Verification Master</v>
-      </c>
-      <c r="C15" t="str">
-        <v>eqc</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Service Operations</v>
-      </c>
-      <c r="E15" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Torque Engineering</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Factory-specified torque values (Nm) for wheel hubs, calipers, subframes, and steering links.</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>bodyshop_process_stages</v>
-      </c>
-      <c r="B16" t="str">
-        <v>BodyShop Denting &amp; Paint Stage Master</v>
-      </c>
-      <c r="C16" t="str">
-        <v>bodyshop</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Service Operations</v>
-      </c>
-      <c r="E16" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F16" t="str">
-        <v>BodyShop Workflow</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Sequenced bodyshop workflow stages from accident survey to bake oven finish.</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>paint_booth_schedule</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Heated Spray Booth &amp; Oven Slot Master</v>
-      </c>
-      <c r="C17" t="str">
-        <v>bodyshop</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Service Operations</v>
-      </c>
-      <c r="E17" t="str">
-        <v>DEALER_ADMIN</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Paint Facilities</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Spray booth slotting, color batching, and energy consumption metrics.</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>amc_pricing</v>
-      </c>
-      <c r="B18" t="str">
-        <v>AMC Products &amp; Pricing Master</v>
-      </c>
-      <c r="C18" t="str">
-        <v>claim</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E18" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Commercial Contracts</v>
-      </c>
-      <c r="G18" t="str">
-        <v>Tata Motors Value Care AMC packages, tenure, coverage limits, and national price schedules.</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>warranty_defect_codes</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Warranty Defect &amp; Causal Part Tagging Master</v>
-      </c>
-      <c r="C19" t="str">
-        <v>claim</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E19" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Warranty Tagging</v>
-      </c>
-      <c r="G19" t="str">
-        <v>Defect classifications for processing OEM claims to Tata Motors and vendor chargebacks.</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>goodwill_approval_limits</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Goodwill &amp; Special Concession Matrix</v>
-      </c>
-      <c r="C20" t="str">
-        <v>claim</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E20" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Approval Authorities</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Financial approval thresholds for out-of-warranty customer goodwill concessions.</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>spd_issuance_priority</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Spare Parts Requisition &amp; Issuance Priority</v>
-      </c>
-      <c r="C21" t="str">
-        <v>spd</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E21" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Inventory Picking</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Prioritizes store counter picking slips by vehicle state: VOR (Vehicle Off Road), Warranty, Running Repair.</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>parts_delay_reasons</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Spare Parts Stockout &amp; Backorder LOV</v>
-      </c>
-      <c r="C22" t="str">
-        <v>spd</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E22" t="str">
-        <v>DEALER_ADMIN</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Stockout Categories</v>
-      </c>
-      <c r="G22" t="str">
-        <v>Stockroom delay categorization for auto-generating SAP parts backorders and customer notifications.</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>thd_escalation_categories</v>
-      </c>
-      <c r="B23" t="str">
-        <v>THD Technical Escalation Category &amp; Severity</v>
-      </c>
-      <c r="C23" t="str">
-        <v>thd</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E23" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F23" t="str">
-        <v>Engineering Escalations</v>
-      </c>
-      <c r="G23" t="str">
-        <v>Field technical issue tickets to Tata Motors plant engineering, crash diagnostics, and high-voltage defects.</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>tib_bulletin_codes</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Technical Information Bulletin (TIB) Advisory Codes</v>
-      </c>
-      <c r="C24" t="str">
-        <v>thd</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E24" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Plant Bulletins</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Tata Motors factory service technical bulletins, software flash versions, and campaign advisories.</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>driver_transit_roster</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Chauffeur &amp; Pick-and-Drop Transit Roster</v>
-      </c>
-      <c r="C25" t="str">
-        <v>reception</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E25" t="str">
-        <v>DEALER_ADMIN</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Transit Chauffeurs</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Driver certifications, assigned zone geofences, and vehicle transit speed monitoring.</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>lounge_reception_checklist</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Customer Reception &amp; Greeting Checklist</v>
-      </c>
-      <c r="C26" t="str">
-        <v>reception</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E26" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Customer Welcome</v>
-      </c>
-      <c r="G26" t="str">
-        <v>Standard OEM lounge customer greeting and advisor electronic tablet handover checklist.</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>gate_security_checklist</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Vehicle Gate Inward / Outward Barrier Checklist</v>
-      </c>
-      <c r="C27" t="str">
-        <v>security</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E27" t="str">
-        <v>TML_ADMIN</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Perimeter Security</v>
-      </c>
-      <c r="G27" t="str">
-        <v>Mandatory perimeter verification rules for automatic ANPR barrier opening and vehicle passes.</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>gate_denial_reasons</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Gate Entry Denial &amp; Security Hold LOV</v>
-      </c>
-      <c r="C28" t="str">
-        <v>security</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Parts, Claims &amp; Support</v>
-      </c>
-      <c r="E28" t="str">
-        <v>DEALER_ADMIN</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Perimeter Security</v>
-      </c>
-      <c r="G28" t="str">
-        <v>Security gate vehicle hold classifications and escalation protocol for police or insurance hold.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G28"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
   <sheetData>
@@ -2566,7 +4017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetData>
@@ -2657,7 +4108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
@@ -2764,604 +4215,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>priorityCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>priorityLevel</v>
-      </c>
-      <c r="D1" t="str">
-        <v>slaMins</v>
-      </c>
-      <c r="E1" t="str">
-        <v>requireOtp</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>SPD-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>PRIO-VOR-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Emergency VOR</v>
-      </c>
-      <c r="D2">
-        <v>15</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>SPD-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>PRIO-RUN-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Running Repair Express</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3" t="str">
-        <v>N</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>SPD-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>PRIO-SCH-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Scheduled Periodic Maintenance</v>
-      </c>
-      <c r="D4">
-        <v>45</v>
-      </c>
-      <c r="E4" t="str">
-        <v>N</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>SPD-04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>PRIO-REC-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Recall Campaign</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>delayCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>reasonName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>autoOrderSap</v>
-      </c>
-      <c r="E1" t="str">
-        <v>smsCustomer</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PDR-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>BO-PLANT-TRANSIT</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Depot stock depleted - Plant in-transit shipment</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>PDR-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>BO-BIN-MISMATCH</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Physical bin inventory variance (Inventory Audit flag)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>N</v>
-      </c>
-      <c r="E3" t="str">
-        <v>N</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PDR-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>BO-SUPPLIER-SHORT</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Tier-1 vendor supply constraint (Critical semiconductor/ECU)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>categoryCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>systemDomain</v>
-      </c>
-      <c r="D1" t="str">
-        <v>severityTier</v>
-      </c>
-      <c r="E1" t="str">
-        <v>requiresPlantVisit</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>THD-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>THD-EV-BAT-ISO</v>
-      </c>
-      <c r="C2" t="str">
-        <v>EV High Voltage Traction</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Tier 1 Critical (&lt; 4 Hours)</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>THD-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>THD-DCA-JERK</v>
-      </c>
-      <c r="C3" t="str">
-        <v>DCA Dual Clutch Transmission</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Tier 2 High (&lt; 12 Hours)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>N</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>THD-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>THD-ADAS-MISALIGN</v>
-      </c>
-      <c r="C4" t="str">
-        <v>ADAS &amp; Radar Calibration</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Tier 2 High (&lt; 12 Hours)</v>
-      </c>
-      <c r="E4" t="str">
-        <v>N</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>THD-04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>THD-CAN-ERR</v>
-      </c>
-      <c r="C5" t="str">
-        <v>CAN Bus Network Communication</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Tier 3 Standard (&lt; 24 Hours)</v>
-      </c>
-      <c r="E5" t="str">
-        <v>N</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>tibNumber</v>
-      </c>
-      <c r="C1" t="str">
-        <v>title</v>
-      </c>
-      <c r="D1" t="str">
-        <v>affectedPpl</v>
-      </c>
-      <c r="E1" t="str">
-        <v>reworkType</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>TIB-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>TIB-2026-PV-089</v>
-      </c>
-      <c r="C2" t="str">
-        <v>BMS High-Voltage Contactor Firmware v4.8 Update</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Nexon EV</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ECU Firmware Update</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>TIB-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>TIB-2026-PV-112</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Rear Suspension Spring Seat Damping Pad Retrofit</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Harrier / Safari</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Hardware Bush Replacement</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>TIB-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>TIB-2026-PV-134</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Steering Column Earth Strap Resistance Check</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Altroz</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Torque Audit</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>driverCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>driverName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>assignedZone</v>
-      </c>
-      <c r="E1" t="str">
-        <v>licenseNumber</v>
-      </c>
-      <c r="F1" t="str">
-        <v>evCertified</v>
-      </c>
-      <c r="G1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>DRV-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>DRV-HYD-101</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Nageshwar Rao</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Zone A - Hitec City</v>
-      </c>
-      <c r="E2" t="str">
-        <v>TS09-2019-0023412</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>DRV-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>DRV-HYD-102</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Mohd Feroz Khan</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Zone B - Secunderabad</v>
-      </c>
-      <c r="E3" t="str">
-        <v>TS10-2018-0056123</v>
-      </c>
-      <c r="F3" t="str">
-        <v>N</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>DRV-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>DRV-HYD-103</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Pradeep Patil</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Zone C - Gachibowli</v>
-      </c>
-      <c r="E4" t="str">
-        <v>TS09-2021-0089145</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>checkpointCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>checkpointDesc</v>
-      </c>
-      <c r="D1" t="str">
-        <v>channel</v>
-      </c>
-      <c r="E1" t="str">
-        <v>mandatoryProof</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>REC-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>REC-VAL-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Digital vehicle outer walk-around photo capture (4 angles)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Pre-Booked Appointment</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>REC-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>REC-VAL-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Fuel / EV SOC level verification &amp; digital customer signature</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Pre-Booked Appointment</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>REC-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>REC-VAL-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Customer personal valuables custody declaration slip</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Walk-in</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3375,16 +4228,16 @@
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>ruleId</v>
+        <v>priorityCode</v>
       </c>
       <c r="C1" t="str">
-        <v>direction</v>
+        <v>priorityLevel</v>
       </c>
       <c r="D1" t="str">
-        <v>verificationItem</v>
+        <v>slaMins</v>
       </c>
       <c r="E1" t="str">
-        <v>anprSync</v>
+        <v>requireOtp</v>
       </c>
       <c r="F1" t="str">
         <v>active</v>
@@ -3392,16 +4245,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SEC-01</v>
+        <v>SPD-01</v>
       </c>
       <c r="B2" t="str">
-        <v>GATE-IN-01</v>
+        <v>PRIO-VOR-01</v>
       </c>
       <c r="C2" t="str">
-        <v>Inward (Check-in)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>ANPR plate scan match against appointment roster or generate walk-in pass</v>
+        <v>Emergency VOR</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
       </c>
       <c r="E2" t="str">
         <v>Y</v>
@@ -3412,16 +4265,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SEC-02</v>
+        <v>SPD-02</v>
       </c>
       <c r="B3" t="str">
-        <v>GATE-IN-02</v>
+        <v>PRIO-RUN-02</v>
       </c>
       <c r="C3" t="str">
-        <v>Inward (Check-in)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Physical chassis plate stamp confirmation against CRM VIN</v>
+        <v>Running Repair Express</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
       </c>
       <c r="E3" t="str">
         <v>N</v>
@@ -3432,19 +4285,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SEC-03</v>
+        <v>SPD-03</v>
       </c>
       <c r="B4" t="str">
-        <v>GATE-OUT-01</v>
+        <v>PRIO-SCH-03</v>
       </c>
       <c r="C4" t="str">
-        <v>Outward (Check-out)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Cashier zero-balance clearance seal &amp; gate pass OTP verification</v>
+        <v>Scheduled Periodic Maintenance</v>
+      </c>
+      <c r="D4">
+        <v>45</v>
       </c>
       <c r="E4" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F4" t="str">
         <v>Y</v>
@@ -3452,19 +4305,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SEC-04</v>
+        <v>SPD-04</v>
       </c>
       <c r="B5" t="str">
-        <v>GATE-OUT-02</v>
+        <v>PRIO-REC-04</v>
       </c>
       <c r="C5" t="str">
-        <v>Outward (Check-out)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Old / replaced warranty parts box inventory verification (if customer request)</v>
+        <v>Recall Campaign</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
       </c>
       <c r="E5" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F5" t="str">
         <v>Y</v>
@@ -3479,7 +4332,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q162"/>
+  <dimension ref="A1:Q207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8518,22 +9371,22 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>eqc_gc_mandate</v>
       </c>
       <c r="B96" t="str">
-        <v>stageCode</v>
+        <v>ppl</v>
       </c>
       <c r="C96" t="str">
-        <v>Stage Code</v>
+        <v>PPL</v>
       </c>
       <c r="D96" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E96" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F96" t="str">
-        <v/>
+        <v>Nexon, Nexon EV, Altroz, Harrier, Safari, Punch, Punch EV, Tiago, Tiago EV, Tigor, Curvv, Curvv EV</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -8566,18 +9419,18 @@
         <v/>
       </c>
       <c r="Q96" t="str">
-        <v/>
+        <v>Leave blank to apply to all PPLs for this Complaint Code.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>eqc_gc_mandate</v>
       </c>
       <c r="B97" t="str">
-        <v>stageName</v>
+        <v>complaintCode</v>
       </c>
       <c r="C97" t="str">
-        <v>Process Stage</v>
+        <v>Complaint Code</v>
       </c>
       <c r="D97" t="str">
         <v>text</v>
@@ -8601,10 +9454,10 @@
         <v/>
       </c>
       <c r="K97" t="str">
-        <v/>
+        <v>^[A-Z0-9]+(-[A-Z0-9]+)*$</v>
       </c>
       <c r="L97" t="str">
-        <v/>
+        <v>Use capitals, digits and hyphens, e.g. BRK-VIB-02.</v>
       </c>
       <c r="M97" t="str">
         <v>N</v>
@@ -8624,22 +9477,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>eqc_gc_mandate</v>
       </c>
       <c r="B98" t="str">
-        <v>standardDurationHrs</v>
+        <v>gcApplicable</v>
       </c>
       <c r="C98" t="str">
-        <v>Standard FRT (Hrs)</v>
+        <v>GC Applicable</v>
       </c>
       <c r="D98" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E98" t="str">
         <v>Y</v>
       </c>
       <c r="F98" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -8677,19 +9530,19 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>eqc_gc_mandate</v>
       </c>
       <c r="B99" t="str">
-        <v>requiresSurveyorApproval</v>
+        <v>gcMandatory</v>
       </c>
       <c r="C99" t="str">
-        <v>Surveyor Sign-off Gate</v>
+        <v>GC Mandatory</v>
       </c>
       <c r="D99" t="str">
         <v>select</v>
       </c>
       <c r="E99" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F99" t="str">
         <v>Y, N</v>
@@ -8730,22 +9583,22 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>eqc_gc_mandate</v>
       </c>
       <c r="B100" t="str">
-        <v>active</v>
+        <v>gcMandatoryTill</v>
       </c>
       <c r="C100" t="str">
-        <v>Active</v>
+        <v>GC Mandatory Till</v>
       </c>
       <c r="D100" t="str">
-        <v>select</v>
+        <v>date</v>
       </c>
       <c r="E100" t="str">
         <v>N</v>
       </c>
       <c r="F100" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -8778,27 +9631,27 @@
         <v/>
       </c>
       <c r="Q100" t="str">
-        <v/>
+        <v>Optional end date. After it, GC stays applicable but is no longer mandatory.</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>paint_booth_schedule</v>
+        <v>eqc_gc_mandate</v>
       </c>
       <c r="B101" t="str">
-        <v>boothName</v>
+        <v>roadTestMandatory</v>
       </c>
       <c r="C101" t="str">
-        <v>Spray Booth Identification</v>
+        <v>Road Test Mandatory</v>
       </c>
       <c r="D101" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E101" t="str">
         <v>Y</v>
       </c>
       <c r="F101" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -8836,22 +9689,22 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>paint_booth_schedule</v>
+        <v>eqc_gc_mandate</v>
       </c>
       <c r="B102" t="str">
-        <v>paintType</v>
+        <v>active</v>
       </c>
       <c r="C102" t="str">
-        <v>Paint Technology</v>
+        <v>Active</v>
       </c>
       <c r="D102" t="str">
         <v>select</v>
       </c>
       <c r="E102" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F102" t="str">
-        <v>Waterborne Eco-Basecoat, Solvent-borne Clearcoat, Matte Finish Specialty</v>
+        <v>Y, N</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -8889,22 +9742,22 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>paint_booth_schedule</v>
+        <v>eqc_gc_steps</v>
       </c>
       <c r="B103" t="str">
-        <v>maxBakeTemp</v>
+        <v>ppl</v>
       </c>
       <c r="C103" t="str">
-        <v>Baking Temperature (°C)</v>
+        <v>PPL</v>
       </c>
       <c r="D103" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E103" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F103" t="str">
-        <v/>
+        <v>Nexon, Nexon EV, Altroz, Harrier, Safari, Punch, Punch EV, Tiago, Tiago EV, Tigor, Curvv, Curvv EV</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -8937,21 +9790,21 @@
         <v/>
       </c>
       <c r="Q103" t="str">
-        <v/>
+        <v>Leave blank to apply to all PPLs.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>paint_booth_schedule</v>
+        <v>eqc_gc_steps</v>
       </c>
       <c r="B104" t="str">
-        <v>dailyCapacityPanels</v>
+        <v>complaintCode</v>
       </c>
       <c r="C104" t="str">
-        <v>Daily Panel Capacity</v>
+        <v>Complaint Code</v>
       </c>
       <c r="D104" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E104" t="str">
         <v>Y</v>
@@ -8972,10 +9825,10 @@
         <v/>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>^[A-Z0-9]+(-[A-Z0-9]+)*$</v>
       </c>
       <c r="L104" t="str">
-        <v/>
+        <v>Use capitals, digits and hyphens, e.g. BRK-VIB-02.</v>
       </c>
       <c r="M104" t="str">
         <v>N</v>
@@ -8995,28 +9848,28 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>paint_booth_schedule</v>
+        <v>eqc_gc_steps</v>
       </c>
       <c r="B105" t="str">
-        <v>active</v>
+        <v>stepNo</v>
       </c>
       <c r="C105" t="str">
-        <v>Active</v>
+        <v>Step No.</v>
       </c>
       <c r="D105" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E105" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F105" t="str">
-        <v>Y, N</v>
-      </c>
-      <c r="G105" t="str">
-        <v/>
-      </c>
-      <c r="H105" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105">
+        <v>99</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -9048,13 +9901,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>amc_pricing</v>
+        <v>eqc_gc_steps</v>
       </c>
       <c r="B106" t="str">
-        <v>amcCode</v>
+        <v>gcStep</v>
       </c>
       <c r="C106" t="str">
-        <v>AMC Plan Code</v>
+        <v>GC Step</v>
       </c>
       <c r="D106" t="str">
         <v>text</v>
@@ -9101,19 +9954,19 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>amc_pricing</v>
+        <v>eqc_gc_steps</v>
       </c>
       <c r="B107" t="str">
-        <v>planName</v>
+        <v>gcImage1</v>
       </c>
       <c r="C107" t="str">
-        <v>AMC Plan Name</v>
+        <v>GC Image 1</v>
       </c>
       <c r="D107" t="str">
         <v>text</v>
       </c>
       <c r="E107" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F107" t="str">
         <v/>
@@ -9149,27 +10002,27 @@
         <v/>
       </c>
       <c r="Q107" t="str">
-        <v/>
+        <v>Image file name or URL shown with the step.</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>amc_pricing</v>
+        <v>eqc_gc_steps</v>
       </c>
       <c r="B108" t="str">
-        <v>pplName</v>
+        <v>gcImage2</v>
       </c>
       <c r="C108" t="str">
-        <v>Applicable PPL</v>
+        <v>GC Image 2</v>
       </c>
       <c r="D108" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E108" t="str">
         <v>N</v>
       </c>
       <c r="F108" t="str">
-        <v>All Models, Nexon, Altroz, Harrier / Safari, EV Fleet</v>
+        <v/>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -9207,22 +10060,22 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>amc_pricing</v>
+        <v>eqc_gc_steps</v>
       </c>
       <c r="B109" t="str">
-        <v>tenureYears</v>
+        <v>active</v>
       </c>
       <c r="C109" t="str">
-        <v>Tenure (Yrs)</v>
+        <v>Active</v>
       </c>
       <c r="D109" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E109" t="str">
         <v>Y</v>
       </c>
       <c r="F109" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -9260,22 +10113,22 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>amc_pricing</v>
+        <v>eqc_ptd_risk</v>
       </c>
       <c r="B110" t="str">
-        <v>maxKms</v>
+        <v>colorCode</v>
       </c>
       <c r="C110" t="str">
-        <v>Max Coverage (KMs)</v>
+        <v>Color Code</v>
       </c>
       <c r="D110" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E110" t="str">
         <v>Y</v>
       </c>
       <c r="F110" t="str">
-        <v/>
+        <v>Orange, Red</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -9313,13 +10166,13 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>amc_pricing</v>
+        <v>eqc_ptd_risk</v>
       </c>
       <c r="B111" t="str">
-        <v>priceInr</v>
+        <v>thresholdHrs</v>
       </c>
       <c r="C111" t="str">
-        <v>Base OEM MRP (₹)</v>
+        <v>Threshold in Hrs</v>
       </c>
       <c r="D111" t="str">
         <v>number</v>
@@ -9330,11 +10183,11 @@
       <c r="F111" t="str">
         <v/>
       </c>
-      <c r="G111" t="str">
-        <v/>
-      </c>
-      <c r="H111" t="str">
-        <v/>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>72</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -9366,28 +10219,28 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>amc_pricing</v>
+        <v>eqc_ptd_risk</v>
       </c>
       <c r="B112" t="str">
-        <v>active</v>
+        <v>thresholdMins</v>
       </c>
       <c r="C112" t="str">
-        <v>Active</v>
+        <v>Threshold in Mins</v>
       </c>
       <c r="D112" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E112" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F112" t="str">
-        <v>Y, N</v>
-      </c>
-      <c r="G112" t="str">
-        <v/>
-      </c>
-      <c r="H112" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>59</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -9419,22 +10272,22 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>warranty_defect_codes</v>
+        <v>eqc_ptd_risk</v>
       </c>
       <c r="B113" t="str">
-        <v>defectCode</v>
+        <v>active</v>
       </c>
       <c r="C113" t="str">
-        <v>Defect Code</v>
+        <v>Active</v>
       </c>
       <c r="D113" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E113" t="str">
         <v>Y</v>
       </c>
       <c r="F113" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -9472,22 +10325,22 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>warranty_defect_codes</v>
+        <v>eqc_did_thresholds</v>
       </c>
       <c r="B114" t="str">
-        <v>defectCategory</v>
+        <v>parameterName</v>
       </c>
       <c r="C114" t="str">
-        <v>Defect Group</v>
+        <v>Parameter Name</v>
       </c>
       <c r="D114" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E114" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F114" t="str">
-        <v>Manufacturing Quality, Material Defect, Vendor Assembly Flaw, Software / Firmware Logic, Corrosion / Paint Flaw</v>
+        <v/>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -9525,22 +10378,22 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>warranty_defect_codes</v>
+        <v>eqc_did_thresholds</v>
       </c>
       <c r="B115" t="str">
-        <v>partCoverage</v>
+        <v>expectedValue</v>
       </c>
       <c r="C115" t="str">
-        <v>Warranty Scheme</v>
+        <v>Expected Value / Range</v>
       </c>
       <c r="D115" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E115" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F115" t="str">
-        <v>Standard 3Yr / 100K Km, Extended Warranty (EW), EV HV Battery 8Yr / 160K Km</v>
+        <v/>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -9555,10 +10408,10 @@
         <v/>
       </c>
       <c r="K115" t="str">
-        <v/>
+        <v>^\s*((-?\d+(\.\d+)?)\s*-\s*(-?\d+(\.\d+)?)|(&gt;=|&lt;=|&gt;|&lt;)\s*-?\d+(\.\d+)?|-?\d+(\.\d+)?)\s*$</v>
       </c>
       <c r="L115" t="str">
-        <v/>
+        <v>Use a range like 11.8-14.5, a limit like &gt;=20 or &lt;=4.2, or a single value.</v>
       </c>
       <c r="M115" t="str">
         <v>N</v>
@@ -9578,22 +10431,22 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>warranty_defect_codes</v>
+        <v>eqc_did_thresholds</v>
       </c>
       <c r="B116" t="str">
-        <v>requiresSampleReturn</v>
+        <v>unit</v>
       </c>
       <c r="C116" t="str">
-        <v>Return Physical Sample to Plant</v>
+        <v>Unit</v>
       </c>
       <c r="D116" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E116" t="str">
         <v>N</v>
       </c>
       <c r="F116" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -9631,13 +10484,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>warranty_defect_codes</v>
+        <v>eqc_did_thresholds</v>
       </c>
       <c r="B117" t="str">
-        <v>active</v>
+        <v>ppl</v>
       </c>
       <c r="C117" t="str">
-        <v>Active</v>
+        <v>PPL</v>
       </c>
       <c r="D117" t="str">
         <v>select</v>
@@ -9646,7 +10499,7 @@
         <v>N</v>
       </c>
       <c r="F117" t="str">
-        <v>Y, N</v>
+        <v>Nexon, Nexon EV, Altroz, Harrier, Safari, Punch, Punch EV, Tiago, Tiago EV, Tigor, Curvv, Curvv EV</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -9679,27 +10532,27 @@
         <v/>
       </c>
       <c r="Q117" t="str">
-        <v/>
+        <v>Leave blank to apply to all PPLs.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>eqc_did_thresholds</v>
       </c>
       <c r="B118" t="str">
-        <v>authorityTier</v>
+        <v>active</v>
       </c>
       <c r="C118" t="str">
-        <v>Approving Authority</v>
+        <v>Active</v>
       </c>
       <c r="D118" t="str">
         <v>select</v>
       </c>
       <c r="E118" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F118" t="str">
-        <v>Works Manager (WM), Area Service Manager (ASM - TML), Regional Customer Care Head (RCCH), DGM Service Central</v>
+        <v>Y, N</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -9737,22 +10590,22 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B119" t="str">
-        <v>maxLaborConcession</v>
+        <v>bu</v>
       </c>
       <c r="C119" t="str">
-        <v>Max Labor Discount (%)</v>
+        <v>BU</v>
       </c>
       <c r="D119" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E119" t="str">
         <v>Y</v>
       </c>
       <c r="F119" t="str">
-        <v/>
+        <v>PV, EV</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -9790,22 +10643,22 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B120" t="str">
-        <v>maxPartsConcession</v>
+        <v>checklistType</v>
       </c>
       <c r="C120" t="str">
-        <v>Max Parts Discount (%)</v>
+        <v>Checklist Type</v>
       </c>
       <c r="D120" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E120" t="str">
         <v>Y</v>
       </c>
       <c r="F120" t="str">
-        <v/>
+        <v>Pre-Delivery Inspection, Road Test, Underbody, Interior &amp; Cleanliness, EV Safety</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -9843,16 +10696,16 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B121" t="str">
-        <v>maxAmountInr</v>
+        <v>checklistItem</v>
       </c>
       <c r="C121" t="str">
-        <v>Max Claim Value (₹)</v>
+        <v>Checklist Item</v>
       </c>
       <c r="D121" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E121" t="str">
         <v>Y</v>
@@ -9896,28 +10749,28 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B122" t="str">
-        <v>active</v>
+        <v>rangeStartKm</v>
       </c>
       <c r="C122" t="str">
-        <v>Active</v>
+        <v>Range Start Km</v>
       </c>
       <c r="D122" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E122" t="str">
         <v>N</v>
       </c>
       <c r="F122" t="str">
-        <v>Y, N</v>
-      </c>
-      <c r="G122" t="str">
-        <v/>
-      </c>
-      <c r="H122" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>999999</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -9949,28 +10802,28 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>spd_issuance_priority</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B123" t="str">
-        <v>priorityCode</v>
+        <v>rangeEndKm</v>
       </c>
       <c r="C123" t="str">
-        <v>Priority Code</v>
+        <v>Range End Km</v>
       </c>
       <c r="D123" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E123" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F123" t="str">
         <v/>
       </c>
-      <c r="G123" t="str">
-        <v/>
-      </c>
-      <c r="H123" t="str">
-        <v/>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>999999</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -10002,13 +10855,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>spd_issuance_priority</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B124" t="str">
-        <v>priorityLevel</v>
+        <v>ppl</v>
       </c>
       <c r="C124" t="str">
-        <v>Priority Tag</v>
+        <v>PPL</v>
       </c>
       <c r="D124" t="str">
         <v>select</v>
@@ -10017,7 +10870,7 @@
         <v>N</v>
       </c>
       <c r="F124" t="str">
-        <v>Emergency VOR, Running Repair Express, Scheduled Periodic Maintenance, Recall Campaign</v>
+        <v>Nexon, Nexon EV, Altroz, Harrier, Safari, Punch, Punch EV, Tiago, Tiago EV, Tigor, Curvv, Curvv EV</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -10050,27 +10903,27 @@
         <v/>
       </c>
       <c r="Q124" t="str">
-        <v/>
+        <v>Leave blank to apply to all PPLs.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>spd_issuance_priority</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B125" t="str">
-        <v>slaMins</v>
+        <v>active</v>
       </c>
       <c r="C125" t="str">
-        <v>Picking SLA (Minutes)</v>
+        <v>Active</v>
       </c>
       <c r="D125" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E125" t="str">
         <v>Y</v>
       </c>
       <c r="F125" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -10108,19 +10961,19 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>spd_issuance_priority</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B126" t="str">
-        <v>requireOtp</v>
+        <v>notOkPhoto</v>
       </c>
       <c r="C126" t="str">
-        <v>Mechanic Fingerprint / OTP Verification</v>
+        <v>Not OK: Photo</v>
       </c>
       <c r="D126" t="str">
         <v>select</v>
       </c>
       <c r="E126" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F126" t="str">
         <v>Y, N</v>
@@ -10156,24 +11009,24 @@
         <v/>
       </c>
       <c r="Q126" t="str">
-        <v/>
+        <v>Photo is mandatory when the item is marked Not OK.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>spd_issuance_priority</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B127" t="str">
-        <v>active</v>
+        <v>notOkAudio</v>
       </c>
       <c r="C127" t="str">
-        <v>Active</v>
+        <v>Not OK: Audio</v>
       </c>
       <c r="D127" t="str">
         <v>select</v>
       </c>
       <c r="E127" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F127" t="str">
         <v>Y, N</v>
@@ -10214,22 +11067,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>parts_delay_reasons</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B128" t="str">
-        <v>delayCode</v>
+        <v>notOkVideo</v>
       </c>
       <c r="C128" t="str">
-        <v>Delay Code</v>
+        <v>Not OK: Video</v>
       </c>
       <c r="D128" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E128" t="str">
         <v>Y</v>
       </c>
       <c r="F128" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -10267,22 +11120,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>parts_delay_reasons</v>
+        <v>eqc_general_checklist</v>
       </c>
       <c r="B129" t="str">
-        <v>reasonName</v>
+        <v>notOkText</v>
       </c>
       <c r="C129" t="str">
-        <v>Non-Availability Root Cause</v>
+        <v>Not OK: Text</v>
       </c>
       <c r="D129" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E129" t="str">
         <v>Y</v>
       </c>
       <c r="F129" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -10320,22 +11173,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>parts_delay_reasons</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B130" t="str">
-        <v>autoOrderSap</v>
+        <v>bu</v>
       </c>
       <c r="C130" t="str">
-        <v>Auto Trigger SAP Emergency Order</v>
+        <v>BU</v>
       </c>
       <c r="D130" t="str">
         <v>select</v>
       </c>
       <c r="E130" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F130" t="str">
-        <v>Y, N</v>
+        <v>PV, EV</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -10373,22 +11226,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>parts_delay_reasons</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B131" t="str">
-        <v>smsCustomer</v>
+        <v>section</v>
       </c>
       <c r="C131" t="str">
-        <v>Trigger Customer ETA SMS</v>
+        <v>Section</v>
       </c>
       <c r="D131" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E131" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F131" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -10426,22 +11279,22 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>parts_delay_reasons</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B132" t="str">
-        <v>active</v>
+        <v>subSection</v>
       </c>
       <c r="C132" t="str">
-        <v>Active</v>
+        <v>Sub-Section</v>
       </c>
       <c r="D132" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E132" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F132" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -10479,22 +11332,22 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>thd_escalation_categories</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B133" t="str">
-        <v>categoryCode</v>
+        <v>ppl</v>
       </c>
       <c r="C133" t="str">
-        <v>Escalation Category</v>
+        <v>PPL</v>
       </c>
       <c r="D133" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E133" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F133" t="str">
-        <v/>
+        <v>Nexon, Nexon EV, Altroz, Harrier, Safari, Punch, Punch EV, Tiago, Tiago EV, Tigor, Curvv, Curvv EV</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -10527,27 +11380,27 @@
         <v/>
       </c>
       <c r="Q133" t="str">
-        <v/>
+        <v>Leave blank to apply to all PPLs.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>thd_escalation_categories</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B134" t="str">
-        <v>systemDomain</v>
+        <v>active</v>
       </c>
       <c r="C134" t="str">
-        <v>Engineering System</v>
+        <v>Active</v>
       </c>
       <c r="D134" t="str">
         <v>select</v>
       </c>
       <c r="E134" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F134" t="str">
-        <v>EV High Voltage Traction, DCA Dual Clutch Transmission, ADAS &amp; Radar Calibration, Braking &amp; ESP Hydraulics, CAN Bus Network Communication</v>
+        <v>Y, N</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -10585,22 +11438,22 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>thd_escalation_categories</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B135" t="str">
-        <v>severityTier</v>
+        <v>notOkPhoto</v>
       </c>
       <c r="C135" t="str">
-        <v>Plant Response SLA</v>
+        <v>Not OK: Photo</v>
       </c>
       <c r="D135" t="str">
         <v>select</v>
       </c>
       <c r="E135" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F135" t="str">
-        <v>Tier 1 Critical (&lt; 4 Hours), Tier 2 High (&lt; 12 Hours), Tier 3 Standard (&lt; 24 Hours)</v>
+        <v>Y, N</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -10633,24 +11486,24 @@
         <v/>
       </c>
       <c r="Q135" t="str">
-        <v/>
+        <v>Photo is mandatory when the item is marked Not OK.</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>thd_escalation_categories</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B136" t="str">
-        <v>requiresPlantVisit</v>
+        <v>notOkAudio</v>
       </c>
       <c r="C136" t="str">
-        <v>Plant Field Engineer Dispatch</v>
+        <v>Not OK: Audio</v>
       </c>
       <c r="D136" t="str">
         <v>select</v>
       </c>
       <c r="E136" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F136" t="str">
         <v>Y, N</v>
@@ -10691,19 +11544,19 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>thd_escalation_categories</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B137" t="str">
-        <v>active</v>
+        <v>notOkVideo</v>
       </c>
       <c r="C137" t="str">
-        <v>Active</v>
+        <v>Not OK: Video</v>
       </c>
       <c r="D137" t="str">
         <v>select</v>
       </c>
       <c r="E137" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F137" t="str">
         <v>Y, N</v>
@@ -10744,22 +11597,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B138" t="str">
-        <v>tibNumber</v>
+        <v>notOkText</v>
       </c>
       <c r="C138" t="str">
-        <v>TIB Bulletin Reference</v>
+        <v>Not OK: Text</v>
       </c>
       <c r="D138" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E138" t="str">
         <v>Y</v>
       </c>
       <c r="F138" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -10797,28 +11650,28 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B139" t="str">
-        <v>title</v>
+        <v>rangeStartKm</v>
       </c>
       <c r="C139" t="str">
-        <v>Subject / Advisory Scope</v>
+        <v>Range Start Km</v>
       </c>
       <c r="D139" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E139" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F139" t="str">
         <v/>
       </c>
-      <c r="G139" t="str">
-        <v/>
-      </c>
-      <c r="H139" t="str">
-        <v/>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>999999</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -10850,28 +11703,28 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>eqc_schedule_checklist</v>
       </c>
       <c r="B140" t="str">
-        <v>affectedPpl</v>
+        <v>rangeEndKm</v>
       </c>
       <c r="C140" t="str">
-        <v>Applicable Vehicle PPL</v>
+        <v>Range End Km</v>
       </c>
       <c r="D140" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E140" t="str">
         <v>N</v>
       </c>
       <c r="F140" t="str">
-        <v>Nexon EV, Nexon ICE, Harrier / Safari, Curvv EV, Altroz</v>
-      </c>
-      <c r="G140" t="str">
-        <v/>
-      </c>
-      <c r="H140" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>999999</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -10903,22 +11756,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B141" t="str">
-        <v>reworkType</v>
+        <v>stageCode</v>
       </c>
       <c r="C141" t="str">
-        <v>Rework Classification</v>
+        <v>Stage Code</v>
       </c>
       <c r="D141" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E141" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F141" t="str">
-        <v>ECU Firmware Update, Harness Rerouting, Hardware Bush Replacement, Torque Audit</v>
+        <v/>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -10956,22 +11809,22 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B142" t="str">
-        <v>active</v>
+        <v>stageName</v>
       </c>
       <c r="C142" t="str">
-        <v>Active</v>
+        <v>Process Stage</v>
       </c>
       <c r="D142" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E142" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F142" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -11009,16 +11862,16 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>driver_transit_roster</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B143" t="str">
-        <v>driverCode</v>
+        <v>standardDurationHrs</v>
       </c>
       <c r="C143" t="str">
-        <v>Driver Code</v>
+        <v>Standard FRT (Hrs)</v>
       </c>
       <c r="D143" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E143" t="str">
         <v>Y</v>
@@ -11062,22 +11915,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>driver_transit_roster</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B144" t="str">
-        <v>driverName</v>
+        <v>requiresSurveyorApproval</v>
       </c>
       <c r="C144" t="str">
-        <v>Driver Full Name</v>
+        <v>Surveyor Sign-off Gate</v>
       </c>
       <c r="D144" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E144" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F144" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -11115,13 +11968,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>driver_transit_roster</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B145" t="str">
-        <v>assignedZone</v>
+        <v>active</v>
       </c>
       <c r="C145" t="str">
-        <v>Assigned Territory Zone</v>
+        <v>Active</v>
       </c>
       <c r="D145" t="str">
         <v>select</v>
@@ -11130,7 +11983,7 @@
         <v>N</v>
       </c>
       <c r="F145" t="str">
-        <v>Zone A - Hitec City, Zone B - Secunderabad, Zone C - Gachibowli, Zone D - Banjara Hills</v>
+        <v>Y, N</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -11168,13 +12021,13 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>driver_transit_roster</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B146" t="str">
-        <v>licenseNumber</v>
+        <v>boothName</v>
       </c>
       <c r="C146" t="str">
-        <v>Commercial DL Number</v>
+        <v>Spray Booth Identification</v>
       </c>
       <c r="D146" t="str">
         <v>text</v>
@@ -11221,13 +12074,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>driver_transit_roster</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B147" t="str">
-        <v>evCertified</v>
+        <v>paintType</v>
       </c>
       <c r="C147" t="str">
-        <v>EV Transit Certified</v>
+        <v>Paint Technology</v>
       </c>
       <c r="D147" t="str">
         <v>select</v>
@@ -11236,7 +12089,7 @@
         <v>N</v>
       </c>
       <c r="F147" t="str">
-        <v>Y, N</v>
+        <v>Waterborne Eco-Basecoat, Solvent-borne Clearcoat, Matte Finish Specialty</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -11274,22 +12127,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>driver_transit_roster</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B148" t="str">
-        <v>active</v>
+        <v>maxBakeTemp</v>
       </c>
       <c r="C148" t="str">
-        <v>Active</v>
+        <v>Baking Temperature (°C)</v>
       </c>
       <c r="D148" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E148" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F148" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -11327,16 +12180,16 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B149" t="str">
-        <v>checkpointCode</v>
+        <v>dailyCapacityPanels</v>
       </c>
       <c r="C149" t="str">
-        <v>Checkpoint Code</v>
+        <v>Daily Panel Capacity</v>
       </c>
       <c r="D149" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E149" t="str">
         <v>Y</v>
@@ -11380,22 +12233,22 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B150" t="str">
-        <v>checkpointDesc</v>
+        <v>active</v>
       </c>
       <c r="C150" t="str">
-        <v>Reception Standard Requirement</v>
+        <v>Active</v>
       </c>
       <c r="D150" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E150" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F150" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -11433,22 +12286,22 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B151" t="str">
-        <v>channel</v>
+        <v>amcCode</v>
       </c>
       <c r="C151" t="str">
-        <v>Intake Channel</v>
+        <v>AMC Plan Code</v>
       </c>
       <c r="D151" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E151" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F151" t="str">
-        <v>Walk-in, Pre-Booked Appointment, Express Valet, Breakdown Flatbed</v>
+        <v/>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -11486,22 +12339,22 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B152" t="str">
-        <v>mandatoryProof</v>
+        <v>planName</v>
       </c>
       <c r="C152" t="str">
-        <v>Mandatory Photo / Signature</v>
+        <v>AMC Plan Name</v>
       </c>
       <c r="D152" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E152" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F152" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -11539,13 +12392,13 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B153" t="str">
-        <v>active</v>
+        <v>pplName</v>
       </c>
       <c r="C153" t="str">
-        <v>Active</v>
+        <v>Applicable PPL</v>
       </c>
       <c r="D153" t="str">
         <v>select</v>
@@ -11554,7 +12407,7 @@
         <v>N</v>
       </c>
       <c r="F153" t="str">
-        <v>Y, N</v>
+        <v>All Models, Nexon, Altroz, Harrier / Safari, EV Fleet</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -11592,16 +12445,16 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>gate_security_checklist</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B154" t="str">
-        <v>ruleId</v>
+        <v>tenureYears</v>
       </c>
       <c r="C154" t="str">
-        <v>Gate Rule Code</v>
+        <v>Tenure (Yrs)</v>
       </c>
       <c r="D154" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E154" t="str">
         <v>Y</v>
@@ -11645,22 +12498,22 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>gate_security_checklist</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B155" t="str">
-        <v>direction</v>
+        <v>maxKms</v>
       </c>
       <c r="C155" t="str">
-        <v>Movement Direction</v>
+        <v>Max Coverage (KMs)</v>
       </c>
       <c r="D155" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E155" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F155" t="str">
-        <v>Inward (Check-in), Outward (Check-out), Internal Bay Transit</v>
+        <v/>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -11698,16 +12551,16 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>gate_security_checklist</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B156" t="str">
-        <v>verificationItem</v>
+        <v>priceInr</v>
       </c>
       <c r="C156" t="str">
-        <v>Verification Protocol</v>
+        <v>Base OEM MRP (₹)</v>
       </c>
       <c r="D156" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E156" t="str">
         <v>Y</v>
@@ -11751,13 +12604,13 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>gate_security_checklist</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B157" t="str">
-        <v>anprSync</v>
+        <v>active</v>
       </c>
       <c r="C157" t="str">
-        <v>ANPR Camera Auto-Verify</v>
+        <v>Active</v>
       </c>
       <c r="D157" t="str">
         <v>select</v>
@@ -11804,22 +12657,22 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>gate_security_checklist</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B158" t="str">
-        <v>active</v>
+        <v>defectCode</v>
       </c>
       <c r="C158" t="str">
-        <v>Active</v>
+        <v>Defect Code</v>
       </c>
       <c r="D158" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E158" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F158" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -11857,22 +12710,22 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>gate_denial_reasons</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B159" t="str">
-        <v>denialCode</v>
+        <v>defectCategory</v>
       </c>
       <c r="C159" t="str">
-        <v>Denial Code</v>
+        <v>Defect Group</v>
       </c>
       <c r="D159" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E159" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F159" t="str">
-        <v/>
+        <v>Manufacturing Quality, Material Defect, Vendor Assembly Flaw, Software / Firmware Logic, Corrosion / Paint Flaw</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -11910,22 +12763,22 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>gate_denial_reasons</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B160" t="str">
-        <v>reason</v>
+        <v>partCoverage</v>
       </c>
       <c r="C160" t="str">
-        <v>Security Denial / Hold Reason</v>
+        <v>Warranty Scheme</v>
       </c>
       <c r="D160" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E160" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F160" t="str">
-        <v/>
+        <v>Standard 3Yr / 100K Km, Extended Warranty (EW), EV HV Battery 8Yr / 160K Km</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -11963,13 +12816,13 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>gate_denial_reasons</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B161" t="str">
-        <v>escalateTo</v>
+        <v>requiresSampleReturn</v>
       </c>
       <c r="C161" t="str">
-        <v>Immediate Notification Target</v>
+        <v>Return Physical Sample to Plant</v>
       </c>
       <c r="D161" t="str">
         <v>select</v>
@@ -11978,7 +12831,7 @@
         <v>N</v>
       </c>
       <c r="F161" t="str">
-        <v>Works Manager, Security Officer In-Charge, Service Head, Customer Relation Manager</v>
+        <v>Y, N</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -12016,7 +12869,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>gate_denial_reasons</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B162" t="str">
         <v>active</v>
@@ -12067,14 +12920,2997 @@
         <v/>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>goodwill_approval_limits</v>
+      </c>
+      <c r="B163" t="str">
+        <v>authorityTier</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Approving Authority</v>
+      </c>
+      <c r="D163" t="str">
+        <v>select</v>
+      </c>
+      <c r="E163" t="str">
+        <v>N</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Works Manager (WM), Area Service Manager (ASM - TML), Regional Customer Care Head (RCCH), DGM Service Central</v>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v>N</v>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>goodwill_approval_limits</v>
+      </c>
+      <c r="B164" t="str">
+        <v>maxLaborConcession</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Max Labor Discount (%)</v>
+      </c>
+      <c r="D164" t="str">
+        <v>number</v>
+      </c>
+      <c r="E164" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
+      <c r="K164" t="str">
+        <v/>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v>N</v>
+      </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>goodwill_approval_limits</v>
+      </c>
+      <c r="B165" t="str">
+        <v>maxPartsConcession</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Max Parts Discount (%)</v>
+      </c>
+      <c r="D165" t="str">
+        <v>number</v>
+      </c>
+      <c r="E165" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
+      <c r="K165" t="str">
+        <v/>
+      </c>
+      <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v>N</v>
+      </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>goodwill_approval_limits</v>
+      </c>
+      <c r="B166" t="str">
+        <v>maxAmountInr</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Max Claim Value (₹)</v>
+      </c>
+      <c r="D166" t="str">
+        <v>number</v>
+      </c>
+      <c r="E166" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v/>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
+      <c r="K166" t="str">
+        <v/>
+      </c>
+      <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v>N</v>
+      </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>goodwill_approval_limits</v>
+      </c>
+      <c r="B167" t="str">
+        <v>active</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D167" t="str">
+        <v>select</v>
+      </c>
+      <c r="E167" t="str">
+        <v>N</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v/>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167" t="str">
+        <v/>
+      </c>
+      <c r="K167" t="str">
+        <v/>
+      </c>
+      <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v>N</v>
+      </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>spd_issuance_priority</v>
+      </c>
+      <c r="B168" t="str">
+        <v>priorityCode</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Priority Code</v>
+      </c>
+      <c r="D168" t="str">
+        <v>text</v>
+      </c>
+      <c r="E168" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v/>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
+      <c r="K168" t="str">
+        <v/>
+      </c>
+      <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v>N</v>
+      </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>spd_issuance_priority</v>
+      </c>
+      <c r="B169" t="str">
+        <v>priorityLevel</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Priority Tag</v>
+      </c>
+      <c r="D169" t="str">
+        <v>select</v>
+      </c>
+      <c r="E169" t="str">
+        <v>N</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Emergency VOR, Running Repair Express, Scheduled Periodic Maintenance, Recall Campaign</v>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v/>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169" t="str">
+        <v/>
+      </c>
+      <c r="K169" t="str">
+        <v/>
+      </c>
+      <c r="L169" t="str">
+        <v/>
+      </c>
+      <c r="M169" t="str">
+        <v>N</v>
+      </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>spd_issuance_priority</v>
+      </c>
+      <c r="B170" t="str">
+        <v>slaMins</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Picking SLA (Minutes)</v>
+      </c>
+      <c r="D170" t="str">
+        <v>number</v>
+      </c>
+      <c r="E170" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v/>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170" t="str">
+        <v/>
+      </c>
+      <c r="K170" t="str">
+        <v/>
+      </c>
+      <c r="L170" t="str">
+        <v/>
+      </c>
+      <c r="M170" t="str">
+        <v>N</v>
+      </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>spd_issuance_priority</v>
+      </c>
+      <c r="B171" t="str">
+        <v>requireOtp</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Mechanic Fingerprint / OTP Verification</v>
+      </c>
+      <c r="D171" t="str">
+        <v>select</v>
+      </c>
+      <c r="E171" t="str">
+        <v>N</v>
+      </c>
+      <c r="F171" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v/>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
+      <c r="K171" t="str">
+        <v/>
+      </c>
+      <c r="L171" t="str">
+        <v/>
+      </c>
+      <c r="M171" t="str">
+        <v>N</v>
+      </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>spd_issuance_priority</v>
+      </c>
+      <c r="B172" t="str">
+        <v>active</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D172" t="str">
+        <v>select</v>
+      </c>
+      <c r="E172" t="str">
+        <v>N</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v/>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
+      <c r="J172" t="str">
+        <v/>
+      </c>
+      <c r="K172" t="str">
+        <v/>
+      </c>
+      <c r="L172" t="str">
+        <v/>
+      </c>
+      <c r="M172" t="str">
+        <v>N</v>
+      </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>parts_delay_reasons</v>
+      </c>
+      <c r="B173" t="str">
+        <v>delayCode</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Delay Code</v>
+      </c>
+      <c r="D173" t="str">
+        <v>text</v>
+      </c>
+      <c r="E173" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v/>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
+      <c r="K173" t="str">
+        <v/>
+      </c>
+      <c r="L173" t="str">
+        <v/>
+      </c>
+      <c r="M173" t="str">
+        <v>N</v>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>parts_delay_reasons</v>
+      </c>
+      <c r="B174" t="str">
+        <v>reasonName</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Non-Availability Root Cause</v>
+      </c>
+      <c r="D174" t="str">
+        <v>text</v>
+      </c>
+      <c r="E174" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v/>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
+      <c r="K174" t="str">
+        <v/>
+      </c>
+      <c r="L174" t="str">
+        <v/>
+      </c>
+      <c r="M174" t="str">
+        <v>N</v>
+      </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>parts_delay_reasons</v>
+      </c>
+      <c r="B175" t="str">
+        <v>autoOrderSap</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Auto Trigger SAP Emergency Order</v>
+      </c>
+      <c r="D175" t="str">
+        <v>select</v>
+      </c>
+      <c r="E175" t="str">
+        <v>N</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v/>
+      </c>
+      <c r="I175" t="str">
+        <v/>
+      </c>
+      <c r="J175" t="str">
+        <v/>
+      </c>
+      <c r="K175" t="str">
+        <v/>
+      </c>
+      <c r="L175" t="str">
+        <v/>
+      </c>
+      <c r="M175" t="str">
+        <v>N</v>
+      </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>parts_delay_reasons</v>
+      </c>
+      <c r="B176" t="str">
+        <v>smsCustomer</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Trigger Customer ETA SMS</v>
+      </c>
+      <c r="D176" t="str">
+        <v>select</v>
+      </c>
+      <c r="E176" t="str">
+        <v>N</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v/>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
+      <c r="K176" t="str">
+        <v/>
+      </c>
+      <c r="L176" t="str">
+        <v/>
+      </c>
+      <c r="M176" t="str">
+        <v>N</v>
+      </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>parts_delay_reasons</v>
+      </c>
+      <c r="B177" t="str">
+        <v>active</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D177" t="str">
+        <v>select</v>
+      </c>
+      <c r="E177" t="str">
+        <v>N</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v/>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
+      <c r="K177" t="str">
+        <v/>
+      </c>
+      <c r="L177" t="str">
+        <v/>
+      </c>
+      <c r="M177" t="str">
+        <v>N</v>
+      </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>thd_escalation_categories</v>
+      </c>
+      <c r="B178" t="str">
+        <v>categoryCode</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Escalation Category</v>
+      </c>
+      <c r="D178" t="str">
+        <v>text</v>
+      </c>
+      <c r="E178" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
+      <c r="K178" t="str">
+        <v/>
+      </c>
+      <c r="L178" t="str">
+        <v/>
+      </c>
+      <c r="M178" t="str">
+        <v>N</v>
+      </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>thd_escalation_categories</v>
+      </c>
+      <c r="B179" t="str">
+        <v>systemDomain</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Engineering System</v>
+      </c>
+      <c r="D179" t="str">
+        <v>select</v>
+      </c>
+      <c r="E179" t="str">
+        <v>N</v>
+      </c>
+      <c r="F179" t="str">
+        <v>EV High Voltage Traction, DCA Dual Clutch Transmission, ADAS &amp; Radar Calibration, Braking &amp; ESP Hydraulics, CAN Bus Network Communication</v>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v/>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
+      <c r="K179" t="str">
+        <v/>
+      </c>
+      <c r="L179" t="str">
+        <v/>
+      </c>
+      <c r="M179" t="str">
+        <v>N</v>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>thd_escalation_categories</v>
+      </c>
+      <c r="B180" t="str">
+        <v>severityTier</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Plant Response SLA</v>
+      </c>
+      <c r="D180" t="str">
+        <v>select</v>
+      </c>
+      <c r="E180" t="str">
+        <v>N</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Tier 1 Critical (&lt; 4 Hours), Tier 2 High (&lt; 12 Hours), Tier 3 Standard (&lt; 24 Hours)</v>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v/>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180" t="str">
+        <v/>
+      </c>
+      <c r="K180" t="str">
+        <v/>
+      </c>
+      <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
+        <v>N</v>
+      </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>thd_escalation_categories</v>
+      </c>
+      <c r="B181" t="str">
+        <v>requiresPlantVisit</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Plant Field Engineer Dispatch</v>
+      </c>
+      <c r="D181" t="str">
+        <v>select</v>
+      </c>
+      <c r="E181" t="str">
+        <v>N</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v/>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
+      <c r="K181" t="str">
+        <v/>
+      </c>
+      <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v>N</v>
+      </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>thd_escalation_categories</v>
+      </c>
+      <c r="B182" t="str">
+        <v>active</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D182" t="str">
+        <v>select</v>
+      </c>
+      <c r="E182" t="str">
+        <v>N</v>
+      </c>
+      <c r="F182" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v/>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182" t="str">
+        <v/>
+      </c>
+      <c r="K182" t="str">
+        <v/>
+      </c>
+      <c r="L182" t="str">
+        <v/>
+      </c>
+      <c r="M182" t="str">
+        <v>N</v>
+      </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B183" t="str">
+        <v>tibNumber</v>
+      </c>
+      <c r="C183" t="str">
+        <v>TIB Bulletin Reference</v>
+      </c>
+      <c r="D183" t="str">
+        <v>text</v>
+      </c>
+      <c r="E183" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v/>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183" t="str">
+        <v/>
+      </c>
+      <c r="K183" t="str">
+        <v/>
+      </c>
+      <c r="L183" t="str">
+        <v/>
+      </c>
+      <c r="M183" t="str">
+        <v>N</v>
+      </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B184" t="str">
+        <v>title</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Subject / Advisory Scope</v>
+      </c>
+      <c r="D184" t="str">
+        <v>text</v>
+      </c>
+      <c r="E184" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v/>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
+      <c r="K184" t="str">
+        <v/>
+      </c>
+      <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v>N</v>
+      </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B185" t="str">
+        <v>affectedPpl</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Applicable Vehicle PPL</v>
+      </c>
+      <c r="D185" t="str">
+        <v>select</v>
+      </c>
+      <c r="E185" t="str">
+        <v>N</v>
+      </c>
+      <c r="F185" t="str">
+        <v>Nexon EV, Nexon ICE, Harrier / Safari, Curvv EV, Altroz</v>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v/>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
+      <c r="K185" t="str">
+        <v/>
+      </c>
+      <c r="L185" t="str">
+        <v/>
+      </c>
+      <c r="M185" t="str">
+        <v>N</v>
+      </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B186" t="str">
+        <v>reworkType</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Rework Classification</v>
+      </c>
+      <c r="D186" t="str">
+        <v>select</v>
+      </c>
+      <c r="E186" t="str">
+        <v>N</v>
+      </c>
+      <c r="F186" t="str">
+        <v>ECU Firmware Update, Harness Rerouting, Hardware Bush Replacement, Torque Audit</v>
+      </c>
+      <c r="G186" t="str">
+        <v/>
+      </c>
+      <c r="H186" t="str">
+        <v/>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
+      <c r="K186" t="str">
+        <v/>
+      </c>
+      <c r="L186" t="str">
+        <v/>
+      </c>
+      <c r="M186" t="str">
+        <v>N</v>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B187" t="str">
+        <v>active</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D187" t="str">
+        <v>select</v>
+      </c>
+      <c r="E187" t="str">
+        <v>N</v>
+      </c>
+      <c r="F187" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v/>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187" t="str">
+        <v/>
+      </c>
+      <c r="K187" t="str">
+        <v/>
+      </c>
+      <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
+        <v>N</v>
+      </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B188" t="str">
+        <v>driverCode</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Driver Code</v>
+      </c>
+      <c r="D188" t="str">
+        <v>text</v>
+      </c>
+      <c r="E188" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v/>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
+      <c r="J188" t="str">
+        <v/>
+      </c>
+      <c r="K188" t="str">
+        <v/>
+      </c>
+      <c r="L188" t="str">
+        <v/>
+      </c>
+      <c r="M188" t="str">
+        <v>N</v>
+      </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B189" t="str">
+        <v>driverName</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Driver Full Name</v>
+      </c>
+      <c r="D189" t="str">
+        <v>text</v>
+      </c>
+      <c r="E189" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v/>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
+      <c r="J189" t="str">
+        <v/>
+      </c>
+      <c r="K189" t="str">
+        <v/>
+      </c>
+      <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
+        <v>N</v>
+      </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B190" t="str">
+        <v>assignedZone</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Assigned Territory Zone</v>
+      </c>
+      <c r="D190" t="str">
+        <v>select</v>
+      </c>
+      <c r="E190" t="str">
+        <v>N</v>
+      </c>
+      <c r="F190" t="str">
+        <v>Zone A - Hitec City, Zone B - Secunderabad, Zone C - Gachibowli, Zone D - Banjara Hills</v>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190" t="str">
+        <v/>
+      </c>
+      <c r="K190" t="str">
+        <v/>
+      </c>
+      <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v>N</v>
+      </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B191" t="str">
+        <v>licenseNumber</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Commercial DL Number</v>
+      </c>
+      <c r="D191" t="str">
+        <v>text</v>
+      </c>
+      <c r="E191" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191" t="str">
+        <v/>
+      </c>
+      <c r="K191" t="str">
+        <v/>
+      </c>
+      <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v>N</v>
+      </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B192" t="str">
+        <v>evCertified</v>
+      </c>
+      <c r="C192" t="str">
+        <v>EV Transit Certified</v>
+      </c>
+      <c r="D192" t="str">
+        <v>select</v>
+      </c>
+      <c r="E192" t="str">
+        <v>N</v>
+      </c>
+      <c r="F192" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
+      <c r="K192" t="str">
+        <v/>
+      </c>
+      <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v>N</v>
+      </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B193" t="str">
+        <v>active</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D193" t="str">
+        <v>select</v>
+      </c>
+      <c r="E193" t="str">
+        <v>N</v>
+      </c>
+      <c r="F193" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
+      <c r="K193" t="str">
+        <v/>
+      </c>
+      <c r="L193" t="str">
+        <v/>
+      </c>
+      <c r="M193" t="str">
+        <v>N</v>
+      </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B194" t="str">
+        <v>checkpointCode</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Checkpoint Code</v>
+      </c>
+      <c r="D194" t="str">
+        <v>text</v>
+      </c>
+      <c r="E194" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
+        <v/>
+      </c>
+      <c r="L194" t="str">
+        <v/>
+      </c>
+      <c r="M194" t="str">
+        <v>N</v>
+      </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B195" t="str">
+        <v>checkpointDesc</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Reception Standard Requirement</v>
+      </c>
+      <c r="D195" t="str">
+        <v>text</v>
+      </c>
+      <c r="E195" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
+      <c r="K195" t="str">
+        <v/>
+      </c>
+      <c r="L195" t="str">
+        <v/>
+      </c>
+      <c r="M195" t="str">
+        <v>N</v>
+      </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B196" t="str">
+        <v>channel</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Intake Channel</v>
+      </c>
+      <c r="D196" t="str">
+        <v>select</v>
+      </c>
+      <c r="E196" t="str">
+        <v>N</v>
+      </c>
+      <c r="F196" t="str">
+        <v>Walk-in, Pre-Booked Appointment, Express Valet, Breakdown Flatbed</v>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" t="str">
+        <v/>
+      </c>
+      <c r="K196" t="str">
+        <v/>
+      </c>
+      <c r="L196" t="str">
+        <v/>
+      </c>
+      <c r="M196" t="str">
+        <v>N</v>
+      </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B197" t="str">
+        <v>mandatoryProof</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Mandatory Photo / Signature</v>
+      </c>
+      <c r="D197" t="str">
+        <v>select</v>
+      </c>
+      <c r="E197" t="str">
+        <v>N</v>
+      </c>
+      <c r="F197" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v/>
+      </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
+      <c r="J197" t="str">
+        <v/>
+      </c>
+      <c r="K197" t="str">
+        <v/>
+      </c>
+      <c r="L197" t="str">
+        <v/>
+      </c>
+      <c r="M197" t="str">
+        <v>N</v>
+      </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B198" t="str">
+        <v>active</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D198" t="str">
+        <v>select</v>
+      </c>
+      <c r="E198" t="str">
+        <v>N</v>
+      </c>
+      <c r="F198" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v/>
+      </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
+      <c r="J198" t="str">
+        <v/>
+      </c>
+      <c r="K198" t="str">
+        <v/>
+      </c>
+      <c r="L198" t="str">
+        <v/>
+      </c>
+      <c r="M198" t="str">
+        <v>N</v>
+      </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B199" t="str">
+        <v>ruleId</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Gate Rule Code</v>
+      </c>
+      <c r="D199" t="str">
+        <v>text</v>
+      </c>
+      <c r="E199" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v/>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
+      <c r="J199" t="str">
+        <v/>
+      </c>
+      <c r="K199" t="str">
+        <v/>
+      </c>
+      <c r="L199" t="str">
+        <v/>
+      </c>
+      <c r="M199" t="str">
+        <v>N</v>
+      </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B200" t="str">
+        <v>direction</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Movement Direction</v>
+      </c>
+      <c r="D200" t="str">
+        <v>select</v>
+      </c>
+      <c r="E200" t="str">
+        <v>N</v>
+      </c>
+      <c r="F200" t="str">
+        <v>Inward (Check-in), Outward (Check-out), Internal Bay Transit</v>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v/>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
+      <c r="J200" t="str">
+        <v/>
+      </c>
+      <c r="K200" t="str">
+        <v/>
+      </c>
+      <c r="L200" t="str">
+        <v/>
+      </c>
+      <c r="M200" t="str">
+        <v>N</v>
+      </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B201" t="str">
+        <v>verificationItem</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Verification Protocol</v>
+      </c>
+      <c r="D201" t="str">
+        <v>text</v>
+      </c>
+      <c r="E201" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F201" t="str">
+        <v/>
+      </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v/>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
+      <c r="J201" t="str">
+        <v/>
+      </c>
+      <c r="K201" t="str">
+        <v/>
+      </c>
+      <c r="L201" t="str">
+        <v/>
+      </c>
+      <c r="M201" t="str">
+        <v>N</v>
+      </c>
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B202" t="str">
+        <v>anprSync</v>
+      </c>
+      <c r="C202" t="str">
+        <v>ANPR Camera Auto-Verify</v>
+      </c>
+      <c r="D202" t="str">
+        <v>select</v>
+      </c>
+      <c r="E202" t="str">
+        <v>N</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
+        <v/>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202" t="str">
+        <v/>
+      </c>
+      <c r="K202" t="str">
+        <v/>
+      </c>
+      <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
+        <v>N</v>
+      </c>
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B203" t="str">
+        <v>active</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D203" t="str">
+        <v>select</v>
+      </c>
+      <c r="E203" t="str">
+        <v>N</v>
+      </c>
+      <c r="F203" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
+        <v/>
+      </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
+      <c r="J203" t="str">
+        <v/>
+      </c>
+      <c r="K203" t="str">
+        <v/>
+      </c>
+      <c r="L203" t="str">
+        <v/>
+      </c>
+      <c r="M203" t="str">
+        <v>N</v>
+      </c>
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B204" t="str">
+        <v>denialCode</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Denial Code</v>
+      </c>
+      <c r="D204" t="str">
+        <v>text</v>
+      </c>
+      <c r="E204" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
+        <v/>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
+      <c r="J204" t="str">
+        <v/>
+      </c>
+      <c r="K204" t="str">
+        <v/>
+      </c>
+      <c r="L204" t="str">
+        <v/>
+      </c>
+      <c r="M204" t="str">
+        <v>N</v>
+      </c>
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
+      <c r="Q204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B205" t="str">
+        <v>reason</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Security Denial / Hold Reason</v>
+      </c>
+      <c r="D205" t="str">
+        <v>text</v>
+      </c>
+      <c r="E205" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v/>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
+      <c r="J205" t="str">
+        <v/>
+      </c>
+      <c r="K205" t="str">
+        <v/>
+      </c>
+      <c r="L205" t="str">
+        <v/>
+      </c>
+      <c r="M205" t="str">
+        <v>N</v>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B206" t="str">
+        <v>escalateTo</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Immediate Notification Target</v>
+      </c>
+      <c r="D206" t="str">
+        <v>select</v>
+      </c>
+      <c r="E206" t="str">
+        <v>N</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Works Manager, Security Officer In-Charge, Service Head, Customer Relation Manager</v>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v/>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206" t="str">
+        <v/>
+      </c>
+      <c r="K206" t="str">
+        <v/>
+      </c>
+      <c r="L206" t="str">
+        <v/>
+      </c>
+      <c r="M206" t="str">
+        <v>N</v>
+      </c>
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B207" t="str">
+        <v>active</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D207" t="str">
+        <v>select</v>
+      </c>
+      <c r="E207" t="str">
+        <v>N</v>
+      </c>
+      <c r="F207" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v/>
+      </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
+      <c r="J207" t="str">
+        <v/>
+      </c>
+      <c r="K207" t="str">
+        <v/>
+      </c>
+      <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str">
+        <v>N</v>
+      </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q162"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q207"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>delayCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>reasonName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>autoOrderSap</v>
+      </c>
+      <c r="E1" t="str">
+        <v>smsCustomer</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>PDR-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>BO-PLANT-TRANSIT</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Depot stock depleted - Plant in-transit shipment</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PDR-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>BO-BIN-MISMATCH</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Physical bin inventory variance (Inventory Audit flag)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>N</v>
+      </c>
+      <c r="E3" t="str">
+        <v>N</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PDR-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>BO-SUPPLIER-SHORT</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Tier-1 vendor supply constraint (Critical semiconductor/ECU)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>categoryCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>systemDomain</v>
+      </c>
+      <c r="D1" t="str">
+        <v>severityTier</v>
+      </c>
+      <c r="E1" t="str">
+        <v>requiresPlantVisit</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>THD-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>THD-EV-BAT-ISO</v>
+      </c>
+      <c r="C2" t="str">
+        <v>EV High Voltage Traction</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Tier 1 Critical (&lt; 4 Hours)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>THD-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>THD-DCA-JERK</v>
+      </c>
+      <c r="C3" t="str">
+        <v>DCA Dual Clutch Transmission</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Tier 2 High (&lt; 12 Hours)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>N</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>THD-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>THD-ADAS-MISALIGN</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ADAS &amp; Radar Calibration</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Tier 2 High (&lt; 12 Hours)</v>
+      </c>
+      <c r="E4" t="str">
+        <v>N</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>THD-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>THD-CAN-ERR</v>
+      </c>
+      <c r="C5" t="str">
+        <v>CAN Bus Network Communication</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Tier 3 Standard (&lt; 24 Hours)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>N</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>tibNumber</v>
+      </c>
+      <c r="C1" t="str">
+        <v>title</v>
+      </c>
+      <c r="D1" t="str">
+        <v>affectedPpl</v>
+      </c>
+      <c r="E1" t="str">
+        <v>reworkType</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TIB-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TIB-2026-PV-089</v>
+      </c>
+      <c r="C2" t="str">
+        <v>BMS High-Voltage Contactor Firmware v4.8 Update</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ECU Firmware Update</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TIB-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TIB-2026-PV-112</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Rear Suspension Spring Seat Damping Pad Retrofit</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Harrier / Safari</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Hardware Bush Replacement</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TIB-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TIB-2026-PV-134</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Steering Column Earth Strap Resistance Check</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Torque Audit</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>driverCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>driverName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>assignedZone</v>
+      </c>
+      <c r="E1" t="str">
+        <v>licenseNumber</v>
+      </c>
+      <c r="F1" t="str">
+        <v>evCertified</v>
+      </c>
+      <c r="G1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DRV-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>DRV-HYD-101</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Nageshwar Rao</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Zone A - Hitec City</v>
+      </c>
+      <c r="E2" t="str">
+        <v>TS09-2019-0023412</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DRV-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>DRV-HYD-102</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Mohd Feroz Khan</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Zone B - Secunderabad</v>
+      </c>
+      <c r="E3" t="str">
+        <v>TS10-2018-0056123</v>
+      </c>
+      <c r="F3" t="str">
+        <v>N</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DRV-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>DRV-HYD-103</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Pradeep Patil</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Zone C - Gachibowli</v>
+      </c>
+      <c r="E4" t="str">
+        <v>TS09-2021-0089145</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>checkpointCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>checkpointDesc</v>
+      </c>
+      <c r="D1" t="str">
+        <v>channel</v>
+      </c>
+      <c r="E1" t="str">
+        <v>mandatoryProof</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>REC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>REC-VAL-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Digital vehicle outer walk-around photo capture (4 angles)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pre-Booked Appointment</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>REC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>REC-VAL-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Fuel / EV SOC level verification &amp; digital customer signature</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Pre-Booked Appointment</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>REC-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>REC-VAL-03</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Customer personal valuables custody declaration slip</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Walk-in</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ruleId</v>
+      </c>
+      <c r="C1" t="str">
+        <v>direction</v>
+      </c>
+      <c r="D1" t="str">
+        <v>verificationItem</v>
+      </c>
+      <c r="E1" t="str">
+        <v>anprSync</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SEC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>GATE-IN-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Inward (Check-in)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>ANPR plate scan match against appointment roster or generate walk-in pass</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SEC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>GATE-IN-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Inward (Check-in)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Physical chassis plate stamp confirmation against CRM VIN</v>
+      </c>
+      <c r="E3" t="str">
+        <v>N</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SEC-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>GATE-OUT-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Outward (Check-out)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Cashier zero-balance clearance seal &amp; gate pass OTP verification</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SEC-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>GATE-OUT-02</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Outward (Check-out)</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Old / replaced warranty parts box inventory verification (if customer request)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>N</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetData>

--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -26,19 +26,22 @@
     <sheet name="eqc_did_thresholds" sheetId="21" r:id="rId21"/>
     <sheet name="eqc_general_checklist" sheetId="22" r:id="rId22"/>
     <sheet name="eqc_schedule_checklist" sheetId="23" r:id="rId23"/>
-    <sheet name="bodyshop_process_stages" sheetId="24" r:id="rId24"/>
-    <sheet name="paint_booth_schedule" sheetId="25" r:id="rId25"/>
-    <sheet name="amc_pricing" sheetId="26" r:id="rId26"/>
-    <sheet name="warranty_defect_codes" sheetId="27" r:id="rId27"/>
-    <sheet name="goodwill_approval_limits" sheetId="28" r:id="rId28"/>
-    <sheet name="spd_issuance_priority" sheetId="29" r:id="rId29"/>
-    <sheet name="parts_delay_reasons" sheetId="30" r:id="rId30"/>
-    <sheet name="thd_escalation_categories" sheetId="31" r:id="rId31"/>
-    <sheet name="tib_bulletin_codes" sheetId="32" r:id="rId32"/>
-    <sheet name="driver_transit_roster" sheetId="33" r:id="rId33"/>
-    <sheet name="lounge_reception_checklist" sheetId="34" r:id="rId34"/>
-    <sheet name="gate_security_checklist" sheetId="35" r:id="rId35"/>
-    <sheet name="gate_denial_reasons" sheetId="36" r:id="rId36"/>
+    <sheet name="bs_inventory_sections" sheetId="24" r:id="rId24"/>
+    <sheet name="bs_inventory_checkpoints" sheetId="25" r:id="rId25"/>
+    <sheet name="bs_insurance_documents" sheetId="26" r:id="rId26"/>
+    <sheet name="bodyshop_process_stages" sheetId="27" r:id="rId27"/>
+    <sheet name="paint_booth_schedule" sheetId="28" r:id="rId28"/>
+    <sheet name="amc_pricing" sheetId="29" r:id="rId29"/>
+    <sheet name="warranty_defect_codes" sheetId="30" r:id="rId30"/>
+    <sheet name="goodwill_approval_limits" sheetId="31" r:id="rId31"/>
+    <sheet name="spd_issuance_priority" sheetId="32" r:id="rId32"/>
+    <sheet name="parts_delay_reasons" sheetId="33" r:id="rId33"/>
+    <sheet name="thd_escalation_categories" sheetId="34" r:id="rId34"/>
+    <sheet name="tib_bulletin_codes" sheetId="35" r:id="rId35"/>
+    <sheet name="driver_transit_roster" sheetId="36" r:id="rId36"/>
+    <sheet name="lounge_reception_checklist" sheetId="37" r:id="rId37"/>
+    <sheet name="gate_security_checklist" sheetId="38" r:id="rId38"/>
+    <sheet name="gate_denial_reasons" sheetId="39" r:id="rId39"/>
   </sheets>
 </workbook>
 </file>
@@ -481,7 +484,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support | Electronic Quality Check</v>
+        <v xml:space="preserve">  Logical Group  One of: Vehicle Data | Dealer Network | Service Operations | Parts, Claims &amp; Support | Electronic Quality Check | Bodyshop</v>
       </c>
     </row>
     <row r="11">
@@ -2086,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2573,128 +2576,128 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>bs_inventory_sections</v>
       </c>
       <c r="B22" t="str">
-        <v>BodyShop Denting &amp; Paint Stage Master</v>
+        <v>Inventory Capture Master — Sections</v>
       </c>
       <c r="C22" t="str">
         <v>bodyshop</v>
       </c>
       <c r="D22" t="str">
-        <v>Service Operations</v>
+        <v>Bodyshop</v>
       </c>
       <c r="E22" t="str">
         <v>TML_ADMIN</v>
       </c>
       <c r="F22" t="str">
-        <v>BodyShop Workflow</v>
+        <v>Inventory Capture</v>
       </c>
       <c r="G22" t="str">
-        <v>Sequenced bodyshop workflow stages from accident survey to bake oven finish.</v>
+        <v>Sections of the vehicle inventory capture, per BU, in Sequence Priority order. Roles decide who sees the section; Service Type "Accident" shows it only for accident jobs.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>paint_booth_schedule</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B23" t="str">
-        <v>Heated Spray Booth &amp; Oven Slot Master</v>
+        <v>Inventory Capture Master — Checkpoints</v>
       </c>
       <c r="C23" t="str">
         <v>bodyshop</v>
       </c>
       <c r="D23" t="str">
-        <v>Service Operations</v>
+        <v>Bodyshop</v>
       </c>
       <c r="E23" t="str">
-        <v>DEALER_ADMIN</v>
+        <v>TML_ADMIN</v>
       </c>
       <c r="F23" t="str">
-        <v>Paint Facilities</v>
+        <v>Inventory Capture</v>
       </c>
       <c r="G23" t="str">
-        <v>Spray booth slotting, color batching, and energy consumption metrics.</v>
+        <v>Rows as given in the BA workbook; incomplete rows are kept and listed in the preview checklist. What is captured inside each section: Sub-Section (Level 1 / Level 2) and Checkpoint, who captures it, acceptable values and the photo / video evidence. A row without a Checkpoint is captured at Sub-Section level.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>amc_pricing</v>
+        <v>bs_insurance_documents</v>
       </c>
       <c r="B24" t="str">
-        <v>AMC Products &amp; Pricing Master</v>
+        <v>Insurance Document Collection — Customer</v>
       </c>
       <c r="C24" t="str">
-        <v>claim</v>
+        <v>bodyshop</v>
       </c>
       <c r="D24" t="str">
-        <v>Parts, Claims &amp; Support</v>
+        <v>Bodyshop</v>
       </c>
       <c r="E24" t="str">
         <v>TML_ADMIN</v>
       </c>
       <c r="F24" t="str">
-        <v>Commercial Contracts</v>
+        <v>Insurance Documents</v>
       </c>
       <c r="G24" t="str">
-        <v>Tata Motors Value Care AMC packages, tenure, coverage limits, and national price schedules.</v>
+        <v>Documents collected from the customer for insurance (accident) jobs, in Sequence order. Only active documents are asked for.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>warranty_defect_codes</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B25" t="str">
-        <v>Warranty Defect &amp; Causal Part Tagging Master</v>
+        <v>BodyShop Denting &amp; Paint Stage Master</v>
       </c>
       <c r="C25" t="str">
-        <v>claim</v>
+        <v>bodyshop</v>
       </c>
       <c r="D25" t="str">
-        <v>Parts, Claims &amp; Support</v>
+        <v>Bodyshop</v>
       </c>
       <c r="E25" t="str">
         <v>TML_ADMIN</v>
       </c>
       <c r="F25" t="str">
-        <v>Warranty Tagging</v>
+        <v>BodyShop Workflow</v>
       </c>
       <c r="G25" t="str">
-        <v>Defect classifications for processing OEM claims to Tata Motors and vendor chargebacks.</v>
+        <v>Sequenced bodyshop workflow stages from accident survey to bake oven finish.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B26" t="str">
-        <v>Goodwill &amp; Special Concession Matrix</v>
+        <v>Heated Spray Booth &amp; Oven Slot Master</v>
       </c>
       <c r="C26" t="str">
-        <v>claim</v>
+        <v>bodyshop</v>
       </c>
       <c r="D26" t="str">
-        <v>Parts, Claims &amp; Support</v>
+        <v>Service Operations</v>
       </c>
       <c r="E26" t="str">
-        <v>TML_ADMIN</v>
+        <v>DEALER_ADMIN</v>
       </c>
       <c r="F26" t="str">
-        <v>Approval Authorities</v>
+        <v>Paint Facilities</v>
       </c>
       <c r="G26" t="str">
-        <v>Financial approval thresholds for out-of-warranty customer goodwill concessions.</v>
+        <v>Spray booth slotting, color batching, and energy consumption metrics.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>spd_issuance_priority</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B27" t="str">
-        <v>Spare Parts Requisition &amp; Issuance Priority</v>
+        <v>AMC Products &amp; Pricing Master</v>
       </c>
       <c r="C27" t="str">
-        <v>spd</v>
+        <v>claim</v>
       </c>
       <c r="D27" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2703,44 +2706,44 @@
         <v>TML_ADMIN</v>
       </c>
       <c r="F27" t="str">
-        <v>Inventory Picking</v>
+        <v>Commercial Contracts</v>
       </c>
       <c r="G27" t="str">
-        <v>Prioritizes store counter picking slips by vehicle state: VOR (Vehicle Off Road), Warranty, Running Repair.</v>
+        <v>Tata Motors Value Care AMC packages, tenure, coverage limits, and national price schedules.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>parts_delay_reasons</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B28" t="str">
-        <v>Spare Parts Stockout &amp; Backorder LOV</v>
+        <v>Warranty Defect &amp; Causal Part Tagging Master</v>
       </c>
       <c r="C28" t="str">
-        <v>spd</v>
+        <v>claim</v>
       </c>
       <c r="D28" t="str">
         <v>Parts, Claims &amp; Support</v>
       </c>
       <c r="E28" t="str">
-        <v>DEALER_ADMIN</v>
+        <v>TML_ADMIN</v>
       </c>
       <c r="F28" t="str">
-        <v>Stockout Categories</v>
+        <v>Warranty Tagging</v>
       </c>
       <c r="G28" t="str">
-        <v>Stockroom delay categorization for auto-generating SAP parts backorders and customer notifications.</v>
+        <v>Defect classifications for processing OEM claims to Tata Motors and vendor chargebacks.</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>thd_escalation_categories</v>
+        <v>goodwill_approval_limits</v>
       </c>
       <c r="B29" t="str">
-        <v>THD Technical Escalation Category &amp; Severity</v>
+        <v>Goodwill &amp; Special Concession Matrix</v>
       </c>
       <c r="C29" t="str">
-        <v>thd</v>
+        <v>claim</v>
       </c>
       <c r="D29" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2749,21 +2752,21 @@
         <v>TML_ADMIN</v>
       </c>
       <c r="F29" t="str">
-        <v>Engineering Escalations</v>
+        <v>Approval Authorities</v>
       </c>
       <c r="G29" t="str">
-        <v>Field technical issue tickets to Tata Motors plant engineering, crash diagnostics, and high-voltage defects.</v>
+        <v>Financial approval thresholds for out-of-warranty customer goodwill concessions.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>spd_issuance_priority</v>
       </c>
       <c r="B30" t="str">
-        <v>Technical Information Bulletin (TIB) Advisory Codes</v>
+        <v>Spare Parts Requisition &amp; Issuance Priority</v>
       </c>
       <c r="C30" t="str">
-        <v>thd</v>
+        <v>spd</v>
       </c>
       <c r="D30" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2772,21 +2775,21 @@
         <v>TML_ADMIN</v>
       </c>
       <c r="F30" t="str">
-        <v>Plant Bulletins</v>
+        <v>Inventory Picking</v>
       </c>
       <c r="G30" t="str">
-        <v>Tata Motors factory service technical bulletins, software flash versions, and campaign advisories.</v>
+        <v>Prioritizes store counter picking slips by vehicle state: VOR (Vehicle Off Road), Warranty, Running Repair.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>driver_transit_roster</v>
+        <v>parts_delay_reasons</v>
       </c>
       <c r="B31" t="str">
-        <v>Chauffeur &amp; Pick-and-Drop Transit Roster</v>
+        <v>Spare Parts Stockout &amp; Backorder LOV</v>
       </c>
       <c r="C31" t="str">
-        <v>reception</v>
+        <v>spd</v>
       </c>
       <c r="D31" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2795,21 +2798,21 @@
         <v>DEALER_ADMIN</v>
       </c>
       <c r="F31" t="str">
-        <v>Transit Chauffeurs</v>
+        <v>Stockout Categories</v>
       </c>
       <c r="G31" t="str">
-        <v>Driver certifications, assigned zone geofences, and vehicle transit speed monitoring.</v>
+        <v>Stockroom delay categorization for auto-generating SAP parts backorders and customer notifications.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>thd_escalation_categories</v>
       </c>
       <c r="B32" t="str">
-        <v>Customer Reception &amp; Greeting Checklist</v>
+        <v>THD Technical Escalation Category &amp; Severity</v>
       </c>
       <c r="C32" t="str">
-        <v>reception</v>
+        <v>thd</v>
       </c>
       <c r="D32" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2818,21 +2821,21 @@
         <v>TML_ADMIN</v>
       </c>
       <c r="F32" t="str">
-        <v>Customer Welcome</v>
+        <v>Engineering Escalations</v>
       </c>
       <c r="G32" t="str">
-        <v>Standard OEM lounge customer greeting and advisor electronic tablet handover checklist.</v>
+        <v>Field technical issue tickets to Tata Motors plant engineering, crash diagnostics, and high-voltage defects.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>gate_security_checklist</v>
+        <v>tib_bulletin_codes</v>
       </c>
       <c r="B33" t="str">
-        <v>Vehicle Gate Inward / Outward Barrier Checklist</v>
+        <v>Technical Information Bulletin (TIB) Advisory Codes</v>
       </c>
       <c r="C33" t="str">
-        <v>security</v>
+        <v>thd</v>
       </c>
       <c r="D33" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2841,21 +2844,21 @@
         <v>TML_ADMIN</v>
       </c>
       <c r="F33" t="str">
-        <v>Perimeter Security</v>
+        <v>Plant Bulletins</v>
       </c>
       <c r="G33" t="str">
-        <v>Mandatory perimeter verification rules for automatic ANPR barrier opening and vehicle passes.</v>
+        <v>Tata Motors factory service technical bulletins, software flash versions, and campaign advisories.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>gate_denial_reasons</v>
+        <v>driver_transit_roster</v>
       </c>
       <c r="B34" t="str">
-        <v>Gate Entry Denial &amp; Security Hold LOV</v>
+        <v>Chauffeur &amp; Pick-and-Drop Transit Roster</v>
       </c>
       <c r="C34" t="str">
-        <v>security</v>
+        <v>reception</v>
       </c>
       <c r="D34" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2864,15 +2867,84 @@
         <v>DEALER_ADMIN</v>
       </c>
       <c r="F34" t="str">
+        <v>Transit Chauffeurs</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Driver certifications, assigned zone geofences, and vehicle transit speed monitoring.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Customer Reception &amp; Greeting Checklist</v>
+      </c>
+      <c r="C35" t="str">
+        <v>reception</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E35" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Customer Welcome</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Standard OEM lounge customer greeting and advisor electronic tablet handover checklist.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Vehicle Gate Inward / Outward Barrier Checklist</v>
+      </c>
+      <c r="C36" t="str">
+        <v>security</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E36" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F36" t="str">
         <v>Perimeter Security</v>
       </c>
-      <c r="G34" t="str">
+      <c r="G36" t="str">
+        <v>Mandatory perimeter verification rules for automatic ANPR barrier opening and vehicle passes.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Gate Entry Denial &amp; Security Hold LOV</v>
+      </c>
+      <c r="C37" t="str">
+        <v>security</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E37" t="str">
+        <v>DEALER_ADMIN</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Perimeter Security</v>
+      </c>
+      <c r="G37" t="str">
         <v>Security gate vehicle hold classifications and escalation protocol for police or insurance hold.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G37"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3722,6 +3794,1053 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>bu</v>
+      </c>
+      <c r="C1" t="str">
+        <v>section</v>
+      </c>
+      <c r="D1" t="str">
+        <v>roles</v>
+      </c>
+      <c r="E1" t="str">
+        <v>sequencePriority</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+      <c r="G1" t="str">
+        <v>serviceType</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>BSS-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D2" t="str">
+        <v>DSvAdv, Driver</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G2" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BSS-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Accident Details</v>
+      </c>
+      <c r="D3" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Accident</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>BSS-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C4" t="str">
+        <v>External</v>
+      </c>
+      <c r="D4" t="str">
+        <v>DSvAdv, Driver</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G4" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BSS-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="D5" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G5" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>BSS-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Inventory</v>
+      </c>
+      <c r="D6" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G6" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>BSS-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Accessories</v>
+      </c>
+      <c r="D7" t="str">
+        <v>DSvAdv, Driver</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G7" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>BSS-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Tyre &amp; Battery</v>
+      </c>
+      <c r="D8" t="str">
+        <v>DSvAdv, Driver</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G8" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>BSS-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D9" t="str">
+        <v>DSvAdv, Driver</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G9" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>BSS-09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Accident Details</v>
+      </c>
+      <c r="D10" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Accident</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BSS-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C11" t="str">
+        <v>External</v>
+      </c>
+      <c r="D11" t="str">
+        <v>DSvAdv, Driver</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G11" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BSS-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="D12" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G12" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>BSS-12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Inventory</v>
+      </c>
+      <c r="D13" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G13" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>BSS-13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Accessories</v>
+      </c>
+      <c r="D14" t="str">
+        <v>DSvAdv, Driver</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G14" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>BSS-14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Tyre &amp; Battery</v>
+      </c>
+      <c r="D15" t="str">
+        <v>DSvAdv, Driver</v>
+      </c>
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G15" t="str">
+        <v>All</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P12"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>section</v>
+      </c>
+      <c r="C1" t="str">
+        <v>subSection1</v>
+      </c>
+      <c r="D1" t="str">
+        <v>subSection1Seq</v>
+      </c>
+      <c r="E1" t="str">
+        <v>subSection2</v>
+      </c>
+      <c r="F1" t="str">
+        <v>subSection2Seq</v>
+      </c>
+      <c r="G1" t="str">
+        <v>checkpoint</v>
+      </c>
+      <c r="H1" t="str">
+        <v>checkpointSeq</v>
+      </c>
+      <c r="I1" t="str">
+        <v>role</v>
+      </c>
+      <c r="J1" t="str">
+        <v>acceptableValues</v>
+      </c>
+      <c r="K1" t="str">
+        <v>mandatory</v>
+      </c>
+      <c r="L1" t="str">
+        <v>active</v>
+      </c>
+      <c r="M1" t="str">
+        <v>mediaType</v>
+      </c>
+      <c r="N1" t="str">
+        <v>imagesRequired</v>
+      </c>
+      <c r="O1" t="str">
+        <v>mediaApplicableOn</v>
+      </c>
+      <c r="P1" t="str">
+        <v>serviceType</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>BSC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Cabin</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Image</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Not OK</v>
+      </c>
+      <c r="P2" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BSC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Instrument Cluster</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Video/Image</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Not OK</v>
+      </c>
+      <c r="P3" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>BSC-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Seats &amp; Belt</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Video/Image</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Not OK</v>
+      </c>
+      <c r="P4" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>BSC-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Steering Controls</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>Steering Wheel Condition</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="J5" t="str">
+        <v>OK</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Image</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="str">
+        <v>All</v>
+      </c>
+      <c r="P5" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>BSC-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Steering Controls</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v>Horn Working</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="J6" t="str">
+        <v>OK, NOT OK, NA</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Image</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6" t="str">
+        <v>All</v>
+      </c>
+      <c r="P6" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>BSC-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Internal</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Steering Controls</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>Steering Controls Working</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="J7" t="str">
+        <v>OK, NOT OK</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Image</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="str">
+        <v>All</v>
+      </c>
+      <c r="P7" t="str">
+        <v>All</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>BSC-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Insurance Copy</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Image</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="str">
+        <v>All</v>
+      </c>
+      <c r="P8" t="str">
+        <v>Accident</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>BSC-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Police Complaint Report</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>DSvAdv</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Image</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="str">
+        <v>All</v>
+      </c>
+      <c r="P9" t="str">
+        <v>Accident</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>BSC-09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Internal-Accessories</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Battery Information</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Driver</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>Video</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BSC-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v>Inventory Categories</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>Accessories Internal</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>Owner's Manual</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Driver</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Count</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BSC-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v/>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>Pen Drive</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Driver</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Count</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:P12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>documentCategory</v>
+      </c>
+      <c r="C1" t="str">
+        <v>mandatoryFlag</v>
+      </c>
+      <c r="D1" t="str">
+        <v>documentType</v>
+      </c>
+      <c r="E1" t="str">
+        <v>imagesRequired</v>
+      </c>
+      <c r="F1" t="str">
+        <v>sequence</v>
+      </c>
+      <c r="G1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>BSD-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Insurance Copy</v>
+      </c>
+      <c r="C2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D2" t="str">
+        <v>PDF/Image</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="str">
+        <v>N</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>BSD-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Police Complaint Report</v>
+      </c>
+      <c r="C3" t="str">
+        <v>N</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Image</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
     <row r="1">
@@ -3831,7 +4950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetData>
@@ -3902,7 +5021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
   <sheetData>
@@ -4017,322 +5136,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>defectCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>defectCategory</v>
-      </c>
-      <c r="D1" t="str">
-        <v>partCoverage</v>
-      </c>
-      <c r="E1" t="str">
-        <v>requiresSampleReturn</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>WDC-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>DEF-MFG-OILSEAL</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Manufacturing Quality</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Standard 3Yr / 100K Km</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>WDC-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>DEF-VEND-SUSPBUSH</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Vendor Assembly Flaw</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Standard 3Yr / 100K Km</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>WDC-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>DEF-EV-CELLIMB</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Material Defect</v>
-      </c>
-      <c r="D4" t="str">
-        <v>EV HV Battery 8Yr / 160K Km</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>authorityTier</v>
-      </c>
-      <c r="C1" t="str">
-        <v>maxLaborConcession</v>
-      </c>
-      <c r="D1" t="str">
-        <v>maxPartsConcession</v>
-      </c>
-      <c r="E1" t="str">
-        <v>maxAmountInr</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>GW-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Works Manager (WM)</v>
-      </c>
-      <c r="C2">
-        <v>25</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2">
-        <v>5000</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>GW-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Area Service Manager (ASM - TML)</v>
-      </c>
-      <c r="C3">
-        <v>50</v>
-      </c>
-      <c r="D3">
-        <v>35</v>
-      </c>
-      <c r="E3">
-        <v>25000</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>GW-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Regional Customer Care Head (RCCH)</v>
-      </c>
-      <c r="C4">
-        <v>75</v>
-      </c>
-      <c r="D4">
-        <v>60</v>
-      </c>
-      <c r="E4">
-        <v>75000</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>GW-04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>DGM Service Central</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
-      <c r="E5">
-        <v>300000</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>priorityCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>priorityLevel</v>
-      </c>
-      <c r="D1" t="str">
-        <v>slaMins</v>
-      </c>
-      <c r="E1" t="str">
-        <v>requireOtp</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>SPD-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>PRIO-VOR-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Emergency VOR</v>
-      </c>
-      <c r="D2">
-        <v>15</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>SPD-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>PRIO-RUN-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Running Repair Express</v>
-      </c>
-      <c r="D3">
-        <v>30</v>
-      </c>
-      <c r="E3" t="str">
-        <v>N</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>SPD-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>PRIO-SCH-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Scheduled Periodic Maintenance</v>
-      </c>
-      <c r="D4">
-        <v>45</v>
-      </c>
-      <c r="E4" t="str">
-        <v>N</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>SPD-04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>PRIO-REC-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Recall Campaign</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q207"/>
+  <dimension ref="A1:Q234"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11756,22 +12562,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>bs_inventory_sections</v>
       </c>
       <c r="B141" t="str">
-        <v>stageCode</v>
+        <v>bu</v>
       </c>
       <c r="C141" t="str">
-        <v>Stage Code</v>
+        <v>BU</v>
       </c>
       <c r="D141" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E141" t="str">
         <v>Y</v>
       </c>
       <c r="F141" t="str">
-        <v/>
+        <v>PV, EV</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -11809,13 +12615,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>bs_inventory_sections</v>
       </c>
       <c r="B142" t="str">
-        <v>stageName</v>
+        <v>section</v>
       </c>
       <c r="C142" t="str">
-        <v>Process Stage</v>
+        <v>Section</v>
       </c>
       <c r="D142" t="str">
         <v>text</v>
@@ -11862,16 +12668,16 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>bs_inventory_sections</v>
       </c>
       <c r="B143" t="str">
-        <v>standardDurationHrs</v>
+        <v>roles</v>
       </c>
       <c r="C143" t="str">
-        <v>Standard FRT (Hrs)</v>
+        <v>Roles</v>
       </c>
       <c r="D143" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E143" t="str">
         <v>Y</v>
@@ -11892,10 +12698,10 @@
         <v/>
       </c>
       <c r="K143" t="str">
-        <v/>
+        <v>^\s*(DSvAdv|Driver)(\s*,\s*(DSvAdv|Driver))?\s*$</v>
       </c>
       <c r="L143" t="str">
-        <v/>
+        <v>Use DSvAdv, Driver or "DSvAdv, Driver".</v>
       </c>
       <c r="M143" t="str">
         <v>N</v>
@@ -11910,33 +12716,33 @@
         <v/>
       </c>
       <c r="Q143" t="str">
-        <v/>
+        <v>DSvAdv, Driver or both (comma separated).</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>bs_inventory_sections</v>
       </c>
       <c r="B144" t="str">
-        <v>requiresSurveyorApproval</v>
+        <v>sequencePriority</v>
       </c>
       <c r="C144" t="str">
-        <v>Surveyor Sign-off Gate</v>
+        <v>Sequence Priority</v>
       </c>
       <c r="D144" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E144" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F144" t="str">
-        <v>Y, N</v>
-      </c>
-      <c r="G144" t="str">
-        <v/>
-      </c>
-      <c r="H144" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+      <c r="H144">
+        <v>99</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -11968,7 +12774,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>bodyshop_process_stages</v>
+        <v>bs_inventory_sections</v>
       </c>
       <c r="B145" t="str">
         <v>active</v>
@@ -11980,7 +12786,7 @@
         <v>select</v>
       </c>
       <c r="E145" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F145" t="str">
         <v>Y, N</v>
@@ -12021,22 +12827,22 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>paint_booth_schedule</v>
+        <v>bs_inventory_sections</v>
       </c>
       <c r="B146" t="str">
-        <v>boothName</v>
+        <v>serviceType</v>
       </c>
       <c r="C146" t="str">
-        <v>Spray Booth Identification</v>
+        <v>Service Type</v>
       </c>
       <c r="D146" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E146" t="str">
         <v>Y</v>
       </c>
       <c r="F146" t="str">
-        <v/>
+        <v>All, Accident</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -12074,22 +12880,22 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>paint_booth_schedule</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B147" t="str">
-        <v>paintType</v>
+        <v>section</v>
       </c>
       <c r="C147" t="str">
-        <v>Paint Technology</v>
+        <v>Section</v>
       </c>
       <c r="D147" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E147" t="str">
         <v>N</v>
       </c>
       <c r="F147" t="str">
-        <v>Waterborne Eco-Basecoat, Solvent-borne Clearcoat, Matte Finish Specialty</v>
+        <v/>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -12122,24 +12928,24 @@
         <v/>
       </c>
       <c r="Q147" t="str">
-        <v/>
+        <v>Must match a Section in the Sections master. Blanks are listed in the preview checklist.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>paint_booth_schedule</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B148" t="str">
-        <v>maxBakeTemp</v>
+        <v>subSection1</v>
       </c>
       <c r="C148" t="str">
-        <v>Baking Temperature (°C)</v>
+        <v>Sub-Section Level 1</v>
       </c>
       <c r="D148" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E148" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F148" t="str">
         <v/>
@@ -12180,28 +12986,28 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>paint_booth_schedule</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B149" t="str">
-        <v>dailyCapacityPanels</v>
+        <v>subSection1Seq</v>
       </c>
       <c r="C149" t="str">
-        <v>Daily Panel Capacity</v>
+        <v>Sub-Section Sequence</v>
       </c>
       <c r="D149" t="str">
         <v>number</v>
       </c>
       <c r="E149" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F149" t="str">
         <v/>
       </c>
-      <c r="G149" t="str">
-        <v/>
-      </c>
-      <c r="H149" t="str">
-        <v/>
+      <c r="G149">
+        <v>1</v>
+      </c>
+      <c r="H149">
+        <v>999</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -12233,22 +13039,22 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>paint_booth_schedule</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B150" t="str">
-        <v>active</v>
+        <v>subSection2</v>
       </c>
       <c r="C150" t="str">
-        <v>Active</v>
+        <v>Sub-Section Level 2</v>
       </c>
       <c r="D150" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E150" t="str">
         <v>N</v>
       </c>
       <c r="F150" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -12286,28 +13092,28 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>amc_pricing</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B151" t="str">
-        <v>amcCode</v>
+        <v>subSection2Seq</v>
       </c>
       <c r="C151" t="str">
-        <v>AMC Plan Code</v>
+        <v>Sub-Section Level 2 Sequence</v>
       </c>
       <c r="D151" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E151" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F151" t="str">
         <v/>
       </c>
-      <c r="G151" t="str">
-        <v/>
-      </c>
-      <c r="H151" t="str">
-        <v/>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>999</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -12339,19 +13145,19 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>amc_pricing</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B152" t="str">
-        <v>planName</v>
+        <v>checkpoint</v>
       </c>
       <c r="C152" t="str">
-        <v>AMC Plan Name</v>
+        <v>Checkpoint</v>
       </c>
       <c r="D152" t="str">
         <v>text</v>
       </c>
       <c r="E152" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F152" t="str">
         <v/>
@@ -12387,33 +13193,33 @@
         <v/>
       </c>
       <c r="Q152" t="str">
-        <v/>
+        <v>Leave blank to capture at Sub-Section level.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>amc_pricing</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B153" t="str">
-        <v>pplName</v>
+        <v>checkpointSeq</v>
       </c>
       <c r="C153" t="str">
-        <v>Applicable PPL</v>
+        <v>Checkpoint Sequence</v>
       </c>
       <c r="D153" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E153" t="str">
         <v>N</v>
       </c>
       <c r="F153" t="str">
-        <v>All Models, Nexon, Altroz, Harrier / Safari, EV Fleet</v>
-      </c>
-      <c r="G153" t="str">
-        <v/>
-      </c>
-      <c r="H153" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G153">
+        <v>1</v>
+      </c>
+      <c r="H153">
+        <v>999</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -12445,22 +13251,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>amc_pricing</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B154" t="str">
-        <v>tenureYears</v>
+        <v>role</v>
       </c>
       <c r="C154" t="str">
-        <v>Tenure (Yrs)</v>
+        <v>Role</v>
       </c>
       <c r="D154" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E154" t="str">
         <v>Y</v>
       </c>
       <c r="F154" t="str">
-        <v/>
+        <v>DSvAdv, Driver</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -12498,19 +13304,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>amc_pricing</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B155" t="str">
-        <v>maxKms</v>
+        <v>acceptableValues</v>
       </c>
       <c r="C155" t="str">
-        <v>Max Coverage (KMs)</v>
+        <v>Acceptable Values</v>
       </c>
       <c r="D155" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E155" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F155" t="str">
         <v/>
@@ -12546,27 +13352,27 @@
         <v/>
       </c>
       <c r="Q155" t="str">
-        <v/>
+        <v>Comma separated, e.g. "OK, NOT OK, NA", or "Count".</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>amc_pricing</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B156" t="str">
-        <v>priceInr</v>
+        <v>mandatory</v>
       </c>
       <c r="C156" t="str">
-        <v>Base OEM MRP (₹)</v>
+        <v>Mandatory</v>
       </c>
       <c r="D156" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E156" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F156" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -12604,7 +13410,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>amc_pricing</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B157" t="str">
         <v>active</v>
@@ -12652,27 +13458,27 @@
         <v/>
       </c>
       <c r="Q157" t="str">
-        <v/>
+        <v>Blank is treated as inactive.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>warranty_defect_codes</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B158" t="str">
-        <v>defectCode</v>
+        <v>mediaType</v>
       </c>
       <c r="C158" t="str">
-        <v>Defect Code</v>
+        <v>Video/Image</v>
       </c>
       <c r="D158" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E158" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F158" t="str">
-        <v/>
+        <v>Image, Video, Video/Image</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -12710,28 +13516,28 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>warranty_defect_codes</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B159" t="str">
-        <v>defectCategory</v>
+        <v>imagesRequired</v>
       </c>
       <c r="C159" t="str">
-        <v>Defect Group</v>
+        <v>No. of Image Required (Max 2)</v>
       </c>
       <c r="D159" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E159" t="str">
         <v>N</v>
       </c>
       <c r="F159" t="str">
-        <v>Manufacturing Quality, Material Defect, Vendor Assembly Flaw, Software / Firmware Logic, Corrosion / Paint Flaw</v>
-      </c>
-      <c r="G159" t="str">
-        <v/>
-      </c>
-      <c r="H159" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G159">
+        <v>1</v>
+      </c>
+      <c r="H159">
+        <v>2</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -12763,13 +13569,13 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>warranty_defect_codes</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B160" t="str">
-        <v>partCoverage</v>
+        <v>mediaApplicableOn</v>
       </c>
       <c r="C160" t="str">
-        <v>Warranty Scheme</v>
+        <v>Image/Video Applicable On</v>
       </c>
       <c r="D160" t="str">
         <v>select</v>
@@ -12778,7 +13584,7 @@
         <v>N</v>
       </c>
       <c r="F160" t="str">
-        <v>Standard 3Yr / 100K Km, Extended Warranty (EW), EV HV Battery 8Yr / 160K Km</v>
+        <v>All, Not OK</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -12816,13 +13622,13 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>warranty_defect_codes</v>
+        <v>bs_inventory_checkpoints</v>
       </c>
       <c r="B161" t="str">
-        <v>requiresSampleReturn</v>
+        <v>serviceType</v>
       </c>
       <c r="C161" t="str">
-        <v>Return Physical Sample to Plant</v>
+        <v>Service Type</v>
       </c>
       <c r="D161" t="str">
         <v>select</v>
@@ -12831,7 +13637,7 @@
         <v>N</v>
       </c>
       <c r="F161" t="str">
-        <v>Y, N</v>
+        <v>All, Accident</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -12869,22 +13675,22 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>warranty_defect_codes</v>
+        <v>bs_insurance_documents</v>
       </c>
       <c r="B162" t="str">
-        <v>active</v>
+        <v>documentCategory</v>
       </c>
       <c r="C162" t="str">
-        <v>Active</v>
+        <v>Document Category</v>
       </c>
       <c r="D162" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E162" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F162" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -12922,22 +13728,22 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>bs_insurance_documents</v>
       </c>
       <c r="B163" t="str">
-        <v>authorityTier</v>
+        <v>mandatoryFlag</v>
       </c>
       <c r="C163" t="str">
-        <v>Approving Authority</v>
+        <v>Mandatory Flag</v>
       </c>
       <c r="D163" t="str">
         <v>select</v>
       </c>
       <c r="E163" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F163" t="str">
-        <v>Works Manager (WM), Area Service Manager (ASM - TML), Regional Customer Care Head (RCCH), DGM Service Central</v>
+        <v>Y, N</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -12975,22 +13781,22 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>bs_insurance_documents</v>
       </c>
       <c r="B164" t="str">
-        <v>maxLaborConcession</v>
+        <v>documentType</v>
       </c>
       <c r="C164" t="str">
-        <v>Max Labor Discount (%)</v>
+        <v>Document Type</v>
       </c>
       <c r="D164" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E164" t="str">
         <v>Y</v>
       </c>
       <c r="F164" t="str">
-        <v/>
+        <v>PDF/Image, Image, PDF</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -13028,28 +13834,28 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>bs_insurance_documents</v>
       </c>
       <c r="B165" t="str">
-        <v>maxPartsConcession</v>
+        <v>imagesRequired</v>
       </c>
       <c r="C165" t="str">
-        <v>Max Parts Discount (%)</v>
+        <v>No. of Image Required (Max 2)</v>
       </c>
       <c r="D165" t="str">
         <v>number</v>
       </c>
       <c r="E165" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F165" t="str">
         <v/>
       </c>
-      <c r="G165" t="str">
-        <v/>
-      </c>
-      <c r="H165" t="str">
-        <v/>
+      <c r="G165">
+        <v>1</v>
+      </c>
+      <c r="H165">
+        <v>2</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -13081,13 +13887,13 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>bs_insurance_documents</v>
       </c>
       <c r="B166" t="str">
-        <v>maxAmountInr</v>
+        <v>sequence</v>
       </c>
       <c r="C166" t="str">
-        <v>Max Claim Value (₹)</v>
+        <v>Sequence</v>
       </c>
       <c r="D166" t="str">
         <v>number</v>
@@ -13098,11 +13904,11 @@
       <c r="F166" t="str">
         <v/>
       </c>
-      <c r="G166" t="str">
-        <v/>
-      </c>
-      <c r="H166" t="str">
-        <v/>
+      <c r="G166">
+        <v>1</v>
+      </c>
+      <c r="H166">
+        <v>99</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -13134,7 +13940,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>goodwill_approval_limits</v>
+        <v>bs_insurance_documents</v>
       </c>
       <c r="B167" t="str">
         <v>active</v>
@@ -13146,7 +13952,7 @@
         <v>select</v>
       </c>
       <c r="E167" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F167" t="str">
         <v>Y, N</v>
@@ -13187,13 +13993,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>spd_issuance_priority</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B168" t="str">
-        <v>priorityCode</v>
+        <v>stageCode</v>
       </c>
       <c r="C168" t="str">
-        <v>Priority Code</v>
+        <v>Stage Code</v>
       </c>
       <c r="D168" t="str">
         <v>text</v>
@@ -13240,22 +14046,22 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>spd_issuance_priority</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B169" t="str">
-        <v>priorityLevel</v>
+        <v>stageName</v>
       </c>
       <c r="C169" t="str">
-        <v>Priority Tag</v>
+        <v>Process Stage</v>
       </c>
       <c r="D169" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E169" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F169" t="str">
-        <v>Emergency VOR, Running Repair Express, Scheduled Periodic Maintenance, Recall Campaign</v>
+        <v/>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -13293,13 +14099,13 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>spd_issuance_priority</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B170" t="str">
-        <v>slaMins</v>
+        <v>standardDurationHrs</v>
       </c>
       <c r="C170" t="str">
-        <v>Picking SLA (Minutes)</v>
+        <v>Standard FRT (Hrs)</v>
       </c>
       <c r="D170" t="str">
         <v>number</v>
@@ -13346,13 +14152,13 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>spd_issuance_priority</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B171" t="str">
-        <v>requireOtp</v>
+        <v>requiresSurveyorApproval</v>
       </c>
       <c r="C171" t="str">
-        <v>Mechanic Fingerprint / OTP Verification</v>
+        <v>Surveyor Sign-off Gate</v>
       </c>
       <c r="D171" t="str">
         <v>select</v>
@@ -13399,7 +14205,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>spd_issuance_priority</v>
+        <v>bodyshop_process_stages</v>
       </c>
       <c r="B172" t="str">
         <v>active</v>
@@ -13452,13 +14258,13 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>parts_delay_reasons</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B173" t="str">
-        <v>delayCode</v>
+        <v>boothName</v>
       </c>
       <c r="C173" t="str">
-        <v>Delay Code</v>
+        <v>Spray Booth Identification</v>
       </c>
       <c r="D173" t="str">
         <v>text</v>
@@ -13505,22 +14311,22 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>parts_delay_reasons</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B174" t="str">
-        <v>reasonName</v>
+        <v>paintType</v>
       </c>
       <c r="C174" t="str">
-        <v>Non-Availability Root Cause</v>
+        <v>Paint Technology</v>
       </c>
       <c r="D174" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E174" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F174" t="str">
-        <v/>
+        <v>Waterborne Eco-Basecoat, Solvent-borne Clearcoat, Matte Finish Specialty</v>
       </c>
       <c r="G174" t="str">
         <v/>
@@ -13558,22 +14364,22 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>parts_delay_reasons</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B175" t="str">
-        <v>autoOrderSap</v>
+        <v>maxBakeTemp</v>
       </c>
       <c r="C175" t="str">
-        <v>Auto Trigger SAP Emergency Order</v>
+        <v>Baking Temperature (°C)</v>
       </c>
       <c r="D175" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E175" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F175" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -13611,22 +14417,22 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>parts_delay_reasons</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B176" t="str">
-        <v>smsCustomer</v>
+        <v>dailyCapacityPanels</v>
       </c>
       <c r="C176" t="str">
-        <v>Trigger Customer ETA SMS</v>
+        <v>Daily Panel Capacity</v>
       </c>
       <c r="D176" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E176" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F176" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -13664,7 +14470,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>parts_delay_reasons</v>
+        <v>paint_booth_schedule</v>
       </c>
       <c r="B177" t="str">
         <v>active</v>
@@ -13717,13 +14523,13 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>thd_escalation_categories</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B178" t="str">
-        <v>categoryCode</v>
+        <v>amcCode</v>
       </c>
       <c r="C178" t="str">
-        <v>Escalation Category</v>
+        <v>AMC Plan Code</v>
       </c>
       <c r="D178" t="str">
         <v>text</v>
@@ -13770,22 +14576,22 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>thd_escalation_categories</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B179" t="str">
-        <v>systemDomain</v>
+        <v>planName</v>
       </c>
       <c r="C179" t="str">
-        <v>Engineering System</v>
+        <v>AMC Plan Name</v>
       </c>
       <c r="D179" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E179" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F179" t="str">
-        <v>EV High Voltage Traction, DCA Dual Clutch Transmission, ADAS &amp; Radar Calibration, Braking &amp; ESP Hydraulics, CAN Bus Network Communication</v>
+        <v/>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -13823,13 +14629,13 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>thd_escalation_categories</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B180" t="str">
-        <v>severityTier</v>
+        <v>pplName</v>
       </c>
       <c r="C180" t="str">
-        <v>Plant Response SLA</v>
+        <v>Applicable PPL</v>
       </c>
       <c r="D180" t="str">
         <v>select</v>
@@ -13838,7 +14644,7 @@
         <v>N</v>
       </c>
       <c r="F180" t="str">
-        <v>Tier 1 Critical (&lt; 4 Hours), Tier 2 High (&lt; 12 Hours), Tier 3 Standard (&lt; 24 Hours)</v>
+        <v>All Models, Nexon, Altroz, Harrier / Safari, EV Fleet</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -13876,22 +14682,22 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>thd_escalation_categories</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B181" t="str">
-        <v>requiresPlantVisit</v>
+        <v>tenureYears</v>
       </c>
       <c r="C181" t="str">
-        <v>Plant Field Engineer Dispatch</v>
+        <v>Tenure (Yrs)</v>
       </c>
       <c r="D181" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E181" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F181" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -13929,22 +14735,22 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>thd_escalation_categories</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B182" t="str">
-        <v>active</v>
+        <v>maxKms</v>
       </c>
       <c r="C182" t="str">
-        <v>Active</v>
+        <v>Max Coverage (KMs)</v>
       </c>
       <c r="D182" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E182" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F182" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -13982,16 +14788,16 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B183" t="str">
-        <v>tibNumber</v>
+        <v>priceInr</v>
       </c>
       <c r="C183" t="str">
-        <v>TIB Bulletin Reference</v>
+        <v>Base OEM MRP (₹)</v>
       </c>
       <c r="D183" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E183" t="str">
         <v>Y</v>
@@ -14035,22 +14841,22 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>amc_pricing</v>
       </c>
       <c r="B184" t="str">
-        <v>title</v>
+        <v>active</v>
       </c>
       <c r="C184" t="str">
-        <v>Subject / Advisory Scope</v>
+        <v>Active</v>
       </c>
       <c r="D184" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E184" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F184" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -14088,22 +14894,22 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B185" t="str">
-        <v>affectedPpl</v>
+        <v>defectCode</v>
       </c>
       <c r="C185" t="str">
-        <v>Applicable Vehicle PPL</v>
+        <v>Defect Code</v>
       </c>
       <c r="D185" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E185" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F185" t="str">
-        <v>Nexon EV, Nexon ICE, Harrier / Safari, Curvv EV, Altroz</v>
+        <v/>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -14141,13 +14947,13 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B186" t="str">
-        <v>reworkType</v>
+        <v>defectCategory</v>
       </c>
       <c r="C186" t="str">
-        <v>Rework Classification</v>
+        <v>Defect Group</v>
       </c>
       <c r="D186" t="str">
         <v>select</v>
@@ -14156,7 +14962,7 @@
         <v>N</v>
       </c>
       <c r="F186" t="str">
-        <v>ECU Firmware Update, Harness Rerouting, Hardware Bush Replacement, Torque Audit</v>
+        <v>Manufacturing Quality, Material Defect, Vendor Assembly Flaw, Software / Firmware Logic, Corrosion / Paint Flaw</v>
       </c>
       <c r="G186" t="str">
         <v/>
@@ -14194,13 +15000,13 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B187" t="str">
-        <v>active</v>
+        <v>partCoverage</v>
       </c>
       <c r="C187" t="str">
-        <v>Active</v>
+        <v>Warranty Scheme</v>
       </c>
       <c r="D187" t="str">
         <v>select</v>
@@ -14209,7 +15015,7 @@
         <v>N</v>
       </c>
       <c r="F187" t="str">
-        <v>Y, N</v>
+        <v>Standard 3Yr / 100K Km, Extended Warranty (EW), EV HV Battery 8Yr / 160K Km</v>
       </c>
       <c r="G187" t="str">
         <v/>
@@ -14247,22 +15053,22 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>driver_transit_roster</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B188" t="str">
-        <v>driverCode</v>
+        <v>requiresSampleReturn</v>
       </c>
       <c r="C188" t="str">
-        <v>Driver Code</v>
+        <v>Return Physical Sample to Plant</v>
       </c>
       <c r="D188" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E188" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F188" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G188" t="str">
         <v/>
@@ -14300,22 +15106,22 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>driver_transit_roster</v>
+        <v>warranty_defect_codes</v>
       </c>
       <c r="B189" t="str">
-        <v>driverName</v>
+        <v>active</v>
       </c>
       <c r="C189" t="str">
-        <v>Driver Full Name</v>
+        <v>Active</v>
       </c>
       <c r="D189" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E189" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F189" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G189" t="str">
         <v/>
@@ -14353,13 +15159,13 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>driver_transit_roster</v>
+        <v>goodwill_approval_limits</v>
       </c>
       <c r="B190" t="str">
-        <v>assignedZone</v>
+        <v>authorityTier</v>
       </c>
       <c r="C190" t="str">
-        <v>Assigned Territory Zone</v>
+        <v>Approving Authority</v>
       </c>
       <c r="D190" t="str">
         <v>select</v>
@@ -14368,7 +15174,7 @@
         <v>N</v>
       </c>
       <c r="F190" t="str">
-        <v>Zone A - Hitec City, Zone B - Secunderabad, Zone C - Gachibowli, Zone D - Banjara Hills</v>
+        <v>Works Manager (WM), Area Service Manager (ASM - TML), Regional Customer Care Head (RCCH), DGM Service Central</v>
       </c>
       <c r="G190" t="str">
         <v/>
@@ -14406,16 +15212,16 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>driver_transit_roster</v>
+        <v>goodwill_approval_limits</v>
       </c>
       <c r="B191" t="str">
-        <v>licenseNumber</v>
+        <v>maxLaborConcession</v>
       </c>
       <c r="C191" t="str">
-        <v>Commercial DL Number</v>
+        <v>Max Labor Discount (%)</v>
       </c>
       <c r="D191" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E191" t="str">
         <v>Y</v>
@@ -14459,22 +15265,22 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>driver_transit_roster</v>
+        <v>goodwill_approval_limits</v>
       </c>
       <c r="B192" t="str">
-        <v>evCertified</v>
+        <v>maxPartsConcession</v>
       </c>
       <c r="C192" t="str">
-        <v>EV Transit Certified</v>
+        <v>Max Parts Discount (%)</v>
       </c>
       <c r="D192" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E192" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F192" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G192" t="str">
         <v/>
@@ -14512,22 +15318,22 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>driver_transit_roster</v>
+        <v>goodwill_approval_limits</v>
       </c>
       <c r="B193" t="str">
-        <v>active</v>
+        <v>maxAmountInr</v>
       </c>
       <c r="C193" t="str">
-        <v>Active</v>
+        <v>Max Claim Value (₹)</v>
       </c>
       <c r="D193" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E193" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F193" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G193" t="str">
         <v/>
@@ -14565,22 +15371,22 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>goodwill_approval_limits</v>
       </c>
       <c r="B194" t="str">
-        <v>checkpointCode</v>
+        <v>active</v>
       </c>
       <c r="C194" t="str">
-        <v>Checkpoint Code</v>
+        <v>Active</v>
       </c>
       <c r="D194" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E194" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F194" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G194" t="str">
         <v/>
@@ -14618,13 +15424,13 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>spd_issuance_priority</v>
       </c>
       <c r="B195" t="str">
-        <v>checkpointDesc</v>
+        <v>priorityCode</v>
       </c>
       <c r="C195" t="str">
-        <v>Reception Standard Requirement</v>
+        <v>Priority Code</v>
       </c>
       <c r="D195" t="str">
         <v>text</v>
@@ -14671,13 +15477,13 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>spd_issuance_priority</v>
       </c>
       <c r="B196" t="str">
-        <v>channel</v>
+        <v>priorityLevel</v>
       </c>
       <c r="C196" t="str">
-        <v>Intake Channel</v>
+        <v>Priority Tag</v>
       </c>
       <c r="D196" t="str">
         <v>select</v>
@@ -14686,7 +15492,7 @@
         <v>N</v>
       </c>
       <c r="F196" t="str">
-        <v>Walk-in, Pre-Booked Appointment, Express Valet, Breakdown Flatbed</v>
+        <v>Emergency VOR, Running Repair Express, Scheduled Periodic Maintenance, Recall Campaign</v>
       </c>
       <c r="G196" t="str">
         <v/>
@@ -14724,22 +15530,22 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>spd_issuance_priority</v>
       </c>
       <c r="B197" t="str">
-        <v>mandatoryProof</v>
+        <v>slaMins</v>
       </c>
       <c r="C197" t="str">
-        <v>Mandatory Photo / Signature</v>
+        <v>Picking SLA (Minutes)</v>
       </c>
       <c r="D197" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E197" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F197" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G197" t="str">
         <v/>
@@ -14777,13 +15583,13 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>spd_issuance_priority</v>
       </c>
       <c r="B198" t="str">
-        <v>active</v>
+        <v>requireOtp</v>
       </c>
       <c r="C198" t="str">
-        <v>Active</v>
+        <v>Mechanic Fingerprint / OTP Verification</v>
       </c>
       <c r="D198" t="str">
         <v>select</v>
@@ -14830,22 +15636,22 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>gate_security_checklist</v>
+        <v>spd_issuance_priority</v>
       </c>
       <c r="B199" t="str">
-        <v>ruleId</v>
+        <v>active</v>
       </c>
       <c r="C199" t="str">
-        <v>Gate Rule Code</v>
+        <v>Active</v>
       </c>
       <c r="D199" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E199" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F199" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G199" t="str">
         <v/>
@@ -14883,22 +15689,22 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>gate_security_checklist</v>
+        <v>parts_delay_reasons</v>
       </c>
       <c r="B200" t="str">
-        <v>direction</v>
+        <v>delayCode</v>
       </c>
       <c r="C200" t="str">
-        <v>Movement Direction</v>
+        <v>Delay Code</v>
       </c>
       <c r="D200" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E200" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F200" t="str">
-        <v>Inward (Check-in), Outward (Check-out), Internal Bay Transit</v>
+        <v/>
       </c>
       <c r="G200" t="str">
         <v/>
@@ -14936,13 +15742,13 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>gate_security_checklist</v>
+        <v>parts_delay_reasons</v>
       </c>
       <c r="B201" t="str">
-        <v>verificationItem</v>
+        <v>reasonName</v>
       </c>
       <c r="C201" t="str">
-        <v>Verification Protocol</v>
+        <v>Non-Availability Root Cause</v>
       </c>
       <c r="D201" t="str">
         <v>text</v>
@@ -14989,13 +15795,13 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>gate_security_checklist</v>
+        <v>parts_delay_reasons</v>
       </c>
       <c r="B202" t="str">
-        <v>anprSync</v>
+        <v>autoOrderSap</v>
       </c>
       <c r="C202" t="str">
-        <v>ANPR Camera Auto-Verify</v>
+        <v>Auto Trigger SAP Emergency Order</v>
       </c>
       <c r="D202" t="str">
         <v>select</v>
@@ -15042,13 +15848,13 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>gate_security_checklist</v>
+        <v>parts_delay_reasons</v>
       </c>
       <c r="B203" t="str">
-        <v>active</v>
+        <v>smsCustomer</v>
       </c>
       <c r="C203" t="str">
-        <v>Active</v>
+        <v>Trigger Customer ETA SMS</v>
       </c>
       <c r="D203" t="str">
         <v>select</v>
@@ -15095,22 +15901,22 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>gate_denial_reasons</v>
+        <v>parts_delay_reasons</v>
       </c>
       <c r="B204" t="str">
-        <v>denialCode</v>
+        <v>active</v>
       </c>
       <c r="C204" t="str">
-        <v>Denial Code</v>
+        <v>Active</v>
       </c>
       <c r="D204" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E204" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F204" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G204" t="str">
         <v/>
@@ -15148,13 +15954,13 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>gate_denial_reasons</v>
+        <v>thd_escalation_categories</v>
       </c>
       <c r="B205" t="str">
-        <v>reason</v>
+        <v>categoryCode</v>
       </c>
       <c r="C205" t="str">
-        <v>Security Denial / Hold Reason</v>
+        <v>Escalation Category</v>
       </c>
       <c r="D205" t="str">
         <v>text</v>
@@ -15201,13 +16007,13 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>gate_denial_reasons</v>
+        <v>thd_escalation_categories</v>
       </c>
       <c r="B206" t="str">
-        <v>escalateTo</v>
+        <v>systemDomain</v>
       </c>
       <c r="C206" t="str">
-        <v>Immediate Notification Target</v>
+        <v>Engineering System</v>
       </c>
       <c r="D206" t="str">
         <v>select</v>
@@ -15216,7 +16022,7 @@
         <v>N</v>
       </c>
       <c r="F206" t="str">
-        <v>Works Manager, Security Officer In-Charge, Service Head, Customer Relation Manager</v>
+        <v>EV High Voltage Traction, DCA Dual Clutch Transmission, ADAS &amp; Radar Calibration, Braking &amp; ESP Hydraulics, CAN Bus Network Communication</v>
       </c>
       <c r="G206" t="str">
         <v/>
@@ -15254,13 +16060,13 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>gate_denial_reasons</v>
+        <v>thd_escalation_categories</v>
       </c>
       <c r="B207" t="str">
-        <v>active</v>
+        <v>severityTier</v>
       </c>
       <c r="C207" t="str">
-        <v>Active</v>
+        <v>Plant Response SLA</v>
       </c>
       <c r="D207" t="str">
         <v>select</v>
@@ -15269,45 +16075,1476 @@
         <v>N</v>
       </c>
       <c r="F207" t="str">
+        <v>Tier 1 Critical (&lt; 4 Hours), Tier 2 High (&lt; 12 Hours), Tier 3 Standard (&lt; 24 Hours)</v>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v/>
+      </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
+      <c r="J207" t="str">
+        <v/>
+      </c>
+      <c r="K207" t="str">
+        <v/>
+      </c>
+      <c r="L207" t="str">
+        <v/>
+      </c>
+      <c r="M207" t="str">
+        <v>N</v>
+      </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>thd_escalation_categories</v>
+      </c>
+      <c r="B208" t="str">
+        <v>requiresPlantVisit</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Plant Field Engineer Dispatch</v>
+      </c>
+      <c r="D208" t="str">
+        <v>select</v>
+      </c>
+      <c r="E208" t="str">
+        <v>N</v>
+      </c>
+      <c r="F208" t="str">
         <v>Y, N</v>
       </c>
-      <c r="G207" t="str">
-        <v/>
-      </c>
-      <c r="H207" t="str">
-        <v/>
-      </c>
-      <c r="I207" t="str">
-        <v/>
-      </c>
-      <c r="J207" t="str">
-        <v/>
-      </c>
-      <c r="K207" t="str">
-        <v/>
-      </c>
-      <c r="L207" t="str">
-        <v/>
-      </c>
-      <c r="M207" t="str">
-        <v>N</v>
-      </c>
-      <c r="N207" t="str">
-        <v/>
-      </c>
-      <c r="O207" t="str">
-        <v/>
-      </c>
-      <c r="P207" t="str">
-        <v/>
-      </c>
-      <c r="Q207" t="str">
+      <c r="G208" t="str">
+        <v/>
+      </c>
+      <c r="H208" t="str">
+        <v/>
+      </c>
+      <c r="I208" t="str">
+        <v/>
+      </c>
+      <c r="J208" t="str">
+        <v/>
+      </c>
+      <c r="K208" t="str">
+        <v/>
+      </c>
+      <c r="L208" t="str">
+        <v/>
+      </c>
+      <c r="M208" t="str">
+        <v>N</v>
+      </c>
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
+        <v/>
+      </c>
+      <c r="P208" t="str">
+        <v/>
+      </c>
+      <c r="Q208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>thd_escalation_categories</v>
+      </c>
+      <c r="B209" t="str">
+        <v>active</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D209" t="str">
+        <v>select</v>
+      </c>
+      <c r="E209" t="str">
+        <v>N</v>
+      </c>
+      <c r="F209" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v/>
+      </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
+      <c r="J209" t="str">
+        <v/>
+      </c>
+      <c r="K209" t="str">
+        <v/>
+      </c>
+      <c r="L209" t="str">
+        <v/>
+      </c>
+      <c r="M209" t="str">
+        <v>N</v>
+      </c>
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" t="str">
+        <v/>
+      </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B210" t="str">
+        <v>tibNumber</v>
+      </c>
+      <c r="C210" t="str">
+        <v>TIB Bulletin Reference</v>
+      </c>
+      <c r="D210" t="str">
+        <v>text</v>
+      </c>
+      <c r="E210" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v/>
+      </c>
+      <c r="I210" t="str">
+        <v/>
+      </c>
+      <c r="J210" t="str">
+        <v/>
+      </c>
+      <c r="K210" t="str">
+        <v/>
+      </c>
+      <c r="L210" t="str">
+        <v/>
+      </c>
+      <c r="M210" t="str">
+        <v>N</v>
+      </c>
+      <c r="N210" t="str">
+        <v/>
+      </c>
+      <c r="O210" t="str">
+        <v/>
+      </c>
+      <c r="P210" t="str">
+        <v/>
+      </c>
+      <c r="Q210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B211" t="str">
+        <v>title</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Subject / Advisory Scope</v>
+      </c>
+      <c r="D211" t="str">
+        <v>text</v>
+      </c>
+      <c r="E211" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211" t="str">
+        <v/>
+      </c>
+      <c r="K211" t="str">
+        <v/>
+      </c>
+      <c r="L211" t="str">
+        <v/>
+      </c>
+      <c r="M211" t="str">
+        <v>N</v>
+      </c>
+      <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v/>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B212" t="str">
+        <v>affectedPpl</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Applicable Vehicle PPL</v>
+      </c>
+      <c r="D212" t="str">
+        <v>select</v>
+      </c>
+      <c r="E212" t="str">
+        <v>N</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Nexon EV, Nexon ICE, Harrier / Safari, Curvv EV, Altroz</v>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
+      <c r="J212" t="str">
+        <v/>
+      </c>
+      <c r="K212" t="str">
+        <v/>
+      </c>
+      <c r="L212" t="str">
+        <v/>
+      </c>
+      <c r="M212" t="str">
+        <v>N</v>
+      </c>
+      <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
+        <v/>
+      </c>
+      <c r="P212" t="str">
+        <v/>
+      </c>
+      <c r="Q212" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B213" t="str">
+        <v>reworkType</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Rework Classification</v>
+      </c>
+      <c r="D213" t="str">
+        <v>select</v>
+      </c>
+      <c r="E213" t="str">
+        <v>N</v>
+      </c>
+      <c r="F213" t="str">
+        <v>ECU Firmware Update, Harness Rerouting, Hardware Bush Replacement, Torque Audit</v>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+      <c r="I213" t="str">
+        <v/>
+      </c>
+      <c r="J213" t="str">
+        <v/>
+      </c>
+      <c r="K213" t="str">
+        <v/>
+      </c>
+      <c r="L213" t="str">
+        <v/>
+      </c>
+      <c r="M213" t="str">
+        <v>N</v>
+      </c>
+      <c r="N213" t="str">
+        <v/>
+      </c>
+      <c r="O213" t="str">
+        <v/>
+      </c>
+      <c r="P213" t="str">
+        <v/>
+      </c>
+      <c r="Q213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>tib_bulletin_codes</v>
+      </c>
+      <c r="B214" t="str">
+        <v>active</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D214" t="str">
+        <v>select</v>
+      </c>
+      <c r="E214" t="str">
+        <v>N</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+      <c r="I214" t="str">
+        <v/>
+      </c>
+      <c r="J214" t="str">
+        <v/>
+      </c>
+      <c r="K214" t="str">
+        <v/>
+      </c>
+      <c r="L214" t="str">
+        <v/>
+      </c>
+      <c r="M214" t="str">
+        <v>N</v>
+      </c>
+      <c r="N214" t="str">
+        <v/>
+      </c>
+      <c r="O214" t="str">
+        <v/>
+      </c>
+      <c r="P214" t="str">
+        <v/>
+      </c>
+      <c r="Q214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B215" t="str">
+        <v>driverCode</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Driver Code</v>
+      </c>
+      <c r="D215" t="str">
+        <v>text</v>
+      </c>
+      <c r="E215" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" t="str">
+        <v/>
+      </c>
+      <c r="H215" t="str">
+        <v/>
+      </c>
+      <c r="I215" t="str">
+        <v/>
+      </c>
+      <c r="J215" t="str">
+        <v/>
+      </c>
+      <c r="K215" t="str">
+        <v/>
+      </c>
+      <c r="L215" t="str">
+        <v/>
+      </c>
+      <c r="M215" t="str">
+        <v>N</v>
+      </c>
+      <c r="N215" t="str">
+        <v/>
+      </c>
+      <c r="O215" t="str">
+        <v/>
+      </c>
+      <c r="P215" t="str">
+        <v/>
+      </c>
+      <c r="Q215" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B216" t="str">
+        <v>driverName</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Driver Full Name</v>
+      </c>
+      <c r="D216" t="str">
+        <v>text</v>
+      </c>
+      <c r="E216" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+      <c r="H216" t="str">
+        <v/>
+      </c>
+      <c r="I216" t="str">
+        <v/>
+      </c>
+      <c r="J216" t="str">
+        <v/>
+      </c>
+      <c r="K216" t="str">
+        <v/>
+      </c>
+      <c r="L216" t="str">
+        <v/>
+      </c>
+      <c r="M216" t="str">
+        <v>N</v>
+      </c>
+      <c r="N216" t="str">
+        <v/>
+      </c>
+      <c r="O216" t="str">
+        <v/>
+      </c>
+      <c r="P216" t="str">
+        <v/>
+      </c>
+      <c r="Q216" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B217" t="str">
+        <v>assignedZone</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Assigned Territory Zone</v>
+      </c>
+      <c r="D217" t="str">
+        <v>select</v>
+      </c>
+      <c r="E217" t="str">
+        <v>N</v>
+      </c>
+      <c r="F217" t="str">
+        <v>Zone A - Hitec City, Zone B - Secunderabad, Zone C - Gachibowli, Zone D - Banjara Hills</v>
+      </c>
+      <c r="G217" t="str">
+        <v/>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
+      <c r="J217" t="str">
+        <v/>
+      </c>
+      <c r="K217" t="str">
+        <v/>
+      </c>
+      <c r="L217" t="str">
+        <v/>
+      </c>
+      <c r="M217" t="str">
+        <v>N</v>
+      </c>
+      <c r="N217" t="str">
+        <v/>
+      </c>
+      <c r="O217" t="str">
+        <v/>
+      </c>
+      <c r="P217" t="str">
+        <v/>
+      </c>
+      <c r="Q217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B218" t="str">
+        <v>licenseNumber</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Commercial DL Number</v>
+      </c>
+      <c r="D218" t="str">
+        <v>text</v>
+      </c>
+      <c r="E218" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+      <c r="H218" t="str">
+        <v/>
+      </c>
+      <c r="I218" t="str">
+        <v/>
+      </c>
+      <c r="J218" t="str">
+        <v/>
+      </c>
+      <c r="K218" t="str">
+        <v/>
+      </c>
+      <c r="L218" t="str">
+        <v/>
+      </c>
+      <c r="M218" t="str">
+        <v>N</v>
+      </c>
+      <c r="N218" t="str">
+        <v/>
+      </c>
+      <c r="O218" t="str">
+        <v/>
+      </c>
+      <c r="P218" t="str">
+        <v/>
+      </c>
+      <c r="Q218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B219" t="str">
+        <v>evCertified</v>
+      </c>
+      <c r="C219" t="str">
+        <v>EV Transit Certified</v>
+      </c>
+      <c r="D219" t="str">
+        <v>select</v>
+      </c>
+      <c r="E219" t="str">
+        <v>N</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G219" t="str">
+        <v/>
+      </c>
+      <c r="H219" t="str">
+        <v/>
+      </c>
+      <c r="I219" t="str">
+        <v/>
+      </c>
+      <c r="J219" t="str">
+        <v/>
+      </c>
+      <c r="K219" t="str">
+        <v/>
+      </c>
+      <c r="L219" t="str">
+        <v/>
+      </c>
+      <c r="M219" t="str">
+        <v>N</v>
+      </c>
+      <c r="N219" t="str">
+        <v/>
+      </c>
+      <c r="O219" t="str">
+        <v/>
+      </c>
+      <c r="P219" t="str">
+        <v/>
+      </c>
+      <c r="Q219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B220" t="str">
+        <v>active</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D220" t="str">
+        <v>select</v>
+      </c>
+      <c r="E220" t="str">
+        <v>N</v>
+      </c>
+      <c r="F220" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G220" t="str">
+        <v/>
+      </c>
+      <c r="H220" t="str">
+        <v/>
+      </c>
+      <c r="I220" t="str">
+        <v/>
+      </c>
+      <c r="J220" t="str">
+        <v/>
+      </c>
+      <c r="K220" t="str">
+        <v/>
+      </c>
+      <c r="L220" t="str">
+        <v/>
+      </c>
+      <c r="M220" t="str">
+        <v>N</v>
+      </c>
+      <c r="N220" t="str">
+        <v/>
+      </c>
+      <c r="O220" t="str">
+        <v/>
+      </c>
+      <c r="P220" t="str">
+        <v/>
+      </c>
+      <c r="Q220" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B221" t="str">
+        <v>checkpointCode</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Checkpoint Code</v>
+      </c>
+      <c r="D221" t="str">
+        <v>text</v>
+      </c>
+      <c r="E221" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+      <c r="H221" t="str">
+        <v/>
+      </c>
+      <c r="I221" t="str">
+        <v/>
+      </c>
+      <c r="J221" t="str">
+        <v/>
+      </c>
+      <c r="K221" t="str">
+        <v/>
+      </c>
+      <c r="L221" t="str">
+        <v/>
+      </c>
+      <c r="M221" t="str">
+        <v>N</v>
+      </c>
+      <c r="N221" t="str">
+        <v/>
+      </c>
+      <c r="O221" t="str">
+        <v/>
+      </c>
+      <c r="P221" t="str">
+        <v/>
+      </c>
+      <c r="Q221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B222" t="str">
+        <v>checkpointDesc</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Reception Standard Requirement</v>
+      </c>
+      <c r="D222" t="str">
+        <v>text</v>
+      </c>
+      <c r="E222" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F222" t="str">
+        <v/>
+      </c>
+      <c r="G222" t="str">
+        <v/>
+      </c>
+      <c r="H222" t="str">
+        <v/>
+      </c>
+      <c r="I222" t="str">
+        <v/>
+      </c>
+      <c r="J222" t="str">
+        <v/>
+      </c>
+      <c r="K222" t="str">
+        <v/>
+      </c>
+      <c r="L222" t="str">
+        <v/>
+      </c>
+      <c r="M222" t="str">
+        <v>N</v>
+      </c>
+      <c r="N222" t="str">
+        <v/>
+      </c>
+      <c r="O222" t="str">
+        <v/>
+      </c>
+      <c r="P222" t="str">
+        <v/>
+      </c>
+      <c r="Q222" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B223" t="str">
+        <v>channel</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Intake Channel</v>
+      </c>
+      <c r="D223" t="str">
+        <v>select</v>
+      </c>
+      <c r="E223" t="str">
+        <v>N</v>
+      </c>
+      <c r="F223" t="str">
+        <v>Walk-in, Pre-Booked Appointment, Express Valet, Breakdown Flatbed</v>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+      <c r="H223" t="str">
+        <v/>
+      </c>
+      <c r="I223" t="str">
+        <v/>
+      </c>
+      <c r="J223" t="str">
+        <v/>
+      </c>
+      <c r="K223" t="str">
+        <v/>
+      </c>
+      <c r="L223" t="str">
+        <v/>
+      </c>
+      <c r="M223" t="str">
+        <v>N</v>
+      </c>
+      <c r="N223" t="str">
+        <v/>
+      </c>
+      <c r="O223" t="str">
+        <v/>
+      </c>
+      <c r="P223" t="str">
+        <v/>
+      </c>
+      <c r="Q223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B224" t="str">
+        <v>mandatoryProof</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Mandatory Photo / Signature</v>
+      </c>
+      <c r="D224" t="str">
+        <v>select</v>
+      </c>
+      <c r="E224" t="str">
+        <v>N</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G224" t="str">
+        <v/>
+      </c>
+      <c r="H224" t="str">
+        <v/>
+      </c>
+      <c r="I224" t="str">
+        <v/>
+      </c>
+      <c r="J224" t="str">
+        <v/>
+      </c>
+      <c r="K224" t="str">
+        <v/>
+      </c>
+      <c r="L224" t="str">
+        <v/>
+      </c>
+      <c r="M224" t="str">
+        <v>N</v>
+      </c>
+      <c r="N224" t="str">
+        <v/>
+      </c>
+      <c r="O224" t="str">
+        <v/>
+      </c>
+      <c r="P224" t="str">
+        <v/>
+      </c>
+      <c r="Q224" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B225" t="str">
+        <v>active</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D225" t="str">
+        <v>select</v>
+      </c>
+      <c r="E225" t="str">
+        <v>N</v>
+      </c>
+      <c r="F225" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G225" t="str">
+        <v/>
+      </c>
+      <c r="H225" t="str">
+        <v/>
+      </c>
+      <c r="I225" t="str">
+        <v/>
+      </c>
+      <c r="J225" t="str">
+        <v/>
+      </c>
+      <c r="K225" t="str">
+        <v/>
+      </c>
+      <c r="L225" t="str">
+        <v/>
+      </c>
+      <c r="M225" t="str">
+        <v>N</v>
+      </c>
+      <c r="N225" t="str">
+        <v/>
+      </c>
+      <c r="O225" t="str">
+        <v/>
+      </c>
+      <c r="P225" t="str">
+        <v/>
+      </c>
+      <c r="Q225" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B226" t="str">
+        <v>ruleId</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Gate Rule Code</v>
+      </c>
+      <c r="D226" t="str">
+        <v>text</v>
+      </c>
+      <c r="E226" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v/>
+      </c>
+      <c r="H226" t="str">
+        <v/>
+      </c>
+      <c r="I226" t="str">
+        <v/>
+      </c>
+      <c r="J226" t="str">
+        <v/>
+      </c>
+      <c r="K226" t="str">
+        <v/>
+      </c>
+      <c r="L226" t="str">
+        <v/>
+      </c>
+      <c r="M226" t="str">
+        <v>N</v>
+      </c>
+      <c r="N226" t="str">
+        <v/>
+      </c>
+      <c r="O226" t="str">
+        <v/>
+      </c>
+      <c r="P226" t="str">
+        <v/>
+      </c>
+      <c r="Q226" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B227" t="str">
+        <v>direction</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Movement Direction</v>
+      </c>
+      <c r="D227" t="str">
+        <v>select</v>
+      </c>
+      <c r="E227" t="str">
+        <v>N</v>
+      </c>
+      <c r="F227" t="str">
+        <v>Inward (Check-in), Outward (Check-out), Internal Bay Transit</v>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+      <c r="H227" t="str">
+        <v/>
+      </c>
+      <c r="I227" t="str">
+        <v/>
+      </c>
+      <c r="J227" t="str">
+        <v/>
+      </c>
+      <c r="K227" t="str">
+        <v/>
+      </c>
+      <c r="L227" t="str">
+        <v/>
+      </c>
+      <c r="M227" t="str">
+        <v>N</v>
+      </c>
+      <c r="N227" t="str">
+        <v/>
+      </c>
+      <c r="O227" t="str">
+        <v/>
+      </c>
+      <c r="P227" t="str">
+        <v/>
+      </c>
+      <c r="Q227" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B228" t="str">
+        <v>verificationItem</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Verification Protocol</v>
+      </c>
+      <c r="D228" t="str">
+        <v>text</v>
+      </c>
+      <c r="E228" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+      <c r="H228" t="str">
+        <v/>
+      </c>
+      <c r="I228" t="str">
+        <v/>
+      </c>
+      <c r="J228" t="str">
+        <v/>
+      </c>
+      <c r="K228" t="str">
+        <v/>
+      </c>
+      <c r="L228" t="str">
+        <v/>
+      </c>
+      <c r="M228" t="str">
+        <v>N</v>
+      </c>
+      <c r="N228" t="str">
+        <v/>
+      </c>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+      <c r="P228" t="str">
+        <v/>
+      </c>
+      <c r="Q228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B229" t="str">
+        <v>anprSync</v>
+      </c>
+      <c r="C229" t="str">
+        <v>ANPR Camera Auto-Verify</v>
+      </c>
+      <c r="D229" t="str">
+        <v>select</v>
+      </c>
+      <c r="E229" t="str">
+        <v>N</v>
+      </c>
+      <c r="F229" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+      <c r="H229" t="str">
+        <v/>
+      </c>
+      <c r="I229" t="str">
+        <v/>
+      </c>
+      <c r="J229" t="str">
+        <v/>
+      </c>
+      <c r="K229" t="str">
+        <v/>
+      </c>
+      <c r="L229" t="str">
+        <v/>
+      </c>
+      <c r="M229" t="str">
+        <v>N</v>
+      </c>
+      <c r="N229" t="str">
+        <v/>
+      </c>
+      <c r="O229" t="str">
+        <v/>
+      </c>
+      <c r="P229" t="str">
+        <v/>
+      </c>
+      <c r="Q229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B230" t="str">
+        <v>active</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D230" t="str">
+        <v>select</v>
+      </c>
+      <c r="E230" t="str">
+        <v>N</v>
+      </c>
+      <c r="F230" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+      <c r="H230" t="str">
+        <v/>
+      </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
+      <c r="J230" t="str">
+        <v/>
+      </c>
+      <c r="K230" t="str">
+        <v/>
+      </c>
+      <c r="L230" t="str">
+        <v/>
+      </c>
+      <c r="M230" t="str">
+        <v>N</v>
+      </c>
+      <c r="N230" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+      <c r="P230" t="str">
+        <v/>
+      </c>
+      <c r="Q230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B231" t="str">
+        <v>denialCode</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Denial Code</v>
+      </c>
+      <c r="D231" t="str">
+        <v>text</v>
+      </c>
+      <c r="E231" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+      <c r="H231" t="str">
+        <v/>
+      </c>
+      <c r="I231" t="str">
+        <v/>
+      </c>
+      <c r="J231" t="str">
+        <v/>
+      </c>
+      <c r="K231" t="str">
+        <v/>
+      </c>
+      <c r="L231" t="str">
+        <v/>
+      </c>
+      <c r="M231" t="str">
+        <v>N</v>
+      </c>
+      <c r="N231" t="str">
+        <v/>
+      </c>
+      <c r="O231" t="str">
+        <v/>
+      </c>
+      <c r="P231" t="str">
+        <v/>
+      </c>
+      <c r="Q231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B232" t="str">
+        <v>reason</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Security Denial / Hold Reason</v>
+      </c>
+      <c r="D232" t="str">
+        <v>text</v>
+      </c>
+      <c r="E232" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+      <c r="H232" t="str">
+        <v/>
+      </c>
+      <c r="I232" t="str">
+        <v/>
+      </c>
+      <c r="J232" t="str">
+        <v/>
+      </c>
+      <c r="K232" t="str">
+        <v/>
+      </c>
+      <c r="L232" t="str">
+        <v/>
+      </c>
+      <c r="M232" t="str">
+        <v>N</v>
+      </c>
+      <c r="N232" t="str">
+        <v/>
+      </c>
+      <c r="O232" t="str">
+        <v/>
+      </c>
+      <c r="P232" t="str">
+        <v/>
+      </c>
+      <c r="Q232" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B233" t="str">
+        <v>escalateTo</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Immediate Notification Target</v>
+      </c>
+      <c r="D233" t="str">
+        <v>select</v>
+      </c>
+      <c r="E233" t="str">
+        <v>N</v>
+      </c>
+      <c r="F233" t="str">
+        <v>Works Manager, Security Officer In-Charge, Service Head, Customer Relation Manager</v>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+      <c r="H233" t="str">
+        <v/>
+      </c>
+      <c r="I233" t="str">
+        <v/>
+      </c>
+      <c r="J233" t="str">
+        <v/>
+      </c>
+      <c r="K233" t="str">
+        <v/>
+      </c>
+      <c r="L233" t="str">
+        <v/>
+      </c>
+      <c r="M233" t="str">
+        <v>N</v>
+      </c>
+      <c r="N233" t="str">
+        <v/>
+      </c>
+      <c r="O233" t="str">
+        <v/>
+      </c>
+      <c r="P233" t="str">
+        <v/>
+      </c>
+      <c r="Q233" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B234" t="str">
+        <v>active</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D234" t="str">
+        <v>select</v>
+      </c>
+      <c r="E234" t="str">
+        <v>N</v>
+      </c>
+      <c r="F234" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <v/>
+      </c>
+      <c r="J234" t="str">
+        <v/>
+      </c>
+      <c r="K234" t="str">
+        <v/>
+      </c>
+      <c r="L234" t="str">
+        <v/>
+      </c>
+      <c r="M234" t="str">
+        <v>N</v>
+      </c>
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+      <c r="P234" t="str">
+        <v/>
+      </c>
+      <c r="Q234" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q234"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15321,16 +17558,16 @@
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>delayCode</v>
+        <v>defectCode</v>
       </c>
       <c r="C1" t="str">
-        <v>reasonName</v>
+        <v>defectCategory</v>
       </c>
       <c r="D1" t="str">
-        <v>autoOrderSap</v>
+        <v>partCoverage</v>
       </c>
       <c r="E1" t="str">
-        <v>smsCustomer</v>
+        <v>requiresSampleReturn</v>
       </c>
       <c r="F1" t="str">
         <v>active</v>
@@ -15338,16 +17575,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PDR-01</v>
+        <v>WDC-01</v>
       </c>
       <c r="B2" t="str">
-        <v>BO-PLANT-TRANSIT</v>
+        <v>DEF-MFG-OILSEAL</v>
       </c>
       <c r="C2" t="str">
-        <v>Depot stock depleted - Plant in-transit shipment</v>
+        <v>Manufacturing Quality</v>
       </c>
       <c r="D2" t="str">
-        <v>Y</v>
+        <v>Standard 3Yr / 100K Km</v>
       </c>
       <c r="E2" t="str">
         <v>Y</v>
@@ -15358,19 +17595,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PDR-02</v>
+        <v>WDC-02</v>
       </c>
       <c r="B3" t="str">
-        <v>BO-BIN-MISMATCH</v>
+        <v>DEF-VEND-SUSPBUSH</v>
       </c>
       <c r="C3" t="str">
-        <v>Physical bin inventory variance (Inventory Audit flag)</v>
+        <v>Vendor Assembly Flaw</v>
       </c>
       <c r="D3" t="str">
-        <v>N</v>
+        <v>Standard 3Yr / 100K Km</v>
       </c>
       <c r="E3" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F3" t="str">
         <v>Y</v>
@@ -15378,16 +17615,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PDR-03</v>
+        <v>WDC-03</v>
       </c>
       <c r="B4" t="str">
-        <v>BO-SUPPLIER-SHORT</v>
+        <v>DEF-EV-CELLIMB</v>
       </c>
       <c r="C4" t="str">
-        <v>Tier-1 vendor supply constraint (Critical semiconductor/ECU)</v>
+        <v>Material Defect</v>
       </c>
       <c r="D4" t="str">
-        <v>Y</v>
+        <v>EV HV Battery 8Yr / 160K Km</v>
       </c>
       <c r="E4" t="str">
         <v>Y</v>
@@ -15412,16 +17649,16 @@
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>categoryCode</v>
+        <v>authorityTier</v>
       </c>
       <c r="C1" t="str">
-        <v>systemDomain</v>
+        <v>maxLaborConcession</v>
       </c>
       <c r="D1" t="str">
-        <v>severityTier</v>
+        <v>maxPartsConcession</v>
       </c>
       <c r="E1" t="str">
-        <v>requiresPlantVisit</v>
+        <v>maxAmountInr</v>
       </c>
       <c r="F1" t="str">
         <v>active</v>
@@ -15429,19 +17666,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>THD-01</v>
+        <v>GW-01</v>
       </c>
       <c r="B2" t="str">
-        <v>THD-EV-BAT-ISO</v>
-      </c>
-      <c r="C2" t="str">
-        <v>EV High Voltage Traction</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Tier 1 Critical (&lt; 4 Hours)</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
+        <v>Works Manager (WM)</v>
+      </c>
+      <c r="C2">
+        <v>25</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>5000</v>
       </c>
       <c r="F2" t="str">
         <v>Y</v>
@@ -15449,19 +17686,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>THD-02</v>
+        <v>GW-02</v>
       </c>
       <c r="B3" t="str">
-        <v>THD-DCA-JERK</v>
-      </c>
-      <c r="C3" t="str">
-        <v>DCA Dual Clutch Transmission</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Tier 2 High (&lt; 12 Hours)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>N</v>
+        <v>Area Service Manager (ASM - TML)</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>35</v>
+      </c>
+      <c r="E3">
+        <v>25000</v>
       </c>
       <c r="F3" t="str">
         <v>Y</v>
@@ -15469,19 +17706,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>THD-03</v>
+        <v>GW-03</v>
       </c>
       <c r="B4" t="str">
-        <v>THD-ADAS-MISALIGN</v>
-      </c>
-      <c r="C4" t="str">
-        <v>ADAS &amp; Radar Calibration</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Tier 2 High (&lt; 12 Hours)</v>
-      </c>
-      <c r="E4" t="str">
-        <v>N</v>
+        <v>Regional Customer Care Head (RCCH)</v>
+      </c>
+      <c r="C4">
+        <v>75</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="E4">
+        <v>75000</v>
       </c>
       <c r="F4" t="str">
         <v>Y</v>
@@ -15489,19 +17726,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>THD-04</v>
+        <v>GW-04</v>
       </c>
       <c r="B5" t="str">
-        <v>THD-CAN-ERR</v>
-      </c>
-      <c r="C5" t="str">
-        <v>CAN Bus Network Communication</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Tier 3 Standard (&lt; 24 Hours)</v>
-      </c>
-      <c r="E5" t="str">
-        <v>N</v>
+        <v>DGM Service Central</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>300000</v>
       </c>
       <c r="F5" t="str">
         <v>Y</v>
@@ -15516,6 +17753,117 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>priorityCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>priorityLevel</v>
+      </c>
+      <c r="D1" t="str">
+        <v>slaMins</v>
+      </c>
+      <c r="E1" t="str">
+        <v>requireOtp</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SPD-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PRIO-VOR-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Emergency VOR</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SPD-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>PRIO-RUN-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Running Repair Express</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3" t="str">
+        <v>N</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SPD-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>PRIO-SCH-03</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Scheduled Periodic Maintenance</v>
+      </c>
+      <c r="D4">
+        <v>45</v>
+      </c>
+      <c r="E4" t="str">
+        <v>N</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SPD-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>PRIO-REC-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Recall Campaign</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
@@ -15523,16 +17871,16 @@
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>tibNumber</v>
+        <v>delayCode</v>
       </c>
       <c r="C1" t="str">
-        <v>title</v>
+        <v>reasonName</v>
       </c>
       <c r="D1" t="str">
-        <v>affectedPpl</v>
+        <v>autoOrderSap</v>
       </c>
       <c r="E1" t="str">
-        <v>reworkType</v>
+        <v>smsCustomer</v>
       </c>
       <c r="F1" t="str">
         <v>active</v>
@@ -15540,19 +17888,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TIB-01</v>
+        <v>PDR-01</v>
       </c>
       <c r="B2" t="str">
-        <v>TIB-2026-PV-089</v>
+        <v>BO-PLANT-TRANSIT</v>
       </c>
       <c r="C2" t="str">
-        <v>BMS High-Voltage Contactor Firmware v4.8 Update</v>
+        <v>Depot stock depleted - Plant in-transit shipment</v>
       </c>
       <c r="D2" t="str">
-        <v>Nexon EV</v>
+        <v>Y</v>
       </c>
       <c r="E2" t="str">
-        <v>ECU Firmware Update</v>
+        <v>Y</v>
       </c>
       <c r="F2" t="str">
         <v>Y</v>
@@ -15560,19 +17908,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TIB-02</v>
+        <v>PDR-02</v>
       </c>
       <c r="B3" t="str">
-        <v>TIB-2026-PV-112</v>
+        <v>BO-BIN-MISMATCH</v>
       </c>
       <c r="C3" t="str">
-        <v>Rear Suspension Spring Seat Damping Pad Retrofit</v>
+        <v>Physical bin inventory variance (Inventory Audit flag)</v>
       </c>
       <c r="D3" t="str">
-        <v>Harrier / Safari</v>
+        <v>N</v>
       </c>
       <c r="E3" t="str">
-        <v>Hardware Bush Replacement</v>
+        <v>N</v>
       </c>
       <c r="F3" t="str">
         <v>Y</v>
@@ -15580,19 +17928,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TIB-03</v>
+        <v>PDR-03</v>
       </c>
       <c r="B4" t="str">
-        <v>TIB-2026-PV-134</v>
+        <v>BO-SUPPLIER-SHORT</v>
       </c>
       <c r="C4" t="str">
-        <v>Steering Column Earth Strap Resistance Check</v>
+        <v>Tier-1 vendor supply constraint (Critical semiconductor/ECU)</v>
       </c>
       <c r="D4" t="str">
-        <v>Altroz</v>
+        <v>Y</v>
       </c>
       <c r="E4" t="str">
-        <v>Torque Audit</v>
+        <v>Y</v>
       </c>
       <c r="F4" t="str">
         <v>Y</v>
@@ -15605,7 +17953,209 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>categoryCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>systemDomain</v>
+      </c>
+      <c r="D1" t="str">
+        <v>severityTier</v>
+      </c>
+      <c r="E1" t="str">
+        <v>requiresPlantVisit</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>THD-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>THD-EV-BAT-ISO</v>
+      </c>
+      <c r="C2" t="str">
+        <v>EV High Voltage Traction</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Tier 1 Critical (&lt; 4 Hours)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>THD-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>THD-DCA-JERK</v>
+      </c>
+      <c r="C3" t="str">
+        <v>DCA Dual Clutch Transmission</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Tier 2 High (&lt; 12 Hours)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>N</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>THD-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>THD-ADAS-MISALIGN</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ADAS &amp; Radar Calibration</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Tier 2 High (&lt; 12 Hours)</v>
+      </c>
+      <c r="E4" t="str">
+        <v>N</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>THD-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>THD-CAN-ERR</v>
+      </c>
+      <c r="C5" t="str">
+        <v>CAN Bus Network Communication</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Tier 3 Standard (&lt; 24 Hours)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>N</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>tibNumber</v>
+      </c>
+      <c r="C1" t="str">
+        <v>title</v>
+      </c>
+      <c r="D1" t="str">
+        <v>affectedPpl</v>
+      </c>
+      <c r="E1" t="str">
+        <v>reworkType</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TIB-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TIB-2026-PV-089</v>
+      </c>
+      <c r="C2" t="str">
+        <v>BMS High-Voltage Contactor Firmware v4.8 Update</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ECU Firmware Update</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TIB-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TIB-2026-PV-112</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Rear Suspension Spring Seat Damping Pad Retrofit</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Harrier / Safari</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Hardware Bush Replacement</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TIB-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TIB-2026-PV-134</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Steering Column Earth Strap Resistance Check</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Torque Audit</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G4"/>
   <sheetData>
@@ -15708,7 +18258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetData>
@@ -15799,7 +18349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
@@ -15910,7 +18460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetData>

--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -38,10 +38,23 @@
     <sheet name="parts_delay_reasons" sheetId="33" r:id="rId33"/>
     <sheet name="thd_escalation_categories" sheetId="34" r:id="rId34"/>
     <sheet name="tib_bulletin_codes" sheetId="35" r:id="rId35"/>
-    <sheet name="driver_transit_roster" sheetId="36" r:id="rId36"/>
-    <sheet name="lounge_reception_checklist" sheetId="37" r:id="rId37"/>
-    <sheet name="gate_security_checklist" sheetId="38" r:id="rId38"/>
-    <sheet name="gate_denial_reasons" sheetId="39" r:id="rId39"/>
+    <sheet name="thd_auto_trigger_rules" sheetId="36" r:id="rId36"/>
+    <sheet name="thd_critical_complaints" sheetId="37" r:id="rId37"/>
+    <sheet name="thd_progress" sheetId="38" r:id="rId38"/>
+    <sheet name="thd_progress_sub_status" sheetId="39" r:id="rId39"/>
+    <sheet name="thd_complaint_type" sheetId="40" r:id="rId40"/>
+    <sheet name="thd_complaint_short_desc" sheetId="41" r:id="rId41"/>
+    <sheet name="thd_action_taken" sheetId="42" r:id="rId42"/>
+    <sheet name="thd_delay_reason" sheetId="43" r:id="rId43"/>
+    <sheet name="thd_closure_action" sheetId="44" r:id="rId44"/>
+    <sheet name="thd_attachment_type" sheetId="45" r:id="rId45"/>
+    <sheet name="thd_kms_range" sheetId="46" r:id="rId46"/>
+    <sheet name="thd_vehicle_age" sheetId="47" r:id="rId47"/>
+    <sheet name="thd_users" sheetId="48" r:id="rId48"/>
+    <sheet name="driver_transit_roster" sheetId="49" r:id="rId49"/>
+    <sheet name="lounge_reception_checklist" sheetId="50" r:id="rId50"/>
+    <sheet name="gate_security_checklist" sheetId="51" r:id="rId51"/>
+    <sheet name="gate_denial_reasons" sheetId="52" r:id="rId52"/>
   </sheets>
 </workbook>
 </file>
@@ -479,7 +492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">  Module Code    One of: appointment, reception, security, jc_creation, jc_tracking, spd, thd, eqc, claim, bodyshop, ira, dealer_network</v>
+        <v xml:space="preserve">  Module Code    One of: appointment, reception, receptionist, security, jc_creation, bodyshop, jc_tracking, eqc, thd, spd, claim, customer_journey</v>
       </c>
     </row>
     <row r="10">
@@ -2089,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2237,10 +2250,10 @@
         <v>EV High-Voltage Safety &amp; Protocols</v>
       </c>
       <c r="C7" t="str">
-        <v>ira</v>
+        <v>eqc</v>
       </c>
       <c r="D7" t="str">
-        <v>Vehicle Data</v>
+        <v>Electronic Quality Check</v>
       </c>
       <c r="E7" t="str">
         <v>TML_ADMIN</v>
@@ -2260,10 +2273,10 @@
         <v>DTC Fault Code Alert &amp; Telematics</v>
       </c>
       <c r="C8" t="str">
-        <v>ira</v>
+        <v>thd</v>
       </c>
       <c r="D8" t="str">
-        <v>Vehicle Data</v>
+        <v>Parts, Claims &amp; Support</v>
       </c>
       <c r="E8" t="str">
         <v>TML_ADMIN</v>
@@ -2677,7 +2690,7 @@
         <v>bodyshop</v>
       </c>
       <c r="D26" t="str">
-        <v>Service Operations</v>
+        <v>Bodyshop</v>
       </c>
       <c r="E26" t="str">
         <v>DEALER_ADMIN</v>
@@ -2852,36 +2865,36 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B34" t="str">
-        <v>Chauffeur &amp; Pick-and-Drop Transit Roster</v>
+        <v>THD Auto-Trigger Rules</v>
       </c>
       <c r="C34" t="str">
-        <v>reception</v>
+        <v>thd</v>
       </c>
       <c r="D34" t="str">
         <v>Parts, Claims &amp; Support</v>
       </c>
       <c r="E34" t="str">
-        <v>DEALER_ADMIN</v>
+        <v>TML_ADMIN</v>
       </c>
       <c r="F34" t="str">
-        <v>Transit Chauffeurs</v>
+        <v>THD Rules</v>
       </c>
       <c r="G34" t="str">
-        <v>Driver certifications, assigned zone geofences, and vehicle transit speed monitoring.</v>
+        <v>When the system raises a THD case automatically (BA sheet "Conditions 4"). A blank Time Window means the value is still pending from business; that rule cannot fire until it is filled.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B35" t="str">
-        <v>Customer Reception &amp; Greeting Checklist</v>
+        <v>THD Critical Complaints Master</v>
       </c>
       <c r="C35" t="str">
-        <v>reception</v>
+        <v>thd</v>
       </c>
       <c r="D35" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2890,21 +2903,21 @@
         <v>TML_ADMIN</v>
       </c>
       <c r="F35" t="str">
-        <v>Customer Welcome</v>
+        <v>THD Rules</v>
       </c>
       <c r="G35" t="str">
-        <v>Standard OEM lounge customer greeting and advisor electronic tablet handover checklist.</v>
+        <v>Complaint codes that automatically raise a THD case when added to a Job Card. Blank PPL = every PPL.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>gate_security_checklist</v>
+        <v>thd_progress</v>
       </c>
       <c r="B36" t="str">
-        <v>Vehicle Gate Inward / Outward Barrier Checklist</v>
+        <v>THD Progress Master</v>
       </c>
       <c r="C36" t="str">
-        <v>security</v>
+        <v>thd</v>
       </c>
       <c r="D36" t="str">
         <v>Parts, Claims &amp; Support</v>
@@ -2913,38 +2926,337 @@
         <v>TML_ADMIN</v>
       </c>
       <c r="F36" t="str">
-        <v>Perimeter Security</v>
+        <v>THD Dropdown Lists</v>
       </c>
       <c r="G36" t="str">
-        <v>Mandatory perimeter verification rules for automatic ANPR barrier opening and vehicle passes.</v>
+        <v>Progress of a THD case (BA sheet "Progress LOV"). Each progress has its own sub-statuses.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>gate_denial_reasons</v>
+        <v>thd_progress_sub_status</v>
       </c>
       <c r="B37" t="str">
-        <v>Gate Entry Denial &amp; Security Hold LOV</v>
+        <v>THD Progress Sub-Status Master</v>
       </c>
       <c r="C37" t="str">
-        <v>security</v>
+        <v>thd</v>
       </c>
       <c r="D37" t="str">
         <v>Parts, Claims &amp; Support</v>
       </c>
       <c r="E37" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F37" t="str">
+        <v>THD Dropdown Lists</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Sub-statuses shown after a Progress is chosen (BA sheet "Progress Sub Status"). Order restarts for each Progress.</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>thd_complaint_type</v>
+      </c>
+      <c r="B38" t="str">
+        <v>THD Type of Complaint Master</v>
+      </c>
+      <c r="C38" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E38" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F38" t="str">
+        <v>THD Dropdown Lists</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Selected when the THD request is closed (BA sheet "Type of Complaint LOV"). Only Active values are shown, in Order.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>thd_complaint_short_desc</v>
+      </c>
+      <c r="B39" t="str">
+        <v>THD Complaint Short Description Master</v>
+      </c>
+      <c r="C39" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E39" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F39" t="str">
+        <v>THD Dropdown Lists</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Selected when the THD request is closed (BA sheet "Complaint Shot Description LOV"). Only Active values are shown, in Order.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>thd_action_taken</v>
+      </c>
+      <c r="B40" t="str">
+        <v>THD Action Taken Master</v>
+      </c>
+      <c r="C40" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E40" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F40" t="str">
+        <v>THD Dropdown Lists</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Selected when the THD request is closed (BA sheet "Action Taken LOV"). Only Active values are shown, in Order.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>thd_delay_reason</v>
+      </c>
+      <c r="B41" t="str">
+        <v>THD Reason for Delay Master</v>
+      </c>
+      <c r="C41" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E41" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F41" t="str">
+        <v>THD Dropdown Lists</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Selected when the THD request is closed (BA sheet "Reason for Delay LOV"). Only Active values are shown, in Order.</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>thd_closure_action</v>
+      </c>
+      <c r="B42" t="str">
+        <v>THD Closure Action Master</v>
+      </c>
+      <c r="C42" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E42" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F42" t="str">
+        <v>THD Dropdown Lists</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Selected when the THD request is closed (BA sheet "Closure Action LOV"). Only Active values are shown, in Order.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>thd_attachment_type</v>
+      </c>
+      <c r="B43" t="str">
+        <v>THD Attachment Type Master</v>
+      </c>
+      <c r="C43" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E43" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F43" t="str">
+        <v>THD Dropdown Lists</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Type of attachment uploaded against a THD case (BA sheet "Attachment LOV").</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>thd_kms_range</v>
+      </c>
+      <c r="B44" t="str">
+        <v>THD Kms Range Filter Master</v>
+      </c>
+      <c r="C44" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E44" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F44" t="str">
+        <v>THD Search Filters</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Km ranges offered when searching THD cases (BA sheet "Kms Range"). From and To are inclusive.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>thd_vehicle_age</v>
+      </c>
+      <c r="B45" t="str">
+        <v>THD Vehicle Age Filter Master</v>
+      </c>
+      <c r="C45" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E45" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F45" t="str">
+        <v>THD Search Filters</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Vehicle age ranges (years) offered when searching THD cases (BA sheet "Vehicle Age"). From and To are inclusive.</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B46" t="str">
+        <v>THD Assignment Users Master</v>
+      </c>
+      <c r="C46" t="str">
+        <v>thd</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E46" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F46" t="str">
+        <v>THD Users</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Users a THD request can be assigned to. One master for the five BA sheets (Tech Executive L1, RTSM, COC L2, Plant, Product Reliability) — the Role column says which list.</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Chauffeur &amp; Pick-and-Drop Transit Roster</v>
+      </c>
+      <c r="C47" t="str">
+        <v>reception</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E47" t="str">
         <v>DEALER_ADMIN</v>
       </c>
-      <c r="F37" t="str">
+      <c r="F47" t="str">
+        <v>Transit Chauffeurs</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Driver certifications, assigned zone geofences, and vehicle transit speed monitoring.</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Customer Reception &amp; Greeting Checklist</v>
+      </c>
+      <c r="C48" t="str">
+        <v>receptionist</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E48" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Customer Welcome</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Standard OEM lounge customer greeting and advisor electronic tablet handover checklist.</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Vehicle Gate Inward / Outward Barrier Checklist</v>
+      </c>
+      <c r="C49" t="str">
+        <v>security</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E49" t="str">
+        <v>TML_ADMIN</v>
+      </c>
+      <c r="F49" t="str">
         <v>Perimeter Security</v>
       </c>
-      <c r="G37" t="str">
+      <c r="G49" t="str">
+        <v>Mandatory perimeter verification rules for automatic ANPR barrier opening and vehicle passes.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Gate Entry Denial &amp; Security Hold LOV</v>
+      </c>
+      <c r="C50" t="str">
+        <v>security</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Parts, Claims &amp; Support</v>
+      </c>
+      <c r="E50" t="str">
+        <v>DEALER_ADMIN</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Perimeter Security</v>
+      </c>
+      <c r="G50" t="str">
         <v>Security gate vehicle hold classifications and escalation protocol for police or insurance hold.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5138,7 +5450,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q234"/>
+  <dimension ref="A1:Q293"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16484,16 +16796,16 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B215" t="str">
-        <v>driverCode</v>
+        <v>ruleNo</v>
       </c>
       <c r="C215" t="str">
-        <v>Driver Code</v>
+        <v>Rule No.</v>
       </c>
       <c r="D215" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E215" t="str">
         <v>Y</v>
@@ -16501,11 +16813,11 @@
       <c r="F215" t="str">
         <v/>
       </c>
-      <c r="G215" t="str">
-        <v/>
-      </c>
-      <c r="H215" t="str">
-        <v/>
+      <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215">
+        <v>99</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -16537,22 +16849,22 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B216" t="str">
-        <v>driverName</v>
+        <v>scenarioCode</v>
       </c>
       <c r="C216" t="str">
-        <v>Driver Full Name</v>
+        <v>Scenario</v>
       </c>
       <c r="D216" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E216" t="str">
         <v>Y</v>
       </c>
       <c r="F216" t="str">
-        <v/>
+        <v>REPEAT_COMPLAINT, CRITICAL_AT_JC_CREATION, CRITICAL_AFTER_JC_CREATION, DELAY_REASON, QI_THD_REQUIRED, OPEN_ESCALATION, CRITICAL_DTC, THD_UNATTENDED</v>
       </c>
       <c r="G216" t="str">
         <v/>
@@ -16585,27 +16897,27 @@
         <v/>
       </c>
       <c r="Q216" t="str">
-        <v/>
+        <v>What the system checks. Fixed list — each one is coded in the rules engine.</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B217" t="str">
-        <v>assignedZone</v>
+        <v>businessCondition</v>
       </c>
       <c r="C217" t="str">
-        <v>Assigned Territory Zone</v>
+        <v>Business Condition</v>
       </c>
       <c r="D217" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E217" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F217" t="str">
-        <v>Zone A - Hitec City, Zone B - Secunderabad, Zone C - Gachibowli, Zone D - Banjara Hills</v>
+        <v/>
       </c>
       <c r="G217" t="str">
         <v/>
@@ -16643,22 +16955,22 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B218" t="str">
-        <v>licenseNumber</v>
+        <v>triggerPoint</v>
       </c>
       <c r="C218" t="str">
-        <v>Commercial DL Number</v>
+        <v>Trigger Point</v>
       </c>
       <c r="D218" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E218" t="str">
         <v>Y</v>
       </c>
       <c r="F218" t="str">
-        <v/>
+        <v>Job Card Creation, Open Job Card, Job Card Closure, THD Age</v>
       </c>
       <c r="G218" t="str">
         <v/>
@@ -16696,28 +17008,28 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B219" t="str">
-        <v>evCertified</v>
+        <v>windowValue</v>
       </c>
       <c r="C219" t="str">
-        <v>EV Transit Certified</v>
+        <v>Time Window</v>
       </c>
       <c r="D219" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E219" t="str">
         <v>N</v>
       </c>
       <c r="F219" t="str">
-        <v>Y, N</v>
-      </c>
-      <c r="G219" t="str">
-        <v/>
-      </c>
-      <c r="H219" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G219">
+        <v>1</v>
+      </c>
+      <c r="H219">
+        <v>999</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -16744,18 +17056,18 @@
         <v/>
       </c>
       <c r="Q219" t="str">
-        <v/>
+        <v>e.g. 30 (days) for repeat visits, 24 (hours) for an unattended THD. Blank = pending from business.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B220" t="str">
-        <v>active</v>
+        <v>windowUnit</v>
       </c>
       <c r="C220" t="str">
-        <v>Active</v>
+        <v>Window Unit</v>
       </c>
       <c r="D220" t="str">
         <v>select</v>
@@ -16764,7 +17076,7 @@
         <v>N</v>
       </c>
       <c r="F220" t="str">
-        <v>Y, N</v>
+        <v>Hours, Days</v>
       </c>
       <c r="G220" t="str">
         <v/>
@@ -16802,19 +17114,19 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B221" t="str">
-        <v>checkpointCode</v>
+        <v>triggerValues</v>
       </c>
       <c r="C221" t="str">
-        <v>Checkpoint Code</v>
+        <v>Trigger Values</v>
       </c>
       <c r="D221" t="str">
         <v>text</v>
       </c>
       <c r="E221" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F221" t="str">
         <v/>
@@ -16850,27 +17162,27 @@
         <v/>
       </c>
       <c r="Q221" t="str">
-        <v/>
+        <v>Comma-separated values the rule looks for, e.g. the Job Card delay reasons.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B222" t="str">
-        <v>checkpointDesc</v>
+        <v>escalationComplaint</v>
       </c>
       <c r="C222" t="str">
-        <v>Reception Standard Requirement</v>
+        <v>Escalation Complaint</v>
       </c>
       <c r="D222" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E222" t="str">
         <v>Y</v>
       </c>
       <c r="F222" t="str">
-        <v/>
+        <v>Yes, No, Yes/No, NA</v>
       </c>
       <c r="G222" t="str">
         <v/>
@@ -16908,22 +17220,22 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B223" t="str">
-        <v>channel</v>
+        <v>thdTag</v>
       </c>
       <c r="C223" t="str">
-        <v>Intake Channel</v>
+        <v>THD Tag</v>
       </c>
       <c r="D223" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E223" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F223" t="str">
-        <v>Walk-in, Pre-Booked Appointment, Express Valet, Breakdown Flatbed</v>
+        <v/>
       </c>
       <c r="G223" t="str">
         <v/>
@@ -16961,22 +17273,22 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B224" t="str">
-        <v>mandatoryProof</v>
+        <v>assignedTo</v>
       </c>
       <c r="C224" t="str">
-        <v>Mandatory Photo / Signature</v>
+        <v>Assigned To</v>
       </c>
       <c r="D224" t="str">
         <v>select</v>
       </c>
       <c r="E224" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F224" t="str">
-        <v>Y, N</v>
+        <v>DET, Tech Executive L1</v>
       </c>
       <c r="G224" t="str">
         <v/>
@@ -17014,22 +17326,22 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B225" t="str">
-        <v>active</v>
+        <v>status</v>
       </c>
       <c r="C225" t="str">
-        <v>Active</v>
+        <v>Status</v>
       </c>
       <c r="D225" t="str">
         <v>select</v>
       </c>
       <c r="E225" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F225" t="str">
-        <v>Y, N</v>
+        <v>Active, Inactive</v>
       </c>
       <c r="G225" t="str">
         <v/>
@@ -17067,22 +17379,22 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>gate_security_checklist</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B226" t="str">
-        <v>ruleId</v>
+        <v>ppl</v>
       </c>
       <c r="C226" t="str">
-        <v>Gate Rule Code</v>
+        <v>PPL</v>
       </c>
       <c r="D226" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E226" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F226" t="str">
-        <v/>
+        <v>Nexon, Nexon EV, Altroz, Harrier, Safari, Punch, Punch EV, Tiago, Tiago EV, Tigor, Curvv, Curvv EV</v>
       </c>
       <c r="G226" t="str">
         <v/>
@@ -17115,27 +17427,27 @@
         <v/>
       </c>
       <c r="Q226" t="str">
-        <v/>
+        <v>Leave blank to apply to all PPLs.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>gate_security_checklist</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B227" t="str">
-        <v>direction</v>
+        <v>complaintCode</v>
       </c>
       <c r="C227" t="str">
-        <v>Movement Direction</v>
+        <v>Complaint Code</v>
       </c>
       <c r="D227" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E227" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F227" t="str">
-        <v>Inward (Check-in), Outward (Check-out), Internal Bay Transit</v>
+        <v/>
       </c>
       <c r="G227" t="str">
         <v/>
@@ -17173,13 +17485,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>gate_security_checklist</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B228" t="str">
-        <v>verificationItem</v>
+        <v>complaintDescription</v>
       </c>
       <c r="C228" t="str">
-        <v>Verification Protocol</v>
+        <v>Complaint Description</v>
       </c>
       <c r="D228" t="str">
         <v>text</v>
@@ -17226,22 +17538,22 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>gate_security_checklist</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B229" t="str">
-        <v>anprSync</v>
+        <v>aggregate</v>
       </c>
       <c r="C229" t="str">
-        <v>ANPR Camera Auto-Verify</v>
+        <v>Aggregate</v>
       </c>
       <c r="D229" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E229" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F229" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G229" t="str">
         <v/>
@@ -17279,22 +17591,22 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>gate_security_checklist</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B230" t="str">
-        <v>active</v>
+        <v>complaintType</v>
       </c>
       <c r="C230" t="str">
-        <v>Active</v>
+        <v>Complaint Type</v>
       </c>
       <c r="D230" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E230" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F230" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G230" t="str">
         <v/>
@@ -17332,22 +17644,22 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>gate_denial_reasons</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B231" t="str">
-        <v>denialCode</v>
+        <v>critical</v>
       </c>
       <c r="C231" t="str">
-        <v>Denial Code</v>
+        <v>Critical Complaint</v>
       </c>
       <c r="D231" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E231" t="str">
         <v>Y</v>
       </c>
       <c r="F231" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G231" t="str">
         <v/>
@@ -17385,22 +17697,22 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>gate_denial_reasons</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B232" t="str">
-        <v>reason</v>
+        <v>status</v>
       </c>
       <c r="C232" t="str">
-        <v>Security Denial / Hold Reason</v>
+        <v>Status</v>
       </c>
       <c r="D232" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E232" t="str">
         <v>Y</v>
       </c>
       <c r="F232" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G232" t="str">
         <v/>
@@ -17438,22 +17750,22 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>gate_denial_reasons</v>
+        <v>thd_progress</v>
       </c>
       <c r="B233" t="str">
-        <v>escalateTo</v>
+        <v>value</v>
       </c>
       <c r="C233" t="str">
-        <v>Immediate Notification Target</v>
+        <v>Progress</v>
       </c>
       <c r="D233" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E233" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F233" t="str">
-        <v>Works Manager, Security Officer In-Charge, Service Head, Customer Relation Manager</v>
+        <v/>
       </c>
       <c r="G233" t="str">
         <v/>
@@ -17491,60 +17803,3187 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>gate_denial_reasons</v>
+        <v>thd_progress</v>
       </c>
       <c r="B234" t="str">
-        <v>active</v>
+        <v>status</v>
       </c>
       <c r="C234" t="str">
-        <v>Active</v>
+        <v>Status</v>
       </c>
       <c r="D234" t="str">
         <v>select</v>
       </c>
       <c r="E234" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F234" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <v/>
+      </c>
+      <c r="J234" t="str">
+        <v/>
+      </c>
+      <c r="K234" t="str">
+        <v/>
+      </c>
+      <c r="L234" t="str">
+        <v/>
+      </c>
+      <c r="M234" t="str">
+        <v>N</v>
+      </c>
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+      <c r="P234" t="str">
+        <v/>
+      </c>
+      <c r="Q234" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>thd_progress</v>
+      </c>
+      <c r="B235" t="str">
+        <v>order</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Order</v>
+      </c>
+      <c r="D235" t="str">
+        <v>number</v>
+      </c>
+      <c r="E235" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235">
+        <v>1</v>
+      </c>
+      <c r="H235">
+        <v>99</v>
+      </c>
+      <c r="I235" t="str">
+        <v/>
+      </c>
+      <c r="J235" t="str">
+        <v/>
+      </c>
+      <c r="K235" t="str">
+        <v/>
+      </c>
+      <c r="L235" t="str">
+        <v/>
+      </c>
+      <c r="M235" t="str">
+        <v>N</v>
+      </c>
+      <c r="N235" t="str">
+        <v/>
+      </c>
+      <c r="O235" t="str">
+        <v/>
+      </c>
+      <c r="P235" t="str">
+        <v/>
+      </c>
+      <c r="Q235" t="str">
+        <v>Display order in the dropdown.</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>thd_progress_sub_status</v>
+      </c>
+      <c r="B236" t="str">
+        <v>progress</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Progress</v>
+      </c>
+      <c r="D236" t="str">
+        <v>select</v>
+      </c>
+      <c r="E236" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F236" t="str">
+        <v>Under Diagnosis, Work in process, Pending for parts, Pending for vendor support, Pending for commercial decision, Pending for Vehicle availability</v>
+      </c>
+      <c r="G236" t="str">
+        <v/>
+      </c>
+      <c r="H236" t="str">
+        <v/>
+      </c>
+      <c r="I236" t="str">
+        <v/>
+      </c>
+      <c r="J236" t="str">
+        <v/>
+      </c>
+      <c r="K236" t="str">
+        <v/>
+      </c>
+      <c r="L236" t="str">
+        <v/>
+      </c>
+      <c r="M236" t="str">
+        <v>N</v>
+      </c>
+      <c r="N236" t="str">
+        <v/>
+      </c>
+      <c r="O236" t="str">
+        <v/>
+      </c>
+      <c r="P236" t="str">
+        <v/>
+      </c>
+      <c r="Q236" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>thd_progress_sub_status</v>
+      </c>
+      <c r="B237" t="str">
+        <v>subStatus</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Progress Sub Status</v>
+      </c>
+      <c r="D237" t="str">
+        <v>text</v>
+      </c>
+      <c r="E237" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <v/>
+      </c>
+      <c r="J237" t="str">
+        <v/>
+      </c>
+      <c r="K237" t="str">
+        <v/>
+      </c>
+      <c r="L237" t="str">
+        <v/>
+      </c>
+      <c r="M237" t="str">
+        <v>N</v>
+      </c>
+      <c r="N237" t="str">
+        <v/>
+      </c>
+      <c r="O237" t="str">
+        <v/>
+      </c>
+      <c r="P237" t="str">
+        <v/>
+      </c>
+      <c r="Q237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>thd_progress_sub_status</v>
+      </c>
+      <c r="B238" t="str">
+        <v>status</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D238" t="str">
+        <v>select</v>
+      </c>
+      <c r="E238" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F238" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+      <c r="H238" t="str">
+        <v/>
+      </c>
+      <c r="I238" t="str">
+        <v/>
+      </c>
+      <c r="J238" t="str">
+        <v/>
+      </c>
+      <c r="K238" t="str">
+        <v/>
+      </c>
+      <c r="L238" t="str">
+        <v/>
+      </c>
+      <c r="M238" t="str">
+        <v>N</v>
+      </c>
+      <c r="N238" t="str">
+        <v/>
+      </c>
+      <c r="O238" t="str">
+        <v/>
+      </c>
+      <c r="P238" t="str">
+        <v/>
+      </c>
+      <c r="Q238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>thd_progress_sub_status</v>
+      </c>
+      <c r="B239" t="str">
+        <v>order</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Order</v>
+      </c>
+      <c r="D239" t="str">
+        <v>number</v>
+      </c>
+      <c r="E239" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239">
+        <v>1</v>
+      </c>
+      <c r="H239">
+        <v>99</v>
+      </c>
+      <c r="I239" t="str">
+        <v/>
+      </c>
+      <c r="J239" t="str">
+        <v/>
+      </c>
+      <c r="K239" t="str">
+        <v/>
+      </c>
+      <c r="L239" t="str">
+        <v/>
+      </c>
+      <c r="M239" t="str">
+        <v>N</v>
+      </c>
+      <c r="N239" t="str">
+        <v/>
+      </c>
+      <c r="O239" t="str">
+        <v/>
+      </c>
+      <c r="P239" t="str">
+        <v/>
+      </c>
+      <c r="Q239" t="str">
+        <v>Display order in the dropdown.</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>thd_complaint_type</v>
+      </c>
+      <c r="B240" t="str">
+        <v>value</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Type of Complaint</v>
+      </c>
+      <c r="D240" t="str">
+        <v>text</v>
+      </c>
+      <c r="E240" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F240" t="str">
+        <v/>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+      <c r="H240" t="str">
+        <v/>
+      </c>
+      <c r="I240" t="str">
+        <v/>
+      </c>
+      <c r="J240" t="str">
+        <v/>
+      </c>
+      <c r="K240" t="str">
+        <v/>
+      </c>
+      <c r="L240" t="str">
+        <v/>
+      </c>
+      <c r="M240" t="str">
+        <v>N</v>
+      </c>
+      <c r="N240" t="str">
+        <v/>
+      </c>
+      <c r="O240" t="str">
+        <v/>
+      </c>
+      <c r="P240" t="str">
+        <v/>
+      </c>
+      <c r="Q240" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>thd_complaint_type</v>
+      </c>
+      <c r="B241" t="str">
+        <v>status</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D241" t="str">
+        <v>select</v>
+      </c>
+      <c r="E241" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F241" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+      <c r="H241" t="str">
+        <v/>
+      </c>
+      <c r="I241" t="str">
+        <v/>
+      </c>
+      <c r="J241" t="str">
+        <v/>
+      </c>
+      <c r="K241" t="str">
+        <v/>
+      </c>
+      <c r="L241" t="str">
+        <v/>
+      </c>
+      <c r="M241" t="str">
+        <v>N</v>
+      </c>
+      <c r="N241" t="str">
+        <v/>
+      </c>
+      <c r="O241" t="str">
+        <v/>
+      </c>
+      <c r="P241" t="str">
+        <v/>
+      </c>
+      <c r="Q241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>thd_complaint_type</v>
+      </c>
+      <c r="B242" t="str">
+        <v>order</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Order</v>
+      </c>
+      <c r="D242" t="str">
+        <v>number</v>
+      </c>
+      <c r="E242" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242">
+        <v>1</v>
+      </c>
+      <c r="H242">
+        <v>99</v>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
+      <c r="J242" t="str">
+        <v/>
+      </c>
+      <c r="K242" t="str">
+        <v/>
+      </c>
+      <c r="L242" t="str">
+        <v/>
+      </c>
+      <c r="M242" t="str">
+        <v>N</v>
+      </c>
+      <c r="N242" t="str">
+        <v/>
+      </c>
+      <c r="O242" t="str">
+        <v/>
+      </c>
+      <c r="P242" t="str">
+        <v/>
+      </c>
+      <c r="Q242" t="str">
+        <v>Display order in the dropdown.</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>thd_complaint_short_desc</v>
+      </c>
+      <c r="B243" t="str">
+        <v>value</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Complaint Short Description</v>
+      </c>
+      <c r="D243" t="str">
+        <v>text</v>
+      </c>
+      <c r="E243" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <v/>
+      </c>
+      <c r="J243" t="str">
+        <v/>
+      </c>
+      <c r="K243" t="str">
+        <v/>
+      </c>
+      <c r="L243" t="str">
+        <v/>
+      </c>
+      <c r="M243" t="str">
+        <v>N</v>
+      </c>
+      <c r="N243" t="str">
+        <v/>
+      </c>
+      <c r="O243" t="str">
+        <v/>
+      </c>
+      <c r="P243" t="str">
+        <v/>
+      </c>
+      <c r="Q243" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>thd_complaint_short_desc</v>
+      </c>
+      <c r="B244" t="str">
+        <v>status</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D244" t="str">
+        <v>select</v>
+      </c>
+      <c r="E244" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F244" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+      <c r="H244" t="str">
+        <v/>
+      </c>
+      <c r="I244" t="str">
+        <v/>
+      </c>
+      <c r="J244" t="str">
+        <v/>
+      </c>
+      <c r="K244" t="str">
+        <v/>
+      </c>
+      <c r="L244" t="str">
+        <v/>
+      </c>
+      <c r="M244" t="str">
+        <v>N</v>
+      </c>
+      <c r="N244" t="str">
+        <v/>
+      </c>
+      <c r="O244" t="str">
+        <v/>
+      </c>
+      <c r="P244" t="str">
+        <v/>
+      </c>
+      <c r="Q244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>thd_complaint_short_desc</v>
+      </c>
+      <c r="B245" t="str">
+        <v>order</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Order</v>
+      </c>
+      <c r="D245" t="str">
+        <v>number</v>
+      </c>
+      <c r="E245" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F245" t="str">
+        <v/>
+      </c>
+      <c r="G245">
+        <v>1</v>
+      </c>
+      <c r="H245">
+        <v>99</v>
+      </c>
+      <c r="I245" t="str">
+        <v/>
+      </c>
+      <c r="J245" t="str">
+        <v/>
+      </c>
+      <c r="K245" t="str">
+        <v/>
+      </c>
+      <c r="L245" t="str">
+        <v/>
+      </c>
+      <c r="M245" t="str">
+        <v>N</v>
+      </c>
+      <c r="N245" t="str">
+        <v/>
+      </c>
+      <c r="O245" t="str">
+        <v/>
+      </c>
+      <c r="P245" t="str">
+        <v/>
+      </c>
+      <c r="Q245" t="str">
+        <v>Display order in the dropdown.</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>thd_action_taken</v>
+      </c>
+      <c r="B246" t="str">
+        <v>value</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Action Taken</v>
+      </c>
+      <c r="D246" t="str">
+        <v>text</v>
+      </c>
+      <c r="E246" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F246" t="str">
+        <v/>
+      </c>
+      <c r="G246" t="str">
+        <v/>
+      </c>
+      <c r="H246" t="str">
+        <v/>
+      </c>
+      <c r="I246" t="str">
+        <v/>
+      </c>
+      <c r="J246" t="str">
+        <v/>
+      </c>
+      <c r="K246" t="str">
+        <v/>
+      </c>
+      <c r="L246" t="str">
+        <v/>
+      </c>
+      <c r="M246" t="str">
+        <v>N</v>
+      </c>
+      <c r="N246" t="str">
+        <v/>
+      </c>
+      <c r="O246" t="str">
+        <v/>
+      </c>
+      <c r="P246" t="str">
+        <v/>
+      </c>
+      <c r="Q246" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>thd_action_taken</v>
+      </c>
+      <c r="B247" t="str">
+        <v>status</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D247" t="str">
+        <v>select</v>
+      </c>
+      <c r="E247" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F247" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G247" t="str">
+        <v/>
+      </c>
+      <c r="H247" t="str">
+        <v/>
+      </c>
+      <c r="I247" t="str">
+        <v/>
+      </c>
+      <c r="J247" t="str">
+        <v/>
+      </c>
+      <c r="K247" t="str">
+        <v/>
+      </c>
+      <c r="L247" t="str">
+        <v/>
+      </c>
+      <c r="M247" t="str">
+        <v>N</v>
+      </c>
+      <c r="N247" t="str">
+        <v/>
+      </c>
+      <c r="O247" t="str">
+        <v/>
+      </c>
+      <c r="P247" t="str">
+        <v/>
+      </c>
+      <c r="Q247" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>thd_action_taken</v>
+      </c>
+      <c r="B248" t="str">
+        <v>order</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Order</v>
+      </c>
+      <c r="D248" t="str">
+        <v>number</v>
+      </c>
+      <c r="E248" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F248" t="str">
+        <v/>
+      </c>
+      <c r="G248">
+        <v>1</v>
+      </c>
+      <c r="H248">
+        <v>99</v>
+      </c>
+      <c r="I248" t="str">
+        <v/>
+      </c>
+      <c r="J248" t="str">
+        <v/>
+      </c>
+      <c r="K248" t="str">
+        <v/>
+      </c>
+      <c r="L248" t="str">
+        <v/>
+      </c>
+      <c r="M248" t="str">
+        <v>N</v>
+      </c>
+      <c r="N248" t="str">
+        <v/>
+      </c>
+      <c r="O248" t="str">
+        <v/>
+      </c>
+      <c r="P248" t="str">
+        <v/>
+      </c>
+      <c r="Q248" t="str">
+        <v>Display order in the dropdown.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>thd_delay_reason</v>
+      </c>
+      <c r="B249" t="str">
+        <v>value</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Reason for Delay</v>
+      </c>
+      <c r="D249" t="str">
+        <v>text</v>
+      </c>
+      <c r="E249" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F249" t="str">
+        <v/>
+      </c>
+      <c r="G249" t="str">
+        <v/>
+      </c>
+      <c r="H249" t="str">
+        <v/>
+      </c>
+      <c r="I249" t="str">
+        <v/>
+      </c>
+      <c r="J249" t="str">
+        <v/>
+      </c>
+      <c r="K249" t="str">
+        <v/>
+      </c>
+      <c r="L249" t="str">
+        <v/>
+      </c>
+      <c r="M249" t="str">
+        <v>N</v>
+      </c>
+      <c r="N249" t="str">
+        <v/>
+      </c>
+      <c r="O249" t="str">
+        <v/>
+      </c>
+      <c r="P249" t="str">
+        <v/>
+      </c>
+      <c r="Q249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>thd_delay_reason</v>
+      </c>
+      <c r="B250" t="str">
+        <v>status</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D250" t="str">
+        <v>select</v>
+      </c>
+      <c r="E250" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F250" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G250" t="str">
+        <v/>
+      </c>
+      <c r="H250" t="str">
+        <v/>
+      </c>
+      <c r="I250" t="str">
+        <v/>
+      </c>
+      <c r="J250" t="str">
+        <v/>
+      </c>
+      <c r="K250" t="str">
+        <v/>
+      </c>
+      <c r="L250" t="str">
+        <v/>
+      </c>
+      <c r="M250" t="str">
+        <v>N</v>
+      </c>
+      <c r="N250" t="str">
+        <v/>
+      </c>
+      <c r="O250" t="str">
+        <v/>
+      </c>
+      <c r="P250" t="str">
+        <v/>
+      </c>
+      <c r="Q250" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>thd_delay_reason</v>
+      </c>
+      <c r="B251" t="str">
+        <v>order</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Order</v>
+      </c>
+      <c r="D251" t="str">
+        <v>number</v>
+      </c>
+      <c r="E251" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F251" t="str">
+        <v/>
+      </c>
+      <c r="G251">
+        <v>1</v>
+      </c>
+      <c r="H251">
+        <v>99</v>
+      </c>
+      <c r="I251" t="str">
+        <v/>
+      </c>
+      <c r="J251" t="str">
+        <v/>
+      </c>
+      <c r="K251" t="str">
+        <v/>
+      </c>
+      <c r="L251" t="str">
+        <v/>
+      </c>
+      <c r="M251" t="str">
+        <v>N</v>
+      </c>
+      <c r="N251" t="str">
+        <v/>
+      </c>
+      <c r="O251" t="str">
+        <v/>
+      </c>
+      <c r="P251" t="str">
+        <v/>
+      </c>
+      <c r="Q251" t="str">
+        <v>Display order in the dropdown.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>thd_closure_action</v>
+      </c>
+      <c r="B252" t="str">
+        <v>value</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Closure Action</v>
+      </c>
+      <c r="D252" t="str">
+        <v>text</v>
+      </c>
+      <c r="E252" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F252" t="str">
+        <v/>
+      </c>
+      <c r="G252" t="str">
+        <v/>
+      </c>
+      <c r="H252" t="str">
+        <v/>
+      </c>
+      <c r="I252" t="str">
+        <v/>
+      </c>
+      <c r="J252" t="str">
+        <v/>
+      </c>
+      <c r="K252" t="str">
+        <v/>
+      </c>
+      <c r="L252" t="str">
+        <v/>
+      </c>
+      <c r="M252" t="str">
+        <v>N</v>
+      </c>
+      <c r="N252" t="str">
+        <v/>
+      </c>
+      <c r="O252" t="str">
+        <v/>
+      </c>
+      <c r="P252" t="str">
+        <v/>
+      </c>
+      <c r="Q252" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>thd_closure_action</v>
+      </c>
+      <c r="B253" t="str">
+        <v>status</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D253" t="str">
+        <v>select</v>
+      </c>
+      <c r="E253" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F253" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G253" t="str">
+        <v/>
+      </c>
+      <c r="H253" t="str">
+        <v/>
+      </c>
+      <c r="I253" t="str">
+        <v/>
+      </c>
+      <c r="J253" t="str">
+        <v/>
+      </c>
+      <c r="K253" t="str">
+        <v/>
+      </c>
+      <c r="L253" t="str">
+        <v/>
+      </c>
+      <c r="M253" t="str">
+        <v>N</v>
+      </c>
+      <c r="N253" t="str">
+        <v/>
+      </c>
+      <c r="O253" t="str">
+        <v/>
+      </c>
+      <c r="P253" t="str">
+        <v/>
+      </c>
+      <c r="Q253" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>thd_closure_action</v>
+      </c>
+      <c r="B254" t="str">
+        <v>order</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Order</v>
+      </c>
+      <c r="D254" t="str">
+        <v>number</v>
+      </c>
+      <c r="E254" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F254" t="str">
+        <v/>
+      </c>
+      <c r="G254">
+        <v>1</v>
+      </c>
+      <c r="H254">
+        <v>99</v>
+      </c>
+      <c r="I254" t="str">
+        <v/>
+      </c>
+      <c r="J254" t="str">
+        <v/>
+      </c>
+      <c r="K254" t="str">
+        <v/>
+      </c>
+      <c r="L254" t="str">
+        <v/>
+      </c>
+      <c r="M254" t="str">
+        <v>N</v>
+      </c>
+      <c r="N254" t="str">
+        <v/>
+      </c>
+      <c r="O254" t="str">
+        <v/>
+      </c>
+      <c r="P254" t="str">
+        <v/>
+      </c>
+      <c r="Q254" t="str">
+        <v>Display order in the dropdown.</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>thd_attachment_type</v>
+      </c>
+      <c r="B255" t="str">
+        <v>value</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Attachment Type</v>
+      </c>
+      <c r="D255" t="str">
+        <v>text</v>
+      </c>
+      <c r="E255" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F255" t="str">
+        <v/>
+      </c>
+      <c r="G255" t="str">
+        <v/>
+      </c>
+      <c r="H255" t="str">
+        <v/>
+      </c>
+      <c r="I255" t="str">
+        <v/>
+      </c>
+      <c r="J255" t="str">
+        <v/>
+      </c>
+      <c r="K255" t="str">
+        <v/>
+      </c>
+      <c r="L255" t="str">
+        <v/>
+      </c>
+      <c r="M255" t="str">
+        <v>N</v>
+      </c>
+      <c r="N255" t="str">
+        <v/>
+      </c>
+      <c r="O255" t="str">
+        <v/>
+      </c>
+      <c r="P255" t="str">
+        <v/>
+      </c>
+      <c r="Q255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>thd_attachment_type</v>
+      </c>
+      <c r="B256" t="str">
+        <v>status</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D256" t="str">
+        <v>select</v>
+      </c>
+      <c r="E256" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F256" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G256" t="str">
+        <v/>
+      </c>
+      <c r="H256" t="str">
+        <v/>
+      </c>
+      <c r="I256" t="str">
+        <v/>
+      </c>
+      <c r="J256" t="str">
+        <v/>
+      </c>
+      <c r="K256" t="str">
+        <v/>
+      </c>
+      <c r="L256" t="str">
+        <v/>
+      </c>
+      <c r="M256" t="str">
+        <v>N</v>
+      </c>
+      <c r="N256" t="str">
+        <v/>
+      </c>
+      <c r="O256" t="str">
+        <v/>
+      </c>
+      <c r="P256" t="str">
+        <v/>
+      </c>
+      <c r="Q256" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>thd_kms_range</v>
+      </c>
+      <c r="B257" t="str">
+        <v>label</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Kms Range</v>
+      </c>
+      <c r="D257" t="str">
+        <v>text</v>
+      </c>
+      <c r="E257" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F257" t="str">
+        <v/>
+      </c>
+      <c r="G257" t="str">
+        <v/>
+      </c>
+      <c r="H257" t="str">
+        <v/>
+      </c>
+      <c r="I257" t="str">
+        <v/>
+      </c>
+      <c r="J257" t="str">
+        <v/>
+      </c>
+      <c r="K257" t="str">
+        <v/>
+      </c>
+      <c r="L257" t="str">
+        <v/>
+      </c>
+      <c r="M257" t="str">
+        <v>N</v>
+      </c>
+      <c r="N257" t="str">
+        <v/>
+      </c>
+      <c r="O257" t="str">
+        <v/>
+      </c>
+      <c r="P257" t="str">
+        <v/>
+      </c>
+      <c r="Q257" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>thd_kms_range</v>
+      </c>
+      <c r="B258" t="str">
+        <v>fromKm</v>
+      </c>
+      <c r="C258" t="str">
+        <v>From Km</v>
+      </c>
+      <c r="D258" t="str">
+        <v>number</v>
+      </c>
+      <c r="E258" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F258" t="str">
+        <v/>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>999999</v>
+      </c>
+      <c r="I258" t="str">
+        <v/>
+      </c>
+      <c r="J258" t="str">
+        <v/>
+      </c>
+      <c r="K258" t="str">
+        <v/>
+      </c>
+      <c r="L258" t="str">
+        <v/>
+      </c>
+      <c r="M258" t="str">
+        <v>N</v>
+      </c>
+      <c r="N258" t="str">
+        <v/>
+      </c>
+      <c r="O258" t="str">
+        <v/>
+      </c>
+      <c r="P258" t="str">
+        <v/>
+      </c>
+      <c r="Q258" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>thd_kms_range</v>
+      </c>
+      <c r="B259" t="str">
+        <v>toKm</v>
+      </c>
+      <c r="C259" t="str">
+        <v>To Km</v>
+      </c>
+      <c r="D259" t="str">
+        <v>number</v>
+      </c>
+      <c r="E259" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F259" t="str">
+        <v/>
+      </c>
+      <c r="G259">
+        <v>0</v>
+      </c>
+      <c r="H259">
+        <v>999999</v>
+      </c>
+      <c r="I259" t="str">
+        <v/>
+      </c>
+      <c r="J259" t="str">
+        <v/>
+      </c>
+      <c r="K259" t="str">
+        <v/>
+      </c>
+      <c r="L259" t="str">
+        <v/>
+      </c>
+      <c r="M259" t="str">
+        <v>N</v>
+      </c>
+      <c r="N259" t="str">
+        <v/>
+      </c>
+      <c r="O259" t="str">
+        <v/>
+      </c>
+      <c r="P259" t="str">
+        <v/>
+      </c>
+      <c r="Q259" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>thd_kms_range</v>
+      </c>
+      <c r="B260" t="str">
+        <v>status</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D260" t="str">
+        <v>select</v>
+      </c>
+      <c r="E260" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F260" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G260" t="str">
+        <v/>
+      </c>
+      <c r="H260" t="str">
+        <v/>
+      </c>
+      <c r="I260" t="str">
+        <v/>
+      </c>
+      <c r="J260" t="str">
+        <v/>
+      </c>
+      <c r="K260" t="str">
+        <v/>
+      </c>
+      <c r="L260" t="str">
+        <v/>
+      </c>
+      <c r="M260" t="str">
+        <v>N</v>
+      </c>
+      <c r="N260" t="str">
+        <v/>
+      </c>
+      <c r="O260" t="str">
+        <v/>
+      </c>
+      <c r="P260" t="str">
+        <v/>
+      </c>
+      <c r="Q260" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>thd_vehicle_age</v>
+      </c>
+      <c r="B261" t="str">
+        <v>label</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Age (In Years)</v>
+      </c>
+      <c r="D261" t="str">
+        <v>text</v>
+      </c>
+      <c r="E261" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F261" t="str">
+        <v/>
+      </c>
+      <c r="G261" t="str">
+        <v/>
+      </c>
+      <c r="H261" t="str">
+        <v/>
+      </c>
+      <c r="I261" t="str">
+        <v/>
+      </c>
+      <c r="J261" t="str">
+        <v/>
+      </c>
+      <c r="K261" t="str">
+        <v/>
+      </c>
+      <c r="L261" t="str">
+        <v/>
+      </c>
+      <c r="M261" t="str">
+        <v>N</v>
+      </c>
+      <c r="N261" t="str">
+        <v/>
+      </c>
+      <c r="O261" t="str">
+        <v/>
+      </c>
+      <c r="P261" t="str">
+        <v/>
+      </c>
+      <c r="Q261" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>thd_vehicle_age</v>
+      </c>
+      <c r="B262" t="str">
+        <v>fromYears</v>
+      </c>
+      <c r="C262" t="str">
+        <v>From (Years)</v>
+      </c>
+      <c r="D262" t="str">
+        <v>number</v>
+      </c>
+      <c r="E262" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F262" t="str">
+        <v/>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="H262">
+        <v>50</v>
+      </c>
+      <c r="I262" t="str">
+        <v/>
+      </c>
+      <c r="J262" t="str">
+        <v/>
+      </c>
+      <c r="K262" t="str">
+        <v/>
+      </c>
+      <c r="L262" t="str">
+        <v/>
+      </c>
+      <c r="M262" t="str">
+        <v>N</v>
+      </c>
+      <c r="N262" t="str">
+        <v/>
+      </c>
+      <c r="O262" t="str">
+        <v/>
+      </c>
+      <c r="P262" t="str">
+        <v/>
+      </c>
+      <c r="Q262" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>thd_vehicle_age</v>
+      </c>
+      <c r="B263" t="str">
+        <v>toYears</v>
+      </c>
+      <c r="C263" t="str">
+        <v>To (Years)</v>
+      </c>
+      <c r="D263" t="str">
+        <v>number</v>
+      </c>
+      <c r="E263" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F263" t="str">
+        <v/>
+      </c>
+      <c r="G263">
+        <v>0</v>
+      </c>
+      <c r="H263">
+        <v>50</v>
+      </c>
+      <c r="I263" t="str">
+        <v/>
+      </c>
+      <c r="J263" t="str">
+        <v/>
+      </c>
+      <c r="K263" t="str">
+        <v/>
+      </c>
+      <c r="L263" t="str">
+        <v/>
+      </c>
+      <c r="M263" t="str">
+        <v>N</v>
+      </c>
+      <c r="N263" t="str">
+        <v/>
+      </c>
+      <c r="O263" t="str">
+        <v/>
+      </c>
+      <c r="P263" t="str">
+        <v/>
+      </c>
+      <c r="Q263" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>thd_vehicle_age</v>
+      </c>
+      <c r="B264" t="str">
+        <v>status</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D264" t="str">
+        <v>select</v>
+      </c>
+      <c r="E264" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F264" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G264" t="str">
+        <v/>
+      </c>
+      <c r="H264" t="str">
+        <v/>
+      </c>
+      <c r="I264" t="str">
+        <v/>
+      </c>
+      <c r="J264" t="str">
+        <v/>
+      </c>
+      <c r="K264" t="str">
+        <v/>
+      </c>
+      <c r="L264" t="str">
+        <v/>
+      </c>
+      <c r="M264" t="str">
+        <v>N</v>
+      </c>
+      <c r="N264" t="str">
+        <v/>
+      </c>
+      <c r="O264" t="str">
+        <v/>
+      </c>
+      <c r="P264" t="str">
+        <v/>
+      </c>
+      <c r="Q264" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B265" t="str">
+        <v>role</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Role</v>
+      </c>
+      <c r="D265" t="str">
+        <v>select</v>
+      </c>
+      <c r="E265" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F265" t="str">
+        <v>Tech Executive L1, RTSM, COC L2, Plant, Product Reliability</v>
+      </c>
+      <c r="G265" t="str">
+        <v/>
+      </c>
+      <c r="H265" t="str">
+        <v/>
+      </c>
+      <c r="I265" t="str">
+        <v/>
+      </c>
+      <c r="J265" t="str">
+        <v/>
+      </c>
+      <c r="K265" t="str">
+        <v/>
+      </c>
+      <c r="L265" t="str">
+        <v/>
+      </c>
+      <c r="M265" t="str">
+        <v>N</v>
+      </c>
+      <c r="N265" t="str">
+        <v/>
+      </c>
+      <c r="O265" t="str">
+        <v/>
+      </c>
+      <c r="P265" t="str">
+        <v/>
+      </c>
+      <c r="Q265" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B266" t="str">
+        <v>bu</v>
+      </c>
+      <c r="C266" t="str">
+        <v>BU</v>
+      </c>
+      <c r="D266" t="str">
+        <v>select</v>
+      </c>
+      <c r="E266" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F266" t="str">
+        <v>PV, EV</v>
+      </c>
+      <c r="G266" t="str">
+        <v/>
+      </c>
+      <c r="H266" t="str">
+        <v/>
+      </c>
+      <c r="I266" t="str">
+        <v/>
+      </c>
+      <c r="J266" t="str">
+        <v/>
+      </c>
+      <c r="K266" t="str">
+        <v/>
+      </c>
+      <c r="L266" t="str">
+        <v/>
+      </c>
+      <c r="M266" t="str">
+        <v>N</v>
+      </c>
+      <c r="N266" t="str">
+        <v/>
+      </c>
+      <c r="O266" t="str">
+        <v/>
+      </c>
+      <c r="P266" t="str">
+        <v/>
+      </c>
+      <c r="Q266" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B267" t="str">
+        <v>userName</v>
+      </c>
+      <c r="C267" t="str">
+        <v>User Name</v>
+      </c>
+      <c r="D267" t="str">
+        <v>text</v>
+      </c>
+      <c r="E267" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F267" t="str">
+        <v/>
+      </c>
+      <c r="G267" t="str">
+        <v/>
+      </c>
+      <c r="H267" t="str">
+        <v/>
+      </c>
+      <c r="I267" t="str">
+        <v/>
+      </c>
+      <c r="J267" t="str">
+        <v/>
+      </c>
+      <c r="K267" t="str">
+        <v/>
+      </c>
+      <c r="L267" t="str">
+        <v/>
+      </c>
+      <c r="M267" t="str">
+        <v>N</v>
+      </c>
+      <c r="N267" t="str">
+        <v/>
+      </c>
+      <c r="O267" t="str">
+        <v/>
+      </c>
+      <c r="P267" t="str">
+        <v/>
+      </c>
+      <c r="Q267" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B268" t="str">
+        <v>plantName</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Plant Name</v>
+      </c>
+      <c r="D268" t="str">
+        <v>text</v>
+      </c>
+      <c r="E268" t="str">
+        <v>N</v>
+      </c>
+      <c r="F268" t="str">
+        <v/>
+      </c>
+      <c r="G268" t="str">
+        <v/>
+      </c>
+      <c r="H268" t="str">
+        <v/>
+      </c>
+      <c r="I268" t="str">
+        <v/>
+      </c>
+      <c r="J268" t="str">
+        <v/>
+      </c>
+      <c r="K268" t="str">
+        <v/>
+      </c>
+      <c r="L268" t="str">
+        <v/>
+      </c>
+      <c r="M268" t="str">
+        <v>N</v>
+      </c>
+      <c r="N268" t="str">
+        <v/>
+      </c>
+      <c r="O268" t="str">
+        <v/>
+      </c>
+      <c r="P268" t="str">
+        <v/>
+      </c>
+      <c r="Q268" t="str">
+        <v>Required for Plant users.</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B269" t="str">
+        <v>zone</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Zone</v>
+      </c>
+      <c r="D269" t="str">
+        <v>text</v>
+      </c>
+      <c r="E269" t="str">
+        <v>N</v>
+      </c>
+      <c r="F269" t="str">
+        <v/>
+      </c>
+      <c r="G269" t="str">
+        <v/>
+      </c>
+      <c r="H269" t="str">
+        <v/>
+      </c>
+      <c r="I269" t="str">
+        <v/>
+      </c>
+      <c r="J269" t="str">
+        <v/>
+      </c>
+      <c r="K269" t="str">
+        <v/>
+      </c>
+      <c r="L269" t="str">
+        <v/>
+      </c>
+      <c r="M269" t="str">
+        <v>N</v>
+      </c>
+      <c r="N269" t="str">
+        <v/>
+      </c>
+      <c r="O269" t="str">
+        <v/>
+      </c>
+      <c r="P269" t="str">
+        <v/>
+      </c>
+      <c r="Q269" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B270" t="str">
+        <v>region</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Region</v>
+      </c>
+      <c r="D270" t="str">
+        <v>text</v>
+      </c>
+      <c r="E270" t="str">
+        <v>N</v>
+      </c>
+      <c r="F270" t="str">
+        <v/>
+      </c>
+      <c r="G270" t="str">
+        <v/>
+      </c>
+      <c r="H270" t="str">
+        <v/>
+      </c>
+      <c r="I270" t="str">
+        <v/>
+      </c>
+      <c r="J270" t="str">
+        <v/>
+      </c>
+      <c r="K270" t="str">
+        <v/>
+      </c>
+      <c r="L270" t="str">
+        <v/>
+      </c>
+      <c r="M270" t="str">
+        <v>N</v>
+      </c>
+      <c r="N270" t="str">
+        <v/>
+      </c>
+      <c r="O270" t="str">
+        <v/>
+      </c>
+      <c r="P270" t="str">
+        <v/>
+      </c>
+      <c r="Q270" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B271" t="str">
+        <v>crmUserId</v>
+      </c>
+      <c r="C271" t="str">
+        <v>CRM User ID</v>
+      </c>
+      <c r="D271" t="str">
+        <v>text</v>
+      </c>
+      <c r="E271" t="str">
+        <v>N</v>
+      </c>
+      <c r="F271" t="str">
+        <v/>
+      </c>
+      <c r="G271" t="str">
+        <v/>
+      </c>
+      <c r="H271" t="str">
+        <v/>
+      </c>
+      <c r="I271" t="str">
+        <v/>
+      </c>
+      <c r="J271" t="str">
+        <v/>
+      </c>
+      <c r="K271" t="str">
+        <v/>
+      </c>
+      <c r="L271" t="str">
+        <v/>
+      </c>
+      <c r="M271" t="str">
+        <v>N</v>
+      </c>
+      <c r="N271" t="str">
+        <v/>
+      </c>
+      <c r="O271" t="str">
+        <v/>
+      </c>
+      <c r="P271" t="str">
+        <v/>
+      </c>
+      <c r="Q271" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B272" t="str">
+        <v>aggregate</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Aggregate</v>
+      </c>
+      <c r="D272" t="str">
+        <v>text</v>
+      </c>
+      <c r="E272" t="str">
+        <v>N</v>
+      </c>
+      <c r="F272" t="str">
+        <v/>
+      </c>
+      <c r="G272" t="str">
+        <v/>
+      </c>
+      <c r="H272" t="str">
+        <v/>
+      </c>
+      <c r="I272" t="str">
+        <v/>
+      </c>
+      <c r="J272" t="str">
+        <v/>
+      </c>
+      <c r="K272" t="str">
+        <v/>
+      </c>
+      <c r="L272" t="str">
+        <v/>
+      </c>
+      <c r="M272" t="str">
+        <v>N</v>
+      </c>
+      <c r="N272" t="str">
+        <v/>
+      </c>
+      <c r="O272" t="str">
+        <v/>
+      </c>
+      <c r="P272" t="str">
+        <v/>
+      </c>
+      <c r="Q272" t="str">
+        <v>COC L2 and Plant users can be limited to one aggregate.</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>thd_users</v>
+      </c>
+      <c r="B273" t="str">
+        <v>status</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D273" t="str">
+        <v>select</v>
+      </c>
+      <c r="E273" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F273" t="str">
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G273" t="str">
+        <v/>
+      </c>
+      <c r="H273" t="str">
+        <v/>
+      </c>
+      <c r="I273" t="str">
+        <v/>
+      </c>
+      <c r="J273" t="str">
+        <v/>
+      </c>
+      <c r="K273" t="str">
+        <v/>
+      </c>
+      <c r="L273" t="str">
+        <v/>
+      </c>
+      <c r="M273" t="str">
+        <v>N</v>
+      </c>
+      <c r="N273" t="str">
+        <v/>
+      </c>
+      <c r="O273" t="str">
+        <v/>
+      </c>
+      <c r="P273" t="str">
+        <v/>
+      </c>
+      <c r="Q273" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B274" t="str">
+        <v>driverCode</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Driver Code</v>
+      </c>
+      <c r="D274" t="str">
+        <v>text</v>
+      </c>
+      <c r="E274" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F274" t="str">
+        <v/>
+      </c>
+      <c r="G274" t="str">
+        <v/>
+      </c>
+      <c r="H274" t="str">
+        <v/>
+      </c>
+      <c r="I274" t="str">
+        <v/>
+      </c>
+      <c r="J274" t="str">
+        <v/>
+      </c>
+      <c r="K274" t="str">
+        <v/>
+      </c>
+      <c r="L274" t="str">
+        <v/>
+      </c>
+      <c r="M274" t="str">
+        <v>N</v>
+      </c>
+      <c r="N274" t="str">
+        <v/>
+      </c>
+      <c r="O274" t="str">
+        <v/>
+      </c>
+      <c r="P274" t="str">
+        <v/>
+      </c>
+      <c r="Q274" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B275" t="str">
+        <v>driverName</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Driver Full Name</v>
+      </c>
+      <c r="D275" t="str">
+        <v>text</v>
+      </c>
+      <c r="E275" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F275" t="str">
+        <v/>
+      </c>
+      <c r="G275" t="str">
+        <v/>
+      </c>
+      <c r="H275" t="str">
+        <v/>
+      </c>
+      <c r="I275" t="str">
+        <v/>
+      </c>
+      <c r="J275" t="str">
+        <v/>
+      </c>
+      <c r="K275" t="str">
+        <v/>
+      </c>
+      <c r="L275" t="str">
+        <v/>
+      </c>
+      <c r="M275" t="str">
+        <v>N</v>
+      </c>
+      <c r="N275" t="str">
+        <v/>
+      </c>
+      <c r="O275" t="str">
+        <v/>
+      </c>
+      <c r="P275" t="str">
+        <v/>
+      </c>
+      <c r="Q275" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B276" t="str">
+        <v>assignedZone</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Assigned Territory Zone</v>
+      </c>
+      <c r="D276" t="str">
+        <v>select</v>
+      </c>
+      <c r="E276" t="str">
+        <v>N</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Zone A - Hitec City, Zone B - Secunderabad, Zone C - Gachibowli, Zone D - Banjara Hills</v>
+      </c>
+      <c r="G276" t="str">
+        <v/>
+      </c>
+      <c r="H276" t="str">
+        <v/>
+      </c>
+      <c r="I276" t="str">
+        <v/>
+      </c>
+      <c r="J276" t="str">
+        <v/>
+      </c>
+      <c r="K276" t="str">
+        <v/>
+      </c>
+      <c r="L276" t="str">
+        <v/>
+      </c>
+      <c r="M276" t="str">
+        <v>N</v>
+      </c>
+      <c r="N276" t="str">
+        <v/>
+      </c>
+      <c r="O276" t="str">
+        <v/>
+      </c>
+      <c r="P276" t="str">
+        <v/>
+      </c>
+      <c r="Q276" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B277" t="str">
+        <v>licenseNumber</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Commercial DL Number</v>
+      </c>
+      <c r="D277" t="str">
+        <v>text</v>
+      </c>
+      <c r="E277" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F277" t="str">
+        <v/>
+      </c>
+      <c r="G277" t="str">
+        <v/>
+      </c>
+      <c r="H277" t="str">
+        <v/>
+      </c>
+      <c r="I277" t="str">
+        <v/>
+      </c>
+      <c r="J277" t="str">
+        <v/>
+      </c>
+      <c r="K277" t="str">
+        <v/>
+      </c>
+      <c r="L277" t="str">
+        <v/>
+      </c>
+      <c r="M277" t="str">
+        <v>N</v>
+      </c>
+      <c r="N277" t="str">
+        <v/>
+      </c>
+      <c r="O277" t="str">
+        <v/>
+      </c>
+      <c r="P277" t="str">
+        <v/>
+      </c>
+      <c r="Q277" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B278" t="str">
+        <v>evCertified</v>
+      </c>
+      <c r="C278" t="str">
+        <v>EV Transit Certified</v>
+      </c>
+      <c r="D278" t="str">
+        <v>select</v>
+      </c>
+      <c r="E278" t="str">
+        <v>N</v>
+      </c>
+      <c r="F278" t="str">
         <v>Y, N</v>
       </c>
-      <c r="G234" t="str">
-        <v/>
-      </c>
-      <c r="H234" t="str">
-        <v/>
-      </c>
-      <c r="I234" t="str">
-        <v/>
-      </c>
-      <c r="J234" t="str">
-        <v/>
-      </c>
-      <c r="K234" t="str">
-        <v/>
-      </c>
-      <c r="L234" t="str">
-        <v/>
-      </c>
-      <c r="M234" t="str">
-        <v>N</v>
-      </c>
-      <c r="N234" t="str">
-        <v/>
-      </c>
-      <c r="O234" t="str">
-        <v/>
-      </c>
-      <c r="P234" t="str">
-        <v/>
-      </c>
-      <c r="Q234" t="str">
+      <c r="G278" t="str">
+        <v/>
+      </c>
+      <c r="H278" t="str">
+        <v/>
+      </c>
+      <c r="I278" t="str">
+        <v/>
+      </c>
+      <c r="J278" t="str">
+        <v/>
+      </c>
+      <c r="K278" t="str">
+        <v/>
+      </c>
+      <c r="L278" t="str">
+        <v/>
+      </c>
+      <c r="M278" t="str">
+        <v>N</v>
+      </c>
+      <c r="N278" t="str">
+        <v/>
+      </c>
+      <c r="O278" t="str">
+        <v/>
+      </c>
+      <c r="P278" t="str">
+        <v/>
+      </c>
+      <c r="Q278" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>driver_transit_roster</v>
+      </c>
+      <c r="B279" t="str">
+        <v>active</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D279" t="str">
+        <v>select</v>
+      </c>
+      <c r="E279" t="str">
+        <v>N</v>
+      </c>
+      <c r="F279" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G279" t="str">
+        <v/>
+      </c>
+      <c r="H279" t="str">
+        <v/>
+      </c>
+      <c r="I279" t="str">
+        <v/>
+      </c>
+      <c r="J279" t="str">
+        <v/>
+      </c>
+      <c r="K279" t="str">
+        <v/>
+      </c>
+      <c r="L279" t="str">
+        <v/>
+      </c>
+      <c r="M279" t="str">
+        <v>N</v>
+      </c>
+      <c r="N279" t="str">
+        <v/>
+      </c>
+      <c r="O279" t="str">
+        <v/>
+      </c>
+      <c r="P279" t="str">
+        <v/>
+      </c>
+      <c r="Q279" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B280" t="str">
+        <v>checkpointCode</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Checkpoint Code</v>
+      </c>
+      <c r="D280" t="str">
+        <v>text</v>
+      </c>
+      <c r="E280" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F280" t="str">
+        <v/>
+      </c>
+      <c r="G280" t="str">
+        <v/>
+      </c>
+      <c r="H280" t="str">
+        <v/>
+      </c>
+      <c r="I280" t="str">
+        <v/>
+      </c>
+      <c r="J280" t="str">
+        <v/>
+      </c>
+      <c r="K280" t="str">
+        <v/>
+      </c>
+      <c r="L280" t="str">
+        <v/>
+      </c>
+      <c r="M280" t="str">
+        <v>N</v>
+      </c>
+      <c r="N280" t="str">
+        <v/>
+      </c>
+      <c r="O280" t="str">
+        <v/>
+      </c>
+      <c r="P280" t="str">
+        <v/>
+      </c>
+      <c r="Q280" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B281" t="str">
+        <v>checkpointDesc</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Reception Standard Requirement</v>
+      </c>
+      <c r="D281" t="str">
+        <v>text</v>
+      </c>
+      <c r="E281" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F281" t="str">
+        <v/>
+      </c>
+      <c r="G281" t="str">
+        <v/>
+      </c>
+      <c r="H281" t="str">
+        <v/>
+      </c>
+      <c r="I281" t="str">
+        <v/>
+      </c>
+      <c r="J281" t="str">
+        <v/>
+      </c>
+      <c r="K281" t="str">
+        <v/>
+      </c>
+      <c r="L281" t="str">
+        <v/>
+      </c>
+      <c r="M281" t="str">
+        <v>N</v>
+      </c>
+      <c r="N281" t="str">
+        <v/>
+      </c>
+      <c r="O281" t="str">
+        <v/>
+      </c>
+      <c r="P281" t="str">
+        <v/>
+      </c>
+      <c r="Q281" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B282" t="str">
+        <v>channel</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Intake Channel</v>
+      </c>
+      <c r="D282" t="str">
+        <v>select</v>
+      </c>
+      <c r="E282" t="str">
+        <v>N</v>
+      </c>
+      <c r="F282" t="str">
+        <v>Walk-in, Pre-Booked Appointment, Express Valet, Breakdown Flatbed</v>
+      </c>
+      <c r="G282" t="str">
+        <v/>
+      </c>
+      <c r="H282" t="str">
+        <v/>
+      </c>
+      <c r="I282" t="str">
+        <v/>
+      </c>
+      <c r="J282" t="str">
+        <v/>
+      </c>
+      <c r="K282" t="str">
+        <v/>
+      </c>
+      <c r="L282" t="str">
+        <v/>
+      </c>
+      <c r="M282" t="str">
+        <v>N</v>
+      </c>
+      <c r="N282" t="str">
+        <v/>
+      </c>
+      <c r="O282" t="str">
+        <v/>
+      </c>
+      <c r="P282" t="str">
+        <v/>
+      </c>
+      <c r="Q282" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B283" t="str">
+        <v>mandatoryProof</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Mandatory Photo / Signature</v>
+      </c>
+      <c r="D283" t="str">
+        <v>select</v>
+      </c>
+      <c r="E283" t="str">
+        <v>N</v>
+      </c>
+      <c r="F283" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G283" t="str">
+        <v/>
+      </c>
+      <c r="H283" t="str">
+        <v/>
+      </c>
+      <c r="I283" t="str">
+        <v/>
+      </c>
+      <c r="J283" t="str">
+        <v/>
+      </c>
+      <c r="K283" t="str">
+        <v/>
+      </c>
+      <c r="L283" t="str">
+        <v/>
+      </c>
+      <c r="M283" t="str">
+        <v>N</v>
+      </c>
+      <c r="N283" t="str">
+        <v/>
+      </c>
+      <c r="O283" t="str">
+        <v/>
+      </c>
+      <c r="P283" t="str">
+        <v/>
+      </c>
+      <c r="Q283" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>lounge_reception_checklist</v>
+      </c>
+      <c r="B284" t="str">
+        <v>active</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D284" t="str">
+        <v>select</v>
+      </c>
+      <c r="E284" t="str">
+        <v>N</v>
+      </c>
+      <c r="F284" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G284" t="str">
+        <v/>
+      </c>
+      <c r="H284" t="str">
+        <v/>
+      </c>
+      <c r="I284" t="str">
+        <v/>
+      </c>
+      <c r="J284" t="str">
+        <v/>
+      </c>
+      <c r="K284" t="str">
+        <v/>
+      </c>
+      <c r="L284" t="str">
+        <v/>
+      </c>
+      <c r="M284" t="str">
+        <v>N</v>
+      </c>
+      <c r="N284" t="str">
+        <v/>
+      </c>
+      <c r="O284" t="str">
+        <v/>
+      </c>
+      <c r="P284" t="str">
+        <v/>
+      </c>
+      <c r="Q284" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B285" t="str">
+        <v>ruleId</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Gate Rule Code</v>
+      </c>
+      <c r="D285" t="str">
+        <v>text</v>
+      </c>
+      <c r="E285" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F285" t="str">
+        <v/>
+      </c>
+      <c r="G285" t="str">
+        <v/>
+      </c>
+      <c r="H285" t="str">
+        <v/>
+      </c>
+      <c r="I285" t="str">
+        <v/>
+      </c>
+      <c r="J285" t="str">
+        <v/>
+      </c>
+      <c r="K285" t="str">
+        <v/>
+      </c>
+      <c r="L285" t="str">
+        <v/>
+      </c>
+      <c r="M285" t="str">
+        <v>N</v>
+      </c>
+      <c r="N285" t="str">
+        <v/>
+      </c>
+      <c r="O285" t="str">
+        <v/>
+      </c>
+      <c r="P285" t="str">
+        <v/>
+      </c>
+      <c r="Q285" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B286" t="str">
+        <v>direction</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Movement Direction</v>
+      </c>
+      <c r="D286" t="str">
+        <v>select</v>
+      </c>
+      <c r="E286" t="str">
+        <v>N</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Inward (Check-in), Outward (Check-out), Internal Bay Transit</v>
+      </c>
+      <c r="G286" t="str">
+        <v/>
+      </c>
+      <c r="H286" t="str">
+        <v/>
+      </c>
+      <c r="I286" t="str">
+        <v/>
+      </c>
+      <c r="J286" t="str">
+        <v/>
+      </c>
+      <c r="K286" t="str">
+        <v/>
+      </c>
+      <c r="L286" t="str">
+        <v/>
+      </c>
+      <c r="M286" t="str">
+        <v>N</v>
+      </c>
+      <c r="N286" t="str">
+        <v/>
+      </c>
+      <c r="O286" t="str">
+        <v/>
+      </c>
+      <c r="P286" t="str">
+        <v/>
+      </c>
+      <c r="Q286" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B287" t="str">
+        <v>verificationItem</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Verification Protocol</v>
+      </c>
+      <c r="D287" t="str">
+        <v>text</v>
+      </c>
+      <c r="E287" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F287" t="str">
+        <v/>
+      </c>
+      <c r="G287" t="str">
+        <v/>
+      </c>
+      <c r="H287" t="str">
+        <v/>
+      </c>
+      <c r="I287" t="str">
+        <v/>
+      </c>
+      <c r="J287" t="str">
+        <v/>
+      </c>
+      <c r="K287" t="str">
+        <v/>
+      </c>
+      <c r="L287" t="str">
+        <v/>
+      </c>
+      <c r="M287" t="str">
+        <v>N</v>
+      </c>
+      <c r="N287" t="str">
+        <v/>
+      </c>
+      <c r="O287" t="str">
+        <v/>
+      </c>
+      <c r="P287" t="str">
+        <v/>
+      </c>
+      <c r="Q287" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B288" t="str">
+        <v>anprSync</v>
+      </c>
+      <c r="C288" t="str">
+        <v>ANPR Camera Auto-Verify</v>
+      </c>
+      <c r="D288" t="str">
+        <v>select</v>
+      </c>
+      <c r="E288" t="str">
+        <v>N</v>
+      </c>
+      <c r="F288" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G288" t="str">
+        <v/>
+      </c>
+      <c r="H288" t="str">
+        <v/>
+      </c>
+      <c r="I288" t="str">
+        <v/>
+      </c>
+      <c r="J288" t="str">
+        <v/>
+      </c>
+      <c r="K288" t="str">
+        <v/>
+      </c>
+      <c r="L288" t="str">
+        <v/>
+      </c>
+      <c r="M288" t="str">
+        <v>N</v>
+      </c>
+      <c r="N288" t="str">
+        <v/>
+      </c>
+      <c r="O288" t="str">
+        <v/>
+      </c>
+      <c r="P288" t="str">
+        <v/>
+      </c>
+      <c r="Q288" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>gate_security_checklist</v>
+      </c>
+      <c r="B289" t="str">
+        <v>active</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D289" t="str">
+        <v>select</v>
+      </c>
+      <c r="E289" t="str">
+        <v>N</v>
+      </c>
+      <c r="F289" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G289" t="str">
+        <v/>
+      </c>
+      <c r="H289" t="str">
+        <v/>
+      </c>
+      <c r="I289" t="str">
+        <v/>
+      </c>
+      <c r="J289" t="str">
+        <v/>
+      </c>
+      <c r="K289" t="str">
+        <v/>
+      </c>
+      <c r="L289" t="str">
+        <v/>
+      </c>
+      <c r="M289" t="str">
+        <v>N</v>
+      </c>
+      <c r="N289" t="str">
+        <v/>
+      </c>
+      <c r="O289" t="str">
+        <v/>
+      </c>
+      <c r="P289" t="str">
+        <v/>
+      </c>
+      <c r="Q289" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B290" t="str">
+        <v>denialCode</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Denial Code</v>
+      </c>
+      <c r="D290" t="str">
+        <v>text</v>
+      </c>
+      <c r="E290" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F290" t="str">
+        <v/>
+      </c>
+      <c r="G290" t="str">
+        <v/>
+      </c>
+      <c r="H290" t="str">
+        <v/>
+      </c>
+      <c r="I290" t="str">
+        <v/>
+      </c>
+      <c r="J290" t="str">
+        <v/>
+      </c>
+      <c r="K290" t="str">
+        <v/>
+      </c>
+      <c r="L290" t="str">
+        <v/>
+      </c>
+      <c r="M290" t="str">
+        <v>N</v>
+      </c>
+      <c r="N290" t="str">
+        <v/>
+      </c>
+      <c r="O290" t="str">
+        <v/>
+      </c>
+      <c r="P290" t="str">
+        <v/>
+      </c>
+      <c r="Q290" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B291" t="str">
+        <v>reason</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Security Denial / Hold Reason</v>
+      </c>
+      <c r="D291" t="str">
+        <v>text</v>
+      </c>
+      <c r="E291" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F291" t="str">
+        <v/>
+      </c>
+      <c r="G291" t="str">
+        <v/>
+      </c>
+      <c r="H291" t="str">
+        <v/>
+      </c>
+      <c r="I291" t="str">
+        <v/>
+      </c>
+      <c r="J291" t="str">
+        <v/>
+      </c>
+      <c r="K291" t="str">
+        <v/>
+      </c>
+      <c r="L291" t="str">
+        <v/>
+      </c>
+      <c r="M291" t="str">
+        <v>N</v>
+      </c>
+      <c r="N291" t="str">
+        <v/>
+      </c>
+      <c r="O291" t="str">
+        <v/>
+      </c>
+      <c r="P291" t="str">
+        <v/>
+      </c>
+      <c r="Q291" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B292" t="str">
+        <v>escalateTo</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Immediate Notification Target</v>
+      </c>
+      <c r="D292" t="str">
+        <v>select</v>
+      </c>
+      <c r="E292" t="str">
+        <v>N</v>
+      </c>
+      <c r="F292" t="str">
+        <v>Works Manager, Security Officer In-Charge, Service Head, Customer Relation Manager</v>
+      </c>
+      <c r="G292" t="str">
+        <v/>
+      </c>
+      <c r="H292" t="str">
+        <v/>
+      </c>
+      <c r="I292" t="str">
+        <v/>
+      </c>
+      <c r="J292" t="str">
+        <v/>
+      </c>
+      <c r="K292" t="str">
+        <v/>
+      </c>
+      <c r="L292" t="str">
+        <v/>
+      </c>
+      <c r="M292" t="str">
+        <v>N</v>
+      </c>
+      <c r="N292" t="str">
+        <v/>
+      </c>
+      <c r="O292" t="str">
+        <v/>
+      </c>
+      <c r="P292" t="str">
+        <v/>
+      </c>
+      <c r="Q292" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B293" t="str">
+        <v>active</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D293" t="str">
+        <v>select</v>
+      </c>
+      <c r="E293" t="str">
+        <v>N</v>
+      </c>
+      <c r="F293" t="str">
+        <v>Y, N</v>
+      </c>
+      <c r="G293" t="str">
+        <v/>
+      </c>
+      <c r="H293" t="str">
+        <v/>
+      </c>
+      <c r="I293" t="str">
+        <v/>
+      </c>
+      <c r="J293" t="str">
+        <v/>
+      </c>
+      <c r="K293" t="str">
+        <v/>
+      </c>
+      <c r="L293" t="str">
+        <v/>
+      </c>
+      <c r="M293" t="str">
+        <v>N</v>
+      </c>
+      <c r="N293" t="str">
+        <v/>
+      </c>
+      <c r="O293" t="str">
+        <v/>
+      </c>
+      <c r="P293" t="str">
+        <v/>
+      </c>
+      <c r="Q293" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q234"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q293"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18157,384 +21596,825 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>driverCode</v>
+        <v>ruleNo</v>
       </c>
       <c r="C1" t="str">
-        <v>driverName</v>
+        <v>scenarioCode</v>
       </c>
       <c r="D1" t="str">
-        <v>assignedZone</v>
+        <v>businessCondition</v>
       </c>
       <c r="E1" t="str">
-        <v>licenseNumber</v>
+        <v>triggerPoint</v>
       </c>
       <c r="F1" t="str">
-        <v>evCertified</v>
+        <v>windowValue</v>
       </c>
       <c r="G1" t="str">
-        <v>active</v>
+        <v>windowUnit</v>
+      </c>
+      <c r="H1" t="str">
+        <v>triggerValues</v>
+      </c>
+      <c r="I1" t="str">
+        <v>escalationComplaint</v>
+      </c>
+      <c r="J1" t="str">
+        <v>thdTag</v>
+      </c>
+      <c r="K1" t="str">
+        <v>assignedTo</v>
+      </c>
+      <c r="L1" t="str">
+        <v>status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DRV-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>DRV-HYD-101</v>
+        <v>THDR-01</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>Nageshwar Rao</v>
+        <v>REPEAT_COMPLAINT</v>
       </c>
       <c r="D2" t="str">
-        <v>Zone A - Hitec City</v>
+        <v>Vehicle returns within 30 days of the previous Job Card closure and a complaint code in the new Job Card has the same Aggregate as one in the previous Job Card.</v>
       </c>
       <c r="E2" t="str">
-        <v>TS09-2019-0023412</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
+        <v>Job Card Creation</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
       </c>
       <c r="G2" t="str">
-        <v>Y</v>
+        <v>Days</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>Yes/No</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Repeat Complaint / Escalation</v>
+      </c>
+      <c r="K2" t="str">
+        <v>DET</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Active</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DRV-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>DRV-HYD-102</v>
+        <v>THDR-02</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>Mohd Feroz Khan</v>
+        <v>CRITICAL_AT_JC_CREATION</v>
       </c>
       <c r="D3" t="str">
-        <v>Zone B - Secunderabad</v>
+        <v>A Critical Complaint (PPL-CC list) is added in the Job Card.</v>
       </c>
       <c r="E3" t="str">
-        <v>TS10-2018-0056123</v>
+        <v>Job Card Creation</v>
       </c>
       <c r="F3" t="str">
-        <v>N</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>Y</v>
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Yes/No</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Critical / Escalation</v>
+      </c>
+      <c r="K3" t="str">
+        <v>DET</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Active</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>DRV-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>DRV-HYD-103</v>
+        <v>THDR-03</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>Pradeep Patil</v>
+        <v>CRITICAL_AFTER_JC_CREATION</v>
       </c>
       <c r="D4" t="str">
-        <v>Zone C - Gachibowli</v>
+        <v>A Critical Complaint is added after the Job Card was created; the case is raised "X" hours after it was added.</v>
       </c>
       <c r="E4" t="str">
-        <v>TS09-2021-0089145</v>
+        <v>Open Job Card</v>
       </c>
       <c r="F4" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>Y</v>
+        <v>Hours</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>No</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Critical</v>
+      </c>
+      <c r="K4" t="str">
+        <v>DET</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>THDR-04</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="str">
+        <v>DELAY_REASON</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Job Card stays Open for more than "Y" hours with one of these delay reasons recorded.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Job Card Closure</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>Hours</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Delayed Diagnosis, Under Investigation</v>
+      </c>
+      <c r="I5" t="str">
+        <v>No</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Delayed</v>
+      </c>
+      <c r="K5" t="str">
+        <v>DET</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>THDR-05</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="str">
+        <v>QI_THD_REQUIRED</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Quality Inspector marks "THD Required" in Pre-Quality Inspection while the Job Card is Open.</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Job Card Creation</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>No</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Quality Inspection</v>
+      </c>
+      <c r="K6" t="str">
+        <v>DET</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>THDR-06</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="str">
+        <v>OPEN_ESCALATION</v>
+      </c>
+      <c r="D7" t="str">
+        <v>An open escalated complaint exists against the chassis at Job Card creation.</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Job Card Creation</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Escalated</v>
+      </c>
+      <c r="K7" t="str">
+        <v>DET</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>THDR-07</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="str">
+        <v>CRITICAL_DTC</v>
+      </c>
+      <c r="D8" t="str">
+        <v>A critical DTC is received from the Connected Cloud platform for the vehicle.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Job Card Creation</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>NA</v>
+      </c>
+      <c r="J8" t="str">
+        <v>DTC</v>
+      </c>
+      <c r="K8" t="str">
+        <v>DET</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>THDR-08</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="str">
+        <v>THD_UNATTENDED</v>
+      </c>
+      <c r="D9" t="str">
+        <v>A THD case stays unattended by DET for more than 24 hours from creation; an auto request goes to Tech Executive L1.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>THD Age</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Hours</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Yes/No</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Any tag</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Tech Executive L1</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Active</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>checkpointCode</v>
+        <v>ppl</v>
       </c>
       <c r="C1" t="str">
-        <v>checkpointDesc</v>
+        <v>complaintCode</v>
       </c>
       <c r="D1" t="str">
-        <v>channel</v>
+        <v>complaintDescription</v>
       </c>
       <c r="E1" t="str">
-        <v>mandatoryProof</v>
+        <v>aggregate</v>
       </c>
       <c r="F1" t="str">
-        <v>active</v>
+        <v>complaintType</v>
+      </c>
+      <c r="G1" t="str">
+        <v>critical</v>
+      </c>
+      <c r="H1" t="str">
+        <v>status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>REC-01</v>
+        <v>THDC-01</v>
       </c>
       <c r="B2" t="str">
-        <v>REC-VAL-01</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>Digital vehicle outer walk-around photo capture (4 angles)</v>
+        <v>E32</v>
       </c>
       <c r="D2" t="str">
-        <v>Pre-Booked Appointment</v>
+        <v>DIGITAL CLOCK NOT WORKING</v>
       </c>
       <c r="E2" t="str">
-        <v>Y</v>
+        <v>Electricals</v>
       </c>
       <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>REC-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>REC-VAL-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Fuel / EV SOC level verification &amp; digital customer signature</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Pre-Booked Appointment</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>REC-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>REC-VAL-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Customer personal valuables custody declaration slip</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Walk-in</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
+        <v>Complaint</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Active</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>ruleId</v>
+        <v>value</v>
       </c>
       <c r="C1" t="str">
-        <v>direction</v>
+        <v>status</v>
       </c>
       <c r="D1" t="str">
-        <v>verificationItem</v>
-      </c>
-      <c r="E1" t="str">
-        <v>anprSync</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
+        <v>order</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SEC-01</v>
+        <v>PRG-01</v>
       </c>
       <c r="B2" t="str">
-        <v>GATE-IN-01</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="C2" t="str">
-        <v>Inward (Check-in)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>ANPR plate scan match against appointment roster or generate walk-in pass</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
+        <v>Active</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SEC-02</v>
+        <v>PRG-02</v>
       </c>
       <c r="B3" t="str">
-        <v>GATE-IN-02</v>
+        <v>Work in process</v>
       </c>
       <c r="C3" t="str">
-        <v>Inward (Check-in)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Physical chassis plate stamp confirmation against CRM VIN</v>
-      </c>
-      <c r="E3" t="str">
-        <v>N</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
+        <v>Active</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SEC-03</v>
+        <v>PRG-03</v>
       </c>
       <c r="B4" t="str">
-        <v>GATE-OUT-01</v>
+        <v>Pending for parts</v>
       </c>
       <c r="C4" t="str">
-        <v>Outward (Check-out)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Cashier zero-balance clearance seal &amp; gate pass OTP verification</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
+        <v>Active</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SEC-04</v>
+        <v>PRG-04</v>
       </c>
       <c r="B5" t="str">
-        <v>GATE-OUT-02</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="C5" t="str">
-        <v>Outward (Check-out)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Old / replaced warranty parts box inventory verification (if customer request)</v>
-      </c>
-      <c r="E5" t="str">
-        <v>N</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Y</v>
+        <v>Active</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PRG-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Pending for commercial decision</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PRG-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Pending for Vehicle availability</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>denialCode</v>
+        <v>progress</v>
       </c>
       <c r="C1" t="str">
-        <v>reason</v>
+        <v>subStatus</v>
       </c>
       <c r="D1" t="str">
-        <v>escalateTo</v>
+        <v>status</v>
       </c>
       <c r="E1" t="str">
-        <v>active</v>
+        <v>order</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>GD-01</v>
+        <v>PSS-101</v>
       </c>
       <c r="B2" t="str">
-        <v>HOLD-CHASSIS-MISMATCH</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="C2" t="str">
-        <v>Physical VIN stamp does not match registration papers</v>
+        <v>U/I DET</v>
       </c>
       <c r="D2" t="str">
-        <v>Works Manager</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
+        <v>Active</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>GD-02</v>
+        <v>PSS-102</v>
       </c>
       <c r="B3" t="str">
-        <v>HOLD-GATEPASS-PENDING</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="C3" t="str">
-        <v>Unsettled invoice amount or missing cashier gate pass release</v>
+        <v>U/I COC</v>
       </c>
       <c r="D3" t="str">
-        <v>Service Head</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Y</v>
+        <v>Active</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>GD-03</v>
+        <v>PSS-103</v>
       </c>
       <c r="B4" t="str">
-        <v>HOLD-POLICE-STOLEN</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="C4" t="str">
-        <v>Chassis flagged in police stolen vehicle database alert</v>
+        <v>U/I Vendor</v>
       </c>
       <c r="D4" t="str">
-        <v>Security Officer In-Charge</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
+        <v>Active</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PSS-104</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Under Diagnosis</v>
+      </c>
+      <c r="C5" t="str">
+        <v>U/I Plant Team</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PSS-201</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Work in process</v>
+      </c>
+      <c r="C6" t="str">
+        <v>WIP DET</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PSS-202</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Work in process</v>
+      </c>
+      <c r="C7" t="str">
+        <v>WIP W/S Team</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PSS-203</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Work in process</v>
+      </c>
+      <c r="C8" t="str">
+        <v>WIP Vendor</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PSS-301</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Pending for parts</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Order status</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PSS-302</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Pending for parts</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Part receipt status</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>PSS-401</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Pending for vendor support</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Vendor details</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>PSS-402</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Pending for vendor support</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Request raised</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>PSS-403</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Pending for vendor support</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Status</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>PSS-501</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Pending for commercial decision</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Pending for approval</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PSS-502</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Pending for commercial decision</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Approval received</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>PSS-601</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Pending for Vehicle availability</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Expected date</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>PSS-602</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Pending for Vehicle availability</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Status as on date</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Active</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18724,6 +22604,1266 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>value</v>
+      </c>
+      <c r="C1" t="str">
+        <v>status</v>
+      </c>
+      <c r="D1" t="str">
+        <v>order</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TOC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Technical Query</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TOC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Technical Support</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D27"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>value</v>
+      </c>
+      <c r="C1" t="str">
+        <v>status</v>
+      </c>
+      <c r="D1" t="str">
+        <v>order</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CSD-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Abnormal noise</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CSD-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Warning lamps ON</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CSD-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Oil leakage</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CSD-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Coolant leakage</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CSD-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Engine overheating</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CSD-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Smell – burning, fuel, foul odor from outside, etc.</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CSD-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Smoke issues</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CSD-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Oil-Coolant mix</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CSD-09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Gear shifting issues</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CSD-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>AC cooling issues</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CSD-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Jerking / vibration / misfiring</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CSD-12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Steering hard</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CSD-13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Vehicle pulling</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CSD-14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Starting problem</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CSD-15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Tyre wear / cut</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CSD-16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Damaged / broken / cracked / soiled</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CSD-17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Part missing / fallen-off</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CSD-18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Uneven gaps / flushness issues</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CSD-19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Paint / rust issues</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CSD-20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Not working / functioning issues / system malfunction</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>CSD-21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Crash / airbag related issues</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>CSD-22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Thermal issues</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>CSD-23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Brake ineffective</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D24">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>CSD-24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Poor pick-up</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>CSD-25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Infotainment system issues</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>CSD-26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Water entry in cabin</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D27">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>value</v>
+      </c>
+      <c r="C1" t="str">
+        <v>status</v>
+      </c>
+      <c r="D1" t="str">
+        <v>order</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ACT-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Issue concluded and proceeded as per Field Investigation</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ACT-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Suggested checks based on observations</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ACT-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Known issue – suggested part replacement</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ACT-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Updated software / parameterization</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ACT-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Suggested part replacement based on observation</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ACT-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Vehicle ready for delivery</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ACT-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Vehicle not available; is with Customer</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D11"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>value</v>
+      </c>
+      <c r="C1" t="str">
+        <v>status</v>
+      </c>
+      <c r="D1" t="str">
+        <v>order</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DLY-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Diagnosis and investigation</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DLY-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Work content</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DLY-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Non-availability of spare parts</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DLY-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Non-availability of vehicle</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DLY-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Dealer response</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>DLY-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Plant / ERC / vendor intervention</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>DLY-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Software / server / TDS Tool issue</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>DLY-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Solution not available</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>DLY-09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Pending for Commercial Decision / Customer Approval</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>DLY-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Dealer not responding</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>value</v>
+      </c>
+      <c r="C1" t="str">
+        <v>status</v>
+      </c>
+      <c r="D1" t="str">
+        <v>order</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CLS-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Closed</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CLS-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Closed With Feedback</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CLS-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Closed With Early Warning</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>value</v>
+      </c>
+      <c r="C1" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ATT-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>DIR Report</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>label</v>
+      </c>
+      <c r="C1" t="str">
+        <v>fromKm</v>
+      </c>
+      <c r="D1" t="str">
+        <v>toKm</v>
+      </c>
+      <c r="E1" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>KMR-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>0 - 1,000</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>KMR-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>1,001 - 10,000</v>
+      </c>
+      <c r="C3">
+        <v>1001</v>
+      </c>
+      <c r="D3">
+        <v>10000</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>label</v>
+      </c>
+      <c r="C1" t="str">
+        <v>fromYears</v>
+      </c>
+      <c r="D1" t="str">
+        <v>toYears</v>
+      </c>
+      <c r="E1" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AGE-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>0 - 1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AGE-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>0 - 5</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>role</v>
+      </c>
+      <c r="C1" t="str">
+        <v>bu</v>
+      </c>
+      <c r="D1" t="str">
+        <v>userName</v>
+      </c>
+      <c r="E1" t="str">
+        <v>plantName</v>
+      </c>
+      <c r="F1" t="str">
+        <v>zone</v>
+      </c>
+      <c r="G1" t="str">
+        <v>region</v>
+      </c>
+      <c r="H1" t="str">
+        <v>crmUserId</v>
+      </c>
+      <c r="I1" t="str">
+        <v>aggregate</v>
+      </c>
+      <c r="J1" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>THDU-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Tech Executive L1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>PV</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Test User TE1</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>West 1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>TU_000101</v>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>THDU-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>RTSM</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PV</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Test User RTSM</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>West 1</v>
+      </c>
+      <c r="H3" t="str">
+        <v>TU_000102</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>THDU-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>COC L2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>PV</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Test User COC</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>West</v>
+      </c>
+      <c r="G4" t="str">
+        <v>West 1</v>
+      </c>
+      <c r="H4" t="str">
+        <v>TU_000103</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>THDU-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Plant</v>
+      </c>
+      <c r="C5" t="str">
+        <v>PV</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Test User Plant</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Pune</v>
+      </c>
+      <c r="F5" t="str">
+        <v>West</v>
+      </c>
+      <c r="G5" t="str">
+        <v>West 1</v>
+      </c>
+      <c r="H5" t="str">
+        <v>TU_000104</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>THDU-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Product Reliability</v>
+      </c>
+      <c r="C6" t="str">
+        <v>PV</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Test User PRT</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>West</v>
+      </c>
+      <c r="G6" t="str">
+        <v>West 1</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>driverCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>driverName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>assignedZone</v>
+      </c>
+      <c r="E1" t="str">
+        <v>licenseNumber</v>
+      </c>
+      <c r="F1" t="str">
+        <v>evCertified</v>
+      </c>
+      <c r="G1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DRV-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>DRV-HYD-101</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Nageshwar Rao</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Zone A - Hitec City</v>
+      </c>
+      <c r="E2" t="str">
+        <v>TS09-2019-0023412</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DRV-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>DRV-HYD-102</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Mohd Feroz Khan</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Zone B - Secunderabad</v>
+      </c>
+      <c r="E3" t="str">
+        <v>TS10-2018-0056123</v>
+      </c>
+      <c r="F3" t="str">
+        <v>N</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DRV-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>DRV-HYD-103</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Pradeep Patil</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Zone C - Gachibowli</v>
+      </c>
+      <c r="E4" t="str">
+        <v>TS09-2021-0089145</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
@@ -19035,6 +24175,287 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>checkpointCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>checkpointDesc</v>
+      </c>
+      <c r="D1" t="str">
+        <v>channel</v>
+      </c>
+      <c r="E1" t="str">
+        <v>mandatoryProof</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>REC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>REC-VAL-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Digital vehicle outer walk-around photo capture (4 angles)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pre-Booked Appointment</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>REC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>REC-VAL-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Fuel / EV SOC level verification &amp; digital customer signature</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Pre-Booked Appointment</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>REC-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>REC-VAL-03</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Customer personal valuables custody declaration slip</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Walk-in</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ruleId</v>
+      </c>
+      <c r="C1" t="str">
+        <v>direction</v>
+      </c>
+      <c r="D1" t="str">
+        <v>verificationItem</v>
+      </c>
+      <c r="E1" t="str">
+        <v>anprSync</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SEC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>GATE-IN-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Inward (Check-in)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>ANPR plate scan match against appointment roster or generate walk-in pass</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SEC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>GATE-IN-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Inward (Check-in)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Physical chassis plate stamp confirmation against CRM VIN</v>
+      </c>
+      <c r="E3" t="str">
+        <v>N</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SEC-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>GATE-OUT-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Outward (Check-out)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Cashier zero-balance clearance seal &amp; gate pass OTP verification</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SEC-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>GATE-OUT-02</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Outward (Check-out)</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Old / replaced warranty parts box inventory verification (if customer request)</v>
+      </c>
+      <c r="E5" t="str">
+        <v>N</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>denialCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>reason</v>
+      </c>
+      <c r="D1" t="str">
+        <v>escalateTo</v>
+      </c>
+      <c r="E1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>GD-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>HOLD-CHASSIS-MISMATCH</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Physical VIN stamp does not match registration papers</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Works Manager</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>GD-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>HOLD-GATEPASS-PENDING</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Unsettled invoice amount or missing cashier gate pass release</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Service Head</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>GD-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>HOLD-POLICE-STOLEN</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Chassis flagged in police stolen vehicle database alert</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Security Officer In-Charge</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -3098,7 +3098,7 @@
         <v>THD Rules</v>
       </c>
       <c r="G43" t="str">
-        <v>Complaint codes that automatically raise a THD case when added to a Job Card. Blank PPL = every PPL.</v>
+        <v>Complaint codes that automatically raise a THD case when added to a Job Card, mapped per PPL as in the CRM complaint master. A row without a PPL does not raise a case until its PPL is filled.</v>
       </c>
     </row>
     <row r="44">
@@ -19368,7 +19368,7 @@
         <v/>
       </c>
       <c r="Q259" t="str">
-        <v>Leave blank to apply to all PPLs.</v>
+        <v>One row per PPL + Complaint Code, as in the CRM complaint master. Needed to raise a case; a row without a PPL is listed as pending.</v>
       </c>
     </row>
     <row r="260">
@@ -24481,7 +24481,7 @@
         <v>THD_UNATTENDED</v>
       </c>
       <c r="D9" t="str">
-        <v>A THD case stays unattended by DET for more than 24 hours from creation; an auto request goes to Tech Executive L1.</v>
+        <v>A THD case stays unattended by DET for more than 24 hours from creation; an auto request goes to Tech Executive L1 (Excel "Tech Executive/CC"; CC = Command Centre, handled as Tech Executive L1).</v>
       </c>
       <c r="E9" t="str">
         <v>THD Age</v>

--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -2822,7 +2822,7 @@
         <v>Claim Dropdown Lists</v>
       </c>
       <c r="G31" t="str">
-        <v>Selected by the Claim Manager for special claim approvals (BA sheet "Special claim"). Only Active values are shown, in Order.</v>
+        <v>Identification tag on a Goodwill Authorization Request (does not change the approval path) (BA sheet "Special claim"). Only Active values are shown, in Order.</v>
       </c>
     </row>
     <row r="32">
@@ -2899,7 +2899,7 @@
         <v>claim_warranty_approval_matrix</v>
       </c>
       <c r="B35" t="str">
-        <v>Warranty Authorization Approval Matrix</v>
+        <v>AMC / Warranty Authorization Approval Matrix</v>
       </c>
       <c r="C35" t="str">
         <v>claim</v>
@@ -2914,7 +2914,7 @@
         <v>Claim Rules</v>
       </c>
       <c r="G35" t="str">
-        <v>Who can approve a Warranty Authorization Request, by Level (BA sheet "Warranty Approval Matrix"). A level approves amounts below its "Approves Below (₹)"; blank = cannot approve and must forward. A reminder goes out after the Reminder hours.</v>
+        <v>Who approves an Authorization Request, level by level (BA sheet "Warranty Approval Matrix" and BA answers). A level with Can Approve = Y approves amounts up to and including its limit; a blank limit means no upper limit. Otherwise the request moves to the next level. After the Reminder hours the pending approver gets a notification and an email only; nothing is escalated automatically.</v>
       </c>
     </row>
     <row r="36">
@@ -5642,7 +5642,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q326"/>
+  <dimension ref="A1:Q328"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16885,25 +16885,25 @@
         <v>claim_warranty_approval_matrix</v>
       </c>
       <c r="B213" t="str">
-        <v>approvesBelow</v>
+        <v>canApprove</v>
       </c>
       <c r="C213" t="str">
-        <v>Approves Below (₹)</v>
+        <v>Can Approve</v>
       </c>
       <c r="D213" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E213" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F213" t="str">
-        <v/>
-      </c>
-      <c r="G213">
-        <v>1</v>
-      </c>
-      <c r="H213">
-        <v>100000000</v>
+        <v>Y, N</v>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213" t="str">
+        <v/>
       </c>
       <c r="I213" t="str">
         <v/>
@@ -16930,7 +16930,7 @@
         <v/>
       </c>
       <c r="Q213" t="str">
-        <v>Blank = this persona cannot approve.</v>
+        <v/>
       </c>
     </row>
     <row r="214">
@@ -16938,25 +16938,25 @@
         <v>claim_warranty_approval_matrix</v>
       </c>
       <c r="B214" t="str">
-        <v>actions</v>
+        <v>approvesUpTo</v>
       </c>
       <c r="C214" t="str">
-        <v>Action / Authority</v>
+        <v>Approves Up To (₹)</v>
       </c>
       <c r="D214" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E214" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F214" t="str">
         <v/>
       </c>
-      <c r="G214" t="str">
-        <v/>
-      </c>
-      <c r="H214" t="str">
-        <v/>
+      <c r="G214">
+        <v>1</v>
+      </c>
+      <c r="H214">
+        <v>100000000</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -16983,7 +16983,7 @@
         <v/>
       </c>
       <c r="Q214" t="str">
-        <v>Comma-separated actions available to this persona.</v>
+        <v>Inclusive. Blank with Can Approve = Y means no upper limit.</v>
       </c>
     </row>
     <row r="215">
@@ -16991,16 +16991,16 @@
         <v>claim_warranty_approval_matrix</v>
       </c>
       <c r="B215" t="str">
-        <v>forwardTo</v>
+        <v>actions</v>
       </c>
       <c r="C215" t="str">
-        <v>Forwards To</v>
+        <v>Action / Authority</v>
       </c>
       <c r="D215" t="str">
         <v>text</v>
       </c>
       <c r="E215" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F215" t="str">
         <v/>
@@ -17036,7 +17036,7 @@
         <v/>
       </c>
       <c r="Q215" t="str">
-        <v>Persona of the next level, when the amount is above this level.</v>
+        <v>Comma-separated actions available to this persona.</v>
       </c>
     </row>
     <row r="216">
@@ -17044,25 +17044,25 @@
         <v>claim_warranty_approval_matrix</v>
       </c>
       <c r="B216" t="str">
-        <v>reminderHours</v>
+        <v>forwardTo</v>
       </c>
       <c r="C216" t="str">
-        <v>Reminder (Hrs)</v>
+        <v>Forwards To</v>
       </c>
       <c r="D216" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E216" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F216" t="str">
         <v/>
       </c>
-      <c r="G216">
-        <v>1</v>
-      </c>
-      <c r="H216">
-        <v>720</v>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+      <c r="H216" t="str">
+        <v/>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -17089,7 +17089,7 @@
         <v/>
       </c>
       <c r="Q216" t="str">
-        <v/>
+        <v>Persona of the next level, for amounts this level cannot approve.</v>
       </c>
     </row>
     <row r="217">
@@ -17097,25 +17097,25 @@
         <v>claim_warranty_approval_matrix</v>
       </c>
       <c r="B217" t="str">
-        <v>status</v>
+        <v>reminderHours</v>
       </c>
       <c r="C217" t="str">
-        <v>Status</v>
+        <v>Reminder (Hrs)</v>
       </c>
       <c r="D217" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E217" t="str">
         <v>Y</v>
       </c>
       <c r="F217" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G217" t="str">
-        <v/>
-      </c>
-      <c r="H217" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G217">
+        <v>1</v>
+      </c>
+      <c r="H217">
+        <v>720</v>
       </c>
       <c r="I217" t="str">
         <v/>
@@ -17147,13 +17147,13 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>claim_service_guideline</v>
+        <v>claim_warranty_approval_matrix</v>
       </c>
       <c r="B218" t="str">
-        <v>requestType</v>
+        <v>reminderVia</v>
       </c>
       <c r="C218" t="str">
-        <v>Request Type</v>
+        <v>Reminder Via</v>
       </c>
       <c r="D218" t="str">
         <v>select</v>
@@ -17162,7 +17162,7 @@
         <v>Y</v>
       </c>
       <c r="F218" t="str">
-        <v>AMC, Extended Warranty</v>
+        <v>Notification + Email</v>
       </c>
       <c r="G218" t="str">
         <v/>
@@ -17200,13 +17200,13 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>claim_service_guideline</v>
+        <v>claim_warranty_approval_matrix</v>
       </c>
       <c r="B219" t="str">
-        <v>bu</v>
+        <v>status</v>
       </c>
       <c r="C219" t="str">
-        <v>BU</v>
+        <v>Status</v>
       </c>
       <c r="D219" t="str">
         <v>select</v>
@@ -17215,7 +17215,7 @@
         <v>Y</v>
       </c>
       <c r="F219" t="str">
-        <v>PV, EV</v>
+        <v>Active, Inactive</v>
       </c>
       <c r="G219" t="str">
         <v/>
@@ -17256,19 +17256,19 @@
         <v>claim_service_guideline</v>
       </c>
       <c r="B220" t="str">
-        <v>fileName</v>
+        <v>requestType</v>
       </c>
       <c r="C220" t="str">
-        <v>Guideline File</v>
+        <v>Request Type</v>
       </c>
       <c r="D220" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E220" t="str">
         <v>Y</v>
       </c>
       <c r="F220" t="str">
-        <v/>
+        <v>AMC, Extended Warranty</v>
       </c>
       <c r="G220" t="str">
         <v/>
@@ -17301,7 +17301,7 @@
         <v/>
       </c>
       <c r="Q220" t="str">
-        <v>File name or link of the PDF.</v>
+        <v/>
       </c>
     </row>
     <row r="221">
@@ -17309,19 +17309,19 @@
         <v>claim_service_guideline</v>
       </c>
       <c r="B221" t="str">
-        <v>version</v>
+        <v>bu</v>
       </c>
       <c r="C221" t="str">
-        <v>Version</v>
+        <v>BU</v>
       </c>
       <c r="D221" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E221" t="str">
         <v>Y</v>
       </c>
       <c r="F221" t="str">
-        <v/>
+        <v>PV, EV</v>
       </c>
       <c r="G221" t="str">
         <v/>
@@ -17362,13 +17362,13 @@
         <v>claim_service_guideline</v>
       </c>
       <c r="B222" t="str">
-        <v>effectiveFrom</v>
+        <v>fileName</v>
       </c>
       <c r="C222" t="str">
-        <v>Effective From</v>
+        <v>Guideline File</v>
       </c>
       <c r="D222" t="str">
-        <v>date</v>
+        <v>text</v>
       </c>
       <c r="E222" t="str">
         <v>Y</v>
@@ -17407,7 +17407,7 @@
         <v/>
       </c>
       <c r="Q222" t="str">
-        <v/>
+        <v>File name or link of the PDF.</v>
       </c>
     </row>
     <row r="223">
@@ -17415,19 +17415,19 @@
         <v>claim_service_guideline</v>
       </c>
       <c r="B223" t="str">
-        <v>status</v>
+        <v>version</v>
       </c>
       <c r="C223" t="str">
-        <v>Status</v>
+        <v>Version</v>
       </c>
       <c r="D223" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E223" t="str">
         <v>Y</v>
       </c>
       <c r="F223" t="str">
-        <v>Active, Inactive</v>
+        <v/>
       </c>
       <c r="G223" t="str">
         <v/>
@@ -17465,22 +17465,22 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>claim_shq_users</v>
+        <v>claim_service_guideline</v>
       </c>
       <c r="B224" t="str">
-        <v>bu</v>
+        <v>effectiveFrom</v>
       </c>
       <c r="C224" t="str">
-        <v>BU</v>
+        <v>Effective From</v>
       </c>
       <c r="D224" t="str">
-        <v>select</v>
+        <v>date</v>
       </c>
       <c r="E224" t="str">
         <v>Y</v>
       </c>
       <c r="F224" t="str">
-        <v>PV, EV</v>
+        <v/>
       </c>
       <c r="G224" t="str">
         <v/>
@@ -17518,22 +17518,22 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>claim_shq_users</v>
+        <v>claim_service_guideline</v>
       </c>
       <c r="B225" t="str">
-        <v>userName</v>
+        <v>status</v>
       </c>
       <c r="C225" t="str">
-        <v>User Name</v>
+        <v>Status</v>
       </c>
       <c r="D225" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E225" t="str">
         <v>Y</v>
       </c>
       <c r="F225" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G225" t="str">
         <v/>
@@ -17574,19 +17574,19 @@
         <v>claim_shq_users</v>
       </c>
       <c r="B226" t="str">
-        <v>crmUserId</v>
+        <v>bu</v>
       </c>
       <c r="C226" t="str">
-        <v>CRM User ID</v>
+        <v>BU</v>
       </c>
       <c r="D226" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E226" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F226" t="str">
-        <v/>
+        <v>PV, EV</v>
       </c>
       <c r="G226" t="str">
         <v/>
@@ -17627,19 +17627,19 @@
         <v>claim_shq_users</v>
       </c>
       <c r="B227" t="str">
-        <v>status</v>
+        <v>userName</v>
       </c>
       <c r="C227" t="str">
-        <v>Status</v>
+        <v>User Name</v>
       </c>
       <c r="D227" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E227" t="str">
         <v>Y</v>
       </c>
       <c r="F227" t="str">
-        <v>Active, Inactive</v>
+        <v/>
       </c>
       <c r="G227" t="str">
         <v/>
@@ -17677,19 +17677,19 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>spd_issuance_priority</v>
+        <v>claim_shq_users</v>
       </c>
       <c r="B228" t="str">
-        <v>priorityCode</v>
+        <v>crmUserId</v>
       </c>
       <c r="C228" t="str">
-        <v>Priority Code</v>
+        <v>CRM User ID</v>
       </c>
       <c r="D228" t="str">
         <v>text</v>
       </c>
       <c r="E228" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F228" t="str">
         <v/>
@@ -17730,22 +17730,22 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>spd_issuance_priority</v>
+        <v>claim_shq_users</v>
       </c>
       <c r="B229" t="str">
-        <v>priorityLevel</v>
+        <v>status</v>
       </c>
       <c r="C229" t="str">
-        <v>Priority Tag</v>
+        <v>Status</v>
       </c>
       <c r="D229" t="str">
         <v>select</v>
       </c>
       <c r="E229" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F229" t="str">
-        <v>Emergency VOR, Running Repair Express, Scheduled Periodic Maintenance, Recall Campaign</v>
+        <v>Active, Inactive</v>
       </c>
       <c r="G229" t="str">
         <v/>
@@ -17786,13 +17786,13 @@
         <v>spd_issuance_priority</v>
       </c>
       <c r="B230" t="str">
-        <v>slaMins</v>
+        <v>priorityCode</v>
       </c>
       <c r="C230" t="str">
-        <v>Picking SLA (Minutes)</v>
+        <v>Priority Code</v>
       </c>
       <c r="D230" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E230" t="str">
         <v>Y</v>
@@ -17839,10 +17839,10 @@
         <v>spd_issuance_priority</v>
       </c>
       <c r="B231" t="str">
-        <v>requireOtp</v>
+        <v>priorityLevel</v>
       </c>
       <c r="C231" t="str">
-        <v>Mechanic Fingerprint / OTP Verification</v>
+        <v>Priority Tag</v>
       </c>
       <c r="D231" t="str">
         <v>select</v>
@@ -17851,7 +17851,7 @@
         <v>N</v>
       </c>
       <c r="F231" t="str">
-        <v>Y, N</v>
+        <v>Emergency VOR, Running Repair Express, Scheduled Periodic Maintenance, Recall Campaign</v>
       </c>
       <c r="G231" t="str">
         <v/>
@@ -17892,19 +17892,19 @@
         <v>spd_issuance_priority</v>
       </c>
       <c r="B232" t="str">
-        <v>active</v>
+        <v>slaMins</v>
       </c>
       <c r="C232" t="str">
-        <v>Active</v>
+        <v>Picking SLA (Minutes)</v>
       </c>
       <c r="D232" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E232" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F232" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G232" t="str">
         <v/>
@@ -17942,22 +17942,22 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>parts_delay_reasons</v>
+        <v>spd_issuance_priority</v>
       </c>
       <c r="B233" t="str">
-        <v>delayCode</v>
+        <v>requireOtp</v>
       </c>
       <c r="C233" t="str">
-        <v>Delay Code</v>
+        <v>Mechanic Fingerprint / OTP Verification</v>
       </c>
       <c r="D233" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E233" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F233" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G233" t="str">
         <v/>
@@ -17995,22 +17995,22 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>parts_delay_reasons</v>
+        <v>spd_issuance_priority</v>
       </c>
       <c r="B234" t="str">
-        <v>reasonName</v>
+        <v>active</v>
       </c>
       <c r="C234" t="str">
-        <v>Non-Availability Root Cause</v>
+        <v>Active</v>
       </c>
       <c r="D234" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E234" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F234" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G234" t="str">
         <v/>
@@ -18051,19 +18051,19 @@
         <v>parts_delay_reasons</v>
       </c>
       <c r="B235" t="str">
-        <v>autoOrderSap</v>
+        <v>delayCode</v>
       </c>
       <c r="C235" t="str">
-        <v>Auto Trigger SAP Emergency Order</v>
+        <v>Delay Code</v>
       </c>
       <c r="D235" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E235" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F235" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G235" t="str">
         <v/>
@@ -18104,19 +18104,19 @@
         <v>parts_delay_reasons</v>
       </c>
       <c r="B236" t="str">
-        <v>smsCustomer</v>
+        <v>reasonName</v>
       </c>
       <c r="C236" t="str">
-        <v>Trigger Customer ETA SMS</v>
+        <v>Non-Availability Root Cause</v>
       </c>
       <c r="D236" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E236" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F236" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G236" t="str">
         <v/>
@@ -18157,10 +18157,10 @@
         <v>parts_delay_reasons</v>
       </c>
       <c r="B237" t="str">
-        <v>active</v>
+        <v>autoOrderSap</v>
       </c>
       <c r="C237" t="str">
-        <v>Active</v>
+        <v>Auto Trigger SAP Emergency Order</v>
       </c>
       <c r="D237" t="str">
         <v>select</v>
@@ -18207,22 +18207,22 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>thd_escalation_categories</v>
+        <v>parts_delay_reasons</v>
       </c>
       <c r="B238" t="str">
-        <v>categoryCode</v>
+        <v>smsCustomer</v>
       </c>
       <c r="C238" t="str">
-        <v>Escalation Category</v>
+        <v>Trigger Customer ETA SMS</v>
       </c>
       <c r="D238" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E238" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F238" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G238" t="str">
         <v/>
@@ -18260,13 +18260,13 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>thd_escalation_categories</v>
+        <v>parts_delay_reasons</v>
       </c>
       <c r="B239" t="str">
-        <v>systemDomain</v>
+        <v>active</v>
       </c>
       <c r="C239" t="str">
-        <v>Engineering System</v>
+        <v>Active</v>
       </c>
       <c r="D239" t="str">
         <v>select</v>
@@ -18275,7 +18275,7 @@
         <v>N</v>
       </c>
       <c r="F239" t="str">
-        <v>EV High Voltage Traction, DCA Dual Clutch Transmission, ADAS &amp; Radar Calibration, Braking &amp; ESP Hydraulics, CAN Bus Network Communication</v>
+        <v>Y, N</v>
       </c>
       <c r="G239" t="str">
         <v/>
@@ -18316,19 +18316,19 @@
         <v>thd_escalation_categories</v>
       </c>
       <c r="B240" t="str">
-        <v>severityTier</v>
+        <v>categoryCode</v>
       </c>
       <c r="C240" t="str">
-        <v>Plant Response SLA</v>
+        <v>Escalation Category</v>
       </c>
       <c r="D240" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E240" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F240" t="str">
-        <v>Tier 1 Critical (&lt; 4 Hours), Tier 2 High (&lt; 12 Hours), Tier 3 Standard (&lt; 24 Hours)</v>
+        <v/>
       </c>
       <c r="G240" t="str">
         <v/>
@@ -18369,10 +18369,10 @@
         <v>thd_escalation_categories</v>
       </c>
       <c r="B241" t="str">
-        <v>requiresPlantVisit</v>
+        <v>systemDomain</v>
       </c>
       <c r="C241" t="str">
-        <v>Plant Field Engineer Dispatch</v>
+        <v>Engineering System</v>
       </c>
       <c r="D241" t="str">
         <v>select</v>
@@ -18381,7 +18381,7 @@
         <v>N</v>
       </c>
       <c r="F241" t="str">
-        <v>Y, N</v>
+        <v>EV High Voltage Traction, DCA Dual Clutch Transmission, ADAS &amp; Radar Calibration, Braking &amp; ESP Hydraulics, CAN Bus Network Communication</v>
       </c>
       <c r="G241" t="str">
         <v/>
@@ -18422,10 +18422,10 @@
         <v>thd_escalation_categories</v>
       </c>
       <c r="B242" t="str">
-        <v>active</v>
+        <v>severityTier</v>
       </c>
       <c r="C242" t="str">
-        <v>Active</v>
+        <v>Plant Response SLA</v>
       </c>
       <c r="D242" t="str">
         <v>select</v>
@@ -18434,7 +18434,7 @@
         <v>N</v>
       </c>
       <c r="F242" t="str">
-        <v>Y, N</v>
+        <v>Tier 1 Critical (&lt; 4 Hours), Tier 2 High (&lt; 12 Hours), Tier 3 Standard (&lt; 24 Hours)</v>
       </c>
       <c r="G242" t="str">
         <v/>
@@ -18472,22 +18472,22 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>thd_escalation_categories</v>
       </c>
       <c r="B243" t="str">
-        <v>tibNumber</v>
+        <v>requiresPlantVisit</v>
       </c>
       <c r="C243" t="str">
-        <v>TIB Bulletin Reference</v>
+        <v>Plant Field Engineer Dispatch</v>
       </c>
       <c r="D243" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E243" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F243" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G243" t="str">
         <v/>
@@ -18525,22 +18525,22 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>tib_bulletin_codes</v>
+        <v>thd_escalation_categories</v>
       </c>
       <c r="B244" t="str">
-        <v>title</v>
+        <v>active</v>
       </c>
       <c r="C244" t="str">
-        <v>Subject / Advisory Scope</v>
+        <v>Active</v>
       </c>
       <c r="D244" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E244" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F244" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G244" t="str">
         <v/>
@@ -18581,19 +18581,19 @@
         <v>tib_bulletin_codes</v>
       </c>
       <c r="B245" t="str">
-        <v>affectedPpl</v>
+        <v>tibNumber</v>
       </c>
       <c r="C245" t="str">
-        <v>Applicable Vehicle PPL</v>
+        <v>TIB Bulletin Reference</v>
       </c>
       <c r="D245" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E245" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F245" t="str">
-        <v>Nexon EV, Nexon ICE, Harrier / Safari, Curvv EV, Altroz</v>
+        <v/>
       </c>
       <c r="G245" t="str">
         <v/>
@@ -18634,19 +18634,19 @@
         <v>tib_bulletin_codes</v>
       </c>
       <c r="B246" t="str">
-        <v>reworkType</v>
+        <v>title</v>
       </c>
       <c r="C246" t="str">
-        <v>Rework Classification</v>
+        <v>Subject / Advisory Scope</v>
       </c>
       <c r="D246" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E246" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F246" t="str">
-        <v>ECU Firmware Update, Harness Rerouting, Hardware Bush Replacement, Torque Audit</v>
+        <v/>
       </c>
       <c r="G246" t="str">
         <v/>
@@ -18687,10 +18687,10 @@
         <v>tib_bulletin_codes</v>
       </c>
       <c r="B247" t="str">
-        <v>active</v>
+        <v>affectedPpl</v>
       </c>
       <c r="C247" t="str">
-        <v>Active</v>
+        <v>Applicable Vehicle PPL</v>
       </c>
       <c r="D247" t="str">
         <v>select</v>
@@ -18699,7 +18699,7 @@
         <v>N</v>
       </c>
       <c r="F247" t="str">
-        <v>Y, N</v>
+        <v>Nexon EV, Nexon ICE, Harrier / Safari, Curvv EV, Altroz</v>
       </c>
       <c r="G247" t="str">
         <v/>
@@ -18737,28 +18737,28 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>thd_auto_trigger_rules</v>
+        <v>tib_bulletin_codes</v>
       </c>
       <c r="B248" t="str">
-        <v>ruleNo</v>
+        <v>reworkType</v>
       </c>
       <c r="C248" t="str">
-        <v>Rule No.</v>
+        <v>Rework Classification</v>
       </c>
       <c r="D248" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E248" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F248" t="str">
-        <v/>
-      </c>
-      <c r="G248">
-        <v>1</v>
-      </c>
-      <c r="H248">
-        <v>99</v>
+        <v>ECU Firmware Update, Harness Rerouting, Hardware Bush Replacement, Torque Audit</v>
+      </c>
+      <c r="G248" t="str">
+        <v/>
+      </c>
+      <c r="H248" t="str">
+        <v/>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -18790,22 +18790,22 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>thd_auto_trigger_rules</v>
+        <v>tib_bulletin_codes</v>
       </c>
       <c r="B249" t="str">
-        <v>scenarioCode</v>
+        <v>active</v>
       </c>
       <c r="C249" t="str">
-        <v>Scenario</v>
+        <v>Active</v>
       </c>
       <c r="D249" t="str">
         <v>select</v>
       </c>
       <c r="E249" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F249" t="str">
-        <v>REPEAT_COMPLAINT, CRITICAL_AT_JC_CREATION, CRITICAL_AFTER_JC_CREATION, DELAY_REASON, QI_THD_REQUIRED, OPEN_ESCALATION, CRITICAL_DTC, THD_UNATTENDED</v>
+        <v>Y, N</v>
       </c>
       <c r="G249" t="str">
         <v/>
@@ -18838,7 +18838,7 @@
         <v/>
       </c>
       <c r="Q249" t="str">
-        <v>What the system checks. Fixed list — each one is coded in the rules engine.</v>
+        <v/>
       </c>
     </row>
     <row r="250">
@@ -18846,13 +18846,13 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B250" t="str">
-        <v>businessCondition</v>
+        <v>ruleNo</v>
       </c>
       <c r="C250" t="str">
-        <v>Business Condition</v>
+        <v>Rule No.</v>
       </c>
       <c r="D250" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E250" t="str">
         <v>Y</v>
@@ -18860,11 +18860,11 @@
       <c r="F250" t="str">
         <v/>
       </c>
-      <c r="G250" t="str">
-        <v/>
-      </c>
-      <c r="H250" t="str">
-        <v/>
+      <c r="G250">
+        <v>1</v>
+      </c>
+      <c r="H250">
+        <v>99</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -18899,10 +18899,10 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B251" t="str">
-        <v>triggerPoint</v>
+        <v>scenarioCode</v>
       </c>
       <c r="C251" t="str">
-        <v>Trigger Point</v>
+        <v>Scenario</v>
       </c>
       <c r="D251" t="str">
         <v>select</v>
@@ -18911,7 +18911,7 @@
         <v>Y</v>
       </c>
       <c r="F251" t="str">
-        <v>Job Card Creation, Open Job Card, Job Card Closure, THD Age</v>
+        <v>REPEAT_COMPLAINT, CRITICAL_AT_JC_CREATION, CRITICAL_AFTER_JC_CREATION, DELAY_REASON, QI_THD_REQUIRED, OPEN_ESCALATION, CRITICAL_DTC, THD_UNATTENDED</v>
       </c>
       <c r="G251" t="str">
         <v/>
@@ -18944,7 +18944,7 @@
         <v/>
       </c>
       <c r="Q251" t="str">
-        <v/>
+        <v>What the system checks. Fixed list — each one is coded in the rules engine.</v>
       </c>
     </row>
     <row r="252">
@@ -18952,25 +18952,25 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B252" t="str">
-        <v>windowValue</v>
+        <v>businessCondition</v>
       </c>
       <c r="C252" t="str">
-        <v>Time Window</v>
+        <v>Business Condition</v>
       </c>
       <c r="D252" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E252" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F252" t="str">
         <v/>
       </c>
-      <c r="G252">
-        <v>1</v>
-      </c>
-      <c r="H252">
-        <v>999</v>
+      <c r="G252" t="str">
+        <v/>
+      </c>
+      <c r="H252" t="str">
+        <v/>
       </c>
       <c r="I252" t="str">
         <v/>
@@ -18997,7 +18997,7 @@
         <v/>
       </c>
       <c r="Q252" t="str">
-        <v>e.g. 30 (days) for repeat visits, 24 (hours) for an unattended THD. Blank = pending from business.</v>
+        <v/>
       </c>
     </row>
     <row r="253">
@@ -19005,19 +19005,19 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B253" t="str">
-        <v>windowUnit</v>
+        <v>triggerPoint</v>
       </c>
       <c r="C253" t="str">
-        <v>Window Unit</v>
+        <v>Trigger Point</v>
       </c>
       <c r="D253" t="str">
         <v>select</v>
       </c>
       <c r="E253" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F253" t="str">
-        <v>Hours, Days</v>
+        <v>Job Card Creation, Open Job Card, Job Card Closure, THD Age</v>
       </c>
       <c r="G253" t="str">
         <v/>
@@ -19058,13 +19058,13 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B254" t="str">
-        <v>triggerValues</v>
+        <v>windowValue</v>
       </c>
       <c r="C254" t="str">
-        <v>Trigger Values</v>
+        <v>Time Window</v>
       </c>
       <c r="D254" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E254" t="str">
         <v>N</v>
@@ -19072,11 +19072,11 @@
       <c r="F254" t="str">
         <v/>
       </c>
-      <c r="G254" t="str">
-        <v/>
-      </c>
-      <c r="H254" t="str">
-        <v/>
+      <c r="G254">
+        <v>1</v>
+      </c>
+      <c r="H254">
+        <v>999</v>
       </c>
       <c r="I254" t="str">
         <v/>
@@ -19103,7 +19103,7 @@
         <v/>
       </c>
       <c r="Q254" t="str">
-        <v>Comma-separated values the rule looks for, e.g. the Job Card delay reasons.</v>
+        <v>e.g. 30 (days) for repeat visits, 24 (hours) for an unattended THD. Blank = pending from business.</v>
       </c>
     </row>
     <row r="255">
@@ -19111,19 +19111,19 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B255" t="str">
-        <v>escalationComplaint</v>
+        <v>windowUnit</v>
       </c>
       <c r="C255" t="str">
-        <v>Escalation Complaint</v>
+        <v>Window Unit</v>
       </c>
       <c r="D255" t="str">
         <v>select</v>
       </c>
       <c r="E255" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F255" t="str">
-        <v>Yes, No, Yes/No, NA</v>
+        <v>Hours, Days</v>
       </c>
       <c r="G255" t="str">
         <v/>
@@ -19164,16 +19164,16 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B256" t="str">
-        <v>thdTag</v>
+        <v>triggerValues</v>
       </c>
       <c r="C256" t="str">
-        <v>THD Tag</v>
+        <v>Trigger Values</v>
       </c>
       <c r="D256" t="str">
         <v>text</v>
       </c>
       <c r="E256" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F256" t="str">
         <v/>
@@ -19209,7 +19209,7 @@
         <v/>
       </c>
       <c r="Q256" t="str">
-        <v/>
+        <v>Comma-separated values the rule looks for, e.g. the Job Card delay reasons.</v>
       </c>
     </row>
     <row r="257">
@@ -19217,10 +19217,10 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B257" t="str">
-        <v>assignedTo</v>
+        <v>escalationComplaint</v>
       </c>
       <c r="C257" t="str">
-        <v>Assigned To</v>
+        <v>Escalation Complaint</v>
       </c>
       <c r="D257" t="str">
         <v>select</v>
@@ -19229,7 +19229,7 @@
         <v>Y</v>
       </c>
       <c r="F257" t="str">
-        <v>DET, Tech Executive L1</v>
+        <v>Yes, No, Yes/No, NA</v>
       </c>
       <c r="G257" t="str">
         <v/>
@@ -19270,19 +19270,19 @@
         <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B258" t="str">
-        <v>status</v>
+        <v>thdTag</v>
       </c>
       <c r="C258" t="str">
-        <v>Status</v>
+        <v>THD Tag</v>
       </c>
       <c r="D258" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E258" t="str">
         <v>Y</v>
       </c>
       <c r="F258" t="str">
-        <v>Active, Inactive</v>
+        <v/>
       </c>
       <c r="G258" t="str">
         <v/>
@@ -19320,22 +19320,22 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>thd_critical_complaints</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B259" t="str">
-        <v>ppl</v>
+        <v>assignedTo</v>
       </c>
       <c r="C259" t="str">
-        <v>PPL</v>
+        <v>Assigned To</v>
       </c>
       <c r="D259" t="str">
         <v>select</v>
       </c>
       <c r="E259" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F259" t="str">
-        <v>Nexon, Nexon EV, Altroz, Harrier, Safari, Punch, Punch EV, Tiago, Tiago EV, Tigor, Curvv, Curvv EV</v>
+        <v>DET, Tech Executive L1</v>
       </c>
       <c r="G259" t="str">
         <v/>
@@ -19368,27 +19368,27 @@
         <v/>
       </c>
       <c r="Q259" t="str">
-        <v>One row per PPL + Complaint Code, as in the CRM complaint master. Needed to raise a case; a row without a PPL is listed as pending.</v>
+        <v/>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>thd_critical_complaints</v>
+        <v>thd_auto_trigger_rules</v>
       </c>
       <c r="B260" t="str">
-        <v>complaintCode</v>
+        <v>status</v>
       </c>
       <c r="C260" t="str">
-        <v>Complaint Code</v>
+        <v>Status</v>
       </c>
       <c r="D260" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E260" t="str">
         <v>Y</v>
       </c>
       <c r="F260" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G260" t="str">
         <v/>
@@ -19429,19 +19429,19 @@
         <v>thd_critical_complaints</v>
       </c>
       <c r="B261" t="str">
-        <v>complaintDescription</v>
+        <v>ppl</v>
       </c>
       <c r="C261" t="str">
-        <v>Complaint Description</v>
+        <v>PPL</v>
       </c>
       <c r="D261" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E261" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F261" t="str">
-        <v/>
+        <v>Nexon, Nexon EV, Altroz, Harrier, Safari, Punch, Punch EV, Tiago, Tiago EV, Tigor, Curvv, Curvv EV</v>
       </c>
       <c r="G261" t="str">
         <v/>
@@ -19474,7 +19474,7 @@
         <v/>
       </c>
       <c r="Q261" t="str">
-        <v/>
+        <v>One row per PPL + Complaint Code, as in the CRM complaint master. Needed to raise a case; a row without a PPL is listed as pending.</v>
       </c>
     </row>
     <row r="262">
@@ -19482,10 +19482,10 @@
         <v>thd_critical_complaints</v>
       </c>
       <c r="B262" t="str">
-        <v>aggregate</v>
+        <v>complaintCode</v>
       </c>
       <c r="C262" t="str">
-        <v>Aggregate</v>
+        <v>Complaint Code</v>
       </c>
       <c r="D262" t="str">
         <v>text</v>
@@ -19535,10 +19535,10 @@
         <v>thd_critical_complaints</v>
       </c>
       <c r="B263" t="str">
-        <v>complaintType</v>
+        <v>complaintDescription</v>
       </c>
       <c r="C263" t="str">
-        <v>Complaint Type</v>
+        <v>Complaint Description</v>
       </c>
       <c r="D263" t="str">
         <v>text</v>
@@ -19588,19 +19588,19 @@
         <v>thd_critical_complaints</v>
       </c>
       <c r="B264" t="str">
-        <v>critical</v>
+        <v>aggregate</v>
       </c>
       <c r="C264" t="str">
-        <v>Critical Complaint</v>
+        <v>Aggregate</v>
       </c>
       <c r="D264" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E264" t="str">
         <v>Y</v>
       </c>
       <c r="F264" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G264" t="str">
         <v/>
@@ -19641,19 +19641,19 @@
         <v>thd_critical_complaints</v>
       </c>
       <c r="B265" t="str">
-        <v>status</v>
+        <v>complaintType</v>
       </c>
       <c r="C265" t="str">
-        <v>Status</v>
+        <v>Complaint Type</v>
       </c>
       <c r="D265" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E265" t="str">
         <v>Y</v>
       </c>
       <c r="F265" t="str">
-        <v>Active, Inactive</v>
+        <v/>
       </c>
       <c r="G265" t="str">
         <v/>
@@ -19691,22 +19691,22 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>thd_progress</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B266" t="str">
-        <v>value</v>
+        <v>critical</v>
       </c>
       <c r="C266" t="str">
-        <v>Progress</v>
+        <v>Critical Complaint</v>
       </c>
       <c r="D266" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E266" t="str">
         <v>Y</v>
       </c>
       <c r="F266" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G266" t="str">
         <v/>
@@ -19744,7 +19744,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>thd_progress</v>
+        <v>thd_critical_complaints</v>
       </c>
       <c r="B267" t="str">
         <v>status</v>
@@ -19800,13 +19800,13 @@
         <v>thd_progress</v>
       </c>
       <c r="B268" t="str">
-        <v>order</v>
+        <v>value</v>
       </c>
       <c r="C268" t="str">
-        <v>Order</v>
+        <v>Progress</v>
       </c>
       <c r="D268" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E268" t="str">
         <v>Y</v>
@@ -19814,11 +19814,11 @@
       <c r="F268" t="str">
         <v/>
       </c>
-      <c r="G268">
-        <v>1</v>
-      </c>
-      <c r="H268">
-        <v>99</v>
+      <c r="G268" t="str">
+        <v/>
+      </c>
+      <c r="H268" t="str">
+        <v/>
       </c>
       <c r="I268" t="str">
         <v/>
@@ -19845,18 +19845,18 @@
         <v/>
       </c>
       <c r="Q268" t="str">
-        <v>Display order in the dropdown.</v>
+        <v/>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>thd_progress_sub_status</v>
+        <v>thd_progress</v>
       </c>
       <c r="B269" t="str">
-        <v>progress</v>
+        <v>status</v>
       </c>
       <c r="C269" t="str">
-        <v>Progress</v>
+        <v>Status</v>
       </c>
       <c r="D269" t="str">
         <v>select</v>
@@ -19865,7 +19865,7 @@
         <v>Y</v>
       </c>
       <c r="F269" t="str">
-        <v>Under Diagnosis, Work in process, Pending for parts, Pending for vendor support, Pending for commercial decision, Pending for Vehicle availability</v>
+        <v>Active, Inactive</v>
       </c>
       <c r="G269" t="str">
         <v/>
@@ -19903,16 +19903,16 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>thd_progress_sub_status</v>
+        <v>thd_progress</v>
       </c>
       <c r="B270" t="str">
-        <v>subStatus</v>
+        <v>order</v>
       </c>
       <c r="C270" t="str">
-        <v>Progress Sub Status</v>
+        <v>Order</v>
       </c>
       <c r="D270" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E270" t="str">
         <v>Y</v>
@@ -19920,11 +19920,11 @@
       <c r="F270" t="str">
         <v/>
       </c>
-      <c r="G270" t="str">
-        <v/>
-      </c>
-      <c r="H270" t="str">
-        <v/>
+      <c r="G270">
+        <v>1</v>
+      </c>
+      <c r="H270">
+        <v>99</v>
       </c>
       <c r="I270" t="str">
         <v/>
@@ -19951,7 +19951,7 @@
         <v/>
       </c>
       <c r="Q270" t="str">
-        <v/>
+        <v>Display order in the dropdown.</v>
       </c>
     </row>
     <row r="271">
@@ -19959,10 +19959,10 @@
         <v>thd_progress_sub_status</v>
       </c>
       <c r="B271" t="str">
-        <v>status</v>
+        <v>progress</v>
       </c>
       <c r="C271" t="str">
-        <v>Status</v>
+        <v>Progress</v>
       </c>
       <c r="D271" t="str">
         <v>select</v>
@@ -19971,7 +19971,7 @@
         <v>Y</v>
       </c>
       <c r="F271" t="str">
-        <v>Active, Inactive</v>
+        <v>Under Diagnosis, Work in process, Pending for parts, Pending for vendor support, Pending for commercial decision, Pending for Vehicle availability</v>
       </c>
       <c r="G271" t="str">
         <v/>
@@ -20012,13 +20012,13 @@
         <v>thd_progress_sub_status</v>
       </c>
       <c r="B272" t="str">
-        <v>order</v>
+        <v>subStatus</v>
       </c>
       <c r="C272" t="str">
-        <v>Order</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="D272" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E272" t="str">
         <v>Y</v>
@@ -20026,11 +20026,11 @@
       <c r="F272" t="str">
         <v/>
       </c>
-      <c r="G272">
-        <v>1</v>
-      </c>
-      <c r="H272">
-        <v>99</v>
+      <c r="G272" t="str">
+        <v/>
+      </c>
+      <c r="H272" t="str">
+        <v/>
       </c>
       <c r="I272" t="str">
         <v/>
@@ -20057,27 +20057,27 @@
         <v/>
       </c>
       <c r="Q272" t="str">
-        <v>Display order in the dropdown.</v>
+        <v/>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>thd_complaint_type</v>
+        <v>thd_progress_sub_status</v>
       </c>
       <c r="B273" t="str">
-        <v>value</v>
+        <v>status</v>
       </c>
       <c r="C273" t="str">
-        <v>Type of Complaint</v>
+        <v>Status</v>
       </c>
       <c r="D273" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E273" t="str">
         <v>Y</v>
       </c>
       <c r="F273" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G273" t="str">
         <v/>
@@ -20115,28 +20115,28 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>thd_complaint_type</v>
+        <v>thd_progress_sub_status</v>
       </c>
       <c r="B274" t="str">
-        <v>status</v>
+        <v>order</v>
       </c>
       <c r="C274" t="str">
-        <v>Status</v>
+        <v>Order</v>
       </c>
       <c r="D274" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E274" t="str">
         <v>Y</v>
       </c>
       <c r="F274" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G274" t="str">
-        <v/>
-      </c>
-      <c r="H274" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G274">
+        <v>1</v>
+      </c>
+      <c r="H274">
+        <v>99</v>
       </c>
       <c r="I274" t="str">
         <v/>
@@ -20163,7 +20163,7 @@
         <v/>
       </c>
       <c r="Q274" t="str">
-        <v/>
+        <v>Display order in the dropdown.</v>
       </c>
     </row>
     <row r="275">
@@ -20171,13 +20171,13 @@
         <v>thd_complaint_type</v>
       </c>
       <c r="B275" t="str">
-        <v>order</v>
+        <v>value</v>
       </c>
       <c r="C275" t="str">
-        <v>Order</v>
+        <v>Type of Complaint</v>
       </c>
       <c r="D275" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E275" t="str">
         <v>Y</v>
@@ -20185,11 +20185,11 @@
       <c r="F275" t="str">
         <v/>
       </c>
-      <c r="G275">
-        <v>1</v>
-      </c>
-      <c r="H275">
-        <v>99</v>
+      <c r="G275" t="str">
+        <v/>
+      </c>
+      <c r="H275" t="str">
+        <v/>
       </c>
       <c r="I275" t="str">
         <v/>
@@ -20216,27 +20216,27 @@
         <v/>
       </c>
       <c r="Q275" t="str">
-        <v>Display order in the dropdown.</v>
+        <v/>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>thd_complaint_short_desc</v>
+        <v>thd_complaint_type</v>
       </c>
       <c r="B276" t="str">
-        <v>value</v>
+        <v>status</v>
       </c>
       <c r="C276" t="str">
-        <v>Complaint Short Description</v>
+        <v>Status</v>
       </c>
       <c r="D276" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E276" t="str">
         <v>Y</v>
       </c>
       <c r="F276" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G276" t="str">
         <v/>
@@ -20274,28 +20274,28 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>thd_complaint_short_desc</v>
+        <v>thd_complaint_type</v>
       </c>
       <c r="B277" t="str">
-        <v>status</v>
+        <v>order</v>
       </c>
       <c r="C277" t="str">
-        <v>Status</v>
+        <v>Order</v>
       </c>
       <c r="D277" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E277" t="str">
         <v>Y</v>
       </c>
       <c r="F277" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G277" t="str">
-        <v/>
-      </c>
-      <c r="H277" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G277">
+        <v>1</v>
+      </c>
+      <c r="H277">
+        <v>99</v>
       </c>
       <c r="I277" t="str">
         <v/>
@@ -20322,7 +20322,7 @@
         <v/>
       </c>
       <c r="Q277" t="str">
-        <v/>
+        <v>Display order in the dropdown.</v>
       </c>
     </row>
     <row r="278">
@@ -20330,13 +20330,13 @@
         <v>thd_complaint_short_desc</v>
       </c>
       <c r="B278" t="str">
-        <v>order</v>
+        <v>value</v>
       </c>
       <c r="C278" t="str">
-        <v>Order</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="D278" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E278" t="str">
         <v>Y</v>
@@ -20344,11 +20344,11 @@
       <c r="F278" t="str">
         <v/>
       </c>
-      <c r="G278">
-        <v>1</v>
-      </c>
-      <c r="H278">
-        <v>99</v>
+      <c r="G278" t="str">
+        <v/>
+      </c>
+      <c r="H278" t="str">
+        <v/>
       </c>
       <c r="I278" t="str">
         <v/>
@@ -20375,27 +20375,27 @@
         <v/>
       </c>
       <c r="Q278" t="str">
-        <v>Display order in the dropdown.</v>
+        <v/>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>thd_action_taken</v>
+        <v>thd_complaint_short_desc</v>
       </c>
       <c r="B279" t="str">
-        <v>value</v>
+        <v>status</v>
       </c>
       <c r="C279" t="str">
-        <v>Action Taken</v>
+        <v>Status</v>
       </c>
       <c r="D279" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E279" t="str">
         <v>Y</v>
       </c>
       <c r="F279" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G279" t="str">
         <v/>
@@ -20433,28 +20433,28 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>thd_action_taken</v>
+        <v>thd_complaint_short_desc</v>
       </c>
       <c r="B280" t="str">
-        <v>status</v>
+        <v>order</v>
       </c>
       <c r="C280" t="str">
-        <v>Status</v>
+        <v>Order</v>
       </c>
       <c r="D280" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E280" t="str">
         <v>Y</v>
       </c>
       <c r="F280" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G280" t="str">
-        <v/>
-      </c>
-      <c r="H280" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G280">
+        <v>1</v>
+      </c>
+      <c r="H280">
+        <v>99</v>
       </c>
       <c r="I280" t="str">
         <v/>
@@ -20481,7 +20481,7 @@
         <v/>
       </c>
       <c r="Q280" t="str">
-        <v/>
+        <v>Display order in the dropdown.</v>
       </c>
     </row>
     <row r="281">
@@ -20489,13 +20489,13 @@
         <v>thd_action_taken</v>
       </c>
       <c r="B281" t="str">
-        <v>order</v>
+        <v>value</v>
       </c>
       <c r="C281" t="str">
-        <v>Order</v>
+        <v>Action Taken</v>
       </c>
       <c r="D281" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E281" t="str">
         <v>Y</v>
@@ -20503,11 +20503,11 @@
       <c r="F281" t="str">
         <v/>
       </c>
-      <c r="G281">
-        <v>1</v>
-      </c>
-      <c r="H281">
-        <v>99</v>
+      <c r="G281" t="str">
+        <v/>
+      </c>
+      <c r="H281" t="str">
+        <v/>
       </c>
       <c r="I281" t="str">
         <v/>
@@ -20534,27 +20534,27 @@
         <v/>
       </c>
       <c r="Q281" t="str">
-        <v>Display order in the dropdown.</v>
+        <v/>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>thd_delay_reason</v>
+        <v>thd_action_taken</v>
       </c>
       <c r="B282" t="str">
-        <v>value</v>
+        <v>status</v>
       </c>
       <c r="C282" t="str">
-        <v>Reason for Delay</v>
+        <v>Status</v>
       </c>
       <c r="D282" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E282" t="str">
         <v>Y</v>
       </c>
       <c r="F282" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G282" t="str">
         <v/>
@@ -20592,28 +20592,28 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>thd_delay_reason</v>
+        <v>thd_action_taken</v>
       </c>
       <c r="B283" t="str">
-        <v>status</v>
+        <v>order</v>
       </c>
       <c r="C283" t="str">
-        <v>Status</v>
+        <v>Order</v>
       </c>
       <c r="D283" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E283" t="str">
         <v>Y</v>
       </c>
       <c r="F283" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G283" t="str">
-        <v/>
-      </c>
-      <c r="H283" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G283">
+        <v>1</v>
+      </c>
+      <c r="H283">
+        <v>99</v>
       </c>
       <c r="I283" t="str">
         <v/>
@@ -20640,7 +20640,7 @@
         <v/>
       </c>
       <c r="Q283" t="str">
-        <v/>
+        <v>Display order in the dropdown.</v>
       </c>
     </row>
     <row r="284">
@@ -20648,13 +20648,13 @@
         <v>thd_delay_reason</v>
       </c>
       <c r="B284" t="str">
-        <v>order</v>
+        <v>value</v>
       </c>
       <c r="C284" t="str">
-        <v>Order</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="D284" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E284" t="str">
         <v>Y</v>
@@ -20662,11 +20662,11 @@
       <c r="F284" t="str">
         <v/>
       </c>
-      <c r="G284">
-        <v>1</v>
-      </c>
-      <c r="H284">
-        <v>99</v>
+      <c r="G284" t="str">
+        <v/>
+      </c>
+      <c r="H284" t="str">
+        <v/>
       </c>
       <c r="I284" t="str">
         <v/>
@@ -20693,27 +20693,27 @@
         <v/>
       </c>
       <c r="Q284" t="str">
-        <v>Display order in the dropdown.</v>
+        <v/>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>thd_closure_action</v>
+        <v>thd_delay_reason</v>
       </c>
       <c r="B285" t="str">
-        <v>value</v>
+        <v>status</v>
       </c>
       <c r="C285" t="str">
-        <v>Closure Action</v>
+        <v>Status</v>
       </c>
       <c r="D285" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E285" t="str">
         <v>Y</v>
       </c>
       <c r="F285" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G285" t="str">
         <v/>
@@ -20751,28 +20751,28 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>thd_closure_action</v>
+        <v>thd_delay_reason</v>
       </c>
       <c r="B286" t="str">
-        <v>status</v>
+        <v>order</v>
       </c>
       <c r="C286" t="str">
-        <v>Status</v>
+        <v>Order</v>
       </c>
       <c r="D286" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E286" t="str">
         <v>Y</v>
       </c>
       <c r="F286" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G286" t="str">
-        <v/>
-      </c>
-      <c r="H286" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G286">
+        <v>1</v>
+      </c>
+      <c r="H286">
+        <v>99</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -20799,7 +20799,7 @@
         <v/>
       </c>
       <c r="Q286" t="str">
-        <v/>
+        <v>Display order in the dropdown.</v>
       </c>
     </row>
     <row r="287">
@@ -20807,13 +20807,13 @@
         <v>thd_closure_action</v>
       </c>
       <c r="B287" t="str">
-        <v>order</v>
+        <v>value</v>
       </c>
       <c r="C287" t="str">
-        <v>Order</v>
+        <v>Closure Action</v>
       </c>
       <c r="D287" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E287" t="str">
         <v>Y</v>
@@ -20821,11 +20821,11 @@
       <c r="F287" t="str">
         <v/>
       </c>
-      <c r="G287">
-        <v>1</v>
-      </c>
-      <c r="H287">
-        <v>99</v>
+      <c r="G287" t="str">
+        <v/>
+      </c>
+      <c r="H287" t="str">
+        <v/>
       </c>
       <c r="I287" t="str">
         <v/>
@@ -20852,27 +20852,27 @@
         <v/>
       </c>
       <c r="Q287" t="str">
-        <v>Display order in the dropdown.</v>
+        <v/>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>thd_attachment_type</v>
+        <v>thd_closure_action</v>
       </c>
       <c r="B288" t="str">
-        <v>value</v>
+        <v>status</v>
       </c>
       <c r="C288" t="str">
-        <v>Attachment Type</v>
+        <v>Status</v>
       </c>
       <c r="D288" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E288" t="str">
         <v>Y</v>
       </c>
       <c r="F288" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G288" t="str">
         <v/>
@@ -20910,28 +20910,28 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>thd_attachment_type</v>
+        <v>thd_closure_action</v>
       </c>
       <c r="B289" t="str">
-        <v>status</v>
+        <v>order</v>
       </c>
       <c r="C289" t="str">
-        <v>Status</v>
+        <v>Order</v>
       </c>
       <c r="D289" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E289" t="str">
         <v>Y</v>
       </c>
       <c r="F289" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G289" t="str">
-        <v/>
-      </c>
-      <c r="H289" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G289">
+        <v>1</v>
+      </c>
+      <c r="H289">
+        <v>99</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -20958,18 +20958,18 @@
         <v/>
       </c>
       <c r="Q289" t="str">
-        <v/>
+        <v>Display order in the dropdown.</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>thd_kms_range</v>
+        <v>thd_attachment_type</v>
       </c>
       <c r="B290" t="str">
-        <v>label</v>
+        <v>value</v>
       </c>
       <c r="C290" t="str">
-        <v>Kms Range</v>
+        <v>Attachment Type</v>
       </c>
       <c r="D290" t="str">
         <v>text</v>
@@ -21016,28 +21016,28 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>thd_kms_range</v>
+        <v>thd_attachment_type</v>
       </c>
       <c r="B291" t="str">
-        <v>fromKm</v>
+        <v>status</v>
       </c>
       <c r="C291" t="str">
-        <v>From Km</v>
+        <v>Status</v>
       </c>
       <c r="D291" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E291" t="str">
         <v>Y</v>
       </c>
       <c r="F291" t="str">
-        <v/>
-      </c>
-      <c r="G291">
-        <v>0</v>
-      </c>
-      <c r="H291">
-        <v>999999</v>
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G291" t="str">
+        <v/>
+      </c>
+      <c r="H291" t="str">
+        <v/>
       </c>
       <c r="I291" t="str">
         <v/>
@@ -21072,13 +21072,13 @@
         <v>thd_kms_range</v>
       </c>
       <c r="B292" t="str">
-        <v>toKm</v>
+        <v>label</v>
       </c>
       <c r="C292" t="str">
-        <v>To Km</v>
+        <v>Kms Range</v>
       </c>
       <c r="D292" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E292" t="str">
         <v>Y</v>
@@ -21086,11 +21086,11 @@
       <c r="F292" t="str">
         <v/>
       </c>
-      <c r="G292">
-        <v>0</v>
-      </c>
-      <c r="H292">
-        <v>999999</v>
+      <c r="G292" t="str">
+        <v/>
+      </c>
+      <c r="H292" t="str">
+        <v/>
       </c>
       <c r="I292" t="str">
         <v/>
@@ -21125,25 +21125,25 @@
         <v>thd_kms_range</v>
       </c>
       <c r="B293" t="str">
-        <v>status</v>
+        <v>fromKm</v>
       </c>
       <c r="C293" t="str">
-        <v>Status</v>
+        <v>From Km</v>
       </c>
       <c r="D293" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E293" t="str">
         <v>Y</v>
       </c>
       <c r="F293" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G293" t="str">
-        <v/>
-      </c>
-      <c r="H293" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="H293">
+        <v>999999</v>
       </c>
       <c r="I293" t="str">
         <v/>
@@ -21175,16 +21175,16 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>thd_vehicle_age</v>
+        <v>thd_kms_range</v>
       </c>
       <c r="B294" t="str">
-        <v>label</v>
+        <v>toKm</v>
       </c>
       <c r="C294" t="str">
-        <v>Age (In Years)</v>
+        <v>To Km</v>
       </c>
       <c r="D294" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E294" t="str">
         <v>Y</v>
@@ -21192,11 +21192,11 @@
       <c r="F294" t="str">
         <v/>
       </c>
-      <c r="G294" t="str">
-        <v/>
-      </c>
-      <c r="H294" t="str">
-        <v/>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>999999</v>
       </c>
       <c r="I294" t="str">
         <v/>
@@ -21228,28 +21228,28 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>thd_vehicle_age</v>
+        <v>thd_kms_range</v>
       </c>
       <c r="B295" t="str">
-        <v>fromYears</v>
+        <v>status</v>
       </c>
       <c r="C295" t="str">
-        <v>From (Years)</v>
+        <v>Status</v>
       </c>
       <c r="D295" t="str">
-        <v>number</v>
+        <v>select</v>
       </c>
       <c r="E295" t="str">
         <v>Y</v>
       </c>
       <c r="F295" t="str">
-        <v/>
-      </c>
-      <c r="G295">
-        <v>0</v>
-      </c>
-      <c r="H295">
-        <v>50</v>
+        <v>Active, Inactive</v>
+      </c>
+      <c r="G295" t="str">
+        <v/>
+      </c>
+      <c r="H295" t="str">
+        <v/>
       </c>
       <c r="I295" t="str">
         <v/>
@@ -21284,13 +21284,13 @@
         <v>thd_vehicle_age</v>
       </c>
       <c r="B296" t="str">
-        <v>toYears</v>
+        <v>label</v>
       </c>
       <c r="C296" t="str">
-        <v>To (Years)</v>
+        <v>Age (In Years)</v>
       </c>
       <c r="D296" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E296" t="str">
         <v>Y</v>
@@ -21298,11 +21298,11 @@
       <c r="F296" t="str">
         <v/>
       </c>
-      <c r="G296">
-        <v>0</v>
-      </c>
-      <c r="H296">
-        <v>50</v>
+      <c r="G296" t="str">
+        <v/>
+      </c>
+      <c r="H296" t="str">
+        <v/>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -21337,25 +21337,25 @@
         <v>thd_vehicle_age</v>
       </c>
       <c r="B297" t="str">
-        <v>status</v>
+        <v>fromYears</v>
       </c>
       <c r="C297" t="str">
-        <v>Status</v>
+        <v>From (Years)</v>
       </c>
       <c r="D297" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E297" t="str">
         <v>Y</v>
       </c>
       <c r="F297" t="str">
-        <v>Active, Inactive</v>
-      </c>
-      <c r="G297" t="str">
-        <v/>
-      </c>
-      <c r="H297" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G297">
+        <v>0</v>
+      </c>
+      <c r="H297">
+        <v>50</v>
       </c>
       <c r="I297" t="str">
         <v/>
@@ -21387,28 +21387,28 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>thd_users</v>
+        <v>thd_vehicle_age</v>
       </c>
       <c r="B298" t="str">
-        <v>role</v>
+        <v>toYears</v>
       </c>
       <c r="C298" t="str">
-        <v>Role</v>
+        <v>To (Years)</v>
       </c>
       <c r="D298" t="str">
-        <v>select</v>
+        <v>number</v>
       </c>
       <c r="E298" t="str">
         <v>Y</v>
       </c>
       <c r="F298" t="str">
-        <v>Tech Executive L1, RTSM, COC L2, Plant, Product Reliability</v>
-      </c>
-      <c r="G298" t="str">
-        <v/>
-      </c>
-      <c r="H298" t="str">
-        <v/>
+        <v/>
+      </c>
+      <c r="G298">
+        <v>0</v>
+      </c>
+      <c r="H298">
+        <v>50</v>
       </c>
       <c r="I298" t="str">
         <v/>
@@ -21440,13 +21440,13 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>thd_users</v>
+        <v>thd_vehicle_age</v>
       </c>
       <c r="B299" t="str">
-        <v>bu</v>
+        <v>status</v>
       </c>
       <c r="C299" t="str">
-        <v>BU</v>
+        <v>Status</v>
       </c>
       <c r="D299" t="str">
         <v>select</v>
@@ -21455,7 +21455,7 @@
         <v>Y</v>
       </c>
       <c r="F299" t="str">
-        <v>PV, EV</v>
+        <v>Active, Inactive</v>
       </c>
       <c r="G299" t="str">
         <v/>
@@ -21496,19 +21496,19 @@
         <v>thd_users</v>
       </c>
       <c r="B300" t="str">
-        <v>userName</v>
+        <v>role</v>
       </c>
       <c r="C300" t="str">
-        <v>User Name</v>
+        <v>Role</v>
       </c>
       <c r="D300" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E300" t="str">
         <v>Y</v>
       </c>
       <c r="F300" t="str">
-        <v/>
+        <v>Tech Executive L1, RTSM, COC L2, Plant, Product Reliability</v>
       </c>
       <c r="G300" t="str">
         <v/>
@@ -21549,19 +21549,19 @@
         <v>thd_users</v>
       </c>
       <c r="B301" t="str">
-        <v>plantName</v>
+        <v>bu</v>
       </c>
       <c r="C301" t="str">
-        <v>Plant Name</v>
+        <v>BU</v>
       </c>
       <c r="D301" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E301" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F301" t="str">
-        <v/>
+        <v>PV, EV</v>
       </c>
       <c r="G301" t="str">
         <v/>
@@ -21594,7 +21594,7 @@
         <v/>
       </c>
       <c r="Q301" t="str">
-        <v>Required for Plant users.</v>
+        <v/>
       </c>
     </row>
     <row r="302">
@@ -21602,16 +21602,16 @@
         <v>thd_users</v>
       </c>
       <c r="B302" t="str">
-        <v>zone</v>
+        <v>userName</v>
       </c>
       <c r="C302" t="str">
-        <v>Zone</v>
+        <v>User Name</v>
       </c>
       <c r="D302" t="str">
         <v>text</v>
       </c>
       <c r="E302" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F302" t="str">
         <v/>
@@ -21655,10 +21655,10 @@
         <v>thd_users</v>
       </c>
       <c r="B303" t="str">
-        <v>region</v>
+        <v>plantName</v>
       </c>
       <c r="C303" t="str">
-        <v>Region</v>
+        <v>Plant Name</v>
       </c>
       <c r="D303" t="str">
         <v>text</v>
@@ -21700,7 +21700,7 @@
         <v/>
       </c>
       <c r="Q303" t="str">
-        <v/>
+        <v>Required for Plant users.</v>
       </c>
     </row>
     <row r="304">
@@ -21708,10 +21708,10 @@
         <v>thd_users</v>
       </c>
       <c r="B304" t="str">
-        <v>crmUserId</v>
+        <v>zone</v>
       </c>
       <c r="C304" t="str">
-        <v>CRM User ID</v>
+        <v>Zone</v>
       </c>
       <c r="D304" t="str">
         <v>text</v>
@@ -21761,10 +21761,10 @@
         <v>thd_users</v>
       </c>
       <c r="B305" t="str">
-        <v>aggregate</v>
+        <v>region</v>
       </c>
       <c r="C305" t="str">
-        <v>Aggregate</v>
+        <v>Region</v>
       </c>
       <c r="D305" t="str">
         <v>text</v>
@@ -21806,7 +21806,7 @@
         <v/>
       </c>
       <c r="Q305" t="str">
-        <v>COC L2 and Plant users can be limited to one aggregate.</v>
+        <v/>
       </c>
     </row>
     <row r="306">
@@ -21814,19 +21814,19 @@
         <v>thd_users</v>
       </c>
       <c r="B306" t="str">
-        <v>status</v>
+        <v>crmUserId</v>
       </c>
       <c r="C306" t="str">
-        <v>Status</v>
+        <v>CRM User ID</v>
       </c>
       <c r="D306" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E306" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F306" t="str">
-        <v>Active, Inactive</v>
+        <v/>
       </c>
       <c r="G306" t="str">
         <v/>
@@ -21864,19 +21864,19 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_users</v>
       </c>
       <c r="B307" t="str">
-        <v>driverCode</v>
+        <v>aggregate</v>
       </c>
       <c r="C307" t="str">
-        <v>Driver Code</v>
+        <v>Aggregate</v>
       </c>
       <c r="D307" t="str">
         <v>text</v>
       </c>
       <c r="E307" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F307" t="str">
         <v/>
@@ -21912,27 +21912,27 @@
         <v/>
       </c>
       <c r="Q307" t="str">
-        <v/>
+        <v>COC L2 and Plant users can be limited to one aggregate.</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>driver_transit_roster</v>
+        <v>thd_users</v>
       </c>
       <c r="B308" t="str">
-        <v>driverName</v>
+        <v>status</v>
       </c>
       <c r="C308" t="str">
-        <v>Driver Full Name</v>
+        <v>Status</v>
       </c>
       <c r="D308" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E308" t="str">
         <v>Y</v>
       </c>
       <c r="F308" t="str">
-        <v/>
+        <v>Active, Inactive</v>
       </c>
       <c r="G308" t="str">
         <v/>
@@ -21973,19 +21973,19 @@
         <v>driver_transit_roster</v>
       </c>
       <c r="B309" t="str">
-        <v>assignedZone</v>
+        <v>driverCode</v>
       </c>
       <c r="C309" t="str">
-        <v>Assigned Territory Zone</v>
+        <v>Driver Code</v>
       </c>
       <c r="D309" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E309" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F309" t="str">
-        <v>Zone A - Hitec City, Zone B - Secunderabad, Zone C - Gachibowli, Zone D - Banjara Hills</v>
+        <v/>
       </c>
       <c r="G309" t="str">
         <v/>
@@ -22026,10 +22026,10 @@
         <v>driver_transit_roster</v>
       </c>
       <c r="B310" t="str">
-        <v>licenseNumber</v>
+        <v>driverName</v>
       </c>
       <c r="C310" t="str">
-        <v>Commercial DL Number</v>
+        <v>Driver Full Name</v>
       </c>
       <c r="D310" t="str">
         <v>text</v>
@@ -22079,10 +22079,10 @@
         <v>driver_transit_roster</v>
       </c>
       <c r="B311" t="str">
-        <v>evCertified</v>
+        <v>assignedZone</v>
       </c>
       <c r="C311" t="str">
-        <v>EV Transit Certified</v>
+        <v>Assigned Territory Zone</v>
       </c>
       <c r="D311" t="str">
         <v>select</v>
@@ -22091,7 +22091,7 @@
         <v>N</v>
       </c>
       <c r="F311" t="str">
-        <v>Y, N</v>
+        <v>Zone A - Hitec City, Zone B - Secunderabad, Zone C - Gachibowli, Zone D - Banjara Hills</v>
       </c>
       <c r="G311" t="str">
         <v/>
@@ -22132,19 +22132,19 @@
         <v>driver_transit_roster</v>
       </c>
       <c r="B312" t="str">
-        <v>active</v>
+        <v>licenseNumber</v>
       </c>
       <c r="C312" t="str">
-        <v>Active</v>
+        <v>Commercial DL Number</v>
       </c>
       <c r="D312" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E312" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F312" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G312" t="str">
         <v/>
@@ -22182,22 +22182,22 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>driver_transit_roster</v>
       </c>
       <c r="B313" t="str">
-        <v>checkpointCode</v>
+        <v>evCertified</v>
       </c>
       <c r="C313" t="str">
-        <v>Checkpoint Code</v>
+        <v>EV Transit Certified</v>
       </c>
       <c r="D313" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E313" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F313" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G313" t="str">
         <v/>
@@ -22235,22 +22235,22 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>lounge_reception_checklist</v>
+        <v>driver_transit_roster</v>
       </c>
       <c r="B314" t="str">
-        <v>checkpointDesc</v>
+        <v>active</v>
       </c>
       <c r="C314" t="str">
-        <v>Reception Standard Requirement</v>
+        <v>Active</v>
       </c>
       <c r="D314" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E314" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F314" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G314" t="str">
         <v/>
@@ -22291,19 +22291,19 @@
         <v>lounge_reception_checklist</v>
       </c>
       <c r="B315" t="str">
-        <v>channel</v>
+        <v>checkpointCode</v>
       </c>
       <c r="C315" t="str">
-        <v>Intake Channel</v>
+        <v>Checkpoint Code</v>
       </c>
       <c r="D315" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E315" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F315" t="str">
-        <v>Walk-in, Pre-Booked Appointment, Express Valet, Breakdown Flatbed</v>
+        <v/>
       </c>
       <c r="G315" t="str">
         <v/>
@@ -22344,19 +22344,19 @@
         <v>lounge_reception_checklist</v>
       </c>
       <c r="B316" t="str">
-        <v>mandatoryProof</v>
+        <v>checkpointDesc</v>
       </c>
       <c r="C316" t="str">
-        <v>Mandatory Photo / Signature</v>
+        <v>Reception Standard Requirement</v>
       </c>
       <c r="D316" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E316" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F316" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G316" t="str">
         <v/>
@@ -22397,10 +22397,10 @@
         <v>lounge_reception_checklist</v>
       </c>
       <c r="B317" t="str">
-        <v>active</v>
+        <v>channel</v>
       </c>
       <c r="C317" t="str">
-        <v>Active</v>
+        <v>Intake Channel</v>
       </c>
       <c r="D317" t="str">
         <v>select</v>
@@ -22409,7 +22409,7 @@
         <v>N</v>
       </c>
       <c r="F317" t="str">
-        <v>Y, N</v>
+        <v>Walk-in, Pre-Booked Appointment, Express Valet, Breakdown Flatbed</v>
       </c>
       <c r="G317" t="str">
         <v/>
@@ -22447,22 +22447,22 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>gate_security_checklist</v>
+        <v>lounge_reception_checklist</v>
       </c>
       <c r="B318" t="str">
-        <v>ruleId</v>
+        <v>mandatoryProof</v>
       </c>
       <c r="C318" t="str">
-        <v>Gate Rule Code</v>
+        <v>Mandatory Photo / Signature</v>
       </c>
       <c r="D318" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E318" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F318" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G318" t="str">
         <v/>
@@ -22500,13 +22500,13 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>gate_security_checklist</v>
+        <v>lounge_reception_checklist</v>
       </c>
       <c r="B319" t="str">
-        <v>direction</v>
+        <v>active</v>
       </c>
       <c r="C319" t="str">
-        <v>Movement Direction</v>
+        <v>Active</v>
       </c>
       <c r="D319" t="str">
         <v>select</v>
@@ -22515,7 +22515,7 @@
         <v>N</v>
       </c>
       <c r="F319" t="str">
-        <v>Inward (Check-in), Outward (Check-out), Internal Bay Transit</v>
+        <v>Y, N</v>
       </c>
       <c r="G319" t="str">
         <v/>
@@ -22556,10 +22556,10 @@
         <v>gate_security_checklist</v>
       </c>
       <c r="B320" t="str">
-        <v>verificationItem</v>
+        <v>ruleId</v>
       </c>
       <c r="C320" t="str">
-        <v>Verification Protocol</v>
+        <v>Gate Rule Code</v>
       </c>
       <c r="D320" t="str">
         <v>text</v>
@@ -22609,10 +22609,10 @@
         <v>gate_security_checklist</v>
       </c>
       <c r="B321" t="str">
-        <v>anprSync</v>
+        <v>direction</v>
       </c>
       <c r="C321" t="str">
-        <v>ANPR Camera Auto-Verify</v>
+        <v>Movement Direction</v>
       </c>
       <c r="D321" t="str">
         <v>select</v>
@@ -22621,7 +22621,7 @@
         <v>N</v>
       </c>
       <c r="F321" t="str">
-        <v>Y, N</v>
+        <v>Inward (Check-in), Outward (Check-out), Internal Bay Transit</v>
       </c>
       <c r="G321" t="str">
         <v/>
@@ -22662,19 +22662,19 @@
         <v>gate_security_checklist</v>
       </c>
       <c r="B322" t="str">
-        <v>active</v>
+        <v>verificationItem</v>
       </c>
       <c r="C322" t="str">
-        <v>Active</v>
+        <v>Verification Protocol</v>
       </c>
       <c r="D322" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E322" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F322" t="str">
-        <v>Y, N</v>
+        <v/>
       </c>
       <c r="G322" t="str">
         <v/>
@@ -22712,22 +22712,22 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>gate_denial_reasons</v>
+        <v>gate_security_checklist</v>
       </c>
       <c r="B323" t="str">
-        <v>denialCode</v>
+        <v>anprSync</v>
       </c>
       <c r="C323" t="str">
-        <v>Denial Code</v>
+        <v>ANPR Camera Auto-Verify</v>
       </c>
       <c r="D323" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E323" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F323" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G323" t="str">
         <v/>
@@ -22765,22 +22765,22 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>gate_denial_reasons</v>
+        <v>gate_security_checklist</v>
       </c>
       <c r="B324" t="str">
-        <v>reason</v>
+        <v>active</v>
       </c>
       <c r="C324" t="str">
-        <v>Security Denial / Hold Reason</v>
+        <v>Active</v>
       </c>
       <c r="D324" t="str">
-        <v>text</v>
+        <v>select</v>
       </c>
       <c r="E324" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F324" t="str">
-        <v/>
+        <v>Y, N</v>
       </c>
       <c r="G324" t="str">
         <v/>
@@ -22821,19 +22821,19 @@
         <v>gate_denial_reasons</v>
       </c>
       <c r="B325" t="str">
-        <v>escalateTo</v>
+        <v>denialCode</v>
       </c>
       <c r="C325" t="str">
-        <v>Immediate Notification Target</v>
+        <v>Denial Code</v>
       </c>
       <c r="D325" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E325" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F325" t="str">
-        <v>Works Manager, Security Officer In-Charge, Service Head, Customer Relation Manager</v>
+        <v/>
       </c>
       <c r="G325" t="str">
         <v/>
@@ -22874,57 +22874,163 @@
         <v>gate_denial_reasons</v>
       </c>
       <c r="B326" t="str">
+        <v>reason</v>
+      </c>
+      <c r="C326" t="str">
+        <v>Security Denial / Hold Reason</v>
+      </c>
+      <c r="D326" t="str">
+        <v>text</v>
+      </c>
+      <c r="E326" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F326" t="str">
+        <v/>
+      </c>
+      <c r="G326" t="str">
+        <v/>
+      </c>
+      <c r="H326" t="str">
+        <v/>
+      </c>
+      <c r="I326" t="str">
+        <v/>
+      </c>
+      <c r="J326" t="str">
+        <v/>
+      </c>
+      <c r="K326" t="str">
+        <v/>
+      </c>
+      <c r="L326" t="str">
+        <v/>
+      </c>
+      <c r="M326" t="str">
+        <v>N</v>
+      </c>
+      <c r="N326" t="str">
+        <v/>
+      </c>
+      <c r="O326" t="str">
+        <v/>
+      </c>
+      <c r="P326" t="str">
+        <v/>
+      </c>
+      <c r="Q326" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B327" t="str">
+        <v>escalateTo</v>
+      </c>
+      <c r="C327" t="str">
+        <v>Immediate Notification Target</v>
+      </c>
+      <c r="D327" t="str">
+        <v>select</v>
+      </c>
+      <c r="E327" t="str">
+        <v>N</v>
+      </c>
+      <c r="F327" t="str">
+        <v>Works Manager, Security Officer In-Charge, Service Head, Customer Relation Manager</v>
+      </c>
+      <c r="G327" t="str">
+        <v/>
+      </c>
+      <c r="H327" t="str">
+        <v/>
+      </c>
+      <c r="I327" t="str">
+        <v/>
+      </c>
+      <c r="J327" t="str">
+        <v/>
+      </c>
+      <c r="K327" t="str">
+        <v/>
+      </c>
+      <c r="L327" t="str">
+        <v/>
+      </c>
+      <c r="M327" t="str">
+        <v>N</v>
+      </c>
+      <c r="N327" t="str">
+        <v/>
+      </c>
+      <c r="O327" t="str">
+        <v/>
+      </c>
+      <c r="P327" t="str">
+        <v/>
+      </c>
+      <c r="Q327" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>gate_denial_reasons</v>
+      </c>
+      <c r="B328" t="str">
         <v>active</v>
       </c>
-      <c r="C326" t="str">
+      <c r="C328" t="str">
         <v>Active</v>
       </c>
-      <c r="D326" t="str">
+      <c r="D328" t="str">
         <v>select</v>
       </c>
-      <c r="E326" t="str">
-        <v>N</v>
-      </c>
-      <c r="F326" t="str">
+      <c r="E328" t="str">
+        <v>N</v>
+      </c>
+      <c r="F328" t="str">
         <v>Y, N</v>
       </c>
-      <c r="G326" t="str">
-        <v/>
-      </c>
-      <c r="H326" t="str">
-        <v/>
-      </c>
-      <c r="I326" t="str">
-        <v/>
-      </c>
-      <c r="J326" t="str">
-        <v/>
-      </c>
-      <c r="K326" t="str">
-        <v/>
-      </c>
-      <c r="L326" t="str">
-        <v/>
-      </c>
-      <c r="M326" t="str">
-        <v>N</v>
-      </c>
-      <c r="N326" t="str">
-        <v/>
-      </c>
-      <c r="O326" t="str">
-        <v/>
-      </c>
-      <c r="P326" t="str">
-        <v/>
-      </c>
-      <c r="Q326" t="str">
+      <c r="G328" t="str">
+        <v/>
+      </c>
+      <c r="H328" t="str">
+        <v/>
+      </c>
+      <c r="I328" t="str">
+        <v/>
+      </c>
+      <c r="J328" t="str">
+        <v/>
+      </c>
+      <c r="K328" t="str">
+        <v/>
+      </c>
+      <c r="L328" t="str">
+        <v/>
+      </c>
+      <c r="M328" t="str">
+        <v>N</v>
+      </c>
+      <c r="N328" t="str">
+        <v/>
+      </c>
+      <c r="O328" t="str">
+        <v/>
+      </c>
+      <c r="P328" t="str">
+        <v/>
+      </c>
+      <c r="Q328" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q326"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q328"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -23407,7 +23513,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -23420,18 +23526,24 @@
         <v>persona</v>
       </c>
       <c r="D1" t="str">
-        <v>approvesBelow</v>
+        <v>canApprove</v>
       </c>
       <c r="E1" t="str">
+        <v>approvesUpTo</v>
+      </c>
+      <c r="F1" t="str">
         <v>actions</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>forwardTo</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>reminderHours</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
+        <v>reminderVia</v>
+      </c>
+      <c r="J1" t="str">
         <v>status</v>
       </c>
     </row>
@@ -23445,19 +23557,25 @@
       <c r="C2" t="str">
         <v>Claim Manager</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E2">
         <v>20000</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>Approve, Send to CCM/ACCM</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>CCM/ACCM</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>24</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
+        <v>Notification + Email</v>
+      </c>
+      <c r="J2" t="str">
         <v>Active</v>
       </c>
     </row>
@@ -23472,24 +23590,62 @@
         <v>CCM/ACCM</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>N</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>Send to SHQ Lead 1, Send Back for Correction</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>SHQ Lead 1</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>24</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
+        <v>Notification + Email</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>WAM-03</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SHQ Lead 1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>Approve</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4">
+        <v>24</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Notification + Email</v>
+      </c>
+      <c r="J4" t="str">
         <v>Active</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -17156,13 +17156,13 @@
         <v>Reminder Via</v>
       </c>
       <c r="D218" t="str">
-        <v>select</v>
+        <v>text</v>
       </c>
       <c r="E218" t="str">
         <v>Y</v>
       </c>
       <c r="F218" t="str">
-        <v>Notification + Email</v>
+        <v/>
       </c>
       <c r="G218" t="str">
         <v/>
@@ -17195,7 +17195,7 @@
         <v/>
       </c>
       <c r="Q218" t="str">
-        <v/>
+        <v>BA: a notification and an email only — no automatic escalation.</v>
       </c>
     </row>
     <row r="219">

--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -768,7 +768,7 @@
         <v>Sample Motors Hyderabad</v>
       </c>
       <c r="D2" t="str">
-        <v>PV + EV</v>
+        <v>PV</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -806,7 +806,7 @@
         <v>Sample Motors Hyderabad</v>
       </c>
       <c r="D3" t="str">
-        <v>PV + EV</v>
+        <v>EV</v>
       </c>
       <c r="E3">
         <v>15</v>
@@ -981,7 +981,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1011,7 +1011,7 @@
         <v>PR-01</v>
       </c>
       <c r="B2" t="str">
-        <v>PV + EV</v>
+        <v>PV</v>
       </c>
       <c r="C2" t="str">
         <v>Parts Not Available</v>
@@ -1031,39 +1031,39 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PR-02</v>
+        <v>PR-01-EV</v>
       </c>
       <c r="B3" t="str">
-        <v>PV + EV</v>
+        <v>EV</v>
       </c>
       <c r="C3" t="str">
-        <v>THD Resolution Pending</v>
+        <v>Parts Not Available</v>
       </c>
       <c r="D3" t="str">
-        <v>THD Number (Open/Closed)</v>
+        <v>Part Description (DPM Unissued)</v>
       </c>
       <c r="E3" t="str">
-        <v>NA</v>
+        <v>Order Number (SAP Order No)</v>
       </c>
       <c r="F3" t="str">
         <v>Y</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PR-03</v>
+        <v>PR-02</v>
       </c>
       <c r="B4" t="str">
-        <v>PV + EV</v>
+        <v>PV</v>
       </c>
       <c r="C4" t="str">
-        <v>Waiting for customer approval</v>
+        <v>THD Resolution Pending</v>
       </c>
       <c r="D4" t="str">
-        <v>Customer Approval Doc / OTP</v>
+        <v>THD Number (Open/Closed)</v>
       </c>
       <c r="E4" t="str">
         <v>NA</v>
@@ -1072,21 +1072,21 @@
         <v>Y</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>PR-04</v>
+        <v>PR-02-EV</v>
       </c>
       <c r="B5" t="str">
-        <v>PV + EV</v>
+        <v>EV</v>
       </c>
       <c r="C5" t="str">
-        <v>Manpower absenteeism</v>
+        <v>THD Resolution Pending</v>
       </c>
       <c r="D5" t="str">
-        <v>Supervisor Override Code</v>
+        <v>THD Number (Open/Closed)</v>
       </c>
       <c r="E5" t="str">
         <v>NA</v>
@@ -1095,104 +1095,265 @@
         <v>Y</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>PR-05</v>
+        <v>PR-03</v>
       </c>
       <c r="B6" t="str">
-        <v>EV</v>
+        <v>PV</v>
       </c>
       <c r="C6" t="str">
-        <v>HV Battery Support Awaited</v>
+        <v>Waiting for customer approval</v>
       </c>
       <c r="D6" t="str">
-        <v>Ticket No (Ticket Description)</v>
+        <v>Customer Approval Doc / OTP</v>
       </c>
       <c r="E6" t="str">
-        <v>Safety Officer Clearance</v>
+        <v>NA</v>
       </c>
       <c r="F6" t="str">
         <v>Y</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>PR-06</v>
+        <v>PR-03-EV</v>
       </c>
       <c r="B7" t="str">
-        <v>PV + EV</v>
+        <v>EV</v>
       </c>
       <c r="C7" t="str">
-        <v>Vendor Support Awaited</v>
+        <v>Waiting for customer approval</v>
       </c>
       <c r="D7" t="str">
-        <v>Vendor Name (BOSCH / Delphi)</v>
+        <v>Customer Approval Doc / OTP</v>
       </c>
       <c r="E7" t="str">
-        <v>Vendor Visit Date</v>
+        <v>NA</v>
       </c>
       <c r="F7" t="str">
         <v>Y</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>PR-07</v>
+        <v>PR-04</v>
       </c>
       <c r="B8" t="str">
-        <v>PV + EV</v>
+        <v>PV</v>
       </c>
       <c r="C8" t="str">
-        <v>Goodwill Approval Awaited</v>
+        <v>Manpower absenteeism</v>
       </c>
       <c r="D8" t="str">
-        <v>Goodwill Request ID (CRM)</v>
+        <v>Supervisor Override Code</v>
       </c>
       <c r="E8" t="str">
-        <v>DGM Endorsement ID</v>
+        <v>NA</v>
       </c>
       <c r="F8" t="str">
         <v>Y</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>PR-04-EV</v>
+      </c>
+      <c r="B9" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Manpower absenteeism</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Supervisor Override Code</v>
+      </c>
+      <c r="E9" t="str">
+        <v>NA</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PR-05</v>
+      </c>
+      <c r="B10" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C10" t="str">
+        <v>HV Battery Support Awaited</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Ticket No (Ticket Description)</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Safety Officer Clearance</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>PR-06</v>
+      </c>
+      <c r="B11" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Vendor Support Awaited</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Vendor Name (BOSCH / Delphi)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Vendor Visit Date</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>PR-06-EV</v>
+      </c>
+      <c r="B12" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Vendor Support Awaited</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Vendor Name (BOSCH / Delphi)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Vendor Visit Date</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>PR-07</v>
+      </c>
+      <c r="B13" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Goodwill Approval Awaited</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Goodwill Request ID (CRM)</v>
+      </c>
+      <c r="E13" t="str">
+        <v>DGM Endorsement ID</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>PR-07-EV</v>
+      </c>
+      <c r="B14" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Goodwill Approval Awaited</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Goodwill Request ID (CRM)</v>
+      </c>
+      <c r="E14" t="str">
+        <v>DGM Endorsement ID</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
         <v>PR-08</v>
       </c>
-      <c r="B9" t="str">
-        <v>PV + EV</v>
-      </c>
-      <c r="C9" t="str">
+      <c r="B15" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C15" t="str">
         <v>Extended Warranty Approval Awaited</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D15" t="str">
         <v>Request ID (Raised to TML)</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E15" t="str">
         <v>Insurance Surveyor Ref</v>
       </c>
-      <c r="F9" t="str">
-        <v>Y</v>
-      </c>
-      <c r="G9">
+      <c r="F15" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>PR-08-EV</v>
+      </c>
+      <c r="B16" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Extended Warranty Approval Awaited</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Request ID (Raised to TML)</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Insurance Surveyor Ref</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G16">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6616,7 +6777,7 @@
         <v>N</v>
       </c>
       <c r="F24" t="str">
-        <v>PV + EV, PV, EV, CV</v>
+        <v>PV, EV, CV</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -8047,7 +8208,7 @@
         <v>N</v>
       </c>
       <c r="F51" t="str">
-        <v>PV + EV, PV, EV, CV</v>
+        <v>PV, EV, CV</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -9001,7 +9162,7 @@
         <v>Y</v>
       </c>
       <c r="F69" t="str">
-        <v>PV + EV, PV, EV, CV</v>
+        <v>PV, EV, CV</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -23487,7 +23648,7 @@
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -23607,19 +23768,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>COMMON_BU_SCOPE-01</v>
+        <v>THD_PROGRESS-01</v>
       </c>
       <c r="B5" t="str">
-        <v>COMMON_BU_SCOPE</v>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="C5" t="str">
-        <v>COMMON</v>
+        <v>THD</v>
       </c>
       <c r="D5" t="str">
-        <v>Applicable BU</v>
+        <v>Progress</v>
       </c>
       <c r="E5" t="str">
-        <v>PV + EV</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -23636,19 +23797,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>COMMON_BU_SCOPE-02</v>
+        <v>THD_PROGRESS-02</v>
       </c>
       <c r="B6" t="str">
-        <v>COMMON_BU_SCOPE</v>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="C6" t="str">
-        <v>COMMON</v>
+        <v>THD</v>
       </c>
       <c r="D6" t="str">
-        <v>Applicable BU</v>
+        <v>Progress</v>
       </c>
       <c r="E6" t="str">
-        <v>PV</v>
+        <v>Work in process</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -23665,19 +23826,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>COMMON_BU_SCOPE-03</v>
+        <v>THD_PROGRESS-03</v>
       </c>
       <c r="B7" t="str">
-        <v>COMMON_BU_SCOPE</v>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="C7" t="str">
-        <v>COMMON</v>
+        <v>THD</v>
       </c>
       <c r="D7" t="str">
-        <v>Applicable BU</v>
+        <v>Progress</v>
       </c>
       <c r="E7" t="str">
-        <v>EV</v>
+        <v>Pending for parts</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -23694,19 +23855,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>COMMON_BU_SCOPE-04</v>
+        <v>THD_PROGRESS-04</v>
       </c>
       <c r="B8" t="str">
-        <v>COMMON_BU_SCOPE</v>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="C8" t="str">
-        <v>COMMON</v>
+        <v>THD</v>
       </c>
       <c r="D8" t="str">
-        <v>Applicable BU</v>
+        <v>Progress</v>
       </c>
       <c r="E8" t="str">
-        <v>CV</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="F8">
         <v>4</v>
@@ -23723,7 +23884,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>THD_PROGRESS-01</v>
+        <v>THD_PROGRESS-05</v>
       </c>
       <c r="B9" t="str">
         <v>THD_PROGRESS</v>
@@ -23735,10 +23896,10 @@
         <v>Progress</v>
       </c>
       <c r="E9" t="str">
-        <v>Under Diagnosis</v>
+        <v>Pending for commercial decision</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -23752,7 +23913,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>THD_PROGRESS-02</v>
+        <v>THD_PROGRESS-06</v>
       </c>
       <c r="B10" t="str">
         <v>THD_PROGRESS</v>
@@ -23764,10 +23925,10 @@
         <v>Progress</v>
       </c>
       <c r="E10" t="str">
-        <v>Work in process</v>
+        <v>Pending for Vehicle availability</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -23781,28 +23942,28 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>THD_PROGRESS-03</v>
+        <v>THD_PROGRESS_SUB_STATUS-01</v>
       </c>
       <c r="B11" t="str">
-        <v>THD_PROGRESS</v>
+        <v>THD_PROGRESS_SUB_STATUS</v>
       </c>
       <c r="C11" t="str">
         <v>THD</v>
       </c>
       <c r="D11" t="str">
-        <v>Progress</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="E11" t="str">
-        <v>Pending for parts</v>
+        <v>U/I DET</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Under Diagnosis</v>
       </c>
       <c r="I11" t="str">
         <v>Active</v>
@@ -23810,28 +23971,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>THD_PROGRESS-04</v>
+        <v>THD_PROGRESS_SUB_STATUS-02</v>
       </c>
       <c r="B12" t="str">
-        <v>THD_PROGRESS</v>
+        <v>THD_PROGRESS_SUB_STATUS</v>
       </c>
       <c r="C12" t="str">
         <v>THD</v>
       </c>
       <c r="D12" t="str">
-        <v>Progress</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="E12" t="str">
-        <v>Pending for vendor support</v>
+        <v>U/I COC</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Under Diagnosis</v>
       </c>
       <c r="I12" t="str">
         <v>Active</v>
@@ -23839,28 +24000,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>THD_PROGRESS-05</v>
+        <v>THD_PROGRESS_SUB_STATUS-03</v>
       </c>
       <c r="B13" t="str">
-        <v>THD_PROGRESS</v>
+        <v>THD_PROGRESS_SUB_STATUS</v>
       </c>
       <c r="C13" t="str">
         <v>THD</v>
       </c>
       <c r="D13" t="str">
-        <v>Progress</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="E13" t="str">
-        <v>Pending for commercial decision</v>
+        <v>U/I Vendor</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>Under Diagnosis</v>
       </c>
       <c r="I13" t="str">
         <v>Active</v>
@@ -23868,28 +24029,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>THD_PROGRESS-06</v>
+        <v>THD_PROGRESS_SUB_STATUS-04</v>
       </c>
       <c r="B14" t="str">
-        <v>THD_PROGRESS</v>
+        <v>THD_PROGRESS_SUB_STATUS</v>
       </c>
       <c r="C14" t="str">
         <v>THD</v>
       </c>
       <c r="D14" t="str">
-        <v>Progress</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="E14" t="str">
-        <v>Pending for Vehicle availability</v>
+        <v>U/I Plant Team</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Under Diagnosis</v>
       </c>
       <c r="I14" t="str">
         <v>Active</v>
@@ -23897,7 +24058,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-01</v>
+        <v>THD_PROGRESS_SUB_STATUS-05</v>
       </c>
       <c r="B15" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -23909,16 +24070,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E15" t="str">
-        <v>U/I DET</v>
+        <v>WIP DET</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G15" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H15" t="str">
-        <v>Under Diagnosis</v>
+        <v>Work in process</v>
       </c>
       <c r="I15" t="str">
         <v>Active</v>
@@ -23926,7 +24087,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-02</v>
+        <v>THD_PROGRESS_SUB_STATUS-06</v>
       </c>
       <c r="B16" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -23938,16 +24099,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E16" t="str">
-        <v>U/I COC</v>
+        <v>WIP W/S Team</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G16" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H16" t="str">
-        <v>Under Diagnosis</v>
+        <v>Work in process</v>
       </c>
       <c r="I16" t="str">
         <v>Active</v>
@@ -23955,7 +24116,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-03</v>
+        <v>THD_PROGRESS_SUB_STATUS-07</v>
       </c>
       <c r="B17" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -23967,16 +24128,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E17" t="str">
-        <v>U/I Vendor</v>
+        <v>WIP Vendor</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G17" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H17" t="str">
-        <v>Under Diagnosis</v>
+        <v>Work in process</v>
       </c>
       <c r="I17" t="str">
         <v>Active</v>
@@ -23984,7 +24145,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-04</v>
+        <v>THD_PROGRESS_SUB_STATUS-08</v>
       </c>
       <c r="B18" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -23996,16 +24157,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E18" t="str">
-        <v>U/I Plant Team</v>
+        <v>Order status</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G18" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H18" t="str">
-        <v>Under Diagnosis</v>
+        <v>Pending for parts</v>
       </c>
       <c r="I18" t="str">
         <v>Active</v>
@@ -24013,7 +24174,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-05</v>
+        <v>THD_PROGRESS_SUB_STATUS-09</v>
       </c>
       <c r="B19" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24025,16 +24186,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E19" t="str">
-        <v>WIP DET</v>
+        <v>Part receipt status</v>
       </c>
       <c r="F19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G19" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H19" t="str">
-        <v>Work in process</v>
+        <v>Pending for parts</v>
       </c>
       <c r="I19" t="str">
         <v>Active</v>
@@ -24042,7 +24203,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-06</v>
+        <v>THD_PROGRESS_SUB_STATUS-10</v>
       </c>
       <c r="B20" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24054,16 +24215,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E20" t="str">
-        <v>WIP W/S Team</v>
+        <v>Vendor details</v>
       </c>
       <c r="F20">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G20" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H20" t="str">
-        <v>Work in process</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="I20" t="str">
         <v>Active</v>
@@ -24071,7 +24232,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-07</v>
+        <v>THD_PROGRESS_SUB_STATUS-11</v>
       </c>
       <c r="B21" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24083,16 +24244,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E21" t="str">
-        <v>WIP Vendor</v>
+        <v>Request raised</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G21" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H21" t="str">
-        <v>Work in process</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="I21" t="str">
         <v>Active</v>
@@ -24100,7 +24261,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-08</v>
+        <v>THD_PROGRESS_SUB_STATUS-12</v>
       </c>
       <c r="B22" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24112,16 +24273,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E22" t="str">
-        <v>Order status</v>
+        <v>Status</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G22" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H22" t="str">
-        <v>Pending for parts</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="I22" t="str">
         <v>Active</v>
@@ -24129,7 +24290,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-09</v>
+        <v>THD_PROGRESS_SUB_STATUS-13</v>
       </c>
       <c r="B23" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24141,16 +24302,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E23" t="str">
-        <v>Part receipt status</v>
+        <v>Pending for approval</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G23" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H23" t="str">
-        <v>Pending for parts</v>
+        <v>Pending for commercial decision</v>
       </c>
       <c r="I23" t="str">
         <v>Active</v>
@@ -24158,7 +24319,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-10</v>
+        <v>THD_PROGRESS_SUB_STATUS-14</v>
       </c>
       <c r="B24" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24170,16 +24331,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E24" t="str">
-        <v>Vendor details</v>
+        <v>Approval received</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G24" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H24" t="str">
-        <v>Pending for vendor support</v>
+        <v>Pending for commercial decision</v>
       </c>
       <c r="I24" t="str">
         <v>Active</v>
@@ -24187,7 +24348,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-11</v>
+        <v>THD_PROGRESS_SUB_STATUS-15</v>
       </c>
       <c r="B25" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24199,16 +24360,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E25" t="str">
-        <v>Request raised</v>
+        <v>Expected date</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G25" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H25" t="str">
-        <v>Pending for vendor support</v>
+        <v>Pending for Vehicle availability</v>
       </c>
       <c r="I25" t="str">
         <v>Active</v>
@@ -24216,7 +24377,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-12</v>
+        <v>THD_PROGRESS_SUB_STATUS-16</v>
       </c>
       <c r="B26" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24228,16 +24389,16 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E26" t="str">
-        <v>Status</v>
+        <v>Status as on date</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G26" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="H26" t="str">
-        <v>Pending for vendor support</v>
+        <v>Pending for Vehicle availability</v>
       </c>
       <c r="I26" t="str">
         <v>Active</v>
@@ -24245,28 +24406,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-13</v>
+        <v>THD_COMPLAINT_TYPE-01</v>
       </c>
       <c r="B27" t="str">
-        <v>THD_PROGRESS_SUB_STATUS</v>
+        <v>THD_COMPLAINT_TYPE</v>
       </c>
       <c r="C27" t="str">
         <v>THD</v>
       </c>
       <c r="D27" t="str">
-        <v>Progress Sub Status</v>
+        <v>Type of Complaint</v>
       </c>
       <c r="E27" t="str">
-        <v>Pending for approval</v>
+        <v>Technical Query</v>
       </c>
       <c r="F27">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G27" t="str">
-        <v>THD_PROGRESS</v>
+        <v/>
       </c>
       <c r="H27" t="str">
-        <v>Pending for commercial decision</v>
+        <v/>
       </c>
       <c r="I27" t="str">
         <v>Active</v>
@@ -24274,28 +24435,28 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-14</v>
+        <v>THD_COMPLAINT_TYPE-02</v>
       </c>
       <c r="B28" t="str">
-        <v>THD_PROGRESS_SUB_STATUS</v>
+        <v>THD_COMPLAINT_TYPE</v>
       </c>
       <c r="C28" t="str">
         <v>THD</v>
       </c>
       <c r="D28" t="str">
-        <v>Progress Sub Status</v>
+        <v>Type of Complaint</v>
       </c>
       <c r="E28" t="str">
-        <v>Approval received</v>
+        <v>Technical Support</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G28" t="str">
-        <v>THD_PROGRESS</v>
+        <v/>
       </c>
       <c r="H28" t="str">
-        <v>Pending for commercial decision</v>
+        <v/>
       </c>
       <c r="I28" t="str">
         <v>Active</v>
@@ -24303,28 +24464,28 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-15</v>
+        <v>THD_COMPLAINT_SHORT_DESC-01</v>
       </c>
       <c r="B29" t="str">
-        <v>THD_PROGRESS_SUB_STATUS</v>
+        <v>THD_COMPLAINT_SHORT_DESC</v>
       </c>
       <c r="C29" t="str">
         <v>THD</v>
       </c>
       <c r="D29" t="str">
-        <v>Progress Sub Status</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="E29" t="str">
-        <v>Expected date</v>
+        <v>Abnormal noise</v>
       </c>
       <c r="F29">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G29" t="str">
-        <v>THD_PROGRESS</v>
+        <v/>
       </c>
       <c r="H29" t="str">
-        <v>Pending for Vehicle availability</v>
+        <v/>
       </c>
       <c r="I29" t="str">
         <v>Active</v>
@@ -24332,28 +24493,28 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-16</v>
+        <v>THD_COMPLAINT_SHORT_DESC-02</v>
       </c>
       <c r="B30" t="str">
-        <v>THD_PROGRESS_SUB_STATUS</v>
+        <v>THD_COMPLAINT_SHORT_DESC</v>
       </c>
       <c r="C30" t="str">
         <v>THD</v>
       </c>
       <c r="D30" t="str">
-        <v>Progress Sub Status</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="E30" t="str">
-        <v>Status as on date</v>
+        <v>Warning lamps ON</v>
       </c>
       <c r="F30">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G30" t="str">
-        <v>THD_PROGRESS</v>
+        <v/>
       </c>
       <c r="H30" t="str">
-        <v>Pending for Vehicle availability</v>
+        <v/>
       </c>
       <c r="I30" t="str">
         <v>Active</v>
@@ -24361,22 +24522,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>THD_COMPLAINT_TYPE-01</v>
+        <v>THD_COMPLAINT_SHORT_DESC-03</v>
       </c>
       <c r="B31" t="str">
-        <v>THD_COMPLAINT_TYPE</v>
+        <v>THD_COMPLAINT_SHORT_DESC</v>
       </c>
       <c r="C31" t="str">
         <v>THD</v>
       </c>
       <c r="D31" t="str">
-        <v>Type of Complaint</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="E31" t="str">
-        <v>Technical Query</v>
+        <v>Oil leakage</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -24390,22 +24551,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>THD_COMPLAINT_TYPE-02</v>
+        <v>THD_COMPLAINT_SHORT_DESC-04</v>
       </c>
       <c r="B32" t="str">
-        <v>THD_COMPLAINT_TYPE</v>
+        <v>THD_COMPLAINT_SHORT_DESC</v>
       </c>
       <c r="C32" t="str">
         <v>THD</v>
       </c>
       <c r="D32" t="str">
-        <v>Type of Complaint</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="E32" t="str">
-        <v>Technical Support</v>
+        <v>Coolant leakage</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -24419,7 +24580,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-01</v>
+        <v>THD_COMPLAINT_SHORT_DESC-05</v>
       </c>
       <c r="B33" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24431,10 +24592,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E33" t="str">
-        <v>Abnormal noise</v>
+        <v>Engine overheating</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -24448,7 +24609,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-02</v>
+        <v>THD_COMPLAINT_SHORT_DESC-06</v>
       </c>
       <c r="B34" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24460,10 +24621,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E34" t="str">
-        <v>Warning lamps ON</v>
+        <v>Smell – burning, fuel, foul odor from outside, etc.</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -24477,7 +24638,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-03</v>
+        <v>THD_COMPLAINT_SHORT_DESC-07</v>
       </c>
       <c r="B35" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24489,10 +24650,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E35" t="str">
-        <v>Oil leakage</v>
+        <v>Smoke issues</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -24506,7 +24667,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-04</v>
+        <v>THD_COMPLAINT_SHORT_DESC-08</v>
       </c>
       <c r="B36" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24518,10 +24679,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E36" t="str">
-        <v>Coolant leakage</v>
+        <v>Oil-Coolant mix</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -24535,7 +24696,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-05</v>
+        <v>THD_COMPLAINT_SHORT_DESC-09</v>
       </c>
       <c r="B37" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24547,10 +24708,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E37" t="str">
-        <v>Engine overheating</v>
+        <v>Gear shifting issues</v>
       </c>
       <c r="F37">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -24564,7 +24725,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-06</v>
+        <v>THD_COMPLAINT_SHORT_DESC-10</v>
       </c>
       <c r="B38" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24576,10 +24737,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E38" t="str">
-        <v>Smell – burning, fuel, foul odor from outside, etc.</v>
+        <v>AC cooling issues</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -24593,7 +24754,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-07</v>
+        <v>THD_COMPLAINT_SHORT_DESC-11</v>
       </c>
       <c r="B39" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24605,10 +24766,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E39" t="str">
-        <v>Smoke issues</v>
+        <v>Jerking / vibration / misfiring</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -24622,7 +24783,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-08</v>
+        <v>THD_COMPLAINT_SHORT_DESC-12</v>
       </c>
       <c r="B40" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24634,10 +24795,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E40" t="str">
-        <v>Oil-Coolant mix</v>
+        <v>Steering hard</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -24651,7 +24812,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-09</v>
+        <v>THD_COMPLAINT_SHORT_DESC-13</v>
       </c>
       <c r="B41" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24663,10 +24824,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E41" t="str">
-        <v>Gear shifting issues</v>
+        <v>Vehicle pulling</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -24680,7 +24841,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-10</v>
+        <v>THD_COMPLAINT_SHORT_DESC-14</v>
       </c>
       <c r="B42" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24692,10 +24853,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E42" t="str">
-        <v>AC cooling issues</v>
+        <v>Starting problem</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -24709,7 +24870,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-11</v>
+        <v>THD_COMPLAINT_SHORT_DESC-15</v>
       </c>
       <c r="B43" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24721,10 +24882,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E43" t="str">
-        <v>Jerking / vibration / misfiring</v>
+        <v>Tyre wear / cut</v>
       </c>
       <c r="F43">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -24738,7 +24899,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-12</v>
+        <v>THD_COMPLAINT_SHORT_DESC-16</v>
       </c>
       <c r="B44" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24750,10 +24911,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E44" t="str">
-        <v>Steering hard</v>
+        <v>Damaged / broken / cracked / soiled</v>
       </c>
       <c r="F44">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -24767,7 +24928,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-13</v>
+        <v>THD_COMPLAINT_SHORT_DESC-17</v>
       </c>
       <c r="B45" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24779,10 +24940,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E45" t="str">
-        <v>Vehicle pulling</v>
+        <v>Part missing / fallen-off</v>
       </c>
       <c r="F45">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -24796,7 +24957,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-14</v>
+        <v>THD_COMPLAINT_SHORT_DESC-18</v>
       </c>
       <c r="B46" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24808,10 +24969,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E46" t="str">
-        <v>Starting problem</v>
+        <v>Uneven gaps / flushness issues</v>
       </c>
       <c r="F46">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -24825,7 +24986,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-15</v>
+        <v>THD_COMPLAINT_SHORT_DESC-19</v>
       </c>
       <c r="B47" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24837,10 +24998,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E47" t="str">
-        <v>Tyre wear / cut</v>
+        <v>Paint / rust issues</v>
       </c>
       <c r="F47">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -24854,7 +25015,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-16</v>
+        <v>THD_COMPLAINT_SHORT_DESC-20</v>
       </c>
       <c r="B48" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24866,10 +25027,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E48" t="str">
-        <v>Damaged / broken / cracked / soiled</v>
+        <v>Not working / functioning issues / system malfunction</v>
       </c>
       <c r="F48">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -24883,7 +25044,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-17</v>
+        <v>THD_COMPLAINT_SHORT_DESC-21</v>
       </c>
       <c r="B49" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24895,10 +25056,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E49" t="str">
-        <v>Part missing / fallen-off</v>
+        <v>Crash / airbag related issues</v>
       </c>
       <c r="F49">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -24912,7 +25073,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-18</v>
+        <v>THD_COMPLAINT_SHORT_DESC-22</v>
       </c>
       <c r="B50" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24924,10 +25085,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E50" t="str">
-        <v>Uneven gaps / flushness issues</v>
+        <v>Thermal issues</v>
       </c>
       <c r="F50">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -24941,7 +25102,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-19</v>
+        <v>THD_COMPLAINT_SHORT_DESC-23</v>
       </c>
       <c r="B51" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24953,10 +25114,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E51" t="str">
-        <v>Paint / rust issues</v>
+        <v>Brake ineffective</v>
       </c>
       <c r="F51">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -24970,7 +25131,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-20</v>
+        <v>THD_COMPLAINT_SHORT_DESC-24</v>
       </c>
       <c r="B52" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24982,10 +25143,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E52" t="str">
-        <v>Not working / functioning issues / system malfunction</v>
+        <v>Poor pick-up</v>
       </c>
       <c r="F52">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -24999,7 +25160,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-21</v>
+        <v>THD_COMPLAINT_SHORT_DESC-25</v>
       </c>
       <c r="B53" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -25011,10 +25172,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E53" t="str">
-        <v>Crash / airbag related issues</v>
+        <v>Infotainment system issues</v>
       </c>
       <c r="F53">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -25028,7 +25189,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-22</v>
+        <v>THD_COMPLAINT_SHORT_DESC-26</v>
       </c>
       <c r="B54" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -25040,10 +25201,10 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E54" t="str">
-        <v>Thermal issues</v>
+        <v>Water entry in cabin</v>
       </c>
       <c r="F54">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -25057,22 +25218,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-23</v>
+        <v>THD_ACTION_TAKEN-01</v>
       </c>
       <c r="B55" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC</v>
+        <v>THD_ACTION_TAKEN</v>
       </c>
       <c r="C55" t="str">
         <v>THD</v>
       </c>
       <c r="D55" t="str">
-        <v>Complaint Short Description</v>
+        <v>Action Taken</v>
       </c>
       <c r="E55" t="str">
-        <v>Brake ineffective</v>
+        <v>Issue concluded and proceeded as per Field Investigation</v>
       </c>
       <c r="F55">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -25086,22 +25247,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-24</v>
+        <v>THD_ACTION_TAKEN-02</v>
       </c>
       <c r="B56" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC</v>
+        <v>THD_ACTION_TAKEN</v>
       </c>
       <c r="C56" t="str">
         <v>THD</v>
       </c>
       <c r="D56" t="str">
-        <v>Complaint Short Description</v>
+        <v>Action Taken</v>
       </c>
       <c r="E56" t="str">
-        <v>Poor pick-up</v>
+        <v>Suggested checks based on observations</v>
       </c>
       <c r="F56">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -25115,22 +25276,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-25</v>
+        <v>THD_ACTION_TAKEN-03</v>
       </c>
       <c r="B57" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC</v>
+        <v>THD_ACTION_TAKEN</v>
       </c>
       <c r="C57" t="str">
         <v>THD</v>
       </c>
       <c r="D57" t="str">
-        <v>Complaint Short Description</v>
+        <v>Action Taken</v>
       </c>
       <c r="E57" t="str">
-        <v>Infotainment system issues</v>
+        <v>Known issue – suggested part replacement</v>
       </c>
       <c r="F57">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -25144,22 +25305,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-26</v>
+        <v>THD_ACTION_TAKEN-04</v>
       </c>
       <c r="B58" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC</v>
+        <v>THD_ACTION_TAKEN</v>
       </c>
       <c r="C58" t="str">
         <v>THD</v>
       </c>
       <c r="D58" t="str">
-        <v>Complaint Short Description</v>
+        <v>Action Taken</v>
       </c>
       <c r="E58" t="str">
-        <v>Water entry in cabin</v>
+        <v>Updated software / parameterization</v>
       </c>
       <c r="F58">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -25173,7 +25334,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>THD_ACTION_TAKEN-01</v>
+        <v>THD_ACTION_TAKEN-05</v>
       </c>
       <c r="B59" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25185,10 +25346,10 @@
         <v>Action Taken</v>
       </c>
       <c r="E59" t="str">
-        <v>Issue concluded and proceeded as per Field Investigation</v>
+        <v>Suggested part replacement based on observation</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -25202,7 +25363,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>THD_ACTION_TAKEN-02</v>
+        <v>THD_ACTION_TAKEN-06</v>
       </c>
       <c r="B60" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25214,10 +25375,10 @@
         <v>Action Taken</v>
       </c>
       <c r="E60" t="str">
-        <v>Suggested checks based on observations</v>
+        <v>Vehicle ready for delivery</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -25231,7 +25392,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>THD_ACTION_TAKEN-03</v>
+        <v>THD_ACTION_TAKEN-07</v>
       </c>
       <c r="B61" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25243,10 +25404,10 @@
         <v>Action Taken</v>
       </c>
       <c r="E61" t="str">
-        <v>Known issue – suggested part replacement</v>
+        <v>Vehicle not available; is with Customer</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -25260,22 +25421,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>THD_ACTION_TAKEN-04</v>
+        <v>THD_DELAY_REASON-01</v>
       </c>
       <c r="B62" t="str">
-        <v>THD_ACTION_TAKEN</v>
+        <v>THD_DELAY_REASON</v>
       </c>
       <c r="C62" t="str">
         <v>THD</v>
       </c>
       <c r="D62" t="str">
-        <v>Action Taken</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="E62" t="str">
-        <v>Updated software / parameterization</v>
+        <v>Diagnosis and investigation</v>
       </c>
       <c r="F62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -25289,22 +25450,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>THD_ACTION_TAKEN-05</v>
+        <v>THD_DELAY_REASON-02</v>
       </c>
       <c r="B63" t="str">
-        <v>THD_ACTION_TAKEN</v>
+        <v>THD_DELAY_REASON</v>
       </c>
       <c r="C63" t="str">
         <v>THD</v>
       </c>
       <c r="D63" t="str">
-        <v>Action Taken</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="E63" t="str">
-        <v>Suggested part replacement based on observation</v>
+        <v>Work content</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -25318,22 +25479,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>THD_ACTION_TAKEN-06</v>
+        <v>THD_DELAY_REASON-03</v>
       </c>
       <c r="B64" t="str">
-        <v>THD_ACTION_TAKEN</v>
+        <v>THD_DELAY_REASON</v>
       </c>
       <c r="C64" t="str">
         <v>THD</v>
       </c>
       <c r="D64" t="str">
-        <v>Action Taken</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="E64" t="str">
-        <v>Vehicle ready for delivery</v>
+        <v>Non-availability of spare parts</v>
       </c>
       <c r="F64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -25347,22 +25508,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>THD_ACTION_TAKEN-07</v>
+        <v>THD_DELAY_REASON-04</v>
       </c>
       <c r="B65" t="str">
-        <v>THD_ACTION_TAKEN</v>
+        <v>THD_DELAY_REASON</v>
       </c>
       <c r="C65" t="str">
         <v>THD</v>
       </c>
       <c r="D65" t="str">
-        <v>Action Taken</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="E65" t="str">
-        <v>Vehicle not available; is with Customer</v>
+        <v>Non-availability of vehicle</v>
       </c>
       <c r="F65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -25376,7 +25537,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>THD_DELAY_REASON-01</v>
+        <v>THD_DELAY_REASON-05</v>
       </c>
       <c r="B66" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25388,10 +25549,10 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E66" t="str">
-        <v>Diagnosis and investigation</v>
+        <v>Dealer response</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -25405,7 +25566,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>THD_DELAY_REASON-02</v>
+        <v>THD_DELAY_REASON-06</v>
       </c>
       <c r="B67" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25417,10 +25578,10 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E67" t="str">
-        <v>Work content</v>
+        <v>Plant / ERC / vendor intervention</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -25434,7 +25595,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>THD_DELAY_REASON-03</v>
+        <v>THD_DELAY_REASON-07</v>
       </c>
       <c r="B68" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25446,10 +25607,10 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E68" t="str">
-        <v>Non-availability of spare parts</v>
+        <v>Software / server / TDS Tool issue</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -25463,7 +25624,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>THD_DELAY_REASON-04</v>
+        <v>THD_DELAY_REASON-08</v>
       </c>
       <c r="B69" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25475,10 +25636,10 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E69" t="str">
-        <v>Non-availability of vehicle</v>
+        <v>Solution not available</v>
       </c>
       <c r="F69">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -25492,7 +25653,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>THD_DELAY_REASON-05</v>
+        <v>THD_DELAY_REASON-09</v>
       </c>
       <c r="B70" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25504,10 +25665,10 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E70" t="str">
-        <v>Dealer response</v>
+        <v>Pending for Commercial Decision / Customer Approval</v>
       </c>
       <c r="F70">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -25521,7 +25682,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>THD_DELAY_REASON-06</v>
+        <v>THD_DELAY_REASON-10</v>
       </c>
       <c r="B71" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25533,10 +25694,10 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E71" t="str">
-        <v>Plant / ERC / vendor intervention</v>
+        <v>Dealer not responding</v>
       </c>
       <c r="F71">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -25550,22 +25711,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>THD_DELAY_REASON-07</v>
+        <v>THD_CLOSURE_ACTION-01</v>
       </c>
       <c r="B72" t="str">
-        <v>THD_DELAY_REASON</v>
+        <v>THD_CLOSURE_ACTION</v>
       </c>
       <c r="C72" t="str">
         <v>THD</v>
       </c>
       <c r="D72" t="str">
-        <v>Reason for Delay</v>
+        <v>Closure Action</v>
       </c>
       <c r="E72" t="str">
-        <v>Software / server / TDS Tool issue</v>
+        <v>Closed</v>
       </c>
       <c r="F72">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -25579,22 +25740,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>THD_DELAY_REASON-08</v>
+        <v>THD_CLOSURE_ACTION-02</v>
       </c>
       <c r="B73" t="str">
-        <v>THD_DELAY_REASON</v>
+        <v>THD_CLOSURE_ACTION</v>
       </c>
       <c r="C73" t="str">
         <v>THD</v>
       </c>
       <c r="D73" t="str">
-        <v>Reason for Delay</v>
+        <v>Closure Action</v>
       </c>
       <c r="E73" t="str">
-        <v>Solution not available</v>
+        <v>Closed With Feedback</v>
       </c>
       <c r="F73">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -25608,22 +25769,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>THD_DELAY_REASON-09</v>
+        <v>THD_CLOSURE_ACTION-03</v>
       </c>
       <c r="B74" t="str">
-        <v>THD_DELAY_REASON</v>
+        <v>THD_CLOSURE_ACTION</v>
       </c>
       <c r="C74" t="str">
         <v>THD</v>
       </c>
       <c r="D74" t="str">
-        <v>Reason for Delay</v>
+        <v>Closure Action</v>
       </c>
       <c r="E74" t="str">
-        <v>Pending for Commercial Decision / Customer Approval</v>
+        <v>Closed With Early Warning</v>
       </c>
       <c r="F74">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -25637,22 +25798,22 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>THD_DELAY_REASON-10</v>
+        <v>THD_ATTACHMENT_TYPE-01</v>
       </c>
       <c r="B75" t="str">
-        <v>THD_DELAY_REASON</v>
+        <v>THD_ATTACHMENT_TYPE</v>
       </c>
       <c r="C75" t="str">
         <v>THD</v>
       </c>
       <c r="D75" t="str">
-        <v>Reason for Delay</v>
+        <v>Attachment Type</v>
       </c>
       <c r="E75" t="str">
-        <v>Dealer not responding</v>
+        <v>DIR Report</v>
       </c>
       <c r="F75">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -25666,19 +25827,19 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>THD_CLOSURE_ACTION-01</v>
+        <v>CLAIM_BUDGET_PURPOSE-01</v>
       </c>
       <c r="B76" t="str">
-        <v>THD_CLOSURE_ACTION</v>
+        <v>CLAIM_BUDGET_PURPOSE</v>
       </c>
       <c r="C76" t="str">
-        <v>THD</v>
+        <v>CLAIM</v>
       </c>
       <c r="D76" t="str">
-        <v>Closure Action</v>
+        <v>Allocation Purpose</v>
       </c>
       <c r="E76" t="str">
-        <v>Closed</v>
+        <v>Approved Yearly Budget</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -25695,19 +25856,19 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>THD_CLOSURE_ACTION-02</v>
+        <v>CLAIM_BUDGET_PURPOSE-02</v>
       </c>
       <c r="B77" t="str">
-        <v>THD_CLOSURE_ACTION</v>
+        <v>CLAIM_BUDGET_PURPOSE</v>
       </c>
       <c r="C77" t="str">
-        <v>THD</v>
+        <v>CLAIM</v>
       </c>
       <c r="D77" t="str">
-        <v>Closure Action</v>
+        <v>Allocation Purpose</v>
       </c>
       <c r="E77" t="str">
-        <v>Closed With Feedback</v>
+        <v>Special Budget</v>
       </c>
       <c r="F77">
         <v>2</v>
@@ -25724,22 +25885,22 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>THD_CLOSURE_ACTION-03</v>
+        <v>CLAIM_SPECIAL_GOODWILL-01</v>
       </c>
       <c r="B78" t="str">
-        <v>THD_CLOSURE_ACTION</v>
+        <v>CLAIM_SPECIAL_GOODWILL</v>
       </c>
       <c r="C78" t="str">
-        <v>THD</v>
+        <v>CLAIM</v>
       </c>
       <c r="D78" t="str">
-        <v>Closure Action</v>
+        <v>Special Claim</v>
       </c>
       <c r="E78" t="str">
-        <v>Closed With Early Warning</v>
+        <v>IUPR</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -25753,22 +25914,22 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>THD_ATTACHMENT_TYPE-01</v>
+        <v>CLAIM_SPECIAL_GOODWILL-02</v>
       </c>
       <c r="B79" t="str">
-        <v>THD_ATTACHMENT_TYPE</v>
+        <v>CLAIM_SPECIAL_GOODWILL</v>
       </c>
       <c r="C79" t="str">
-        <v>THD</v>
+        <v>CLAIM</v>
       </c>
       <c r="D79" t="str">
-        <v>Attachment Type</v>
+        <v>Special Claim</v>
       </c>
       <c r="E79" t="str">
-        <v>DIR Report</v>
+        <v>Thrive</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -25782,19 +25943,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>CLAIM_BUDGET_PURPOSE-01</v>
+        <v>CLAIM_ISSUE_DESCRIPTION-01</v>
       </c>
       <c r="B80" t="str">
-        <v>CLAIM_BUDGET_PURPOSE</v>
+        <v>CLAIM_ISSUE_DESCRIPTION</v>
       </c>
       <c r="C80" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D80" t="str">
-        <v>Allocation Purpose</v>
+        <v>Issue Description</v>
       </c>
       <c r="E80" t="str">
-        <v>Approved Yearly Budget</v>
+        <v>Thermal Incident</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -25811,19 +25972,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>CLAIM_BUDGET_PURPOSE-02</v>
+        <v>CLAIM_ISSUE_DESCRIPTION-02</v>
       </c>
       <c r="B81" t="str">
-        <v>CLAIM_BUDGET_PURPOSE</v>
+        <v>CLAIM_ISSUE_DESCRIPTION</v>
       </c>
       <c r="C81" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D81" t="str">
-        <v>Allocation Purpose</v>
+        <v>Issue Description</v>
       </c>
       <c r="E81" t="str">
-        <v>Special Budget</v>
+        <v>Engine Failure</v>
       </c>
       <c r="F81">
         <v>2</v>
@@ -25840,19 +26001,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL-01</v>
+        <v>CLAIM_COMPLAINT_TYPE-01</v>
       </c>
       <c r="B82" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL</v>
+        <v>CLAIM_COMPLAINT_TYPE</v>
       </c>
       <c r="C82" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D82" t="str">
-        <v>Special Claim</v>
+        <v>Complaint Type</v>
       </c>
       <c r="E82" t="str">
-        <v>IUPR</v>
+        <v>Transmission</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -25869,19 +26030,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL-02</v>
+        <v>CLAIM_COMPLAINT_TYPE-02</v>
       </c>
       <c r="B83" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL</v>
+        <v>CLAIM_COMPLAINT_TYPE</v>
       </c>
       <c r="C83" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D83" t="str">
-        <v>Special Claim</v>
+        <v>Complaint Type</v>
       </c>
       <c r="E83" t="str">
-        <v>Thrive</v>
+        <v>Clutch</v>
       </c>
       <c r="F83">
         <v>2</v>
@@ -25896,125 +26057,9 @@
         <v>Active</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION-01</v>
-      </c>
-      <c r="B84" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION</v>
-      </c>
-      <c r="C84" t="str">
-        <v>CLAIM</v>
-      </c>
-      <c r="D84" t="str">
-        <v>Issue Description</v>
-      </c>
-      <c r="E84" t="str">
-        <v>Thermal Incident</v>
-      </c>
-      <c r="F84">
-        <v>1</v>
-      </c>
-      <c r="G84" t="str">
-        <v/>
-      </c>
-      <c r="H84" t="str">
-        <v/>
-      </c>
-      <c r="I84" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION-02</v>
-      </c>
-      <c r="B85" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION</v>
-      </c>
-      <c r="C85" t="str">
-        <v>CLAIM</v>
-      </c>
-      <c r="D85" t="str">
-        <v>Issue Description</v>
-      </c>
-      <c r="E85" t="str">
-        <v>Engine Failure</v>
-      </c>
-      <c r="F85">
-        <v>2</v>
-      </c>
-      <c r="G85" t="str">
-        <v/>
-      </c>
-      <c r="H85" t="str">
-        <v/>
-      </c>
-      <c r="I85" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>CLAIM_COMPLAINT_TYPE-01</v>
-      </c>
-      <c r="B86" t="str">
-        <v>CLAIM_COMPLAINT_TYPE</v>
-      </c>
-      <c r="C86" t="str">
-        <v>CLAIM</v>
-      </c>
-      <c r="D86" t="str">
-        <v>Complaint Type</v>
-      </c>
-      <c r="E86" t="str">
-        <v>Transmission</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-      <c r="G86" t="str">
-        <v/>
-      </c>
-      <c r="H86" t="str">
-        <v/>
-      </c>
-      <c r="I86" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>CLAIM_COMPLAINT_TYPE-02</v>
-      </c>
-      <c r="B87" t="str">
-        <v>CLAIM_COMPLAINT_TYPE</v>
-      </c>
-      <c r="C87" t="str">
-        <v>CLAIM</v>
-      </c>
-      <c r="D87" t="str">
-        <v>Complaint Type</v>
-      </c>
-      <c r="E87" t="str">
-        <v>Clutch</v>
-      </c>
-      <c r="F87">
-        <v>2</v>
-      </c>
-      <c r="G87" t="str">
-        <v/>
-      </c>
-      <c r="H87" t="str">
-        <v/>
-      </c>
-      <c r="I87" t="str">
-        <v>Active</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -26336,7 +26381,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -26398,7 +26443,7 @@
         <v>Steering shudder or brake pedal vibration on deceleration</v>
       </c>
       <c r="E3" t="str">
-        <v>PV + EV</v>
+        <v>PV</v>
       </c>
       <c r="F3" t="str">
         <v>High</v>
@@ -26409,16 +26454,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CC-03</v>
+        <v>CC-02-EV</v>
       </c>
       <c r="B4" t="str">
-        <v>BAT-SOC-03</v>
+        <v>BRK-VIB-02</v>
       </c>
       <c r="C4" t="str">
-        <v>Electrical &amp; Battery</v>
+        <v>Brakes &amp; Suspension</v>
       </c>
       <c r="D4" t="str">
-        <v>Sudden drop in EV Battery SOC / Limited Performance turtle lamp</v>
+        <v>Steering shudder or brake pedal vibration on deceleration</v>
       </c>
       <c r="E4" t="str">
         <v>EV</v>
@@ -26432,22 +26477,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CC-04</v>
+        <v>CC-03</v>
       </c>
       <c r="B5" t="str">
-        <v>AC-COOL-04</v>
+        <v>BAT-SOC-03</v>
       </c>
       <c r="C5" t="str">
-        <v>HVAC &amp; AC</v>
+        <v>Electrical &amp; Battery</v>
       </c>
       <c r="D5" t="str">
-        <v>Insufficient cooling during idle or city traffic</v>
+        <v>Sudden drop in EV Battery SOC / Limited Performance turtle lamp</v>
       </c>
       <c r="E5" t="str">
-        <v>PV + EV</v>
+        <v>EV</v>
       </c>
       <c r="F5" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="G5" t="str">
         <v>Y</v>
@@ -26455,30 +26500,99 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>CC-04</v>
+      </c>
+      <c r="B6" t="str">
+        <v>AC-COOL-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>HVAC &amp; AC</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Insufficient cooling during idle or city traffic</v>
+      </c>
+      <c r="E6" t="str">
+        <v>PV</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CC-04-EV</v>
+      </c>
+      <c r="B7" t="str">
+        <v>AC-COOL-04</v>
+      </c>
+      <c r="C7" t="str">
+        <v>HVAC &amp; AC</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Insufficient cooling during idle or city traffic</v>
+      </c>
+      <c r="E7" t="str">
+        <v>EV</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
         <v>CC-05</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B8" t="str">
         <v>INFO-SCR-05</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C8" t="str">
         <v>Infotainment &amp; Connected</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D8" t="str">
         <v>Harman touchscreen blanking / Apple CarPlay disconnects</v>
       </c>
-      <c r="E6" t="str">
-        <v>PV + EV</v>
-      </c>
-      <c r="F6" t="str">
+      <c r="E8" t="str">
+        <v>PV</v>
+      </c>
+      <c r="F8" t="str">
         <v>Low</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G8" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CC-05-EV</v>
+      </c>
+      <c r="B9" t="str">
+        <v>INFO-SCR-05</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Infotainment &amp; Connected</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Harman touchscreen blanking / Apple CarPlay disconnects</v>
+      </c>
+      <c r="E9" t="str">
+        <v>EV</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="G9" t="str">
         <v>Y</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G9"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -5539,7 +5539,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q300"/>
+  <dimension ref="A1:Q302"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5611,7 +5611,7 @@
         <v>Y</v>
       </c>
       <c r="F2" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -6777,7 +6777,7 @@
         <v>N</v>
       </c>
       <c r="F24" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -8208,7 +8208,7 @@
         <v>N</v>
       </c>
       <c r="F51" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -9162,7 +9162,7 @@
         <v>Y</v>
       </c>
       <c r="F69" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -11812,7 +11812,7 @@
         <v>Y</v>
       </c>
       <c r="F119" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -12395,7 +12395,7 @@
         <v>Y</v>
       </c>
       <c r="F130" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -12978,7 +12978,7 @@
         <v>Y</v>
       </c>
       <c r="F141" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -16582,7 +16582,7 @@
         <v>Y</v>
       </c>
       <c r="F209" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G209" t="str">
         <v/>
@@ -16847,7 +16847,7 @@
         <v>Y</v>
       </c>
       <c r="F214" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G214" t="str">
         <v/>
@@ -19550,7 +19550,7 @@
         <v>Y</v>
       </c>
       <c r="F265" t="str">
-        <v>PV, EV, CV</v>
+        <v>PV, EV</v>
       </c>
       <c r="G265" t="str">
         <v/>
@@ -21025,7 +21025,7 @@
         <v>lovCode</v>
       </c>
       <c r="C293" t="str">
-        <v>Parameter (LOV Code)</v>
+        <v>LOV Type (Parameter)</v>
       </c>
       <c r="D293" t="str">
         <v>text</v>
@@ -21184,7 +21184,7 @@
         <v>value</v>
       </c>
       <c r="C296" t="str">
-        <v>Value</v>
+        <v>Display Value</v>
       </c>
       <c r="D296" t="str">
         <v>text</v>
@@ -21226,7 +21226,7 @@
         <v/>
       </c>
       <c r="Q296" t="str">
-        <v/>
+        <v>What users see in the dropdown.</v>
       </c>
     </row>
     <row r="297">
@@ -21234,25 +21234,25 @@
         <v>common_lov</v>
       </c>
       <c r="B297" t="str">
-        <v>order</v>
+        <v>lic</v>
       </c>
       <c r="C297" t="str">
-        <v>Order</v>
+        <v>Code (LIC)</v>
       </c>
       <c r="D297" t="str">
-        <v>number</v>
+        <v>text</v>
       </c>
       <c r="E297" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F297" t="str">
         <v/>
       </c>
-      <c r="G297">
-        <v>1</v>
-      </c>
-      <c r="H297">
-        <v>999</v>
+      <c r="G297" t="str">
+        <v/>
+      </c>
+      <c r="H297" t="str">
+        <v/>
       </c>
       <c r="I297" t="str">
         <v/>
@@ -21261,10 +21261,10 @@
         <v/>
       </c>
       <c r="K297" t="str">
-        <v/>
+        <v>^[A-Z0-9][A-Z0-9_]*$</v>
       </c>
       <c r="L297" t="str">
-        <v/>
+        <v>Capitals, digits and _ only, e.g. WORK_IN_PROCESS.</v>
       </c>
       <c r="M297" t="str">
         <v>N</v>
@@ -21279,7 +21279,7 @@
         <v/>
       </c>
       <c r="Q297" t="str">
-        <v>Position in the dropdown.</v>
+        <v>Language-independent code kept in records; stays the same when the Display Value wording changes.</v>
       </c>
     </row>
     <row r="298">
@@ -21287,25 +21287,25 @@
         <v>common_lov</v>
       </c>
       <c r="B298" t="str">
-        <v>parentLovCode</v>
+        <v>order</v>
       </c>
       <c r="C298" t="str">
-        <v>Parent LOV Code</v>
+        <v>Order</v>
       </c>
       <c r="D298" t="str">
-        <v>text</v>
+        <v>number</v>
       </c>
       <c r="E298" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F298" t="str">
         <v/>
       </c>
-      <c r="G298" t="str">
-        <v/>
-      </c>
-      <c r="H298" t="str">
-        <v/>
+      <c r="G298">
+        <v>1</v>
+      </c>
+      <c r="H298">
+        <v>999</v>
       </c>
       <c r="I298" t="str">
         <v/>
@@ -21332,7 +21332,7 @@
         <v/>
       </c>
       <c r="Q298" t="str">
-        <v>Dependent dropdowns only: the list this value depends on.</v>
+        <v>Position in the dropdown.</v>
       </c>
     </row>
     <row r="299">
@@ -21340,10 +21340,10 @@
         <v>common_lov</v>
       </c>
       <c r="B299" t="str">
-        <v>parentValue</v>
+        <v>parentLovCode</v>
       </c>
       <c r="C299" t="str">
-        <v>Parent Value</v>
+        <v>Parent LOV Code</v>
       </c>
       <c r="D299" t="str">
         <v>text</v>
@@ -21385,7 +21385,7 @@
         <v/>
       </c>
       <c r="Q299" t="str">
-        <v>Dependent dropdowns only: the parent list value that shows this value.</v>
+        <v>Dependent dropdowns only: the list this value depends on.</v>
       </c>
     </row>
     <row r="300">
@@ -21393,57 +21393,163 @@
         <v>common_lov</v>
       </c>
       <c r="B300" t="str">
+        <v>parentValue</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Parent Value</v>
+      </c>
+      <c r="D300" t="str">
+        <v>text</v>
+      </c>
+      <c r="E300" t="str">
+        <v>N</v>
+      </c>
+      <c r="F300" t="str">
+        <v/>
+      </c>
+      <c r="G300" t="str">
+        <v/>
+      </c>
+      <c r="H300" t="str">
+        <v/>
+      </c>
+      <c r="I300" t="str">
+        <v/>
+      </c>
+      <c r="J300" t="str">
+        <v/>
+      </c>
+      <c r="K300" t="str">
+        <v/>
+      </c>
+      <c r="L300" t="str">
+        <v/>
+      </c>
+      <c r="M300" t="str">
+        <v>N</v>
+      </c>
+      <c r="N300" t="str">
+        <v/>
+      </c>
+      <c r="O300" t="str">
+        <v/>
+      </c>
+      <c r="P300" t="str">
+        <v/>
+      </c>
+      <c r="Q300" t="str">
+        <v>Dependent dropdowns only: the parent list value that shows this value.</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>common_lov</v>
+      </c>
+      <c r="B301" t="str">
+        <v>description</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Description</v>
+      </c>
+      <c r="D301" t="str">
+        <v>text</v>
+      </c>
+      <c r="E301" t="str">
+        <v>N</v>
+      </c>
+      <c r="F301" t="str">
+        <v/>
+      </c>
+      <c r="G301" t="str">
+        <v/>
+      </c>
+      <c r="H301" t="str">
+        <v/>
+      </c>
+      <c r="I301" t="str">
+        <v/>
+      </c>
+      <c r="J301" t="str">
+        <v/>
+      </c>
+      <c r="K301" t="str">
+        <v/>
+      </c>
+      <c r="L301" t="str">
+        <v/>
+      </c>
+      <c r="M301" t="str">
+        <v>N</v>
+      </c>
+      <c r="N301" t="str">
+        <v/>
+      </c>
+      <c r="O301" t="str">
+        <v/>
+      </c>
+      <c r="P301" t="str">
+        <v/>
+      </c>
+      <c r="Q301" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>common_lov</v>
+      </c>
+      <c r="B302" t="str">
         <v>status</v>
       </c>
-      <c r="C300" t="str">
+      <c r="C302" t="str">
         <v>Status</v>
       </c>
-      <c r="D300" t="str">
+      <c r="D302" t="str">
         <v>select</v>
       </c>
-      <c r="E300" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F300" t="str">
+      <c r="E302" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F302" t="str">
         <v>Active, Inactive</v>
       </c>
-      <c r="G300" t="str">
-        <v/>
-      </c>
-      <c r="H300" t="str">
-        <v/>
-      </c>
-      <c r="I300" t="str">
-        <v/>
-      </c>
-      <c r="J300" t="str">
-        <v/>
-      </c>
-      <c r="K300" t="str">
-        <v/>
-      </c>
-      <c r="L300" t="str">
-        <v/>
-      </c>
-      <c r="M300" t="str">
-        <v>N</v>
-      </c>
-      <c r="N300" t="str">
-        <v/>
-      </c>
-      <c r="O300" t="str">
-        <v/>
-      </c>
-      <c r="P300" t="str">
-        <v/>
-      </c>
-      <c r="Q300" t="str">
+      <c r="G302" t="str">
+        <v/>
+      </c>
+      <c r="H302" t="str">
+        <v/>
+      </c>
+      <c r="I302" t="str">
+        <v/>
+      </c>
+      <c r="J302" t="str">
+        <v/>
+      </c>
+      <c r="K302" t="str">
+        <v/>
+      </c>
+      <c r="L302" t="str">
+        <v/>
+      </c>
+      <c r="M302" t="str">
+        <v>N</v>
+      </c>
+      <c r="N302" t="str">
+        <v/>
+      </c>
+      <c r="O302" t="str">
+        <v/>
+      </c>
+      <c r="P302" t="str">
+        <v/>
+      </c>
+      <c r="Q302" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q300"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q302"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -23648,7 +23754,7 @@
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:K82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -23667,15 +23773,21 @@
         <v>value</v>
       </c>
       <c r="F1" t="str">
+        <v>lic</v>
+      </c>
+      <c r="G1" t="str">
         <v>order</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>parentLovCode</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>parentValue</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
+        <v>description</v>
+      </c>
+      <c r="K1" t="str">
         <v>status</v>
       </c>
     </row>
@@ -23695,16 +23807,22 @@
       <c r="E2" t="str">
         <v>PV</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <v>PV</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
         <v>Active</v>
       </c>
     </row>
@@ -23724,51 +23842,63 @@
       <c r="E3" t="str">
         <v>EV</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
+        <v>EV</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>COMMON_BU-03</v>
+        <v>THD_PROGRESS-01</v>
       </c>
       <c r="B4" t="str">
-        <v>COMMON_BU</v>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="C4" t="str">
-        <v>COMMON</v>
+        <v>THD</v>
       </c>
       <c r="D4" t="str">
-        <v>BU</v>
+        <v>Progress</v>
       </c>
       <c r="E4" t="str">
-        <v>CV</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
+        <v>Under Diagnosis</v>
+      </c>
+      <c r="F4" t="str">
+        <v>UNDER_DIAGNOSIS</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>THD_PROGRESS-01</v>
+        <v>THD_PROGRESS-02</v>
       </c>
       <c r="B5" t="str">
         <v>THD_PROGRESS</v>
@@ -23780,24 +23910,30 @@
         <v>Progress</v>
       </c>
       <c r="E5" t="str">
-        <v>Under Diagnosis</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
+        <v>Work in process</v>
+      </c>
+      <c r="F5" t="str">
+        <v>WORK_IN_PROCESS</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>THD_PROGRESS-02</v>
+        <v>THD_PROGRESS-03</v>
       </c>
       <c r="B6" t="str">
         <v>THD_PROGRESS</v>
@@ -23809,24 +23945,30 @@
         <v>Progress</v>
       </c>
       <c r="E6" t="str">
-        <v>Work in process</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
+        <v>Pending for parts</v>
+      </c>
+      <c r="F6" t="str">
+        <v>PENDING_FOR_PARTS</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>THD_PROGRESS-03</v>
+        <v>THD_PROGRESS-04</v>
       </c>
       <c r="B7" t="str">
         <v>THD_PROGRESS</v>
@@ -23838,24 +23980,30 @@
         <v>Progress</v>
       </c>
       <c r="E7" t="str">
-        <v>Pending for parts</v>
-      </c>
-      <c r="F7">
-        <v>3</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
+        <v>Pending for vendor support</v>
+      </c>
+      <c r="F7" t="str">
+        <v>PENDING_FOR_VENDOR_SUPPORT</v>
+      </c>
+      <c r="G7">
+        <v>4</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>THD_PROGRESS-04</v>
+        <v>THD_PROGRESS-05</v>
       </c>
       <c r="B8" t="str">
         <v>THD_PROGRESS</v>
@@ -23867,24 +24015,30 @@
         <v>Progress</v>
       </c>
       <c r="E8" t="str">
-        <v>Pending for vendor support</v>
-      </c>
-      <c r="F8">
-        <v>4</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
+        <v>Pending for commercial decision</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PENDING_FOR_COMMERCIAL_DECISION</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>THD_PROGRESS-05</v>
+        <v>THD_PROGRESS-06</v>
       </c>
       <c r="B9" t="str">
         <v>THD_PROGRESS</v>
@@ -23896,53 +24050,65 @@
         <v>Progress</v>
       </c>
       <c r="E9" t="str">
-        <v>Pending for commercial decision</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
+        <v>Pending for Vehicle availability</v>
+      </c>
+      <c r="F9" t="str">
+        <v>PENDING_FOR_VEHICLE_AVAILABILITY</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>THD_PROGRESS-06</v>
+        <v>THD_PROGRESS_SUB_STATUS-01</v>
       </c>
       <c r="B10" t="str">
-        <v>THD_PROGRESS</v>
+        <v>THD_PROGRESS_SUB_STATUS</v>
       </c>
       <c r="C10" t="str">
         <v>THD</v>
       </c>
       <c r="D10" t="str">
-        <v>Progress</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="E10" t="str">
-        <v>Pending for Vehicle availability</v>
-      </c>
-      <c r="F10">
-        <v>6</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
+        <v>U/I DET</v>
+      </c>
+      <c r="F10" t="str">
+        <v>U_I_DET</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="I10" t="str">
+        <v>Under Diagnosis</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-01</v>
+        <v>THD_PROGRESS_SUB_STATUS-02</v>
       </c>
       <c r="B11" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -23954,24 +24120,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E11" t="str">
-        <v>U/I DET</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
+        <v>U/I COC</v>
+      </c>
+      <c r="F11" t="str">
+        <v>U_I_COC</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>Under Diagnosis</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-02</v>
+        <v>THD_PROGRESS_SUB_STATUS-03</v>
       </c>
       <c r="B12" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -23983,24 +24155,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E12" t="str">
-        <v>U/I COC</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12" t="str">
+        <v>U/I Vendor</v>
+      </c>
+      <c r="F12" t="str">
+        <v>U_I_VENDOR</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>Under Diagnosis</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-03</v>
+        <v>THD_PROGRESS_SUB_STATUS-04</v>
       </c>
       <c r="B13" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24012,24 +24190,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E13" t="str">
-        <v>U/I Vendor</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13" t="str">
+        <v>U/I Plant Team</v>
+      </c>
+      <c r="F13" t="str">
+        <v>U_I_PLANT_TEAM</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>Under Diagnosis</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-04</v>
+        <v>THD_PROGRESS_SUB_STATUS-05</v>
       </c>
       <c r="B14" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24041,24 +24225,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E14" t="str">
-        <v>U/I Plant Team</v>
-      </c>
-      <c r="F14">
-        <v>4</v>
-      </c>
-      <c r="G14" t="str">
+        <v>WIP DET</v>
+      </c>
+      <c r="F14" t="str">
+        <v>WIP_DET</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H14" t="str">
-        <v>Under Diagnosis</v>
-      </c>
       <c r="I14" t="str">
+        <v>Work in process</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-05</v>
+        <v>THD_PROGRESS_SUB_STATUS-06</v>
       </c>
       <c r="B15" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24070,24 +24260,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E15" t="str">
-        <v>WIP DET</v>
-      </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-      <c r="G15" t="str">
+        <v>WIP W/S Team</v>
+      </c>
+      <c r="F15" t="str">
+        <v>WIP_W_S_TEAM</v>
+      </c>
+      <c r="G15">
+        <v>6</v>
+      </c>
+      <c r="H15" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <v>Work in process</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-06</v>
+        <v>THD_PROGRESS_SUB_STATUS-07</v>
       </c>
       <c r="B16" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24099,24 +24295,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E16" t="str">
-        <v>WIP W/S Team</v>
-      </c>
-      <c r="F16">
-        <v>6</v>
-      </c>
-      <c r="G16" t="str">
+        <v>WIP Vendor</v>
+      </c>
+      <c r="F16" t="str">
+        <v>WIP_VENDOR</v>
+      </c>
+      <c r="G16">
+        <v>7</v>
+      </c>
+      <c r="H16" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <v>Work in process</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-07</v>
+        <v>THD_PROGRESS_SUB_STATUS-08</v>
       </c>
       <c r="B17" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24128,24 +24330,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E17" t="str">
-        <v>WIP Vendor</v>
-      </c>
-      <c r="F17">
-        <v>7</v>
-      </c>
-      <c r="G17" t="str">
+        <v>Order status</v>
+      </c>
+      <c r="F17" t="str">
+        <v>ORDER_STATUS</v>
+      </c>
+      <c r="G17">
+        <v>8</v>
+      </c>
+      <c r="H17" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H17" t="str">
-        <v>Work in process</v>
-      </c>
       <c r="I17" t="str">
+        <v>Pending for parts</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-08</v>
+        <v>THD_PROGRESS_SUB_STATUS-09</v>
       </c>
       <c r="B18" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24157,24 +24365,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E18" t="str">
-        <v>Order status</v>
-      </c>
-      <c r="F18">
-        <v>8</v>
-      </c>
-      <c r="G18" t="str">
+        <v>Part receipt status</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PART_RECEIPT_STATUS</v>
+      </c>
+      <c r="G18">
+        <v>9</v>
+      </c>
+      <c r="H18" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <v>Pending for parts</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-09</v>
+        <v>THD_PROGRESS_SUB_STATUS-10</v>
       </c>
       <c r="B19" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24186,24 +24400,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E19" t="str">
-        <v>Part receipt status</v>
-      </c>
-      <c r="F19">
-        <v>9</v>
-      </c>
-      <c r="G19" t="str">
+        <v>Vendor details</v>
+      </c>
+      <c r="F19" t="str">
+        <v>VENDOR_DETAILS</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H19" t="str">
-        <v>Pending for parts</v>
-      </c>
       <c r="I19" t="str">
+        <v>Pending for vendor support</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-10</v>
+        <v>THD_PROGRESS_SUB_STATUS-11</v>
       </c>
       <c r="B20" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24215,24 +24435,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E20" t="str">
-        <v>Vendor details</v>
-      </c>
-      <c r="F20">
-        <v>10</v>
-      </c>
-      <c r="G20" t="str">
+        <v>Request raised</v>
+      </c>
+      <c r="F20" t="str">
+        <v>REQUEST_RAISED</v>
+      </c>
+      <c r="G20">
+        <v>11</v>
+      </c>
+      <c r="H20" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <v>Pending for vendor support</v>
       </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-11</v>
+        <v>THD_PROGRESS_SUB_STATUS-12</v>
       </c>
       <c r="B21" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24244,24 +24470,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E21" t="str">
-        <v>Request raised</v>
-      </c>
-      <c r="F21">
-        <v>11</v>
-      </c>
-      <c r="G21" t="str">
+        <v>Status</v>
+      </c>
+      <c r="F21" t="str">
+        <v>STATUS</v>
+      </c>
+      <c r="G21">
+        <v>12</v>
+      </c>
+      <c r="H21" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <v>Pending for vendor support</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-12</v>
+        <v>THD_PROGRESS_SUB_STATUS-13</v>
       </c>
       <c r="B22" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24273,24 +24505,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E22" t="str">
-        <v>Status</v>
-      </c>
-      <c r="F22">
-        <v>12</v>
-      </c>
-      <c r="G22" t="str">
+        <v>Pending for approval</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PENDING_FOR_APPROVAL</v>
+      </c>
+      <c r="G22">
+        <v>13</v>
+      </c>
+      <c r="H22" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H22" t="str">
-        <v>Pending for vendor support</v>
-      </c>
       <c r="I22" t="str">
+        <v>Pending for commercial decision</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-13</v>
+        <v>THD_PROGRESS_SUB_STATUS-14</v>
       </c>
       <c r="B23" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24302,24 +24540,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E23" t="str">
-        <v>Pending for approval</v>
-      </c>
-      <c r="F23">
-        <v>13</v>
-      </c>
-      <c r="G23" t="str">
+        <v>Approval received</v>
+      </c>
+      <c r="F23" t="str">
+        <v>APPROVAL_RECEIVED</v>
+      </c>
+      <c r="G23">
+        <v>14</v>
+      </c>
+      <c r="H23" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <v>Pending for commercial decision</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-14</v>
+        <v>THD_PROGRESS_SUB_STATUS-15</v>
       </c>
       <c r="B24" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24331,24 +24575,30 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E24" t="str">
-        <v>Approval received</v>
-      </c>
-      <c r="F24">
-        <v>14</v>
-      </c>
-      <c r="G24" t="str">
+        <v>Expected date</v>
+      </c>
+      <c r="F24" t="str">
+        <v>EXPECTED_DATE</v>
+      </c>
+      <c r="G24">
+        <v>15</v>
+      </c>
+      <c r="H24" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H24" t="str">
-        <v>Pending for commercial decision</v>
-      </c>
       <c r="I24" t="str">
+        <v>Pending for Vehicle availability</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-15</v>
+        <v>THD_PROGRESS_SUB_STATUS-16</v>
       </c>
       <c r="B25" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -24360,53 +24610,65 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E25" t="str">
-        <v>Expected date</v>
-      </c>
-      <c r="F25">
-        <v>15</v>
-      </c>
-      <c r="G25" t="str">
+        <v>Status as on date</v>
+      </c>
+      <c r="F25" t="str">
+        <v>STATUS_AS_ON_DATE</v>
+      </c>
+      <c r="G25">
+        <v>16</v>
+      </c>
+      <c r="H25" t="str">
         <v>THD_PROGRESS</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <v>Pending for Vehicle availability</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-16</v>
+        <v>THD_COMPLAINT_TYPE-01</v>
       </c>
       <c r="B26" t="str">
-        <v>THD_PROGRESS_SUB_STATUS</v>
+        <v>THD_COMPLAINT_TYPE</v>
       </c>
       <c r="C26" t="str">
         <v>THD</v>
       </c>
       <c r="D26" t="str">
-        <v>Progress Sub Status</v>
+        <v>Type of Complaint</v>
       </c>
       <c r="E26" t="str">
-        <v>Status as on date</v>
-      </c>
-      <c r="F26">
-        <v>16</v>
-      </c>
-      <c r="G26" t="str">
-        <v>THD_PROGRESS</v>
+        <v>Technical Query</v>
+      </c>
+      <c r="F26" t="str">
+        <v>TECHNICAL_QUERY</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
       </c>
       <c r="H26" t="str">
-        <v>Pending for Vehicle availability</v>
+        <v/>
       </c>
       <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>THD_COMPLAINT_TYPE-01</v>
+        <v>THD_COMPLAINT_TYPE-02</v>
       </c>
       <c r="B27" t="str">
         <v>THD_COMPLAINT_TYPE</v>
@@ -24418,53 +24680,65 @@
         <v>Type of Complaint</v>
       </c>
       <c r="E27" t="str">
-        <v>Technical Query</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" t="str">
-        <v/>
+        <v>Technical Support</v>
+      </c>
+      <c r="F27" t="str">
+        <v>TECHNICAL_SUPPORT</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
       </c>
       <c r="H27" t="str">
         <v/>
       </c>
       <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>THD_COMPLAINT_TYPE-02</v>
+        <v>THD_COMPLAINT_SHORT_DESC-01</v>
       </c>
       <c r="B28" t="str">
-        <v>THD_COMPLAINT_TYPE</v>
+        <v>THD_COMPLAINT_SHORT_DESC</v>
       </c>
       <c r="C28" t="str">
         <v>THD</v>
       </c>
       <c r="D28" t="str">
-        <v>Type of Complaint</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="E28" t="str">
-        <v>Technical Support</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
-      <c r="G28" t="str">
-        <v/>
+        <v>Abnormal noise</v>
+      </c>
+      <c r="F28" t="str">
+        <v>ABNORMAL_NOISE</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
       </c>
       <c r="H28" t="str">
         <v/>
       </c>
       <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-01</v>
+        <v>THD_COMPLAINT_SHORT_DESC-02</v>
       </c>
       <c r="B29" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24476,24 +24750,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E29" t="str">
-        <v>Abnormal noise</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="str">
-        <v/>
+        <v>Warning lamps ON</v>
+      </c>
+      <c r="F29" t="str">
+        <v>WARNING_LAMPS_ON</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
       </c>
       <c r="H29" t="str">
         <v/>
       </c>
       <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-02</v>
+        <v>THD_COMPLAINT_SHORT_DESC-03</v>
       </c>
       <c r="B30" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24505,24 +24785,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E30" t="str">
-        <v>Warning lamps ON</v>
-      </c>
-      <c r="F30">
-        <v>2</v>
-      </c>
-      <c r="G30" t="str">
-        <v/>
+        <v>Oil leakage</v>
+      </c>
+      <c r="F30" t="str">
+        <v>OIL_LEAKAGE</v>
+      </c>
+      <c r="G30">
+        <v>3</v>
       </c>
       <c r="H30" t="str">
         <v/>
       </c>
       <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-03</v>
+        <v>THD_COMPLAINT_SHORT_DESC-04</v>
       </c>
       <c r="B31" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24534,24 +24820,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E31" t="str">
-        <v>Oil leakage</v>
-      </c>
-      <c r="F31">
-        <v>3</v>
-      </c>
-      <c r="G31" t="str">
-        <v/>
+        <v>Coolant leakage</v>
+      </c>
+      <c r="F31" t="str">
+        <v>COOLANT_LEAKAGE</v>
+      </c>
+      <c r="G31">
+        <v>4</v>
       </c>
       <c r="H31" t="str">
         <v/>
       </c>
       <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-04</v>
+        <v>THD_COMPLAINT_SHORT_DESC-05</v>
       </c>
       <c r="B32" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24563,24 +24855,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E32" t="str">
-        <v>Coolant leakage</v>
-      </c>
-      <c r="F32">
-        <v>4</v>
-      </c>
-      <c r="G32" t="str">
-        <v/>
+        <v>Engine overheating</v>
+      </c>
+      <c r="F32" t="str">
+        <v>ENGINE_OVERHEATING</v>
+      </c>
+      <c r="G32">
+        <v>5</v>
       </c>
       <c r="H32" t="str">
         <v/>
       </c>
       <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-05</v>
+        <v>THD_COMPLAINT_SHORT_DESC-06</v>
       </c>
       <c r="B33" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24592,24 +24890,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E33" t="str">
-        <v>Engine overheating</v>
-      </c>
-      <c r="F33">
-        <v>5</v>
-      </c>
-      <c r="G33" t="str">
-        <v/>
+        <v>Smell – burning, fuel, foul odor from outside, etc.</v>
+      </c>
+      <c r="F33" t="str">
+        <v>SMELL_BURNING_FUEL_FOUL_ODOR_FROM_OUTSID</v>
+      </c>
+      <c r="G33">
+        <v>6</v>
       </c>
       <c r="H33" t="str">
         <v/>
       </c>
       <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-06</v>
+        <v>THD_COMPLAINT_SHORT_DESC-07</v>
       </c>
       <c r="B34" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24621,24 +24925,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E34" t="str">
-        <v>Smell – burning, fuel, foul odor from outside, etc.</v>
-      </c>
-      <c r="F34">
-        <v>6</v>
-      </c>
-      <c r="G34" t="str">
-        <v/>
+        <v>Smoke issues</v>
+      </c>
+      <c r="F34" t="str">
+        <v>SMOKE_ISSUES</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
       </c>
       <c r="H34" t="str">
         <v/>
       </c>
       <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-07</v>
+        <v>THD_COMPLAINT_SHORT_DESC-08</v>
       </c>
       <c r="B35" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24650,24 +24960,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E35" t="str">
-        <v>Smoke issues</v>
-      </c>
-      <c r="F35">
-        <v>7</v>
-      </c>
-      <c r="G35" t="str">
-        <v/>
+        <v>Oil-Coolant mix</v>
+      </c>
+      <c r="F35" t="str">
+        <v>OIL_COOLANT_MIX</v>
+      </c>
+      <c r="G35">
+        <v>8</v>
       </c>
       <c r="H35" t="str">
         <v/>
       </c>
       <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-08</v>
+        <v>THD_COMPLAINT_SHORT_DESC-09</v>
       </c>
       <c r="B36" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24679,24 +24995,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E36" t="str">
-        <v>Oil-Coolant mix</v>
-      </c>
-      <c r="F36">
-        <v>8</v>
-      </c>
-      <c r="G36" t="str">
-        <v/>
+        <v>Gear shifting issues</v>
+      </c>
+      <c r="F36" t="str">
+        <v>GEAR_SHIFTING_ISSUES</v>
+      </c>
+      <c r="G36">
+        <v>9</v>
       </c>
       <c r="H36" t="str">
         <v/>
       </c>
       <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-09</v>
+        <v>THD_COMPLAINT_SHORT_DESC-10</v>
       </c>
       <c r="B37" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24708,24 +25030,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E37" t="str">
-        <v>Gear shifting issues</v>
-      </c>
-      <c r="F37">
-        <v>9</v>
-      </c>
-      <c r="G37" t="str">
-        <v/>
+        <v>AC cooling issues</v>
+      </c>
+      <c r="F37" t="str">
+        <v>AC_COOLING_ISSUES</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
       </c>
       <c r="H37" t="str">
         <v/>
       </c>
       <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-10</v>
+        <v>THD_COMPLAINT_SHORT_DESC-11</v>
       </c>
       <c r="B38" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24737,24 +25065,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E38" t="str">
-        <v>AC cooling issues</v>
-      </c>
-      <c r="F38">
-        <v>10</v>
-      </c>
-      <c r="G38" t="str">
-        <v/>
+        <v>Jerking / vibration / misfiring</v>
+      </c>
+      <c r="F38" t="str">
+        <v>JERKING_VIBRATION_MISFIRING</v>
+      </c>
+      <c r="G38">
+        <v>11</v>
       </c>
       <c r="H38" t="str">
         <v/>
       </c>
       <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-11</v>
+        <v>THD_COMPLAINT_SHORT_DESC-12</v>
       </c>
       <c r="B39" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24766,24 +25100,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E39" t="str">
-        <v>Jerking / vibration / misfiring</v>
-      </c>
-      <c r="F39">
-        <v>11</v>
-      </c>
-      <c r="G39" t="str">
-        <v/>
+        <v>Steering hard</v>
+      </c>
+      <c r="F39" t="str">
+        <v>STEERING_HARD</v>
+      </c>
+      <c r="G39">
+        <v>12</v>
       </c>
       <c r="H39" t="str">
         <v/>
       </c>
       <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-12</v>
+        <v>THD_COMPLAINT_SHORT_DESC-13</v>
       </c>
       <c r="B40" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24795,24 +25135,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E40" t="str">
-        <v>Steering hard</v>
-      </c>
-      <c r="F40">
-        <v>12</v>
-      </c>
-      <c r="G40" t="str">
-        <v/>
+        <v>Vehicle pulling</v>
+      </c>
+      <c r="F40" t="str">
+        <v>VEHICLE_PULLING</v>
+      </c>
+      <c r="G40">
+        <v>13</v>
       </c>
       <c r="H40" t="str">
         <v/>
       </c>
       <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-13</v>
+        <v>THD_COMPLAINT_SHORT_DESC-14</v>
       </c>
       <c r="B41" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24824,24 +25170,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E41" t="str">
-        <v>Vehicle pulling</v>
-      </c>
-      <c r="F41">
-        <v>13</v>
-      </c>
-      <c r="G41" t="str">
-        <v/>
+        <v>Starting problem</v>
+      </c>
+      <c r="F41" t="str">
+        <v>STARTING_PROBLEM</v>
+      </c>
+      <c r="G41">
+        <v>14</v>
       </c>
       <c r="H41" t="str">
         <v/>
       </c>
       <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-14</v>
+        <v>THD_COMPLAINT_SHORT_DESC-15</v>
       </c>
       <c r="B42" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24853,24 +25205,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E42" t="str">
-        <v>Starting problem</v>
-      </c>
-      <c r="F42">
-        <v>14</v>
-      </c>
-      <c r="G42" t="str">
-        <v/>
+        <v>Tyre wear / cut</v>
+      </c>
+      <c r="F42" t="str">
+        <v>TYRE_WEAR_CUT</v>
+      </c>
+      <c r="G42">
+        <v>15</v>
       </c>
       <c r="H42" t="str">
         <v/>
       </c>
       <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-15</v>
+        <v>THD_COMPLAINT_SHORT_DESC-16</v>
       </c>
       <c r="B43" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24882,24 +25240,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E43" t="str">
-        <v>Tyre wear / cut</v>
-      </c>
-      <c r="F43">
-        <v>15</v>
-      </c>
-      <c r="G43" t="str">
-        <v/>
+        <v>Damaged / broken / cracked / soiled</v>
+      </c>
+      <c r="F43" t="str">
+        <v>DAMAGED_BROKEN_CRACKED_SOILED</v>
+      </c>
+      <c r="G43">
+        <v>16</v>
       </c>
       <c r="H43" t="str">
         <v/>
       </c>
       <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-16</v>
+        <v>THD_COMPLAINT_SHORT_DESC-17</v>
       </c>
       <c r="B44" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24911,24 +25275,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E44" t="str">
-        <v>Damaged / broken / cracked / soiled</v>
-      </c>
-      <c r="F44">
-        <v>16</v>
-      </c>
-      <c r="G44" t="str">
-        <v/>
+        <v>Part missing / fallen-off</v>
+      </c>
+      <c r="F44" t="str">
+        <v>PART_MISSING_FALLEN_OFF</v>
+      </c>
+      <c r="G44">
+        <v>17</v>
       </c>
       <c r="H44" t="str">
         <v/>
       </c>
       <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-17</v>
+        <v>THD_COMPLAINT_SHORT_DESC-18</v>
       </c>
       <c r="B45" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24940,24 +25310,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E45" t="str">
-        <v>Part missing / fallen-off</v>
-      </c>
-      <c r="F45">
-        <v>17</v>
-      </c>
-      <c r="G45" t="str">
-        <v/>
+        <v>Uneven gaps / flushness issues</v>
+      </c>
+      <c r="F45" t="str">
+        <v>UNEVEN_GAPS_FLUSHNESS_ISSUES</v>
+      </c>
+      <c r="G45">
+        <v>18</v>
       </c>
       <c r="H45" t="str">
         <v/>
       </c>
       <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-18</v>
+        <v>THD_COMPLAINT_SHORT_DESC-19</v>
       </c>
       <c r="B46" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24969,24 +25345,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E46" t="str">
-        <v>Uneven gaps / flushness issues</v>
-      </c>
-      <c r="F46">
-        <v>18</v>
-      </c>
-      <c r="G46" t="str">
-        <v/>
+        <v>Paint / rust issues</v>
+      </c>
+      <c r="F46" t="str">
+        <v>PAINT_RUST_ISSUES</v>
+      </c>
+      <c r="G46">
+        <v>19</v>
       </c>
       <c r="H46" t="str">
         <v/>
       </c>
       <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-19</v>
+        <v>THD_COMPLAINT_SHORT_DESC-20</v>
       </c>
       <c r="B47" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -24998,24 +25380,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E47" t="str">
-        <v>Paint / rust issues</v>
-      </c>
-      <c r="F47">
-        <v>19</v>
-      </c>
-      <c r="G47" t="str">
-        <v/>
+        <v>Not working / functioning issues / system malfunction</v>
+      </c>
+      <c r="F47" t="str">
+        <v>NOT_WORKING_FUNCTIONING_ISSUES_SYSTEM_MA</v>
+      </c>
+      <c r="G47">
+        <v>20</v>
       </c>
       <c r="H47" t="str">
         <v/>
       </c>
       <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-20</v>
+        <v>THD_COMPLAINT_SHORT_DESC-21</v>
       </c>
       <c r="B48" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -25027,24 +25415,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E48" t="str">
-        <v>Not working / functioning issues / system malfunction</v>
-      </c>
-      <c r="F48">
-        <v>20</v>
-      </c>
-      <c r="G48" t="str">
-        <v/>
+        <v>Crash / airbag related issues</v>
+      </c>
+      <c r="F48" t="str">
+        <v>CRASH_AIRBAG_RELATED_ISSUES</v>
+      </c>
+      <c r="G48">
+        <v>21</v>
       </c>
       <c r="H48" t="str">
         <v/>
       </c>
       <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-21</v>
+        <v>THD_COMPLAINT_SHORT_DESC-22</v>
       </c>
       <c r="B49" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -25056,24 +25450,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E49" t="str">
-        <v>Crash / airbag related issues</v>
-      </c>
-      <c r="F49">
-        <v>21</v>
-      </c>
-      <c r="G49" t="str">
-        <v/>
+        <v>Thermal issues</v>
+      </c>
+      <c r="F49" t="str">
+        <v>THERMAL_ISSUES</v>
+      </c>
+      <c r="G49">
+        <v>22</v>
       </c>
       <c r="H49" t="str">
         <v/>
       </c>
       <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-22</v>
+        <v>THD_COMPLAINT_SHORT_DESC-23</v>
       </c>
       <c r="B50" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -25085,24 +25485,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E50" t="str">
-        <v>Thermal issues</v>
-      </c>
-      <c r="F50">
-        <v>22</v>
-      </c>
-      <c r="G50" t="str">
-        <v/>
+        <v>Brake ineffective</v>
+      </c>
+      <c r="F50" t="str">
+        <v>BRAKE_INEFFECTIVE</v>
+      </c>
+      <c r="G50">
+        <v>23</v>
       </c>
       <c r="H50" t="str">
         <v/>
       </c>
       <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-23</v>
+        <v>THD_COMPLAINT_SHORT_DESC-24</v>
       </c>
       <c r="B51" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -25114,24 +25520,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E51" t="str">
-        <v>Brake ineffective</v>
-      </c>
-      <c r="F51">
-        <v>23</v>
-      </c>
-      <c r="G51" t="str">
-        <v/>
+        <v>Poor pick-up</v>
+      </c>
+      <c r="F51" t="str">
+        <v>POOR_PICK_UP</v>
+      </c>
+      <c r="G51">
+        <v>24</v>
       </c>
       <c r="H51" t="str">
         <v/>
       </c>
       <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-24</v>
+        <v>THD_COMPLAINT_SHORT_DESC-25</v>
       </c>
       <c r="B52" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -25143,24 +25555,30 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E52" t="str">
-        <v>Poor pick-up</v>
-      </c>
-      <c r="F52">
-        <v>24</v>
-      </c>
-      <c r="G52" t="str">
-        <v/>
+        <v>Infotainment system issues</v>
+      </c>
+      <c r="F52" t="str">
+        <v>INFOTAINMENT_SYSTEM_ISSUES</v>
+      </c>
+      <c r="G52">
+        <v>25</v>
       </c>
       <c r="H52" t="str">
         <v/>
       </c>
       <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-25</v>
+        <v>THD_COMPLAINT_SHORT_DESC-26</v>
       </c>
       <c r="B53" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -25172,53 +25590,65 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E53" t="str">
-        <v>Infotainment system issues</v>
-      </c>
-      <c r="F53">
-        <v>25</v>
-      </c>
-      <c r="G53" t="str">
-        <v/>
+        <v>Water entry in cabin</v>
+      </c>
+      <c r="F53" t="str">
+        <v>WATER_ENTRY_IN_CABIN</v>
+      </c>
+      <c r="G53">
+        <v>26</v>
       </c>
       <c r="H53" t="str">
         <v/>
       </c>
       <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-26</v>
+        <v>THD_ACTION_TAKEN-01</v>
       </c>
       <c r="B54" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC</v>
+        <v>THD_ACTION_TAKEN</v>
       </c>
       <c r="C54" t="str">
         <v>THD</v>
       </c>
       <c r="D54" t="str">
-        <v>Complaint Short Description</v>
+        <v>Action Taken</v>
       </c>
       <c r="E54" t="str">
-        <v>Water entry in cabin</v>
-      </c>
-      <c r="F54">
-        <v>26</v>
-      </c>
-      <c r="G54" t="str">
-        <v/>
+        <v>Issue concluded and proceeded as per Field Investigation</v>
+      </c>
+      <c r="F54" t="str">
+        <v>ISSUE_CONCLUDED_AND_PROCEEDED_AS_PER_FIE</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
       </c>
       <c r="H54" t="str">
         <v/>
       </c>
       <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>THD_ACTION_TAKEN-01</v>
+        <v>THD_ACTION_TAKEN-02</v>
       </c>
       <c r="B55" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25230,24 +25660,30 @@
         <v>Action Taken</v>
       </c>
       <c r="E55" t="str">
-        <v>Issue concluded and proceeded as per Field Investigation</v>
-      </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
-      <c r="G55" t="str">
-        <v/>
+        <v>Suggested checks based on observations</v>
+      </c>
+      <c r="F55" t="str">
+        <v>SUGGESTED_CHECKS_BASED_ON_OBSERVATIONS</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
       </c>
       <c r="H55" t="str">
         <v/>
       </c>
       <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>THD_ACTION_TAKEN-02</v>
+        <v>THD_ACTION_TAKEN-03</v>
       </c>
       <c r="B56" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25259,24 +25695,30 @@
         <v>Action Taken</v>
       </c>
       <c r="E56" t="str">
-        <v>Suggested checks based on observations</v>
-      </c>
-      <c r="F56">
-        <v>2</v>
-      </c>
-      <c r="G56" t="str">
-        <v/>
+        <v>Known issue – suggested part replacement</v>
+      </c>
+      <c r="F56" t="str">
+        <v>KNOWN_ISSUE_SUGGESTED_PART_REPLACEMENT</v>
+      </c>
+      <c r="G56">
+        <v>3</v>
       </c>
       <c r="H56" t="str">
         <v/>
       </c>
       <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>THD_ACTION_TAKEN-03</v>
+        <v>THD_ACTION_TAKEN-04</v>
       </c>
       <c r="B57" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25288,24 +25730,30 @@
         <v>Action Taken</v>
       </c>
       <c r="E57" t="str">
-        <v>Known issue – suggested part replacement</v>
-      </c>
-      <c r="F57">
-        <v>3</v>
-      </c>
-      <c r="G57" t="str">
-        <v/>
+        <v>Updated software / parameterization</v>
+      </c>
+      <c r="F57" t="str">
+        <v>UPDATED_SOFTWARE_PARAMETERIZATION</v>
+      </c>
+      <c r="G57">
+        <v>4</v>
       </c>
       <c r="H57" t="str">
         <v/>
       </c>
       <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>THD_ACTION_TAKEN-04</v>
+        <v>THD_ACTION_TAKEN-05</v>
       </c>
       <c r="B58" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25317,24 +25765,30 @@
         <v>Action Taken</v>
       </c>
       <c r="E58" t="str">
-        <v>Updated software / parameterization</v>
-      </c>
-      <c r="F58">
-        <v>4</v>
-      </c>
-      <c r="G58" t="str">
-        <v/>
+        <v>Suggested part replacement based on observation</v>
+      </c>
+      <c r="F58" t="str">
+        <v>SUGGESTED_PART_REPLACEMENT_BASED_ON_OBSE</v>
+      </c>
+      <c r="G58">
+        <v>5</v>
       </c>
       <c r="H58" t="str">
         <v/>
       </c>
       <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>THD_ACTION_TAKEN-05</v>
+        <v>THD_ACTION_TAKEN-06</v>
       </c>
       <c r="B59" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25346,24 +25800,30 @@
         <v>Action Taken</v>
       </c>
       <c r="E59" t="str">
-        <v>Suggested part replacement based on observation</v>
-      </c>
-      <c r="F59">
-        <v>5</v>
-      </c>
-      <c r="G59" t="str">
-        <v/>
+        <v>Vehicle ready for delivery</v>
+      </c>
+      <c r="F59" t="str">
+        <v>VEHICLE_READY_FOR_DELIVERY</v>
+      </c>
+      <c r="G59">
+        <v>6</v>
       </c>
       <c r="H59" t="str">
         <v/>
       </c>
       <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>THD_ACTION_TAKEN-06</v>
+        <v>THD_ACTION_TAKEN-07</v>
       </c>
       <c r="B60" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -25375,53 +25835,65 @@
         <v>Action Taken</v>
       </c>
       <c r="E60" t="str">
-        <v>Vehicle ready for delivery</v>
-      </c>
-      <c r="F60">
-        <v>6</v>
-      </c>
-      <c r="G60" t="str">
-        <v/>
+        <v>Vehicle not available; is with Customer</v>
+      </c>
+      <c r="F60" t="str">
+        <v>VEHICLE_NOT_AVAILABLE_IS_WITH_CUSTOMER</v>
+      </c>
+      <c r="G60">
+        <v>7</v>
       </c>
       <c r="H60" t="str">
         <v/>
       </c>
       <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>THD_ACTION_TAKEN-07</v>
+        <v>THD_DELAY_REASON-01</v>
       </c>
       <c r="B61" t="str">
-        <v>THD_ACTION_TAKEN</v>
+        <v>THD_DELAY_REASON</v>
       </c>
       <c r="C61" t="str">
         <v>THD</v>
       </c>
       <c r="D61" t="str">
-        <v>Action Taken</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="E61" t="str">
-        <v>Vehicle not available; is with Customer</v>
-      </c>
-      <c r="F61">
-        <v>7</v>
-      </c>
-      <c r="G61" t="str">
-        <v/>
+        <v>Diagnosis and investigation</v>
+      </c>
+      <c r="F61" t="str">
+        <v>DIAGNOSIS_AND_INVESTIGATION</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
       </c>
       <c r="H61" t="str">
         <v/>
       </c>
       <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>THD_DELAY_REASON-01</v>
+        <v>THD_DELAY_REASON-02</v>
       </c>
       <c r="B62" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25433,24 +25905,30 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E62" t="str">
-        <v>Diagnosis and investigation</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
-      </c>
-      <c r="G62" t="str">
-        <v/>
+        <v>Work content</v>
+      </c>
+      <c r="F62" t="str">
+        <v>WORK_CONTENT</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
       </c>
       <c r="H62" t="str">
         <v/>
       </c>
       <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>THD_DELAY_REASON-02</v>
+        <v>THD_DELAY_REASON-03</v>
       </c>
       <c r="B63" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25462,24 +25940,30 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E63" t="str">
-        <v>Work content</v>
-      </c>
-      <c r="F63">
-        <v>2</v>
-      </c>
-      <c r="G63" t="str">
-        <v/>
+        <v>Non-availability of spare parts</v>
+      </c>
+      <c r="F63" t="str">
+        <v>NON_AVAILABILITY_OF_SPARE_PARTS</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
       </c>
       <c r="H63" t="str">
         <v/>
       </c>
       <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>THD_DELAY_REASON-03</v>
+        <v>THD_DELAY_REASON-04</v>
       </c>
       <c r="B64" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25491,24 +25975,30 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E64" t="str">
-        <v>Non-availability of spare parts</v>
-      </c>
-      <c r="F64">
-        <v>3</v>
-      </c>
-      <c r="G64" t="str">
-        <v/>
+        <v>Non-availability of vehicle</v>
+      </c>
+      <c r="F64" t="str">
+        <v>NON_AVAILABILITY_OF_VEHICLE</v>
+      </c>
+      <c r="G64">
+        <v>4</v>
       </c>
       <c r="H64" t="str">
         <v/>
       </c>
       <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>THD_DELAY_REASON-04</v>
+        <v>THD_DELAY_REASON-05</v>
       </c>
       <c r="B65" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25520,24 +26010,30 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E65" t="str">
-        <v>Non-availability of vehicle</v>
-      </c>
-      <c r="F65">
-        <v>4</v>
-      </c>
-      <c r="G65" t="str">
-        <v/>
+        <v>Dealer response</v>
+      </c>
+      <c r="F65" t="str">
+        <v>DEALER_RESPONSE</v>
+      </c>
+      <c r="G65">
+        <v>5</v>
       </c>
       <c r="H65" t="str">
         <v/>
       </c>
       <c r="I65" t="str">
+        <v/>
+      </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>THD_DELAY_REASON-05</v>
+        <v>THD_DELAY_REASON-06</v>
       </c>
       <c r="B66" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25549,24 +26045,30 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E66" t="str">
-        <v>Dealer response</v>
-      </c>
-      <c r="F66">
-        <v>5</v>
-      </c>
-      <c r="G66" t="str">
-        <v/>
+        <v>Plant / ERC / vendor intervention</v>
+      </c>
+      <c r="F66" t="str">
+        <v>PLANT_ERC_VENDOR_INTERVENTION</v>
+      </c>
+      <c r="G66">
+        <v>6</v>
       </c>
       <c r="H66" t="str">
         <v/>
       </c>
       <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>THD_DELAY_REASON-06</v>
+        <v>THD_DELAY_REASON-07</v>
       </c>
       <c r="B67" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25578,24 +26080,30 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E67" t="str">
-        <v>Plant / ERC / vendor intervention</v>
-      </c>
-      <c r="F67">
-        <v>6</v>
-      </c>
-      <c r="G67" t="str">
-        <v/>
+        <v>Software / server / TDS Tool issue</v>
+      </c>
+      <c r="F67" t="str">
+        <v>SOFTWARE_SERVER_TDS_TOOL_ISSUE</v>
+      </c>
+      <c r="G67">
+        <v>7</v>
       </c>
       <c r="H67" t="str">
         <v/>
       </c>
       <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>THD_DELAY_REASON-07</v>
+        <v>THD_DELAY_REASON-08</v>
       </c>
       <c r="B68" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25607,24 +26115,30 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E68" t="str">
-        <v>Software / server / TDS Tool issue</v>
-      </c>
-      <c r="F68">
-        <v>7</v>
-      </c>
-      <c r="G68" t="str">
-        <v/>
+        <v>Solution not available</v>
+      </c>
+      <c r="F68" t="str">
+        <v>SOLUTION_NOT_AVAILABLE</v>
+      </c>
+      <c r="G68">
+        <v>8</v>
       </c>
       <c r="H68" t="str">
         <v/>
       </c>
       <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>THD_DELAY_REASON-08</v>
+        <v>THD_DELAY_REASON-09</v>
       </c>
       <c r="B69" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25636,24 +26150,30 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E69" t="str">
-        <v>Solution not available</v>
-      </c>
-      <c r="F69">
-        <v>8</v>
-      </c>
-      <c r="G69" t="str">
-        <v/>
+        <v>Pending for Commercial Decision / Customer Approval</v>
+      </c>
+      <c r="F69" t="str">
+        <v>PENDING_FOR_COMMERCIAL_DECISION_CUSTOMER</v>
+      </c>
+      <c r="G69">
+        <v>9</v>
       </c>
       <c r="H69" t="str">
         <v/>
       </c>
       <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>THD_DELAY_REASON-09</v>
+        <v>THD_DELAY_REASON-10</v>
       </c>
       <c r="B70" t="str">
         <v>THD_DELAY_REASON</v>
@@ -25665,53 +26185,65 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E70" t="str">
-        <v>Pending for Commercial Decision / Customer Approval</v>
-      </c>
-      <c r="F70">
-        <v>9</v>
-      </c>
-      <c r="G70" t="str">
-        <v/>
+        <v>Dealer not responding</v>
+      </c>
+      <c r="F70" t="str">
+        <v>DEALER_NOT_RESPONDING</v>
+      </c>
+      <c r="G70">
+        <v>10</v>
       </c>
       <c r="H70" t="str">
         <v/>
       </c>
       <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>THD_DELAY_REASON-10</v>
+        <v>THD_CLOSURE_ACTION-01</v>
       </c>
       <c r="B71" t="str">
-        <v>THD_DELAY_REASON</v>
+        <v>THD_CLOSURE_ACTION</v>
       </c>
       <c r="C71" t="str">
         <v>THD</v>
       </c>
       <c r="D71" t="str">
-        <v>Reason for Delay</v>
+        <v>Closure Action</v>
       </c>
       <c r="E71" t="str">
-        <v>Dealer not responding</v>
-      </c>
-      <c r="F71">
-        <v>10</v>
-      </c>
-      <c r="G71" t="str">
-        <v/>
+        <v>Closed</v>
+      </c>
+      <c r="F71" t="str">
+        <v>CLOSED</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
       </c>
       <c r="H71" t="str">
         <v/>
       </c>
       <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>THD_CLOSURE_ACTION-01</v>
+        <v>THD_CLOSURE_ACTION-02</v>
       </c>
       <c r="B72" t="str">
         <v>THD_CLOSURE_ACTION</v>
@@ -25723,24 +26255,30 @@
         <v>Closure Action</v>
       </c>
       <c r="E72" t="str">
-        <v>Closed</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72" t="str">
-        <v/>
+        <v>Closed With Feedback</v>
+      </c>
+      <c r="F72" t="str">
+        <v>CLOSED_WITH_FEEDBACK</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
       </c>
       <c r="H72" t="str">
         <v/>
       </c>
       <c r="I72" t="str">
+        <v/>
+      </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>THD_CLOSURE_ACTION-02</v>
+        <v>THD_CLOSURE_ACTION-03</v>
       </c>
       <c r="B73" t="str">
         <v>THD_CLOSURE_ACTION</v>
@@ -25752,82 +26290,100 @@
         <v>Closure Action</v>
       </c>
       <c r="E73" t="str">
-        <v>Closed With Feedback</v>
-      </c>
-      <c r="F73">
-        <v>2</v>
-      </c>
-      <c r="G73" t="str">
-        <v/>
+        <v>Closed With Early Warning</v>
+      </c>
+      <c r="F73" t="str">
+        <v>CLOSED_WITH_EARLY_WARNING</v>
+      </c>
+      <c r="G73">
+        <v>3</v>
       </c>
       <c r="H73" t="str">
         <v/>
       </c>
       <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>THD_CLOSURE_ACTION-03</v>
+        <v>THD_ATTACHMENT_TYPE-01</v>
       </c>
       <c r="B74" t="str">
-        <v>THD_CLOSURE_ACTION</v>
+        <v>THD_ATTACHMENT_TYPE</v>
       </c>
       <c r="C74" t="str">
         <v>THD</v>
       </c>
       <c r="D74" t="str">
-        <v>Closure Action</v>
+        <v>Attachment Type</v>
       </c>
       <c r="E74" t="str">
-        <v>Closed With Early Warning</v>
-      </c>
-      <c r="F74">
-        <v>3</v>
-      </c>
-      <c r="G74" t="str">
-        <v/>
+        <v>DIR Report</v>
+      </c>
+      <c r="F74" t="str">
+        <v>DIR_REPORT</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
       </c>
       <c r="H74" t="str">
         <v/>
       </c>
       <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>THD_ATTACHMENT_TYPE-01</v>
+        <v>CLAIM_BUDGET_PURPOSE-01</v>
       </c>
       <c r="B75" t="str">
-        <v>THD_ATTACHMENT_TYPE</v>
+        <v>CLAIM_BUDGET_PURPOSE</v>
       </c>
       <c r="C75" t="str">
-        <v>THD</v>
+        <v>CLAIM</v>
       </c>
       <c r="D75" t="str">
-        <v>Attachment Type</v>
+        <v>Allocation Purpose</v>
       </c>
       <c r="E75" t="str">
-        <v>DIR Report</v>
-      </c>
-      <c r="F75">
+        <v>Approved Yearly Budget</v>
+      </c>
+      <c r="F75" t="str">
+        <v>APPROVED_YEARLY_BUDGET</v>
+      </c>
+      <c r="G75">
         <v>1</v>
       </c>
-      <c r="G75" t="str">
-        <v/>
-      </c>
       <c r="H75" t="str">
         <v/>
       </c>
       <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>CLAIM_BUDGET_PURPOSE-01</v>
+        <v>CLAIM_BUDGET_PURPOSE-02</v>
       </c>
       <c r="B76" t="str">
         <v>CLAIM_BUDGET_PURPOSE</v>
@@ -25839,53 +26395,65 @@
         <v>Allocation Purpose</v>
       </c>
       <c r="E76" t="str">
-        <v>Approved Yearly Budget</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76" t="str">
-        <v/>
+        <v>Special Budget</v>
+      </c>
+      <c r="F76" t="str">
+        <v>SPECIAL_BUDGET</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
       </c>
       <c r="H76" t="str">
         <v/>
       </c>
       <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>CLAIM_BUDGET_PURPOSE-02</v>
+        <v>CLAIM_SPECIAL_GOODWILL-01</v>
       </c>
       <c r="B77" t="str">
-        <v>CLAIM_BUDGET_PURPOSE</v>
+        <v>CLAIM_SPECIAL_GOODWILL</v>
       </c>
       <c r="C77" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D77" t="str">
-        <v>Allocation Purpose</v>
+        <v>Special Claim</v>
       </c>
       <c r="E77" t="str">
-        <v>Special Budget</v>
-      </c>
-      <c r="F77">
-        <v>2</v>
-      </c>
-      <c r="G77" t="str">
-        <v/>
+        <v>IUPR</v>
+      </c>
+      <c r="F77" t="str">
+        <v>IUPR</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
       </c>
       <c r="H77" t="str">
         <v/>
       </c>
       <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL-01</v>
+        <v>CLAIM_SPECIAL_GOODWILL-02</v>
       </c>
       <c r="B78" t="str">
         <v>CLAIM_SPECIAL_GOODWILL</v>
@@ -25897,53 +26465,65 @@
         <v>Special Claim</v>
       </c>
       <c r="E78" t="str">
-        <v>IUPR</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="G78" t="str">
-        <v/>
+        <v>Thrive</v>
+      </c>
+      <c r="F78" t="str">
+        <v>THRIVE</v>
+      </c>
+      <c r="G78">
+        <v>2</v>
       </c>
       <c r="H78" t="str">
         <v/>
       </c>
       <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL-02</v>
+        <v>CLAIM_ISSUE_DESCRIPTION-01</v>
       </c>
       <c r="B79" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL</v>
+        <v>CLAIM_ISSUE_DESCRIPTION</v>
       </c>
       <c r="C79" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D79" t="str">
-        <v>Special Claim</v>
+        <v>Issue Description</v>
       </c>
       <c r="E79" t="str">
-        <v>Thrive</v>
-      </c>
-      <c r="F79">
-        <v>2</v>
-      </c>
-      <c r="G79" t="str">
-        <v/>
+        <v>Thermal Incident</v>
+      </c>
+      <c r="F79" t="str">
+        <v>THERMAL_INCIDENT</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
       </c>
       <c r="H79" t="str">
         <v/>
       </c>
       <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION-01</v>
+        <v>CLAIM_ISSUE_DESCRIPTION-02</v>
       </c>
       <c r="B80" t="str">
         <v>CLAIM_ISSUE_DESCRIPTION</v>
@@ -25955,53 +26535,65 @@
         <v>Issue Description</v>
       </c>
       <c r="E80" t="str">
-        <v>Thermal Incident</v>
-      </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-      <c r="G80" t="str">
-        <v/>
+        <v>Engine Failure</v>
+      </c>
+      <c r="F80" t="str">
+        <v>ENGINE_FAILURE</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
       </c>
       <c r="H80" t="str">
         <v/>
       </c>
       <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION-02</v>
+        <v>CLAIM_COMPLAINT_TYPE-01</v>
       </c>
       <c r="B81" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION</v>
+        <v>CLAIM_COMPLAINT_TYPE</v>
       </c>
       <c r="C81" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D81" t="str">
-        <v>Issue Description</v>
+        <v>Complaint Type</v>
       </c>
       <c r="E81" t="str">
-        <v>Engine Failure</v>
-      </c>
-      <c r="F81">
-        <v>2</v>
-      </c>
-      <c r="G81" t="str">
-        <v/>
+        <v>Transmission</v>
+      </c>
+      <c r="F81" t="str">
+        <v>TRANSMISSION</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
       </c>
       <c r="H81" t="str">
         <v/>
       </c>
       <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
         <v>Active</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLAIM_COMPLAINT_TYPE-01</v>
+        <v>CLAIM_COMPLAINT_TYPE-02</v>
       </c>
       <c r="B82" t="str">
         <v>CLAIM_COMPLAINT_TYPE</v>
@@ -26013,53 +26605,30 @@
         <v>Complaint Type</v>
       </c>
       <c r="E82" t="str">
-        <v>Transmission</v>
-      </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-      <c r="G82" t="str">
-        <v/>
+        <v>Clutch</v>
+      </c>
+      <c r="F82" t="str">
+        <v>CLUTCH</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
       </c>
       <c r="H82" t="str">
         <v/>
       </c>
       <c r="I82" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>CLAIM_COMPLAINT_TYPE-02</v>
-      </c>
-      <c r="B83" t="str">
-        <v>CLAIM_COMPLAINT_TYPE</v>
-      </c>
-      <c r="C83" t="str">
-        <v>CLAIM</v>
-      </c>
-      <c r="D83" t="str">
-        <v>Complaint Type</v>
-      </c>
-      <c r="E83" t="str">
-        <v>Clutch</v>
-      </c>
-      <c r="F83">
-        <v>2</v>
-      </c>
-      <c r="G83" t="str">
-        <v/>
-      </c>
-      <c r="H83" t="str">
-        <v/>
-      </c>
-      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
         <v>Active</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K82"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -6,52 +6,53 @@
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Masters" sheetId="2" r:id="rId2"/>
     <sheet name="Fields" sheetId="3" r:id="rId3"/>
-    <sheet name="ppl_master" sheetId="4" r:id="rId4"/>
-    <sheet name="model_checklists" sheetId="5" r:id="rId5"/>
-    <sheet name="complaint_codes" sheetId="6" r:id="rId6"/>
-    <sheet name="job_codes" sheetId="7" r:id="rId7"/>
-    <sheet name="complaint_job_linkage" sheetId="8" r:id="rId8"/>
-    <sheet name="ev_safety_protocols" sheetId="9" r:id="rId9"/>
-    <sheet name="dtc_telematics_alerts" sheetId="10" r:id="rId10"/>
-    <sheet name="bay_division_summary" sheetId="11" r:id="rId11"/>
-    <sheet name="bay_technician" sheetId="12" r:id="rId12"/>
-    <sheet name="pause_reasons" sheetId="13" r:id="rId13"/>
-    <sheet name="revisit_reasons" sheetId="14" r:id="rId14"/>
-    <sheet name="appointment_cancellation_lov" sheetId="15" r:id="rId15"/>
-    <sheet name="eqc_inspection_checklist" sheetId="16" r:id="rId16"/>
-    <sheet name="torque_verification_standards" sheetId="17" r:id="rId17"/>
-    <sheet name="eqc_gc_mandate" sheetId="18" r:id="rId18"/>
-    <sheet name="eqc_gc_steps" sheetId="19" r:id="rId19"/>
-    <sheet name="eqc_ptd_risk" sheetId="20" r:id="rId20"/>
-    <sheet name="eqc_did_thresholds" sheetId="21" r:id="rId21"/>
-    <sheet name="eqc_general_checklist" sheetId="22" r:id="rId22"/>
-    <sheet name="eqc_schedule_checklist" sheetId="23" r:id="rId23"/>
-    <sheet name="bs_inventory_sections" sheetId="24" r:id="rId24"/>
-    <sheet name="bs_inventory_checkpoints" sheetId="25" r:id="rId25"/>
-    <sheet name="bs_insurance_documents" sheetId="26" r:id="rId26"/>
-    <sheet name="bodyshop_process_stages" sheetId="27" r:id="rId27"/>
-    <sheet name="paint_booth_schedule" sheetId="28" r:id="rId28"/>
-    <sheet name="amc_pricing" sheetId="29" r:id="rId29"/>
-    <sheet name="warranty_defect_codes" sheetId="30" r:id="rId30"/>
-    <sheet name="goodwill_approval_limits" sheetId="31" r:id="rId31"/>
-    <sheet name="claim_goodwill_category" sheetId="32" r:id="rId32"/>
-    <sheet name="claim_warranty_approval_matrix" sheetId="33" r:id="rId33"/>
-    <sheet name="claim_service_guideline" sheetId="34" r:id="rId34"/>
-    <sheet name="claim_shq_users" sheetId="35" r:id="rId35"/>
-    <sheet name="spd_issuance_priority" sheetId="36" r:id="rId36"/>
-    <sheet name="parts_delay_reasons" sheetId="37" r:id="rId37"/>
-    <sheet name="thd_escalation_categories" sheetId="38" r:id="rId38"/>
-    <sheet name="tib_bulletin_codes" sheetId="39" r:id="rId39"/>
-    <sheet name="thd_auto_trigger_rules" sheetId="40" r:id="rId40"/>
-    <sheet name="thd_critical_complaints" sheetId="41" r:id="rId41"/>
-    <sheet name="thd_kms_range" sheetId="42" r:id="rId42"/>
-    <sheet name="thd_vehicle_age" sheetId="43" r:id="rId43"/>
-    <sheet name="thd_users" sheetId="44" r:id="rId44"/>
-    <sheet name="driver_transit_roster" sheetId="45" r:id="rId45"/>
-    <sheet name="lounge_reception_checklist" sheetId="46" r:id="rId46"/>
-    <sheet name="gate_security_checklist" sheetId="47" r:id="rId47"/>
-    <sheet name="gate_denial_reasons" sheetId="48" r:id="rId48"/>
-    <sheet name="common_lov" sheetId="49" r:id="rId49"/>
+    <sheet name="Rules" sheetId="4" r:id="rId4"/>
+    <sheet name="ppl_master" sheetId="5" r:id="rId5"/>
+    <sheet name="model_checklists" sheetId="6" r:id="rId6"/>
+    <sheet name="complaint_codes" sheetId="7" r:id="rId7"/>
+    <sheet name="job_codes" sheetId="8" r:id="rId8"/>
+    <sheet name="complaint_job_linkage" sheetId="9" r:id="rId9"/>
+    <sheet name="ev_safety_protocols" sheetId="10" r:id="rId10"/>
+    <sheet name="dtc_telematics_alerts" sheetId="11" r:id="rId11"/>
+    <sheet name="bay_division_summary" sheetId="12" r:id="rId12"/>
+    <sheet name="bay_technician" sheetId="13" r:id="rId13"/>
+    <sheet name="pause_reasons" sheetId="14" r:id="rId14"/>
+    <sheet name="revisit_reasons" sheetId="15" r:id="rId15"/>
+    <sheet name="appointment_cancellation_lov" sheetId="16" r:id="rId16"/>
+    <sheet name="eqc_inspection_checklist" sheetId="17" r:id="rId17"/>
+    <sheet name="torque_verification_standards" sheetId="18" r:id="rId18"/>
+    <sheet name="eqc_gc_mandate" sheetId="19" r:id="rId19"/>
+    <sheet name="eqc_gc_steps" sheetId="20" r:id="rId20"/>
+    <sheet name="eqc_ptd_risk" sheetId="21" r:id="rId21"/>
+    <sheet name="eqc_did_thresholds" sheetId="22" r:id="rId22"/>
+    <sheet name="eqc_general_checklist" sheetId="23" r:id="rId23"/>
+    <sheet name="eqc_schedule_checklist" sheetId="24" r:id="rId24"/>
+    <sheet name="bs_inventory_sections" sheetId="25" r:id="rId25"/>
+    <sheet name="bs_inventory_checkpoints" sheetId="26" r:id="rId26"/>
+    <sheet name="bs_insurance_documents" sheetId="27" r:id="rId27"/>
+    <sheet name="bodyshop_process_stages" sheetId="28" r:id="rId28"/>
+    <sheet name="paint_booth_schedule" sheetId="29" r:id="rId29"/>
+    <sheet name="amc_pricing" sheetId="30" r:id="rId30"/>
+    <sheet name="warranty_defect_codes" sheetId="31" r:id="rId31"/>
+    <sheet name="goodwill_approval_limits" sheetId="32" r:id="rId32"/>
+    <sheet name="claim_goodwill_category" sheetId="33" r:id="rId33"/>
+    <sheet name="claim_warranty_approval_matrix" sheetId="34" r:id="rId34"/>
+    <sheet name="claim_service_guideline" sheetId="35" r:id="rId35"/>
+    <sheet name="claim_shq_users" sheetId="36" r:id="rId36"/>
+    <sheet name="spd_issuance_priority" sheetId="37" r:id="rId37"/>
+    <sheet name="parts_delay_reasons" sheetId="38" r:id="rId38"/>
+    <sheet name="thd_escalation_categories" sheetId="39" r:id="rId39"/>
+    <sheet name="tib_bulletin_codes" sheetId="40" r:id="rId40"/>
+    <sheet name="thd_auto_trigger_rules" sheetId="41" r:id="rId41"/>
+    <sheet name="thd_critical_complaints" sheetId="42" r:id="rId42"/>
+    <sheet name="thd_kms_range" sheetId="43" r:id="rId43"/>
+    <sheet name="thd_vehicle_age" sheetId="44" r:id="rId44"/>
+    <sheet name="thd_users" sheetId="45" r:id="rId45"/>
+    <sheet name="driver_transit_roster" sheetId="46" r:id="rId46"/>
+    <sheet name="lounge_reception_checklist" sheetId="47" r:id="rId47"/>
+    <sheet name="gate_security_checklist" sheetId="48" r:id="rId48"/>
+    <sheet name="gate_denial_reasons" sheetId="49" r:id="rId49"/>
+    <sheet name="common_lov" sheetId="50" r:id="rId50"/>
   </sheets>
 </workbook>
 </file>
@@ -445,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A48"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -579,47 +580,117 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>RECORDS — one sheet per master, named exactly as its Master ID</v>
+        <v>SHEET "Rules" (optional) — business rules, one row per rule; checked on every save and upload, no coding</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  Row 1 = column headers: "id" plus each Field Key (the Field Label also works).</v>
+        <v xml:space="preserve">  Rule Type      required_if | unique | not_greater | allowed_if | exists_in | range | pattern</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  "id" is optional; blank ids are generated. Booleans: Y/N. Dates: YYYY-MM-DD.</v>
+        <v xml:space="preserve">    required_if  A field must be filled when another field has a certain value. e.g. Plant Name is required when Role is Plant.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">  For an existing record, blank cells are left unchanged — you only need id + the columns you are filling in.</v>
+        <v xml:space="preserve">    unique       No two active rows may have the same values in these fields. e.g. PPL + Complaint Code must be unique.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v xml:space="preserve">    not_greater  One number or date must not be greater than another. e.g. From Km must not be greater than To Km.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Adding things you missed later: add the new master/field/rows to a workbook and import it again with</v>
+        <v xml:space="preserve">    allowed_if   While a condition holds, a field may only take some values. e.g. When BU is EV, Powertrain may only be EV.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>"Update existing masters" selected. Existing fields are never changed or removed by an import;</v>
+        <v xml:space="preserve">    exists_in    The value must be an active value of a field in another master. e.g. Dealer Code must exist in the Dealer Registry.</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v xml:space="preserve">    range        A number must be within a minimum and / or maximum. e.g. Warranty Months between 0 and 120.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">    pattern      A text must follow a fixed pattern. e.g. Dealer Code: 3 capitals, a hyphen and 3 digits.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">  Field / When Field / Other Field   field key or label; Fields (No duplicates) and value lists are comma separated</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">  When Values    condition values (blank = "is filled"); Allowed Values: values allowed while the condition holds</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">  Min / Max      for "range"; Format: a pattern for "pattern"; Other Master / Other Master Field: for "exists_in"</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">  Severity       error (row refused) or warning (saved, user warned); Message: optional own wording; Enabled: Y / N</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>RECORDS — one sheet per master, named exactly as its Master ID</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v xml:space="preserve">  Row 1 = column headers: "id" plus each Field Key (the Field Label also works).</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">  "id" is optional; blank ids are generated. Booleans: Y/N. Dates: YYYY-MM-DD.</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">  For an existing record, blank cells are left unchanged — you only need id + the columns you are filling in.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Adding things you missed later: add the new master/field/rows to a workbook and import it again with</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>"Update existing masters" selected. Existing fields are never changed or removed by an import;</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
         <v>records are matched by id (existing ids are updated, new ids are added).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A48"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -633,16 +704,16 @@
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>dtcCode</v>
+        <v>protocolCode</v>
       </c>
       <c r="C1" t="str">
-        <v>description</v>
+        <v>safetyGate</v>
       </c>
       <c r="D1" t="str">
-        <v>alertSeverity</v>
+        <v>requiredPpe</v>
       </c>
       <c r="E1" t="str">
-        <v>autoBookAppointment</v>
+        <v>digitalMultimeterCheck</v>
       </c>
       <c r="F1" t="str">
         <v>active</v>
@@ -650,16 +721,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DTC-01</v>
+        <v>EV-01</v>
       </c>
       <c r="B2" t="str">
-        <v>P0A80-00</v>
+        <v>EV-ISO-01</v>
       </c>
       <c r="C2" t="str">
-        <v>HV Battery Pack Cell Imbalance &gt; 150mV across modules</v>
+        <v>Manual Service Disconnect (MSD) orange plug removal &amp; lock-out tag-out (LOTO)</v>
       </c>
       <c r="D2" t="str">
-        <v>Critical Emergency (Red Lamp)</v>
+        <v>Class 0 1000V Insulated Gloves + Face Shield</v>
       </c>
       <c r="E2" t="str">
         <v>Y</v>
@@ -670,16 +741,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DTC-02</v>
+        <v>EV-02</v>
       </c>
       <c r="B3" t="str">
-        <v>P1A02-14</v>
+        <v>EV-ISO-02</v>
       </c>
       <c r="C3" t="str">
-        <v>Electric Motor Inverter Coolant Flow Below Threshold</v>
+        <v>12V Auxiliary battery terminal disconnection to disable HV contactor control</v>
       </c>
       <c r="D3" t="str">
-        <v>Warning Advisory (Amber Lamp)</v>
+        <v>Class 0 1000V Insulated Gloves + Face Shield</v>
       </c>
       <c r="E3" t="str">
         <v>Y</v>
@@ -690,19 +761,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>DTC-03</v>
+        <v>EV-03</v>
       </c>
       <c r="B4" t="str">
-        <v>B1245-01</v>
+        <v>EV-ISO-03</v>
       </c>
       <c r="C4" t="str">
-        <v>Smart Key Fob Battery Low (30-day forecast)</v>
+        <v>Capacitor discharge wait cycle (10 mins) and inverter busbar residual test</v>
       </c>
       <c r="D4" t="str">
-        <v>Informational Routine (Blue)</v>
+        <v>Rubber Insulated Floor Matting 17kV</v>
       </c>
       <c r="E4" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F4" t="str">
         <v>Y</v>
@@ -717,6 +788,97 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>dtcCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>description</v>
+      </c>
+      <c r="D1" t="str">
+        <v>alertSeverity</v>
+      </c>
+      <c r="E1" t="str">
+        <v>autoBookAppointment</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DTC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>P0A80-00</v>
+      </c>
+      <c r="C2" t="str">
+        <v>HV Battery Pack Cell Imbalance &gt; 150mV across modules</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Critical Emergency (Red Lamp)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DTC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>P1A02-14</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Electric Motor Inverter Coolant Flow Below Threshold</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Warning Advisory (Amber Lamp)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DTC-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>B1245-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Smart Key Fob Battery Low (30-day forecast)</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Informational Routine (Blue)</v>
+      </c>
+      <c r="E4" t="str">
+        <v>N</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
@@ -840,7 +1002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J4"/>
   <sheetData>
@@ -979,7 +1141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G16"/>
   <sheetData>
@@ -1354,117 +1516,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>reasonCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>reasonName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>department</v>
-      </c>
-      <c r="E1" t="str">
-        <v>escalateToDGM</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>RR-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>REV-TECH-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Incomplete torque or loose fastener during initial repair</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Workmanship / Technician</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>RR-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>REV-PART-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>New spare part premature failure within warranty</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Parts Quality / Defective Spare</v>
-      </c>
-      <c r="E3" t="str">
-        <v>N</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>RR-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>REV-DIAG-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Incorrect fault diagnosis (Replaced wrong component)</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Diagnosis Error</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>RR-04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>REV-CUST-04</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Operating nuance / normal NVH characteristic explained</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Customer Education</v>
-      </c>
-      <c r="E5" t="str">
-        <v>N</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1484,10 +1535,10 @@
         <v>reasonName</v>
       </c>
       <c r="D1" t="str">
-        <v>category</v>
+        <v>department</v>
       </c>
       <c r="E1" t="str">
-        <v>allowAutoReschedule</v>
+        <v>escalateToDGM</v>
       </c>
       <c r="F1" t="str">
         <v>active</v>
@@ -1495,16 +1546,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AC-01</v>
+        <v>RR-01</v>
       </c>
       <c r="B2" t="str">
-        <v>CANC-CUST-OUT</v>
+        <v>REV-TECH-01</v>
       </c>
       <c r="C2" t="str">
-        <v>Customer out of town / traveling</v>
+        <v>Incomplete torque or loose fastener during initial repair</v>
       </c>
       <c r="D2" t="str">
-        <v>Customer Request</v>
+        <v>Workmanship / Technician</v>
       </c>
       <c r="E2" t="str">
         <v>Y</v>
@@ -1515,16 +1566,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AC-02</v>
+        <v>RR-02</v>
       </c>
       <c r="B3" t="str">
-        <v>CANC-PRICE-HIGH</v>
+        <v>REV-PART-02</v>
       </c>
       <c r="C3" t="str">
-        <v>Service estimate higher than expected (Cost objection)</v>
+        <v>New spare part premature failure within warranty</v>
       </c>
       <c r="D3" t="str">
-        <v>Customer Request</v>
+        <v>Parts Quality / Defective Spare</v>
       </c>
       <c r="E3" t="str">
         <v>N</v>
@@ -1535,16 +1586,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AC-03</v>
+        <v>RR-03</v>
       </c>
       <c r="B4" t="str">
-        <v>CANC-BAY-CAP</v>
+        <v>REV-DIAG-03</v>
       </c>
       <c r="C4" t="str">
-        <v>Specialized EV / Alignment bay overbooked</v>
+        <v>Incorrect fault diagnosis (Replaced wrong component)</v>
       </c>
       <c r="D4" t="str">
-        <v>Dealership Capacity Constrained</v>
+        <v>Diagnosis Error</v>
       </c>
       <c r="E4" t="str">
         <v>Y</v>
@@ -1555,19 +1606,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AC-04</v>
+        <v>RR-04</v>
       </c>
       <c r="B5" t="str">
-        <v>CANC-PART-BO</v>
+        <v>REV-CUST-04</v>
       </c>
       <c r="C5" t="str">
-        <v>Critical spare part on transit backorder</v>
+        <v>Operating nuance / normal NVH characteristic explained</v>
       </c>
       <c r="D5" t="str">
-        <v>Parts Shortage</v>
+        <v>Customer Education</v>
       </c>
       <c r="E5" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F5" t="str">
         <v>Y</v>
@@ -1589,16 +1640,16 @@
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>checkCode</v>
+        <v>reasonCode</v>
       </c>
       <c r="C1" t="str">
-        <v>stageName</v>
+        <v>reasonName</v>
       </c>
       <c r="D1" t="str">
-        <v>description</v>
+        <v>category</v>
       </c>
       <c r="E1" t="str">
-        <v>mandatoryPass</v>
+        <v>allowAutoReschedule</v>
       </c>
       <c r="F1" t="str">
         <v>active</v>
@@ -1606,16 +1657,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>EQC-01</v>
+        <v>AC-01</v>
       </c>
       <c r="B2" t="str">
-        <v>EQC-OBD-01</v>
+        <v>CANC-CUST-OUT</v>
       </c>
       <c r="C2" t="str">
-        <v>Diagnostic Scan &amp; OBD-II</v>
+        <v>Customer out of town / traveling</v>
       </c>
       <c r="D2" t="str">
-        <v>Complete ECU fault code clear verification (Zero active DTCs)</v>
+        <v>Customer Request</v>
       </c>
       <c r="E2" t="str">
         <v>Y</v>
@@ -1626,19 +1677,19 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>EQC-02</v>
+        <v>AC-02</v>
       </c>
       <c r="B3" t="str">
-        <v>EQC-TORQ-02</v>
+        <v>CANC-PRICE-HIGH</v>
       </c>
       <c r="C3" t="str">
-        <v>Underbody &amp; Suspension</v>
+        <v>Service estimate higher than expected (Cost objection)</v>
       </c>
       <c r="D3" t="str">
-        <v>Four-wheel lug nuts torque verification with calibrated digital wrench</v>
+        <v>Customer Request</v>
       </c>
       <c r="E3" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="F3" t="str">
         <v>Y</v>
@@ -1646,16 +1697,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>EQC-03</v>
+        <v>AC-03</v>
       </c>
       <c r="B4" t="str">
-        <v>EQC-ROAD-03</v>
+        <v>CANC-BAY-CAP</v>
       </c>
       <c r="C4" t="str">
-        <v>Road Test Evaluation</v>
+        <v>Specialized EV / Alignment bay overbooked</v>
       </c>
       <c r="D4" t="str">
-        <v>5 km dynamic road test: straight line tracking and ABS bite test</v>
+        <v>Dealership Capacity Constrained</v>
       </c>
       <c r="E4" t="str">
         <v>Y</v>
@@ -1666,19 +1717,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EQC-04</v>
+        <v>AC-04</v>
       </c>
       <c r="B5" t="str">
-        <v>EQC-WASH-04</v>
+        <v>CANC-PART-BO</v>
       </c>
       <c r="C5" t="str">
-        <v>Washing &amp; Interior Cleanliness</v>
+        <v>Critical spare part on transit backorder</v>
       </c>
       <c r="D5" t="str">
-        <v>Zero water seepage, spotless dashboard, paper floor mats installed</v>
+        <v>Parts Shortage</v>
       </c>
       <c r="E5" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="F5" t="str">
         <v>Y</v>
@@ -1693,6 +1744,117 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>checkCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>stageName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>mandatoryPass</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>EQC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>EQC-OBD-01</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Diagnostic Scan &amp; OBD-II</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Complete ECU fault code clear verification (Zero active DTCs)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>EQC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>EQC-TORQ-02</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Underbody &amp; Suspension</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Four-wheel lug nuts torque verification with calibrated digital wrench</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>EQC-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>EQC-ROAD-03</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Road Test Evaluation</v>
+      </c>
+      <c r="D4" t="str">
+        <v>5 km dynamic road test: straight line tracking and ABS bite test</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>EQC-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>EQC-WASH-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Washing &amp; Interior Cleanliness</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Zero water seepage, spotless dashboard, paper floor mats installed</v>
+      </c>
+      <c r="E5" t="str">
+        <v>N</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
@@ -1794,7 +1956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H7"/>
   <sheetData>
@@ -1983,277 +2145,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ppl</v>
-      </c>
-      <c r="C1" t="str">
-        <v>complaintCode</v>
-      </c>
-      <c r="D1" t="str">
-        <v>stepNo</v>
-      </c>
-      <c r="E1" t="str">
-        <v>gcStep</v>
-      </c>
-      <c r="F1" t="str">
-        <v>gcImage1</v>
-      </c>
-      <c r="G1" t="str">
-        <v>gcImage2</v>
-      </c>
-      <c r="H1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>GCS-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>BRK-VIB-02</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Measure front disc run-out with dial gauge (limit 0.05 mm)</v>
-      </c>
-      <c r="F2" t="str">
-        <v>gc/brk-disc-runout.jpg</v>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>GCS-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>BRK-VIB-02</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Check caliper guide pins for free movement and grease</v>
-      </c>
-      <c r="F3" t="str">
-        <v>gc/brk-guide-pins.jpg</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>GCS-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>BRK-VIB-02</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Inspect wheel balancing and tyre wear pattern</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>GCS-04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Nexon EV</v>
-      </c>
-      <c r="C5" t="str">
-        <v>BAT-SOC-03</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Read HV battery SOC and cell voltage spread via VCI</v>
-      </c>
-      <c r="F5" t="str">
-        <v>gc/ev-vci-soc.jpg</v>
-      </c>
-      <c r="G5" t="str">
-        <v>gc/ev-cell-spread.jpg</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>GCS-05</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Nexon EV</v>
-      </c>
-      <c r="C6" t="str">
-        <v>BAT-SOC-03</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Check BMS DTC history and last OTA version</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>GCS-06</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v>BAT-SOC-03</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Check 12V auxiliary battery voltage and terminals</v>
-      </c>
-      <c r="F7" t="str">
-        <v>gc/12v-terminals.jpg</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>GCS-07</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Altroz</v>
-      </c>
-      <c r="C8" t="str">
-        <v>ENG-NOIS-01</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Cold start: listen at timing belt tensioner with stethoscope</v>
-      </c>
-      <c r="F8" t="str">
-        <v>gc/eng-tensioner.jpg</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>GCS-08</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Altroz</v>
-      </c>
-      <c r="C9" t="str">
-        <v>ENG-NOIS-01</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Check engine mount bushes for cracks</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>GCS-09</v>
-      </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v>AC-COOL-04</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Measure vent outlet temperature at idle (target ≤ 8 °C)</v>
-      </c>
-      <c r="F10" t="str">
-        <v>gc/ac-vent-temp.jpg</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3352,6 +3243,277 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ppl</v>
+      </c>
+      <c r="C1" t="str">
+        <v>complaintCode</v>
+      </c>
+      <c r="D1" t="str">
+        <v>stepNo</v>
+      </c>
+      <c r="E1" t="str">
+        <v>gcStep</v>
+      </c>
+      <c r="F1" t="str">
+        <v>gcImage1</v>
+      </c>
+      <c r="G1" t="str">
+        <v>gcImage2</v>
+      </c>
+      <c r="H1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>GCS-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>BRK-VIB-02</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Measure front disc run-out with dial gauge (limit 0.05 mm)</v>
+      </c>
+      <c r="F2" t="str">
+        <v>gc/brk-disc-runout.jpg</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>GCS-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+      <c r="C3" t="str">
+        <v>BRK-VIB-02</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Check caliper guide pins for free movement and grease</v>
+      </c>
+      <c r="F3" t="str">
+        <v>gc/brk-guide-pins.jpg</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>GCS-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v>BRK-VIB-02</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Inspect wheel balancing and tyre wear pattern</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>GCS-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="C5" t="str">
+        <v>BAT-SOC-03</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Read HV battery SOC and cell voltage spread via VCI</v>
+      </c>
+      <c r="F5" t="str">
+        <v>gc/ev-vci-soc.jpg</v>
+      </c>
+      <c r="G5" t="str">
+        <v>gc/ev-cell-spread.jpg</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>GCS-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Nexon EV</v>
+      </c>
+      <c r="C6" t="str">
+        <v>BAT-SOC-03</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Check BMS DTC history and last OTA version</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>GCS-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v>BAT-SOC-03</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Check 12V auxiliary battery voltage and terminals</v>
+      </c>
+      <c r="F7" t="str">
+        <v>gc/12v-terminals.jpg</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>GCS-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ENG-NOIS-01</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Cold start: listen at timing belt tensioner with stethoscope</v>
+      </c>
+      <c r="F8" t="str">
+        <v>gc/eng-tensioner.jpg</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>GCS-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ENG-NOIS-01</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Check engine mount bushes for cracks</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>GCS-09</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>AC-COOL-04</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Measure vent outlet temperature at idle (target ≤ 8 °C)</v>
+      </c>
+      <c r="F10" t="str">
+        <v>gc/ac-vent-temp.jpg</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
@@ -3412,7 +3574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F7"/>
   <sheetData>
@@ -3559,321 +3721,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>bu</v>
-      </c>
-      <c r="C1" t="str">
-        <v>checklistType</v>
-      </c>
-      <c r="D1" t="str">
-        <v>checklistItem</v>
-      </c>
-      <c r="E1" t="str">
-        <v>rangeStartKm</v>
-      </c>
-      <c r="F1" t="str">
-        <v>rangeEndKm</v>
-      </c>
-      <c r="G1" t="str">
-        <v>ppl</v>
-      </c>
-      <c r="H1" t="str">
-        <v>active</v>
-      </c>
-      <c r="I1" t="str">
-        <v>notOkPhoto</v>
-      </c>
-      <c r="J1" t="str">
-        <v>notOkAudio</v>
-      </c>
-      <c r="K1" t="str">
-        <v>notOkVideo</v>
-      </c>
-      <c r="L1" t="str">
-        <v>notOkText</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>GCL-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>PV</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Pre-Delivery Inspection</v>
-      </c>
-      <c r="D2" t="str">
-        <v>All warning lamps OFF after engine start</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="J2" t="str">
-        <v>N</v>
-      </c>
-      <c r="K2" t="str">
-        <v>N</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>GCL-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>PV</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Road Test</v>
-      </c>
-      <c r="D3" t="str">
-        <v>No pull to either side under braking</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I3" t="str">
-        <v>N</v>
-      </c>
-      <c r="J3" t="str">
-        <v>N</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>GCL-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>PV</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Underbody</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Clutch plate wear within limit</v>
-      </c>
-      <c r="E4">
-        <v>40000</v>
-      </c>
-      <c r="F4">
-        <v>80000</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="J4" t="str">
-        <v>N</v>
-      </c>
-      <c r="K4" t="str">
-        <v>N</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>GCL-04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>PV</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Road Test</v>
-      </c>
-      <c r="D5" t="str">
-        <v>DCA gear shift smooth, no judder at 1st–2nd</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v>Altroz</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I5" t="str">
-        <v>N</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Y</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>GCL-05</v>
-      </c>
-      <c r="B6" t="str">
-        <v>EV</v>
-      </c>
-      <c r="C6" t="str">
-        <v>EV Safety</v>
-      </c>
-      <c r="D6" t="str">
-        <v>HV connector seals and orange cable insulation intact</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Y</v>
-      </c>
-      <c r="J6" t="str">
-        <v>N</v>
-      </c>
-      <c r="K6" t="str">
-        <v>N</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>GCL-06</v>
-      </c>
-      <c r="B7" t="str">
-        <v>EV</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Pre-Delivery Inspection</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Regen braking levels switch correctly</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v>Nexon EV</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Y</v>
-      </c>
-      <c r="I7" t="str">
-        <v>N</v>
-      </c>
-      <c r="J7" t="str">
-        <v>N</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Y</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>GCL-07</v>
-      </c>
-      <c r="B8" t="str">
-        <v>PV</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Interior &amp; Cleanliness</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Paper floor mats and seat covers removed</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v>N</v>
-      </c>
-      <c r="I8" t="str">
-        <v>N</v>
-      </c>
-      <c r="J8" t="str">
-        <v>N</v>
-      </c>
-      <c r="K8" t="str">
-        <v>N</v>
-      </c>
-      <c r="L8" t="str">
-        <v>N</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3890,174 +3737,174 @@
         <v>bu</v>
       </c>
       <c r="C1" t="str">
-        <v>section</v>
+        <v>checklistType</v>
       </c>
       <c r="D1" t="str">
-        <v>subSection</v>
+        <v>checklistItem</v>
       </c>
       <c r="E1" t="str">
+        <v>rangeStartKm</v>
+      </c>
+      <c r="F1" t="str">
+        <v>rangeEndKm</v>
+      </c>
+      <c r="G1" t="str">
         <v>ppl</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>active</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>notOkPhoto</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>notOkAudio</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>notOkVideo</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>notOkText</v>
-      </c>
-      <c r="K1" t="str">
-        <v>rangeStartKm</v>
-      </c>
-      <c r="L1" t="str">
-        <v>rangeEndKm</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SCL-01</v>
+        <v>GCL-01</v>
       </c>
       <c r="B2" t="str">
         <v>PV</v>
       </c>
       <c r="C2" t="str">
-        <v>Engine Compartment</v>
+        <v>Pre-Delivery Inspection</v>
       </c>
       <c r="D2" t="str">
-        <v>Engine oil level and leakage</v>
+        <v>All warning lamps OFF after engine start</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="I2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J2" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>N</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>Y</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>SCL-02</v>
+        <v>GCL-02</v>
       </c>
       <c r="B3" t="str">
         <v>PV</v>
       </c>
       <c r="C3" t="str">
-        <v>Engine Compartment</v>
+        <v>Road Test</v>
       </c>
       <c r="D3" t="str">
-        <v>Drive belt condition</v>
+        <v>No pull to either side under braking</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="I3" t="str">
         <v>N</v>
       </c>
       <c r="J3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K3">
-        <v>20000</v>
+        <v>N</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Y</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>Y</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>SCL-03</v>
+        <v>GCL-03</v>
       </c>
       <c r="B4" t="str">
         <v>PV</v>
       </c>
       <c r="C4" t="str">
-        <v>Brakes</v>
+        <v>Underbody</v>
       </c>
       <c r="D4" t="str">
-        <v>Front pad thickness ≥ 3 mm</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
+        <v>Clutch plate wear within limit</v>
+      </c>
+      <c r="E4">
+        <v>40000</v>
+      </c>
+      <c r="F4">
+        <v>80000</v>
       </c>
       <c r="G4" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="I4" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K4">
-        <v>10000</v>
+        <v>N</v>
+      </c>
+      <c r="K4" t="str">
+        <v>N</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>Y</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SCL-04</v>
+        <v>GCL-04</v>
       </c>
       <c r="B5" t="str">
         <v>PV</v>
       </c>
       <c r="C5" t="str">
-        <v>Underbody</v>
+        <v>Road Test</v>
       </c>
       <c r="D5" t="str">
-        <v>Turbo intercooler hoses</v>
+        <v>DCA gear shift smooth, no judder at 1st–2nd</v>
       </c>
       <c r="E5" t="str">
-        <v>Harrier</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>Y</v>
+        <v>Altroz</v>
       </c>
       <c r="H5" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="I5" t="str">
         <v>N</v>
@@ -4066,124 +3913,124 @@
         <v>Y</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>Y</v>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>Y</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SCL-05</v>
+        <v>GCL-05</v>
       </c>
       <c r="B6" t="str">
         <v>EV</v>
       </c>
       <c r="C6" t="str">
-        <v>HV System</v>
+        <v>EV Safety</v>
       </c>
       <c r="D6" t="str">
-        <v>Battery pack mounting bolts torque</v>
+        <v>HV connector seals and orange cable insulation intact</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="I6" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="J6" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K6">
-        <v>15000</v>
+        <v>N</v>
+      </c>
+      <c r="K6" t="str">
+        <v>N</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>Y</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SCL-06</v>
+        <v>GCL-06</v>
       </c>
       <c r="B7" t="str">
         <v>EV</v>
       </c>
       <c r="C7" t="str">
-        <v>HV System</v>
+        <v>Pre-Delivery Inspection</v>
       </c>
       <c r="D7" t="str">
-        <v>Coolant level in battery thermal loop</v>
+        <v>Regen braking levels switch correctly</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>Y</v>
+        <v>Nexon EV</v>
       </c>
       <c r="H7" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="I7" t="str">
         <v>N</v>
       </c>
       <c r="J7" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>Y</v>
       </c>
       <c r="L7" t="str">
-        <v/>
+        <v>Y</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SCL-07</v>
+        <v>GCL-07</v>
       </c>
       <c r="B8" t="str">
         <v>PV</v>
       </c>
       <c r="C8" t="str">
-        <v>Electricals</v>
+        <v>Interior &amp; Cleanliness</v>
       </c>
       <c r="D8" t="str">
-        <v>Headlamp aim and fog lamps</v>
+        <v>Paper floor mats and seat covers removed</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>N</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>N</v>
       </c>
       <c r="I8" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="J8" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8">
-        <v>30000</v>
+        <v>N</v>
+      </c>
+      <c r="L8" t="str">
+        <v>N</v>
       </c>
     </row>
   </sheetData>
@@ -4195,6 +4042,321 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>bu</v>
+      </c>
+      <c r="C1" t="str">
+        <v>section</v>
+      </c>
+      <c r="D1" t="str">
+        <v>subSection</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ppl</v>
+      </c>
+      <c r="F1" t="str">
+        <v>active</v>
+      </c>
+      <c r="G1" t="str">
+        <v>notOkPhoto</v>
+      </c>
+      <c r="H1" t="str">
+        <v>notOkAudio</v>
+      </c>
+      <c r="I1" t="str">
+        <v>notOkVideo</v>
+      </c>
+      <c r="J1" t="str">
+        <v>notOkText</v>
+      </c>
+      <c r="K1" t="str">
+        <v>rangeStartKm</v>
+      </c>
+      <c r="L1" t="str">
+        <v>rangeEndKm</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SCL-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Engine Compartment</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Engine oil level and leakage</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H2" t="str">
+        <v>N</v>
+      </c>
+      <c r="I2" t="str">
+        <v>N</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>SCL-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Engine Compartment</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Drive belt condition</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H3" t="str">
+        <v>N</v>
+      </c>
+      <c r="I3" t="str">
+        <v>N</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K3">
+        <v>20000</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>SCL-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Brakes</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Front pad thickness ≥ 3 mm</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H4" t="str">
+        <v>N</v>
+      </c>
+      <c r="I4" t="str">
+        <v>N</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K4">
+        <v>10000</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>SCL-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Underbody</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Turbo intercooler hoses</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Harrier</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H5" t="str">
+        <v>N</v>
+      </c>
+      <c r="I5" t="str">
+        <v>N</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>SCL-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C6" t="str">
+        <v>HV System</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Battery pack mounting bolts torque</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H6" t="str">
+        <v>N</v>
+      </c>
+      <c r="I6" t="str">
+        <v>N</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K6">
+        <v>15000</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>SCL-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C7" t="str">
+        <v>HV System</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Coolant level in battery thermal loop</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H7" t="str">
+        <v>N</v>
+      </c>
+      <c r="I7" t="str">
+        <v>N</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>SCL-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Electricals</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Headlamp aim and fog lamps</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="G8" t="str">
+        <v>N</v>
+      </c>
+      <c r="H8" t="str">
+        <v>N</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8">
+        <v>30000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G15"/>
   <sheetData>
     <row r="1">
@@ -4549,7 +4711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P12"/>
   <sheetData>
@@ -5160,7 +5322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G3"/>
   <sheetData>
@@ -5240,7 +5402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
@@ -5351,7 +5513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <sheetData>
@@ -5418,121 +5580,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>amcCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>planName</v>
-      </c>
-      <c r="D1" t="str">
-        <v>pplName</v>
-      </c>
-      <c r="E1" t="str">
-        <v>tenureYears</v>
-      </c>
-      <c r="F1" t="str">
-        <v>maxKms</v>
-      </c>
-      <c r="G1" t="str">
-        <v>priceInr</v>
-      </c>
-      <c r="H1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>AMC-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>TML-VC-SILVER-02</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Value Care Silver (Scheduled Lube &amp; Filters)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Nexon</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>30000</v>
-      </c>
-      <c r="G2">
-        <v>12500</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>AMC-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>TML-VC-GOLD-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Value Care Gold (Wear &amp; Tear + Scheduled)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Harrier / Safari</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>45000</v>
-      </c>
-      <c r="G3">
-        <v>34000</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>AMC-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>TML-EV-PROMISE-05</v>
-      </c>
-      <c r="C4" t="str">
-        <v>EV Battery &amp; Motor Health Guard AMC</v>
-      </c>
-      <c r="D4" t="str">
-        <v>EV Fleet</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>100000</v>
-      </c>
-      <c r="G4">
-        <v>28500</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -21556,6 +21603,121 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>amcCode</v>
+      </c>
+      <c r="C1" t="str">
+        <v>planName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>pplName</v>
+      </c>
+      <c r="E1" t="str">
+        <v>tenureYears</v>
+      </c>
+      <c r="F1" t="str">
+        <v>maxKms</v>
+      </c>
+      <c r="G1" t="str">
+        <v>priceInr</v>
+      </c>
+      <c r="H1" t="str">
+        <v>active</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AMC-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TML-VC-SILVER-02</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Value Care Silver (Scheduled Lube &amp; Filters)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Nexon</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>30000</v>
+      </c>
+      <c r="G2">
+        <v>12500</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AMC-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TML-VC-GOLD-03</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Value Care Gold (Wear &amp; Tear + Scheduled)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Harrier / Safari</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>45000</v>
+      </c>
+      <c r="G3">
+        <v>34000</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AMC-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TML-EV-PROMISE-05</v>
+      </c>
+      <c r="C4" t="str">
+        <v>EV Battery &amp; Motor Health Guard AMC</v>
+      </c>
+      <c r="D4" t="str">
+        <v>EV Fleet</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>100000</v>
+      </c>
+      <c r="G4">
+        <v>28500</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
@@ -21645,7 +21807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
@@ -21756,7 +21918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <sheetData>
@@ -21818,7 +21980,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J4"/>
   <sheetData>
@@ -21957,7 +22119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G1"/>
   <sheetData>
@@ -21991,7 +22153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetData>
@@ -22036,7 +22198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
@@ -22147,7 +22309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetData>
@@ -22238,7 +22400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
@@ -22349,7 +22511,68 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Master ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Rule Type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Field</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Fields (No duplicates)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>When Field</v>
+      </c>
+      <c r="F1" t="str">
+        <v>When Values</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Other Field</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Allowed Values</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Min</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Max</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Format</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Other Master</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Other Master Field</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Severity</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Message</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Enabled</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetData>
@@ -22440,192 +22663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>bu</v>
-      </c>
-      <c r="C1" t="str">
-        <v>pplCode</v>
-      </c>
-      <c r="D1" t="str">
-        <v>pplName</v>
-      </c>
-      <c r="E1" t="str">
-        <v>plName</v>
-      </c>
-      <c r="F1" t="str">
-        <v>fuelType</v>
-      </c>
-      <c r="G1" t="str">
-        <v>active</v>
-      </c>
-      <c r="H1" t="str">
-        <v>extended_warranty_tier</v>
-      </c>
-      <c r="I1" t="str">
-        <v>telematics_ota_status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PPL-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>EV</v>
-      </c>
-      <c r="C2" t="str">
-        <v>PPL-NEXON-EV</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Nexon</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Nexon EV Long Range (45 kWh)</v>
-      </c>
-      <c r="F2" t="str">
-        <v>EV</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="H2" t="str">
-        <v>PLATINUM</v>
-      </c>
-      <c r="I2" t="str">
-        <v>OTA_ACTIVE</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>PPL-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>PV</v>
-      </c>
-      <c r="C3" t="str">
-        <v>PPL-NEXON-ICE</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Nexon</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Nexon Fearless+ DCA Petrol</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Petrol</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="H3" t="str">
-        <v>GOLD</v>
-      </c>
-      <c r="I3" t="str">
-        <v>OTA_ACTIVE</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PPL-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>PV</v>
-      </c>
-      <c r="C4" t="str">
-        <v>PPL-ALTROZ</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Altroz</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Altroz XZ i-CNG Twin Cylinder</v>
-      </c>
-      <c r="F4" t="str">
-        <v>CNG</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="H4" t="str">
-        <v>GOLD</v>
-      </c>
-      <c r="I4" t="str">
-        <v>NON_CONNECTED</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PPL-04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>PV</v>
-      </c>
-      <c r="C5" t="str">
-        <v>PPL-HARRIER</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Harrier</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Harrier Fearless Dark 2.0L Diesel AT</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Diesel</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Y</v>
-      </c>
-      <c r="H5" t="str">
-        <v>PLATINUM</v>
-      </c>
-      <c r="I5" t="str">
-        <v>ECU_FLASH_REQ</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>PPL-05</v>
-      </c>
-      <c r="B6" t="str">
-        <v>EV</v>
-      </c>
-      <c r="C6" t="str">
-        <v>PPL-CURVV-EV</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Curvv</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Curvv EV 55 kWh Hyperion</v>
-      </c>
-      <c r="F6" t="str">
-        <v>EV</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Y</v>
-      </c>
-      <c r="H6" t="str">
-        <v>PLATINUM</v>
-      </c>
-      <c r="I6" t="str">
-        <v>OTA_ACTIVE</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L9"/>
   <sheetData>
@@ -22978,7 +23016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H2"/>
   <sheetData>
@@ -23037,68 +23075,6 @@
   </sheetData>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>label</v>
-      </c>
-      <c r="C1" t="str">
-        <v>fromKm</v>
-      </c>
-      <c r="D1" t="str">
-        <v>toKm</v>
-      </c>
-      <c r="E1" t="str">
-        <v>status</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>KMR-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>0 - 1,000</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1000</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>KMR-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1,001 - 10,000</v>
-      </c>
-      <c r="C3">
-        <v>1001</v>
-      </c>
-      <c r="D3">
-        <v>10000</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -23115,10 +23091,10 @@
         <v>label</v>
       </c>
       <c r="C1" t="str">
-        <v>fromYears</v>
+        <v>fromKm</v>
       </c>
       <c r="D1" t="str">
-        <v>toYears</v>
+        <v>toKm</v>
       </c>
       <c r="E1" t="str">
         <v>status</v>
@@ -23126,16 +23102,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AGE-01</v>
+        <v>KMR-01</v>
       </c>
       <c r="B2" t="str">
-        <v>0 - 1</v>
+        <v>0 - 1,000</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="E2" t="str">
         <v>Active</v>
@@ -23143,16 +23119,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AGE-02</v>
+        <v>KMR-02</v>
       </c>
       <c r="B3" t="str">
-        <v>0 - 5</v>
+        <v>1,001 - 10,000</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>10000</v>
       </c>
       <c r="E3" t="str">
         <v>Active</v>
@@ -23167,6 +23143,68 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>label</v>
+      </c>
+      <c r="C1" t="str">
+        <v>fromYears</v>
+      </c>
+      <c r="D1" t="str">
+        <v>toYears</v>
+      </c>
+      <c r="E1" t="str">
+        <v>status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AGE-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>0 - 1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AGE-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>0 - 5</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
@@ -23368,7 +23406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G4"/>
   <sheetData>
@@ -23471,7 +23509,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetData>
@@ -23562,7 +23600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetData>
@@ -23673,7 +23711,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetData>
@@ -23752,7 +23790,192 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>bu</v>
+      </c>
+      <c r="C1" t="str">
+        <v>pplCode</v>
+      </c>
+      <c r="D1" t="str">
+        <v>pplName</v>
+      </c>
+      <c r="E1" t="str">
+        <v>plName</v>
+      </c>
+      <c r="F1" t="str">
+        <v>fuelType</v>
+      </c>
+      <c r="G1" t="str">
+        <v>active</v>
+      </c>
+      <c r="H1" t="str">
+        <v>extended_warranty_tier</v>
+      </c>
+      <c r="I1" t="str">
+        <v>telematics_ota_status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>PPL-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C2" t="str">
+        <v>PPL-NEXON-EV</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Nexon</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Nexon EV Long Range (45 kWh)</v>
+      </c>
+      <c r="F2" t="str">
+        <v>EV</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H2" t="str">
+        <v>PLATINUM</v>
+      </c>
+      <c r="I2" t="str">
+        <v>OTA_ACTIVE</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PPL-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C3" t="str">
+        <v>PPL-NEXON-ICE</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Nexon</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Nexon Fearless+ DCA Petrol</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Petrol</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H3" t="str">
+        <v>GOLD</v>
+      </c>
+      <c r="I3" t="str">
+        <v>OTA_ACTIVE</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PPL-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C4" t="str">
+        <v>PPL-ALTROZ</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Altroz</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Altroz XZ i-CNG Twin Cylinder</v>
+      </c>
+      <c r="F4" t="str">
+        <v>CNG</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H4" t="str">
+        <v>GOLD</v>
+      </c>
+      <c r="I4" t="str">
+        <v>NON_CONNECTED</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PPL-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>PV</v>
+      </c>
+      <c r="C5" t="str">
+        <v>PPL-HARRIER</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Harrier</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Harrier Fearless Dark 2.0L Diesel AT</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Diesel</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H5" t="str">
+        <v>PLATINUM</v>
+      </c>
+      <c r="I5" t="str">
+        <v>ECU_FLASH_REQ</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PPL-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>EV</v>
+      </c>
+      <c r="C6" t="str">
+        <v>PPL-CURVV-EV</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Curvv</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Curvv EV 55 kWh Hyperion</v>
+      </c>
+      <c r="F6" t="str">
+        <v>EV</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H6" t="str">
+        <v>PLATINUM</v>
+      </c>
+      <c r="I6" t="str">
+        <v>OTA_ACTIVE</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K82"/>
   <sheetData>
@@ -26633,7 +26856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L8"/>
   <sheetData>
@@ -26948,7 +27171,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G9"/>
   <sheetData>
@@ -27166,7 +27389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetData>
@@ -27292,7 +27515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G4"/>
   <sheetData>
@@ -27393,95 +27616,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>protocolCode</v>
-      </c>
-      <c r="C1" t="str">
-        <v>safetyGate</v>
-      </c>
-      <c r="D1" t="str">
-        <v>requiredPpe</v>
-      </c>
-      <c r="E1" t="str">
-        <v>digitalMultimeterCheck</v>
-      </c>
-      <c r="F1" t="str">
-        <v>active</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>EV-01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>EV-ISO-01</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Manual Service Disconnect (MSD) orange plug removal &amp; lock-out tag-out (LOTO)</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Class 0 1000V Insulated Gloves + Face Shield</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>EV-02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>EV-ISO-02</v>
-      </c>
-      <c r="C3" t="str">
-        <v>12V Auxiliary battery terminal disconnection to disable HV contactor control</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Class 0 1000V Insulated Gloves + Face Shield</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>EV-03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>EV-ISO-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Capacitor discharge wait cycle (10 mins) and inverter busbar residual test</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Rubber Insulated Floor Matting 17kV</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/public/downloads/TML_Existing_Masters_Catalogue.xlsx
+++ b/public/downloads/TML_Existing_Masters_Catalogue.xlsx
@@ -31679,7 +31679,7 @@
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32024,19 +32024,19 @@
         <v>SKL-13</v>
       </c>
       <c r="B14" t="str">
-        <v>PART-INV</v>
+        <v>SA-MECH</v>
       </c>
       <c r="C14" t="str">
-        <v>Parts Issue &amp; Inventory</v>
+        <v>Service Advisory — Mechanical jobs</v>
       </c>
       <c r="D14" t="str">
-        <v>Parts &amp; Inventory</v>
+        <v>Customer Handling</v>
       </c>
       <c r="E14" t="str">
         <v>PV</v>
       </c>
       <c r="F14" t="str">
-        <v>Parts Store Officer</v>
+        <v>Service Advisor</v>
       </c>
       <c r="G14" t="str">
         <v>N</v>
@@ -32050,30 +32050,82 @@
         <v>SKL-14</v>
       </c>
       <c r="B15" t="str">
-        <v>SAFE-FIRE</v>
+        <v>SA-BODY</v>
       </c>
       <c r="C15" t="str">
-        <v>Workshop Safety &amp; Fire Response</v>
+        <v>Service Advisory — Bodyshop &amp; Insurance jobs</v>
       </c>
       <c r="D15" t="str">
-        <v>Safety</v>
+        <v>Customer Handling</v>
       </c>
       <c r="E15" t="str">
         <v>PV</v>
       </c>
       <c r="F15" t="str">
-        <v>Any</v>
+        <v>Service Advisor</v>
       </c>
       <c r="G15" t="str">
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="H15" t="str">
         <v>Active</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SKL-15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PART-INV</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Parts Issue &amp; Inventory</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Parts &amp; Inventory</v>
+      </c>
+      <c r="E16" t="str">
+        <v>PV</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Parts Store Officer</v>
+      </c>
+      <c r="G16" t="str">
+        <v>N</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SKL-16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>SAFE-FIRE</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Workshop Safety &amp; Fire Response</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Safety</v>
+      </c>
+      <c r="E17" t="str">
+        <v>PV</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Any</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Y</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Active</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -34755,7 +34807,7 @@
 
 <file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K193"/>
+  <dimension ref="A1:K196"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -38049,22 +38101,22 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ADMIN_EMPLOYMENT_TYPE-01</v>
+        <v>ADMIN_SA_EXPERTISE-01</v>
       </c>
       <c r="B95" t="str">
-        <v>ADMIN_EMPLOYMENT_TYPE</v>
+        <v>ADMIN_SA_EXPERTISE</v>
       </c>
       <c r="C95" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D95" t="str">
-        <v>Employment Type</v>
+        <v>Service Advisor Expertise</v>
       </c>
       <c r="E95" t="str">
-        <v>Permanent</v>
+        <v>Mechanical</v>
       </c>
       <c r="F95" t="str">
-        <v>PERMANENT</v>
+        <v>MECHANICAL</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -38084,22 +38136,22 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>ADMIN_EMPLOYMENT_TYPE-02</v>
+        <v>ADMIN_SA_EXPERTISE-02</v>
       </c>
       <c r="B96" t="str">
-        <v>ADMIN_EMPLOYMENT_TYPE</v>
+        <v>ADMIN_SA_EXPERTISE</v>
       </c>
       <c r="C96" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D96" t="str">
-        <v>Employment Type</v>
+        <v>Service Advisor Expertise</v>
       </c>
       <c r="E96" t="str">
-        <v>Contract</v>
+        <v>Bodyshop</v>
       </c>
       <c r="F96" t="str">
-        <v>CONTRACT</v>
+        <v>BODYSHOP</v>
       </c>
       <c r="G96">
         <v>2</v>
@@ -38119,22 +38171,22 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ADMIN_EMPLOYMENT_TYPE-03</v>
+        <v>ADMIN_SA_EXPERTISE-03</v>
       </c>
       <c r="B97" t="str">
-        <v>ADMIN_EMPLOYMENT_TYPE</v>
+        <v>ADMIN_SA_EXPERTISE</v>
       </c>
       <c r="C97" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D97" t="str">
-        <v>Employment Type</v>
+        <v>Service Advisor Expertise</v>
       </c>
       <c r="E97" t="str">
-        <v>Apprentice</v>
+        <v>Both</v>
       </c>
       <c r="F97" t="str">
-        <v>APPRENTICE</v>
+        <v>BOTH</v>
       </c>
       <c r="G97">
         <v>3</v>
@@ -38154,7 +38206,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ADMIN_EMPLOYMENT_TYPE-04</v>
+        <v>ADMIN_EMPLOYMENT_TYPE-01</v>
       </c>
       <c r="B98" t="str">
         <v>ADMIN_EMPLOYMENT_TYPE</v>
@@ -38166,13 +38218,13 @@
         <v>Employment Type</v>
       </c>
       <c r="E98" t="str">
-        <v>Trainee</v>
+        <v>Permanent</v>
       </c>
       <c r="F98" t="str">
-        <v>TRAINEE</v>
+        <v>PERMANENT</v>
       </c>
       <c r="G98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -38189,7 +38241,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>ADMIN_EMPLOYMENT_TYPE-05</v>
+        <v>ADMIN_EMPLOYMENT_TYPE-02</v>
       </c>
       <c r="B99" t="str">
         <v>ADMIN_EMPLOYMENT_TYPE</v>
@@ -38201,13 +38253,13 @@
         <v>Employment Type</v>
       </c>
       <c r="E99" t="str">
-        <v>Consultant</v>
+        <v>Contract</v>
       </c>
       <c r="F99" t="str">
-        <v>CONSULTANT</v>
+        <v>CONTRACT</v>
       </c>
       <c r="G99">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H99" t="str">
         <v/>
@@ -38224,25 +38276,25 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>ADMIN_EMPLOYEE_LIFECYCLE-01</v>
+        <v>ADMIN_EMPLOYMENT_TYPE-03</v>
       </c>
       <c r="B100" t="str">
-        <v>ADMIN_EMPLOYEE_LIFECYCLE</v>
+        <v>ADMIN_EMPLOYMENT_TYPE</v>
       </c>
       <c r="C100" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D100" t="str">
-        <v>Employment Status</v>
+        <v>Employment Type</v>
       </c>
       <c r="E100" t="str">
-        <v>Active</v>
+        <v>Apprentice</v>
       </c>
       <c r="F100" t="str">
-        <v>ACTIVE</v>
+        <v>APPRENTICE</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H100" t="str">
         <v/>
@@ -38259,25 +38311,25 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>ADMIN_EMPLOYEE_LIFECYCLE-02</v>
+        <v>ADMIN_EMPLOYMENT_TYPE-04</v>
       </c>
       <c r="B101" t="str">
-        <v>ADMIN_EMPLOYEE_LIFECYCLE</v>
+        <v>ADMIN_EMPLOYMENT_TYPE</v>
       </c>
       <c r="C101" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D101" t="str">
-        <v>Employment Status</v>
+        <v>Employment Type</v>
       </c>
       <c r="E101" t="str">
-        <v>On Leave</v>
+        <v>Trainee</v>
       </c>
       <c r="F101" t="str">
-        <v>ON_LEAVE</v>
+        <v>TRAINEE</v>
       </c>
       <c r="G101">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H101" t="str">
         <v/>
@@ -38294,25 +38346,25 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ADMIN_EMPLOYEE_LIFECYCLE-03</v>
+        <v>ADMIN_EMPLOYMENT_TYPE-05</v>
       </c>
       <c r="B102" t="str">
-        <v>ADMIN_EMPLOYEE_LIFECYCLE</v>
+        <v>ADMIN_EMPLOYMENT_TYPE</v>
       </c>
       <c r="C102" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D102" t="str">
-        <v>Employment Status</v>
+        <v>Employment Type</v>
       </c>
       <c r="E102" t="str">
-        <v>On Notice</v>
+        <v>Consultant</v>
       </c>
       <c r="F102" t="str">
-        <v>ON_NOTICE</v>
+        <v>CONSULTANT</v>
       </c>
       <c r="G102">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H102" t="str">
         <v/>
@@ -38329,7 +38381,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ADMIN_EMPLOYEE_LIFECYCLE-04</v>
+        <v>ADMIN_EMPLOYEE_LIFECYCLE-01</v>
       </c>
       <c r="B103" t="str">
         <v>ADMIN_EMPLOYEE_LIFECYCLE</v>
@@ -38341,13 +38393,13 @@
         <v>Employment Status</v>
       </c>
       <c r="E103" t="str">
-        <v>Left</v>
+        <v>Active</v>
       </c>
       <c r="F103" t="str">
-        <v>LEFT</v>
+        <v>ACTIVE</v>
       </c>
       <c r="G103">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H103" t="str">
         <v/>
@@ -38364,25 +38416,25 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ADMIN_SKILL_CATEGORY-01</v>
+        <v>ADMIN_EMPLOYEE_LIFECYCLE-02</v>
       </c>
       <c r="B104" t="str">
-        <v>ADMIN_SKILL_CATEGORY</v>
+        <v>ADMIN_EMPLOYEE_LIFECYCLE</v>
       </c>
       <c r="C104" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D104" t="str">
-        <v>Skill Category</v>
+        <v>Employment Status</v>
       </c>
       <c r="E104" t="str">
-        <v>Mechanical</v>
+        <v>On Leave</v>
       </c>
       <c r="F104" t="str">
-        <v>MECHANICAL</v>
+        <v>ON_LEAVE</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" t="str">
         <v/>
@@ -38399,25 +38451,25 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ADMIN_SKILL_CATEGORY-02</v>
+        <v>ADMIN_EMPLOYEE_LIFECYCLE-03</v>
       </c>
       <c r="B105" t="str">
-        <v>ADMIN_SKILL_CATEGORY</v>
+        <v>ADMIN_EMPLOYEE_LIFECYCLE</v>
       </c>
       <c r="C105" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D105" t="str">
-        <v>Skill Category</v>
+        <v>Employment Status</v>
       </c>
       <c r="E105" t="str">
-        <v>Electrical</v>
+        <v>On Notice</v>
       </c>
       <c r="F105" t="str">
-        <v>ELECTRICAL</v>
+        <v>ON_NOTICE</v>
       </c>
       <c r="G105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H105" t="str">
         <v/>
@@ -38434,25 +38486,25 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ADMIN_SKILL_CATEGORY-03</v>
+        <v>ADMIN_EMPLOYEE_LIFECYCLE-04</v>
       </c>
       <c r="B106" t="str">
-        <v>ADMIN_SKILL_CATEGORY</v>
+        <v>ADMIN_EMPLOYEE_LIFECYCLE</v>
       </c>
       <c r="C106" t="str">
         <v>ADMIN</v>
       </c>
       <c r="D106" t="str">
-        <v>Skill Category</v>
+        <v>Employment Status</v>
       </c>
       <c r="E106" t="str">
-        <v>EV / High Voltage</v>
+        <v>Left</v>
       </c>
       <c r="F106" t="str">
-        <v>EV_HIGH_VOLTAGE</v>
+        <v>LEFT</v>
       </c>
       <c r="G106">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H106" t="str">
         <v/>
@@ -38469,7 +38521,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ADMIN_SKILL_CATEGORY-04</v>
+        <v>ADMIN_SKILL_CATEGORY-01</v>
       </c>
       <c r="B107" t="str">
         <v>ADMIN_SKILL_CATEGORY</v>
@@ -38481,13 +38533,13 @@
         <v>Skill Category</v>
       </c>
       <c r="E107" t="str">
-        <v>Bodyshop</v>
+        <v>Mechanical</v>
       </c>
       <c r="F107" t="str">
-        <v>BODYSHOP</v>
+        <v>MECHANICAL</v>
       </c>
       <c r="G107">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H107" t="str">
         <v/>
@@ -38504,7 +38556,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>ADMIN_SKILL_CATEGORY-05</v>
+        <v>ADMIN_SKILL_CATEGORY-02</v>
       </c>
       <c r="B108" t="str">
         <v>ADMIN_SKILL_CATEGORY</v>
@@ -38516,13 +38568,13 @@
         <v>Skill Category</v>
       </c>
       <c r="E108" t="str">
-        <v>Paint</v>
+        <v>Electrical</v>
       </c>
       <c r="F108" t="str">
-        <v>PAINT</v>
+        <v>ELECTRICAL</v>
       </c>
       <c r="G108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H108" t="str">
         <v/>
@@ -38539,7 +38591,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ADMIN_SKILL_CATEGORY-06</v>
+        <v>ADMIN_SKILL_CATEGORY-03</v>
       </c>
       <c r="B109" t="str">
         <v>ADMIN_SKILL_CATEGORY</v>
@@ -38551,13 +38603,13 @@
         <v>Skill Category</v>
       </c>
       <c r="E109" t="str">
-        <v>AC &amp; Cooling</v>
+        <v>EV / High Voltage</v>
       </c>
       <c r="F109" t="str">
-        <v>AC_COOLING</v>
+        <v>EV_HIGH_VOLTAGE</v>
       </c>
       <c r="G109">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H109" t="str">
         <v/>
@@ -38574,7 +38626,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ADMIN_SKILL_CATEGORY-07</v>
+        <v>ADMIN_SKILL_CATEGORY-04</v>
       </c>
       <c r="B110" t="str">
         <v>ADMIN_SKILL_CATEGORY</v>
@@ -38586,13 +38638,13 @@
         <v>Skill Category</v>
       </c>
       <c r="E110" t="str">
-        <v>Diagnostics</v>
+        <v>Bodyshop</v>
       </c>
       <c r="F110" t="str">
-        <v>DIAGNOSTICS</v>
+        <v>BODYSHOP</v>
       </c>
       <c r="G110">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H110" t="str">
         <v/>
@@ -38609,7 +38661,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ADMIN_SKILL_CATEGORY-08</v>
+        <v>ADMIN_SKILL_CATEGORY-05</v>
       </c>
       <c r="B111" t="str">
         <v>ADMIN_SKILL_CATEGORY</v>
@@ -38621,13 +38673,13 @@
         <v>Skill Category</v>
       </c>
       <c r="E111" t="str">
-        <v>Customer Handling</v>
+        <v>Paint</v>
       </c>
       <c r="F111" t="str">
-        <v>CUSTOMER_HANDLING</v>
+        <v>PAINT</v>
       </c>
       <c r="G111">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H111" t="str">
         <v/>
@@ -38644,7 +38696,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ADMIN_SKILL_CATEGORY-09</v>
+        <v>ADMIN_SKILL_CATEGORY-06</v>
       </c>
       <c r="B112" t="str">
         <v>ADMIN_SKILL_CATEGORY</v>
@@ -38656,13 +38708,13 @@
         <v>Skill Category</v>
       </c>
       <c r="E112" t="str">
-        <v>Parts &amp; Inventory</v>
+        <v>AC &amp; Cooling</v>
       </c>
       <c r="F112" t="str">
-        <v>PARTS_INVENTORY</v>
+        <v>AC_COOLING</v>
       </c>
       <c r="G112">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H112" t="str">
         <v/>
@@ -38679,7 +38731,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>ADMIN_SKILL_CATEGORY-10</v>
+        <v>ADMIN_SKILL_CATEGORY-07</v>
       </c>
       <c r="B113" t="str">
         <v>ADMIN_SKILL_CATEGORY</v>
@@ -38691,13 +38743,13 @@
         <v>Skill Category</v>
       </c>
       <c r="E113" t="str">
-        <v>Quality</v>
+        <v>Diagnostics</v>
       </c>
       <c r="F113" t="str">
-        <v>QUALITY</v>
+        <v>DIAGNOSTICS</v>
       </c>
       <c r="G113">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H113" t="str">
         <v/>
@@ -38714,7 +38766,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>ADMIN_SKILL_CATEGORY-11</v>
+        <v>ADMIN_SKILL_CATEGORY-08</v>
       </c>
       <c r="B114" t="str">
         <v>ADMIN_SKILL_CATEGORY</v>
@@ -38726,13 +38778,13 @@
         <v>Skill Category</v>
       </c>
       <c r="E114" t="str">
-        <v>Safety</v>
+        <v>Customer Handling</v>
       </c>
       <c r="F114" t="str">
-        <v>SAFETY</v>
+        <v>CUSTOMER_HANDLING</v>
       </c>
       <c r="G114">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H114" t="str">
         <v/>
@@ -38749,25 +38801,25 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>THD_PROGRESS-01</v>
+        <v>ADMIN_SKILL_CATEGORY-09</v>
       </c>
       <c r="B115" t="str">
-        <v>THD_PROGRESS</v>
+        <v>ADMIN_SKILL_CATEGORY</v>
       </c>
       <c r="C115" t="str">
-        <v>THD</v>
+        <v>ADMIN</v>
       </c>
       <c r="D115" t="str">
-        <v>Progress</v>
+        <v>Skill Category</v>
       </c>
       <c r="E115" t="str">
-        <v>Under Diagnosis</v>
+        <v>Parts &amp; Inventory</v>
       </c>
       <c r="F115" t="str">
-        <v>UNDER_DIAGNOSIS</v>
+        <v>PARTS_INVENTORY</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H115" t="str">
         <v/>
@@ -38784,25 +38836,25 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>THD_PROGRESS-02</v>
+        <v>ADMIN_SKILL_CATEGORY-10</v>
       </c>
       <c r="B116" t="str">
-        <v>THD_PROGRESS</v>
+        <v>ADMIN_SKILL_CATEGORY</v>
       </c>
       <c r="C116" t="str">
-        <v>THD</v>
+        <v>ADMIN</v>
       </c>
       <c r="D116" t="str">
-        <v>Progress</v>
+        <v>Skill Category</v>
       </c>
       <c r="E116" t="str">
-        <v>Work in process</v>
+        <v>Quality</v>
       </c>
       <c r="F116" t="str">
-        <v>WORK_IN_PROCESS</v>
+        <v>QUALITY</v>
       </c>
       <c r="G116">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H116" t="str">
         <v/>
@@ -38819,25 +38871,25 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>THD_PROGRESS-03</v>
+        <v>ADMIN_SKILL_CATEGORY-11</v>
       </c>
       <c r="B117" t="str">
-        <v>THD_PROGRESS</v>
+        <v>ADMIN_SKILL_CATEGORY</v>
       </c>
       <c r="C117" t="str">
-        <v>THD</v>
+        <v>ADMIN</v>
       </c>
       <c r="D117" t="str">
-        <v>Progress</v>
+        <v>Skill Category</v>
       </c>
       <c r="E117" t="str">
-        <v>Pending for parts</v>
+        <v>Safety</v>
       </c>
       <c r="F117" t="str">
-        <v>PENDING_FOR_PARTS</v>
+        <v>SAFETY</v>
       </c>
       <c r="G117">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H117" t="str">
         <v/>
@@ -38854,7 +38906,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>THD_PROGRESS-04</v>
+        <v>THD_PROGRESS-01</v>
       </c>
       <c r="B118" t="str">
         <v>THD_PROGRESS</v>
@@ -38866,13 +38918,13 @@
         <v>Progress</v>
       </c>
       <c r="E118" t="str">
-        <v>Pending for vendor support</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="F118" t="str">
-        <v>PENDING_FOR_VENDOR_SUPPORT</v>
+        <v>UNDER_DIAGNOSIS</v>
       </c>
       <c r="G118">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H118" t="str">
         <v/>
@@ -38889,7 +38941,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>THD_PROGRESS-05</v>
+        <v>THD_PROGRESS-02</v>
       </c>
       <c r="B119" t="str">
         <v>THD_PROGRESS</v>
@@ -38901,13 +38953,13 @@
         <v>Progress</v>
       </c>
       <c r="E119" t="str">
-        <v>Pending for commercial decision</v>
+        <v>Work in process</v>
       </c>
       <c r="F119" t="str">
-        <v>PENDING_FOR_COMMERCIAL_DECISION</v>
+        <v>WORK_IN_PROCESS</v>
       </c>
       <c r="G119">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H119" t="str">
         <v/>
@@ -38924,7 +38976,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>THD_PROGRESS-06</v>
+        <v>THD_PROGRESS-03</v>
       </c>
       <c r="B120" t="str">
         <v>THD_PROGRESS</v>
@@ -38936,13 +38988,13 @@
         <v>Progress</v>
       </c>
       <c r="E120" t="str">
-        <v>Pending for Vehicle availability</v>
+        <v>Pending for parts</v>
       </c>
       <c r="F120" t="str">
-        <v>PENDING_FOR_VEHICLE_AVAILABILITY</v>
+        <v>PENDING_FOR_PARTS</v>
       </c>
       <c r="G120">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H120" t="str">
         <v/>
@@ -38959,31 +39011,31 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-01</v>
+        <v>THD_PROGRESS-04</v>
       </c>
       <c r="B121" t="str">
-        <v>THD_PROGRESS_SUB_STATUS</v>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="C121" t="str">
         <v>THD</v>
       </c>
       <c r="D121" t="str">
-        <v>Progress Sub Status</v>
+        <v>Progress</v>
       </c>
       <c r="E121" t="str">
-        <v>U/I DET</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="F121" t="str">
-        <v>U_I_DET</v>
+        <v>PENDING_FOR_VENDOR_SUPPORT</v>
       </c>
       <c r="G121">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H121" t="str">
-        <v>THD_PROGRESS</v>
+        <v/>
       </c>
       <c r="I121" t="str">
-        <v>Under Diagnosis</v>
+        <v/>
       </c>
       <c r="J121" t="str">
         <v/>
@@ -38994,31 +39046,31 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-02</v>
+        <v>THD_PROGRESS-05</v>
       </c>
       <c r="B122" t="str">
-        <v>THD_PROGRESS_SUB_STATUS</v>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="C122" t="str">
         <v>THD</v>
       </c>
       <c r="D122" t="str">
-        <v>Progress Sub Status</v>
+        <v>Progress</v>
       </c>
       <c r="E122" t="str">
-        <v>U/I COC</v>
+        <v>Pending for commercial decision</v>
       </c>
       <c r="F122" t="str">
-        <v>U_I_COC</v>
+        <v>PENDING_FOR_COMMERCIAL_DECISION</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H122" t="str">
-        <v>THD_PROGRESS</v>
+        <v/>
       </c>
       <c r="I122" t="str">
-        <v>Under Diagnosis</v>
+        <v/>
       </c>
       <c r="J122" t="str">
         <v/>
@@ -39029,31 +39081,31 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-03</v>
+        <v>THD_PROGRESS-06</v>
       </c>
       <c r="B123" t="str">
-        <v>THD_PROGRESS_SUB_STATUS</v>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="C123" t="str">
         <v>THD</v>
       </c>
       <c r="D123" t="str">
-        <v>Progress Sub Status</v>
+        <v>Progress</v>
       </c>
       <c r="E123" t="str">
-        <v>U/I Vendor</v>
+        <v>Pending for Vehicle availability</v>
       </c>
       <c r="F123" t="str">
-        <v>U_I_VENDOR</v>
+        <v>PENDING_FOR_VEHICLE_AVAILABILITY</v>
       </c>
       <c r="G123">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H123" t="str">
-        <v>THD_PROGRESS</v>
+        <v/>
       </c>
       <c r="I123" t="str">
-        <v>Under Diagnosis</v>
+        <v/>
       </c>
       <c r="J123" t="str">
         <v/>
@@ -39064,7 +39116,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-04</v>
+        <v>THD_PROGRESS_SUB_STATUS-01</v>
       </c>
       <c r="B124" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39076,13 +39128,13 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E124" t="str">
-        <v>U/I Plant Team</v>
+        <v>U/I DET</v>
       </c>
       <c r="F124" t="str">
-        <v>U_I_PLANT_TEAM</v>
+        <v>U_I_DET</v>
       </c>
       <c r="G124">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H124" t="str">
         <v>THD_PROGRESS</v>
@@ -39099,7 +39151,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-05</v>
+        <v>THD_PROGRESS_SUB_STATUS-02</v>
       </c>
       <c r="B125" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39111,19 +39163,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E125" t="str">
-        <v>WIP DET</v>
+        <v>U/I COC</v>
       </c>
       <c r="F125" t="str">
-        <v>WIP_DET</v>
+        <v>U_I_COC</v>
       </c>
       <c r="G125">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H125" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I125" t="str">
-        <v>Work in process</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="J125" t="str">
         <v/>
@@ -39134,7 +39186,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-06</v>
+        <v>THD_PROGRESS_SUB_STATUS-03</v>
       </c>
       <c r="B126" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39146,19 +39198,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E126" t="str">
-        <v>WIP W/S Team</v>
+        <v>U/I Vendor</v>
       </c>
       <c r="F126" t="str">
-        <v>WIP_W_S_TEAM</v>
+        <v>U_I_VENDOR</v>
       </c>
       <c r="G126">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H126" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I126" t="str">
-        <v>Work in process</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="J126" t="str">
         <v/>
@@ -39169,7 +39221,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-07</v>
+        <v>THD_PROGRESS_SUB_STATUS-04</v>
       </c>
       <c r="B127" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39181,19 +39233,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E127" t="str">
-        <v>WIP Vendor</v>
+        <v>U/I Plant Team</v>
       </c>
       <c r="F127" t="str">
-        <v>WIP_VENDOR</v>
+        <v>U_I_PLANT_TEAM</v>
       </c>
       <c r="G127">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H127" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I127" t="str">
-        <v>Work in process</v>
+        <v>Under Diagnosis</v>
       </c>
       <c r="J127" t="str">
         <v/>
@@ -39204,7 +39256,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-08</v>
+        <v>THD_PROGRESS_SUB_STATUS-05</v>
       </c>
       <c r="B128" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39216,19 +39268,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E128" t="str">
-        <v>Order status</v>
+        <v>WIP DET</v>
       </c>
       <c r="F128" t="str">
-        <v>ORDER_STATUS</v>
+        <v>WIP_DET</v>
       </c>
       <c r="G128">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H128" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I128" t="str">
-        <v>Pending for parts</v>
+        <v>Work in process</v>
       </c>
       <c r="J128" t="str">
         <v/>
@@ -39239,7 +39291,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-09</v>
+        <v>THD_PROGRESS_SUB_STATUS-06</v>
       </c>
       <c r="B129" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39251,19 +39303,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E129" t="str">
-        <v>Part receipt status</v>
+        <v>WIP W/S Team</v>
       </c>
       <c r="F129" t="str">
-        <v>PART_RECEIPT_STATUS</v>
+        <v>WIP_W_S_TEAM</v>
       </c>
       <c r="G129">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H129" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I129" t="str">
-        <v>Pending for parts</v>
+        <v>Work in process</v>
       </c>
       <c r="J129" t="str">
         <v/>
@@ -39274,7 +39326,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-10</v>
+        <v>THD_PROGRESS_SUB_STATUS-07</v>
       </c>
       <c r="B130" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39286,19 +39338,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E130" t="str">
-        <v>Vendor details</v>
+        <v>WIP Vendor</v>
       </c>
       <c r="F130" t="str">
-        <v>VENDOR_DETAILS</v>
+        <v>WIP_VENDOR</v>
       </c>
       <c r="G130">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H130" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I130" t="str">
-        <v>Pending for vendor support</v>
+        <v>Work in process</v>
       </c>
       <c r="J130" t="str">
         <v/>
@@ -39309,7 +39361,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-11</v>
+        <v>THD_PROGRESS_SUB_STATUS-08</v>
       </c>
       <c r="B131" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39321,19 +39373,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E131" t="str">
-        <v>Request raised</v>
+        <v>Order status</v>
       </c>
       <c r="F131" t="str">
-        <v>REQUEST_RAISED</v>
+        <v>ORDER_STATUS</v>
       </c>
       <c r="G131">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H131" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I131" t="str">
-        <v>Pending for vendor support</v>
+        <v>Pending for parts</v>
       </c>
       <c r="J131" t="str">
         <v/>
@@ -39344,7 +39396,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-12</v>
+        <v>THD_PROGRESS_SUB_STATUS-09</v>
       </c>
       <c r="B132" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39356,19 +39408,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E132" t="str">
-        <v>Status</v>
+        <v>Part receipt status</v>
       </c>
       <c r="F132" t="str">
-        <v>STATUS</v>
+        <v>PART_RECEIPT_STATUS</v>
       </c>
       <c r="G132">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H132" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I132" t="str">
-        <v>Pending for vendor support</v>
+        <v>Pending for parts</v>
       </c>
       <c r="J132" t="str">
         <v/>
@@ -39379,7 +39431,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-13</v>
+        <v>THD_PROGRESS_SUB_STATUS-10</v>
       </c>
       <c r="B133" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39391,19 +39443,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E133" t="str">
-        <v>Pending for approval</v>
+        <v>Vendor details</v>
       </c>
       <c r="F133" t="str">
-        <v>PENDING_FOR_APPROVAL</v>
+        <v>VENDOR_DETAILS</v>
       </c>
       <c r="G133">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H133" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I133" t="str">
-        <v>Pending for commercial decision</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="J133" t="str">
         <v/>
@@ -39414,7 +39466,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-14</v>
+        <v>THD_PROGRESS_SUB_STATUS-11</v>
       </c>
       <c r="B134" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39426,19 +39478,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E134" t="str">
-        <v>Approval received</v>
+        <v>Request raised</v>
       </c>
       <c r="F134" t="str">
-        <v>APPROVAL_RECEIVED</v>
+        <v>REQUEST_RAISED</v>
       </c>
       <c r="G134">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H134" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I134" t="str">
-        <v>Pending for commercial decision</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="J134" t="str">
         <v/>
@@ -39449,7 +39501,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-15</v>
+        <v>THD_PROGRESS_SUB_STATUS-12</v>
       </c>
       <c r="B135" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39461,19 +39513,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E135" t="str">
-        <v>Expected date</v>
+        <v>Status</v>
       </c>
       <c r="F135" t="str">
-        <v>EXPECTED_DATE</v>
+        <v>STATUS</v>
       </c>
       <c r="G135">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H135" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I135" t="str">
-        <v>Pending for Vehicle availability</v>
+        <v>Pending for vendor support</v>
       </c>
       <c r="J135" t="str">
         <v/>
@@ -39484,7 +39536,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>THD_PROGRESS_SUB_STATUS-16</v>
+        <v>THD_PROGRESS_SUB_STATUS-13</v>
       </c>
       <c r="B136" t="str">
         <v>THD_PROGRESS_SUB_STATUS</v>
@@ -39496,19 +39548,19 @@
         <v>Progress Sub Status</v>
       </c>
       <c r="E136" t="str">
-        <v>Status as on date</v>
+        <v>Pending for approval</v>
       </c>
       <c r="F136" t="str">
-        <v>STATUS_AS_ON_DATE</v>
+        <v>PENDING_FOR_APPROVAL</v>
       </c>
       <c r="G136">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H136" t="str">
         <v>THD_PROGRESS</v>
       </c>
       <c r="I136" t="str">
-        <v>Pending for Vehicle availability</v>
+        <v>Pending for commercial decision</v>
       </c>
       <c r="J136" t="str">
         <v/>
@@ -39519,31 +39571,31 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>THD_COMPLAINT_TYPE-01</v>
+        <v>THD_PROGRESS_SUB_STATUS-14</v>
       </c>
       <c r="B137" t="str">
-        <v>THD_COMPLAINT_TYPE</v>
+        <v>THD_PROGRESS_SUB_STATUS</v>
       </c>
       <c r="C137" t="str">
         <v>THD</v>
       </c>
       <c r="D137" t="str">
-        <v>Type of Complaint</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="E137" t="str">
-        <v>Technical Query</v>
+        <v>Approval received</v>
       </c>
       <c r="F137" t="str">
-        <v>TECHNICAL_QUERY</v>
+        <v>APPROVAL_RECEIVED</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H137" t="str">
-        <v/>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="I137" t="str">
-        <v/>
+        <v>Pending for commercial decision</v>
       </c>
       <c r="J137" t="str">
         <v/>
@@ -39554,31 +39606,31 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>THD_COMPLAINT_TYPE-02</v>
+        <v>THD_PROGRESS_SUB_STATUS-15</v>
       </c>
       <c r="B138" t="str">
-        <v>THD_COMPLAINT_TYPE</v>
+        <v>THD_PROGRESS_SUB_STATUS</v>
       </c>
       <c r="C138" t="str">
         <v>THD</v>
       </c>
       <c r="D138" t="str">
-        <v>Type of Complaint</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="E138" t="str">
-        <v>Technical Support</v>
+        <v>Expected date</v>
       </c>
       <c r="F138" t="str">
-        <v>TECHNICAL_SUPPORT</v>
+        <v>EXPECTED_DATE</v>
       </c>
       <c r="G138">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H138" t="str">
-        <v/>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="I138" t="str">
-        <v/>
+        <v>Pending for Vehicle availability</v>
       </c>
       <c r="J138" t="str">
         <v/>
@@ -39589,31 +39641,31 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-01</v>
+        <v>THD_PROGRESS_SUB_STATUS-16</v>
       </c>
       <c r="B139" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC</v>
+        <v>THD_PROGRESS_SUB_STATUS</v>
       </c>
       <c r="C139" t="str">
         <v>THD</v>
       </c>
       <c r="D139" t="str">
-        <v>Complaint Short Description</v>
+        <v>Progress Sub Status</v>
       </c>
       <c r="E139" t="str">
-        <v>Abnormal noise</v>
+        <v>Status as on date</v>
       </c>
       <c r="F139" t="str">
-        <v>ABNORMAL_NOISE</v>
+        <v>STATUS_AS_ON_DATE</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H139" t="str">
-        <v/>
+        <v>THD_PROGRESS</v>
       </c>
       <c r="I139" t="str">
-        <v/>
+        <v>Pending for Vehicle availability</v>
       </c>
       <c r="J139" t="str">
         <v/>
@@ -39624,25 +39676,25 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-02</v>
+        <v>THD_COMPLAINT_TYPE-01</v>
       </c>
       <c r="B140" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC</v>
+        <v>THD_COMPLAINT_TYPE</v>
       </c>
       <c r="C140" t="str">
         <v>THD</v>
       </c>
       <c r="D140" t="str">
-        <v>Complaint Short Description</v>
+        <v>Type of Complaint</v>
       </c>
       <c r="E140" t="str">
-        <v>Warning lamps ON</v>
+        <v>Technical Query</v>
       </c>
       <c r="F140" t="str">
-        <v>WARNING_LAMPS_ON</v>
+        <v>TECHNICAL_QUERY</v>
       </c>
       <c r="G140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H140" t="str">
         <v/>
@@ -39659,25 +39711,25 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-03</v>
+        <v>THD_COMPLAINT_TYPE-02</v>
       </c>
       <c r="B141" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC</v>
+        <v>THD_COMPLAINT_TYPE</v>
       </c>
       <c r="C141" t="str">
         <v>THD</v>
       </c>
       <c r="D141" t="str">
-        <v>Complaint Short Description</v>
+        <v>Type of Complaint</v>
       </c>
       <c r="E141" t="str">
-        <v>Oil leakage</v>
+        <v>Technical Support</v>
       </c>
       <c r="F141" t="str">
-        <v>OIL_LEAKAGE</v>
+        <v>TECHNICAL_SUPPORT</v>
       </c>
       <c r="G141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H141" t="str">
         <v/>
@@ -39694,7 +39746,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-04</v>
+        <v>THD_COMPLAINT_SHORT_DESC-01</v>
       </c>
       <c r="B142" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39706,13 +39758,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E142" t="str">
-        <v>Coolant leakage</v>
+        <v>Abnormal noise</v>
       </c>
       <c r="F142" t="str">
-        <v>COOLANT_LEAKAGE</v>
+        <v>ABNORMAL_NOISE</v>
       </c>
       <c r="G142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H142" t="str">
         <v/>
@@ -39729,7 +39781,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-05</v>
+        <v>THD_COMPLAINT_SHORT_DESC-02</v>
       </c>
       <c r="B143" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39741,13 +39793,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E143" t="str">
-        <v>Engine overheating</v>
+        <v>Warning lamps ON</v>
       </c>
       <c r="F143" t="str">
-        <v>ENGINE_OVERHEATING</v>
+        <v>WARNING_LAMPS_ON</v>
       </c>
       <c r="G143">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H143" t="str">
         <v/>
@@ -39764,7 +39816,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-06</v>
+        <v>THD_COMPLAINT_SHORT_DESC-03</v>
       </c>
       <c r="B144" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39776,13 +39828,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E144" t="str">
-        <v>Smell – burning, fuel, foul odor from outside, etc.</v>
+        <v>Oil leakage</v>
       </c>
       <c r="F144" t="str">
-        <v>SMELL_BURNING_FUEL_FOUL_ODOR_FROM_OUTSID</v>
+        <v>OIL_LEAKAGE</v>
       </c>
       <c r="G144">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H144" t="str">
         <v/>
@@ -39799,7 +39851,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-07</v>
+        <v>THD_COMPLAINT_SHORT_DESC-04</v>
       </c>
       <c r="B145" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39811,13 +39863,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E145" t="str">
-        <v>Smoke issues</v>
+        <v>Coolant leakage</v>
       </c>
       <c r="F145" t="str">
-        <v>SMOKE_ISSUES</v>
+        <v>COOLANT_LEAKAGE</v>
       </c>
       <c r="G145">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H145" t="str">
         <v/>
@@ -39834,7 +39886,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-08</v>
+        <v>THD_COMPLAINT_SHORT_DESC-05</v>
       </c>
       <c r="B146" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39846,13 +39898,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E146" t="str">
-        <v>Oil-Coolant mix</v>
+        <v>Engine overheating</v>
       </c>
       <c r="F146" t="str">
-        <v>OIL_COOLANT_MIX</v>
+        <v>ENGINE_OVERHEATING</v>
       </c>
       <c r="G146">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H146" t="str">
         <v/>
@@ -39869,7 +39921,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-09</v>
+        <v>THD_COMPLAINT_SHORT_DESC-06</v>
       </c>
       <c r="B147" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39881,13 +39933,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E147" t="str">
-        <v>Gear shifting issues</v>
+        <v>Smell – burning, fuel, foul odor from outside, etc.</v>
       </c>
       <c r="F147" t="str">
-        <v>GEAR_SHIFTING_ISSUES</v>
+        <v>SMELL_BURNING_FUEL_FOUL_ODOR_FROM_OUTSID</v>
       </c>
       <c r="G147">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H147" t="str">
         <v/>
@@ -39904,7 +39956,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-10</v>
+        <v>THD_COMPLAINT_SHORT_DESC-07</v>
       </c>
       <c r="B148" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39916,13 +39968,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E148" t="str">
-        <v>AC cooling issues</v>
+        <v>Smoke issues</v>
       </c>
       <c r="F148" t="str">
-        <v>AC_COOLING_ISSUES</v>
+        <v>SMOKE_ISSUES</v>
       </c>
       <c r="G148">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H148" t="str">
         <v/>
@@ -39939,7 +39991,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-11</v>
+        <v>THD_COMPLAINT_SHORT_DESC-08</v>
       </c>
       <c r="B149" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39951,13 +40003,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E149" t="str">
-        <v>Jerking / vibration / misfiring</v>
+        <v>Oil-Coolant mix</v>
       </c>
       <c r="F149" t="str">
-        <v>JERKING_VIBRATION_MISFIRING</v>
+        <v>OIL_COOLANT_MIX</v>
       </c>
       <c r="G149">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H149" t="str">
         <v/>
@@ -39974,7 +40026,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-12</v>
+        <v>THD_COMPLAINT_SHORT_DESC-09</v>
       </c>
       <c r="B150" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -39986,13 +40038,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E150" t="str">
-        <v>Steering hard</v>
+        <v>Gear shifting issues</v>
       </c>
       <c r="F150" t="str">
-        <v>STEERING_HARD</v>
+        <v>GEAR_SHIFTING_ISSUES</v>
       </c>
       <c r="G150">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H150" t="str">
         <v/>
@@ -40009,7 +40061,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-13</v>
+        <v>THD_COMPLAINT_SHORT_DESC-10</v>
       </c>
       <c r="B151" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40021,13 +40073,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E151" t="str">
-        <v>Vehicle pulling</v>
+        <v>AC cooling issues</v>
       </c>
       <c r="F151" t="str">
-        <v>VEHICLE_PULLING</v>
+        <v>AC_COOLING_ISSUES</v>
       </c>
       <c r="G151">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H151" t="str">
         <v/>
@@ -40044,7 +40096,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-14</v>
+        <v>THD_COMPLAINT_SHORT_DESC-11</v>
       </c>
       <c r="B152" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40056,13 +40108,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E152" t="str">
-        <v>Starting problem</v>
+        <v>Jerking / vibration / misfiring</v>
       </c>
       <c r="F152" t="str">
-        <v>STARTING_PROBLEM</v>
+        <v>JERKING_VIBRATION_MISFIRING</v>
       </c>
       <c r="G152">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H152" t="str">
         <v/>
@@ -40079,7 +40131,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-15</v>
+        <v>THD_COMPLAINT_SHORT_DESC-12</v>
       </c>
       <c r="B153" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40091,13 +40143,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E153" t="str">
-        <v>Tyre wear / cut</v>
+        <v>Steering hard</v>
       </c>
       <c r="F153" t="str">
-        <v>TYRE_WEAR_CUT</v>
+        <v>STEERING_HARD</v>
       </c>
       <c r="G153">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H153" t="str">
         <v/>
@@ -40114,7 +40166,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-16</v>
+        <v>THD_COMPLAINT_SHORT_DESC-13</v>
       </c>
       <c r="B154" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40126,13 +40178,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E154" t="str">
-        <v>Damaged / broken / cracked / soiled</v>
+        <v>Vehicle pulling</v>
       </c>
       <c r="F154" t="str">
-        <v>DAMAGED_BROKEN_CRACKED_SOILED</v>
+        <v>VEHICLE_PULLING</v>
       </c>
       <c r="G154">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H154" t="str">
         <v/>
@@ -40149,7 +40201,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-17</v>
+        <v>THD_COMPLAINT_SHORT_DESC-14</v>
       </c>
       <c r="B155" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40161,13 +40213,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E155" t="str">
-        <v>Part missing / fallen-off</v>
+        <v>Starting problem</v>
       </c>
       <c r="F155" t="str">
-        <v>PART_MISSING_FALLEN_OFF</v>
+        <v>STARTING_PROBLEM</v>
       </c>
       <c r="G155">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H155" t="str">
         <v/>
@@ -40184,7 +40236,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-18</v>
+        <v>THD_COMPLAINT_SHORT_DESC-15</v>
       </c>
       <c r="B156" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40196,13 +40248,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E156" t="str">
-        <v>Uneven gaps / flushness issues</v>
+        <v>Tyre wear / cut</v>
       </c>
       <c r="F156" t="str">
-        <v>UNEVEN_GAPS_FLUSHNESS_ISSUES</v>
+        <v>TYRE_WEAR_CUT</v>
       </c>
       <c r="G156">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H156" t="str">
         <v/>
@@ -40219,7 +40271,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-19</v>
+        <v>THD_COMPLAINT_SHORT_DESC-16</v>
       </c>
       <c r="B157" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40231,13 +40283,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E157" t="str">
-        <v>Paint / rust issues</v>
+        <v>Damaged / broken / cracked / soiled</v>
       </c>
       <c r="F157" t="str">
-        <v>PAINT_RUST_ISSUES</v>
+        <v>DAMAGED_BROKEN_CRACKED_SOILED</v>
       </c>
       <c r="G157">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H157" t="str">
         <v/>
@@ -40254,7 +40306,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-20</v>
+        <v>THD_COMPLAINT_SHORT_DESC-17</v>
       </c>
       <c r="B158" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40266,13 +40318,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E158" t="str">
-        <v>Not working / functioning issues / system malfunction</v>
+        <v>Part missing / fallen-off</v>
       </c>
       <c r="F158" t="str">
-        <v>NOT_WORKING_FUNCTIONING_ISSUES_SYSTEM_MA</v>
+        <v>PART_MISSING_FALLEN_OFF</v>
       </c>
       <c r="G158">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H158" t="str">
         <v/>
@@ -40289,7 +40341,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-21</v>
+        <v>THD_COMPLAINT_SHORT_DESC-18</v>
       </c>
       <c r="B159" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40301,13 +40353,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E159" t="str">
-        <v>Crash / airbag related issues</v>
+        <v>Uneven gaps / flushness issues</v>
       </c>
       <c r="F159" t="str">
-        <v>CRASH_AIRBAG_RELATED_ISSUES</v>
+        <v>UNEVEN_GAPS_FLUSHNESS_ISSUES</v>
       </c>
       <c r="G159">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H159" t="str">
         <v/>
@@ -40324,7 +40376,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-22</v>
+        <v>THD_COMPLAINT_SHORT_DESC-19</v>
       </c>
       <c r="B160" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40336,13 +40388,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E160" t="str">
-        <v>Thermal issues</v>
+        <v>Paint / rust issues</v>
       </c>
       <c r="F160" t="str">
-        <v>THERMAL_ISSUES</v>
+        <v>PAINT_RUST_ISSUES</v>
       </c>
       <c r="G160">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H160" t="str">
         <v/>
@@ -40359,7 +40411,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-23</v>
+        <v>THD_COMPLAINT_SHORT_DESC-20</v>
       </c>
       <c r="B161" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40371,13 +40423,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E161" t="str">
-        <v>Brake ineffective</v>
+        <v>Not working / functioning issues / system malfunction</v>
       </c>
       <c r="F161" t="str">
-        <v>BRAKE_INEFFECTIVE</v>
+        <v>NOT_WORKING_FUNCTIONING_ISSUES_SYSTEM_MA</v>
       </c>
       <c r="G161">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H161" t="str">
         <v/>
@@ -40394,7 +40446,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-24</v>
+        <v>THD_COMPLAINT_SHORT_DESC-21</v>
       </c>
       <c r="B162" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40406,13 +40458,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E162" t="str">
-        <v>Poor pick-up</v>
+        <v>Crash / airbag related issues</v>
       </c>
       <c r="F162" t="str">
-        <v>POOR_PICK_UP</v>
+        <v>CRASH_AIRBAG_RELATED_ISSUES</v>
       </c>
       <c r="G162">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H162" t="str">
         <v/>
@@ -40429,7 +40481,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-25</v>
+        <v>THD_COMPLAINT_SHORT_DESC-22</v>
       </c>
       <c r="B163" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40441,13 +40493,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E163" t="str">
-        <v>Infotainment system issues</v>
+        <v>Thermal issues</v>
       </c>
       <c r="F163" t="str">
-        <v>INFOTAINMENT_SYSTEM_ISSUES</v>
+        <v>THERMAL_ISSUES</v>
       </c>
       <c r="G163">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H163" t="str">
         <v/>
@@ -40464,7 +40516,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>THD_COMPLAINT_SHORT_DESC-26</v>
+        <v>THD_COMPLAINT_SHORT_DESC-23</v>
       </c>
       <c r="B164" t="str">
         <v>THD_COMPLAINT_SHORT_DESC</v>
@@ -40476,13 +40528,13 @@
         <v>Complaint Short Description</v>
       </c>
       <c r="E164" t="str">
-        <v>Water entry in cabin</v>
+        <v>Brake ineffective</v>
       </c>
       <c r="F164" t="str">
-        <v>WATER_ENTRY_IN_CABIN</v>
+        <v>BRAKE_INEFFECTIVE</v>
       </c>
       <c r="G164">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H164" t="str">
         <v/>
@@ -40499,25 +40551,25 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>THD_ACTION_TAKEN-01</v>
+        <v>THD_COMPLAINT_SHORT_DESC-24</v>
       </c>
       <c r="B165" t="str">
-        <v>THD_ACTION_TAKEN</v>
+        <v>THD_COMPLAINT_SHORT_DESC</v>
       </c>
       <c r="C165" t="str">
         <v>THD</v>
       </c>
       <c r="D165" t="str">
-        <v>Action Taken</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="E165" t="str">
-        <v>Issue concluded and proceeded as per Field Investigation</v>
+        <v>Poor pick-up</v>
       </c>
       <c r="F165" t="str">
-        <v>ISSUE_CONCLUDED_AND_PROCEEDED_AS_PER_FIE</v>
+        <v>POOR_PICK_UP</v>
       </c>
       <c r="G165">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H165" t="str">
         <v/>
@@ -40534,25 +40586,25 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>THD_ACTION_TAKEN-02</v>
+        <v>THD_COMPLAINT_SHORT_DESC-25</v>
       </c>
       <c r="B166" t="str">
-        <v>THD_ACTION_TAKEN</v>
+        <v>THD_COMPLAINT_SHORT_DESC</v>
       </c>
       <c r="C166" t="str">
         <v>THD</v>
       </c>
       <c r="D166" t="str">
-        <v>Action Taken</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="E166" t="str">
-        <v>Suggested checks based on observations</v>
+        <v>Infotainment system issues</v>
       </c>
       <c r="F166" t="str">
-        <v>SUGGESTED_CHECKS_BASED_ON_OBSERVATIONS</v>
+        <v>INFOTAINMENT_SYSTEM_ISSUES</v>
       </c>
       <c r="G166">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H166" t="str">
         <v/>
@@ -40569,25 +40621,25 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>THD_ACTION_TAKEN-03</v>
+        <v>THD_COMPLAINT_SHORT_DESC-26</v>
       </c>
       <c r="B167" t="str">
-        <v>THD_ACTION_TAKEN</v>
+        <v>THD_COMPLAINT_SHORT_DESC</v>
       </c>
       <c r="C167" t="str">
         <v>THD</v>
       </c>
       <c r="D167" t="str">
-        <v>Action Taken</v>
+        <v>Complaint Short Description</v>
       </c>
       <c r="E167" t="str">
-        <v>Known issue – suggested part replacement</v>
+        <v>Water entry in cabin</v>
       </c>
       <c r="F167" t="str">
-        <v>KNOWN_ISSUE_SUGGESTED_PART_REPLACEMENT</v>
+        <v>WATER_ENTRY_IN_CABIN</v>
       </c>
       <c r="G167">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H167" t="str">
         <v/>
@@ -40604,7 +40656,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>THD_ACTION_TAKEN-04</v>
+        <v>THD_ACTION_TAKEN-01</v>
       </c>
       <c r="B168" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -40616,13 +40668,13 @@
         <v>Action Taken</v>
       </c>
       <c r="E168" t="str">
-        <v>Updated software / parameterization</v>
+        <v>Issue concluded and proceeded as per Field Investigation</v>
       </c>
       <c r="F168" t="str">
-        <v>UPDATED_SOFTWARE_PARAMETERIZATION</v>
+        <v>ISSUE_CONCLUDED_AND_PROCEEDED_AS_PER_FIE</v>
       </c>
       <c r="G168">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H168" t="str">
         <v/>
@@ -40639,7 +40691,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>THD_ACTION_TAKEN-05</v>
+        <v>THD_ACTION_TAKEN-02</v>
       </c>
       <c r="B169" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -40651,13 +40703,13 @@
         <v>Action Taken</v>
       </c>
       <c r="E169" t="str">
-        <v>Suggested part replacement based on observation</v>
+        <v>Suggested checks based on observations</v>
       </c>
       <c r="F169" t="str">
-        <v>SUGGESTED_PART_REPLACEMENT_BASED_ON_OBSE</v>
+        <v>SUGGESTED_CHECKS_BASED_ON_OBSERVATIONS</v>
       </c>
       <c r="G169">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H169" t="str">
         <v/>
@@ -40674,7 +40726,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>THD_ACTION_TAKEN-06</v>
+        <v>THD_ACTION_TAKEN-03</v>
       </c>
       <c r="B170" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -40686,13 +40738,13 @@
         <v>Action Taken</v>
       </c>
       <c r="E170" t="str">
-        <v>Vehicle ready for delivery</v>
+        <v>Known issue – suggested part replacement</v>
       </c>
       <c r="F170" t="str">
-        <v>VEHICLE_READY_FOR_DELIVERY</v>
+        <v>KNOWN_ISSUE_SUGGESTED_PART_REPLACEMENT</v>
       </c>
       <c r="G170">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H170" t="str">
         <v/>
@@ -40709,7 +40761,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>THD_ACTION_TAKEN-07</v>
+        <v>THD_ACTION_TAKEN-04</v>
       </c>
       <c r="B171" t="str">
         <v>THD_ACTION_TAKEN</v>
@@ -40721,13 +40773,13 @@
         <v>Action Taken</v>
       </c>
       <c r="E171" t="str">
-        <v>Vehicle not available; is with Customer</v>
+        <v>Updated software / parameterization</v>
       </c>
       <c r="F171" t="str">
-        <v>VEHICLE_NOT_AVAILABLE_IS_WITH_CUSTOMER</v>
+        <v>UPDATED_SOFTWARE_PARAMETERIZATION</v>
       </c>
       <c r="G171">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H171" t="str">
         <v/>
@@ -40744,25 +40796,25 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>THD_DELAY_REASON-01</v>
+        <v>THD_ACTION_TAKEN-05</v>
       </c>
       <c r="B172" t="str">
-        <v>THD_DELAY_REASON</v>
+        <v>THD_ACTION_TAKEN</v>
       </c>
       <c r="C172" t="str">
         <v>THD</v>
       </c>
       <c r="D172" t="str">
-        <v>Reason for Delay</v>
+        <v>Action Taken</v>
       </c>
       <c r="E172" t="str">
-        <v>Diagnosis and investigation</v>
+        <v>Suggested part replacement based on observation</v>
       </c>
       <c r="F172" t="str">
-        <v>DIAGNOSIS_AND_INVESTIGATION</v>
+        <v>SUGGESTED_PART_REPLACEMENT_BASED_ON_OBSE</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H172" t="str">
         <v/>
@@ -40779,25 +40831,25 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>THD_DELAY_REASON-02</v>
+        <v>THD_ACTION_TAKEN-06</v>
       </c>
       <c r="B173" t="str">
-        <v>THD_DELAY_REASON</v>
+        <v>THD_ACTION_TAKEN</v>
       </c>
       <c r="C173" t="str">
         <v>THD</v>
       </c>
       <c r="D173" t="str">
-        <v>Reason for Delay</v>
+        <v>Action Taken</v>
       </c>
       <c r="E173" t="str">
-        <v>Work content</v>
+        <v>Vehicle ready for delivery</v>
       </c>
       <c r="F173" t="str">
-        <v>WORK_CONTENT</v>
+        <v>VEHICLE_READY_FOR_DELIVERY</v>
       </c>
       <c r="G173">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H173" t="str">
         <v/>
@@ -40814,25 +40866,25 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>THD_DELAY_REASON-03</v>
+        <v>THD_ACTION_TAKEN-07</v>
       </c>
       <c r="B174" t="str">
-        <v>THD_DELAY_REASON</v>
+        <v>THD_ACTION_TAKEN</v>
       </c>
       <c r="C174" t="str">
         <v>THD</v>
       </c>
       <c r="D174" t="str">
-        <v>Reason for Delay</v>
+        <v>Action Taken</v>
       </c>
       <c r="E174" t="str">
-        <v>Non-availability of spare parts</v>
+        <v>Vehicle not available; is with Customer</v>
       </c>
       <c r="F174" t="str">
-        <v>NON_AVAILABILITY_OF_SPARE_PARTS</v>
+        <v>VEHICLE_NOT_AVAILABLE_IS_WITH_CUSTOMER</v>
       </c>
       <c r="G174">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H174" t="str">
         <v/>
@@ -40849,7 +40901,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>THD_DELAY_REASON-04</v>
+        <v>THD_DELAY_REASON-01</v>
       </c>
       <c r="B175" t="str">
         <v>THD_DELAY_REASON</v>
@@ -40861,13 +40913,13 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E175" t="str">
-        <v>Non-availability of vehicle</v>
+        <v>Diagnosis and investigation</v>
       </c>
       <c r="F175" t="str">
-        <v>NON_AVAILABILITY_OF_VEHICLE</v>
+        <v>DIAGNOSIS_AND_INVESTIGATION</v>
       </c>
       <c r="G175">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H175" t="str">
         <v/>
@@ -40884,7 +40936,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>THD_DELAY_REASON-05</v>
+        <v>THD_DELAY_REASON-02</v>
       </c>
       <c r="B176" t="str">
         <v>THD_DELAY_REASON</v>
@@ -40896,13 +40948,13 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E176" t="str">
-        <v>Dealer response</v>
+        <v>Work content</v>
       </c>
       <c r="F176" t="str">
-        <v>DEALER_RESPONSE</v>
+        <v>WORK_CONTENT</v>
       </c>
       <c r="G176">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H176" t="str">
         <v/>
@@ -40919,7 +40971,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>THD_DELAY_REASON-06</v>
+        <v>THD_DELAY_REASON-03</v>
       </c>
       <c r="B177" t="str">
         <v>THD_DELAY_REASON</v>
@@ -40931,13 +40983,13 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E177" t="str">
-        <v>Plant / ERC / vendor intervention</v>
+        <v>Non-availability of spare parts</v>
       </c>
       <c r="F177" t="str">
-        <v>PLANT_ERC_VENDOR_INTERVENTION</v>
+        <v>NON_AVAILABILITY_OF_SPARE_PARTS</v>
       </c>
       <c r="G177">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H177" t="str">
         <v/>
@@ -40954,7 +41006,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>THD_DELAY_REASON-07</v>
+        <v>THD_DELAY_REASON-04</v>
       </c>
       <c r="B178" t="str">
         <v>THD_DELAY_REASON</v>
@@ -40966,13 +41018,13 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E178" t="str">
-        <v>Software / server / TDS Tool issue</v>
+        <v>Non-availability of vehicle</v>
       </c>
       <c r="F178" t="str">
-        <v>SOFTWARE_SERVER_TDS_TOOL_ISSUE</v>
+        <v>NON_AVAILABILITY_OF_VEHICLE</v>
       </c>
       <c r="G178">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H178" t="str">
         <v/>
@@ -40989,7 +41041,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>THD_DELAY_REASON-08</v>
+        <v>THD_DELAY_REASON-05</v>
       </c>
       <c r="B179" t="str">
         <v>THD_DELAY_REASON</v>
@@ -41001,13 +41053,13 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E179" t="str">
-        <v>Solution not available</v>
+        <v>Dealer response</v>
       </c>
       <c r="F179" t="str">
-        <v>SOLUTION_NOT_AVAILABLE</v>
+        <v>DEALER_RESPONSE</v>
       </c>
       <c r="G179">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H179" t="str">
         <v/>
@@ -41024,7 +41076,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>THD_DELAY_REASON-09</v>
+        <v>THD_DELAY_REASON-06</v>
       </c>
       <c r="B180" t="str">
         <v>THD_DELAY_REASON</v>
@@ -41036,13 +41088,13 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E180" t="str">
-        <v>Pending for Commercial Decision / Customer Approval</v>
+        <v>Plant / ERC / vendor intervention</v>
       </c>
       <c r="F180" t="str">
-        <v>PENDING_FOR_COMMERCIAL_DECISION_CUSTOMER</v>
+        <v>PLANT_ERC_VENDOR_INTERVENTION</v>
       </c>
       <c r="G180">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H180" t="str">
         <v/>
@@ -41059,7 +41111,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>THD_DELAY_REASON-10</v>
+        <v>THD_DELAY_REASON-07</v>
       </c>
       <c r="B181" t="str">
         <v>THD_DELAY_REASON</v>
@@ -41071,13 +41123,13 @@
         <v>Reason for Delay</v>
       </c>
       <c r="E181" t="str">
-        <v>Dealer not responding</v>
+        <v>Software / server / TDS Tool issue</v>
       </c>
       <c r="F181" t="str">
-        <v>DEALER_NOT_RESPONDING</v>
+        <v>SOFTWARE_SERVER_TDS_TOOL_ISSUE</v>
       </c>
       <c r="G181">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H181" t="str">
         <v/>
@@ -41094,25 +41146,25 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>THD_CLOSURE_ACTION-01</v>
+        <v>THD_DELAY_REASON-08</v>
       </c>
       <c r="B182" t="str">
-        <v>THD_CLOSURE_ACTION</v>
+        <v>THD_DELAY_REASON</v>
       </c>
       <c r="C182" t="str">
         <v>THD</v>
       </c>
       <c r="D182" t="str">
-        <v>Closure Action</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="E182" t="str">
-        <v>Closed</v>
+        <v>Solution not available</v>
       </c>
       <c r="F182" t="str">
-        <v>CLOSED</v>
+        <v>SOLUTION_NOT_AVAILABLE</v>
       </c>
       <c r="G182">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H182" t="str">
         <v/>
@@ -41129,25 +41181,25 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>THD_CLOSURE_ACTION-02</v>
+        <v>THD_DELAY_REASON-09</v>
       </c>
       <c r="B183" t="str">
-        <v>THD_CLOSURE_ACTION</v>
+        <v>THD_DELAY_REASON</v>
       </c>
       <c r="C183" t="str">
         <v>THD</v>
       </c>
       <c r="D183" t="str">
-        <v>Closure Action</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="E183" t="str">
-        <v>Closed With Feedback</v>
+        <v>Pending for Commercial Decision / Customer Approval</v>
       </c>
       <c r="F183" t="str">
-        <v>CLOSED_WITH_FEEDBACK</v>
+        <v>PENDING_FOR_COMMERCIAL_DECISION_CUSTOMER</v>
       </c>
       <c r="G183">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H183" t="str">
         <v/>
@@ -41164,25 +41216,25 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>THD_CLOSURE_ACTION-03</v>
+        <v>THD_DELAY_REASON-10</v>
       </c>
       <c r="B184" t="str">
-        <v>THD_CLOSURE_ACTION</v>
+        <v>THD_DELAY_REASON</v>
       </c>
       <c r="C184" t="str">
         <v>THD</v>
       </c>
       <c r="D184" t="str">
-        <v>Closure Action</v>
+        <v>Reason for Delay</v>
       </c>
       <c r="E184" t="str">
-        <v>Closed With Early Warning</v>
+        <v>Dealer not responding</v>
       </c>
       <c r="F184" t="str">
-        <v>CLOSED_WITH_EARLY_WARNING</v>
+        <v>DEALER_NOT_RESPONDING</v>
       </c>
       <c r="G184">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H184" t="str">
         <v/>
@@ -41199,22 +41251,22 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>THD_ATTACHMENT_TYPE-01</v>
+        <v>THD_CLOSURE_ACTION-01</v>
       </c>
       <c r="B185" t="str">
-        <v>THD_ATTACHMENT_TYPE</v>
+        <v>THD_CLOSURE_ACTION</v>
       </c>
       <c r="C185" t="str">
         <v>THD</v>
       </c>
       <c r="D185" t="str">
-        <v>Attachment Type</v>
+        <v>Closure Action</v>
       </c>
       <c r="E185" t="str">
-        <v>DIR Report</v>
+        <v>Closed</v>
       </c>
       <c r="F185" t="str">
-        <v>DIR_REPORT</v>
+        <v>CLOSED</v>
       </c>
       <c r="G185">
         <v>1</v>
@@ -41234,25 +41286,25 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>CLAIM_BUDGET_PURPOSE-01</v>
+        <v>THD_CLOSURE_ACTION-02</v>
       </c>
       <c r="B186" t="str">
-        <v>CLAIM_BUDGET_PURPOSE</v>
+        <v>THD_CLOSURE_ACTION</v>
       </c>
       <c r="C186" t="str">
-        <v>CLAIM</v>
+        <v>THD</v>
       </c>
       <c r="D186" t="str">
-        <v>Allocation Purpose</v>
+        <v>Closure Action</v>
       </c>
       <c r="E186" t="str">
-        <v>Approved Yearly Budget</v>
+        <v>Closed With Feedback</v>
       </c>
       <c r="F186" t="str">
-        <v>APPROVED_YEARLY_BUDGET</v>
+        <v>CLOSED_WITH_FEEDBACK</v>
       </c>
       <c r="G186">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H186" t="str">
         <v/>
@@ -41269,25 +41321,25 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>CLAIM_BUDGET_PURPOSE-02</v>
+        <v>THD_CLOSURE_ACTION-03</v>
       </c>
       <c r="B187" t="str">
-        <v>CLAIM_BUDGET_PURPOSE</v>
+        <v>THD_CLOSURE_ACTION</v>
       </c>
       <c r="C187" t="str">
-        <v>CLAIM</v>
+        <v>THD</v>
       </c>
       <c r="D187" t="str">
-        <v>Allocation Purpose</v>
+        <v>Closure Action</v>
       </c>
       <c r="E187" t="str">
-        <v>Special Budget</v>
+        <v>Closed With Early Warning</v>
       </c>
       <c r="F187" t="str">
-        <v>SPECIAL_BUDGET</v>
+        <v>CLOSED_WITH_EARLY_WARNING</v>
       </c>
       <c r="G187">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H187" t="str">
         <v/>
@@ -41304,22 +41356,22 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL-01</v>
+        <v>THD_ATTACHMENT_TYPE-01</v>
       </c>
       <c r="B188" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL</v>
+        <v>THD_ATTACHMENT_TYPE</v>
       </c>
       <c r="C188" t="str">
-        <v>CLAIM</v>
+        <v>THD</v>
       </c>
       <c r="D188" t="str">
-        <v>Special Claim</v>
+        <v>Attachment Type</v>
       </c>
       <c r="E188" t="str">
-        <v>IUPR</v>
+        <v>DIR Report</v>
       </c>
       <c r="F188" t="str">
-        <v>IUPR</v>
+        <v>DIR_REPORT</v>
       </c>
       <c r="G188">
         <v>1</v>
@@ -41339,25 +41391,25 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL-02</v>
+        <v>CLAIM_BUDGET_PURPOSE-01</v>
       </c>
       <c r="B189" t="str">
-        <v>CLAIM_SPECIAL_GOODWILL</v>
+        <v>CLAIM_BUDGET_PURPOSE</v>
       </c>
       <c r="C189" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D189" t="str">
-        <v>Special Claim</v>
+        <v>Allocation Purpose</v>
       </c>
       <c r="E189" t="str">
-        <v>Thrive</v>
+        <v>Approved Yearly Budget</v>
       </c>
       <c r="F189" t="str">
-        <v>THRIVE</v>
+        <v>APPROVED_YEARLY_BUDGET</v>
       </c>
       <c r="G189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" t="str">
         <v/>
@@ -41374,25 +41426,25 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION-01</v>
+        <v>CLAIM_BUDGET_PURPOSE-02</v>
       </c>
       <c r="B190" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION</v>
+        <v>CLAIM_BUDGET_PURPOSE</v>
       </c>
       <c r="C190" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D190" t="str">
-        <v>Issue Description</v>
+        <v>Allocation Purpose</v>
       </c>
       <c r="E190" t="str">
-        <v>Thermal Incident</v>
+        <v>Special Budget</v>
       </c>
       <c r="F190" t="str">
-        <v>THERMAL_INCIDENT</v>
+        <v>SPECIAL_BUDGET</v>
       </c>
       <c r="G190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H190" t="str">
         <v/>
@@ -41409,25 +41461,25 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION-02</v>
+        <v>CLAIM_SPECIAL_GOODWILL-01</v>
       </c>
       <c r="B191" t="str">
-        <v>CLAIM_ISSUE_DESCRIPTION</v>
+        <v>CLAIM_SPECIAL_GOODWILL</v>
       </c>
       <c r="C191" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D191" t="str">
-        <v>Issue Description</v>
+        <v>Special Claim</v>
       </c>
       <c r="E191" t="str">
-        <v>Engine Failure</v>
+        <v>IUPR</v>
       </c>
       <c r="F191" t="str">
-        <v>ENGINE_FAILURE</v>
+        <v>IUPR</v>
       </c>
       <c r="G191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H191" t="str">
         <v/>
@@ -41444,25 +41496,25 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>CLAIM_COMPLAINT_TYPE-01</v>
+        <v>CLAIM_SPECIAL_GOODWILL-02</v>
       </c>
       <c r="B192" t="str">
-        <v>CLAIM_COMPLAINT_TYPE</v>
+        <v>CLAIM_SPECIAL_GOODWILL</v>
       </c>
       <c r="C192" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D192" t="str">
-        <v>Complaint Type</v>
+        <v>Special Claim</v>
       </c>
       <c r="E192" t="str">
-        <v>Transmission</v>
+        <v>Thrive</v>
       </c>
       <c r="F192" t="str">
-        <v>TRANSMISSION</v>
+        <v>THRIVE</v>
       </c>
       <c r="G192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H192" t="str">
         <v/>
@@ -41479,25 +41531,25 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>CLAIM_COMPLAINT_TYPE-02</v>
+        <v>CLAIM_ISSUE_DESCRIPTION-01</v>
       </c>
       <c r="B193" t="str">
-        <v>CLAIM_COMPLAINT_TYPE</v>
+        <v>CLAIM_ISSUE_DESCRIPTION</v>
       </c>
       <c r="C193" t="str">
         <v>CLAIM</v>
       </c>
       <c r="D193" t="str">
-        <v>Complaint Type</v>
+        <v>Issue Description</v>
       </c>
       <c r="E193" t="str">
-        <v>Clutch</v>
+        <v>Thermal Incident</v>
       </c>
       <c r="F193" t="str">
-        <v>CLUTCH</v>
+        <v>THERMAL_INCIDENT</v>
       </c>
       <c r="G193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H193" t="str">
         <v/>
@@ -41512,9 +41564,114 @@
         <v>Active</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>CLAIM_ISSUE_DESCRIPTION-02</v>
+      </c>
+      <c r="B194" t="str">
+        <v>CLAIM_ISSUE_DESCRIPTION</v>
+      </c>
+      <c r="C194" t="str">
+        <v>CLAIM</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Issue Description</v>
+      </c>
+      <c r="E194" t="str">
+        <v>Engine Failure</v>
+      </c>
+      <c r="F194" t="str">
+        <v>ENGINE_FAILURE</v>
+      </c>
+      <c r="G194">
+        <v>2</v>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
+      <c r="K194" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>CLAIM_COMPLAINT_TYPE-01</v>
+      </c>
+      <c r="B195" t="str">
+        <v>CLAIM_COMPLAINT_TYPE</v>
+      </c>
+      <c r="C195" t="str">
+        <v>CLAIM</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Complaint Type</v>
+      </c>
+      <c r="E195" t="str">
+        <v>Transmission</v>
+      </c>
+      <c r="F195" t="str">
+        <v>TRANSMISSION</v>
+      </c>
+      <c r="G195">
+        <v>1</v>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
+      <c r="K195" t="str">
+        <v>Active</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>CLAIM_COMPLAINT_TYPE-02</v>
+      </c>
+      <c r="B196" t="str">
+        <v>CLAIM_COMPLAINT_TYPE</v>
+      </c>
+      <c r="C196" t="str">
+        <v>CLAIM</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Complaint Type</v>
+      </c>
+      <c r="E196" t="str">
+        <v>Clutch</v>
+      </c>
+      <c r="F196" t="str">
+        <v>CLUTCH</v>
+      </c>
+      <c r="G196">
+        <v>2</v>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196" t="str">
+        <v/>
+      </c>
+      <c r="K196" t="str">
+        <v>Active</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K193"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K196"/>
   </ignoredErrors>
 </worksheet>
 </file>
